--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8336DFEE-3941-469C-BB24-7443D7D5D77C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AD3A05E-BC24-4A2B-B17E-EF00FA63AB80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -573,13 +573,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S2aH2,S3aH2,S1aH2,S4aH2</t>
+    <t>S1aH2,S3aH2,S4aH2,S2aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S2aH3,S3aH3,S4aH1,S1aH3,S3aH1,S1aH1,S4aH3,S2aH1</t>
+    <t>S1aH1,S4aH3,S1aH3,S2aH1,S3aH1,S2aH3,S3aH3,S4aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S2aH3,S3aH3,S4aH1,S1aH3,S3aH1,S1aH1,S4aH3,S2aH1</v>
+        <v>S1aH1,S4aH3,S1aH3,S2aH1,S3aH1,S2aH3,S3aH3,S4aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S2aH2,S3aH2,S1aH2,S4aH2</v>
+        <v>S1aH2,S3aH2,S4aH2,S2aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1302,7 +1302,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F01BF8-C4D8-4719-B6E1-54C6DEB4BE41}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60C02DEA-6F20-4F91-9E58-8547DC0A0A1C}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1386,7 +1386,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{935D3822-4110-4595-A8AB-E3B24F468C71}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53A9ED8E-0288-4406-9C3D-383F82C6453F}">
   <dimension ref="B9:O250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1488,7 +1488,7 @@
         <v>54</v>
       </c>
       <c r="D12">
-        <v>8.0883750674477645E-2</v>
+        <v>8.0700550115698211E-2</v>
       </c>
       <c r="E12" t="s">
         <v>53</v>
@@ -1526,7 +1526,7 @@
         <v>55</v>
       </c>
       <c r="D13">
-        <v>3.4620477319853018E-6</v>
+        <v>4.3445580452208842E-6</v>
       </c>
       <c r="E13" t="s">
         <v>53</v>
@@ -1564,7 +1564,7 @@
         <v>56</v>
       </c>
       <c r="D14">
-        <v>2.2166155095552746E-2</v>
+        <v>2.2083955786590101E-2</v>
       </c>
       <c r="E14" t="s">
         <v>53</v>
@@ -1602,7 +1602,7 @@
         <v>57</v>
       </c>
       <c r="D15">
-        <v>0.28775697504362335</v>
+        <v>0.28716645138107261</v>
       </c>
       <c r="E15" t="s">
         <v>53</v>
@@ -1640,7 +1640,7 @@
         <v>58</v>
       </c>
       <c r="D16">
-        <v>1.7628868992700539E-2</v>
+        <v>1.7574242612038646E-2</v>
       </c>
       <c r="E16" t="s">
         <v>53</v>
@@ -1678,7 +1678,7 @@
         <v>59</v>
       </c>
       <c r="D17">
-        <v>3.96887783747416E-2</v>
+        <v>3.95737417241376E-2</v>
       </c>
       <c r="E17" t="s">
         <v>53</v>
@@ -1716,7 +1716,7 @@
         <v>60</v>
       </c>
       <c r="D18">
-        <v>0.34853773133598859</v>
+        <v>0.34914689039572977</v>
       </c>
       <c r="E18" t="s">
         <v>53</v>
@@ -1754,7 +1754,7 @@
         <v>61</v>
       </c>
       <c r="D19">
-        <v>3.6769461539659827E-2</v>
+        <v>3.6947590512206724E-2</v>
       </c>
       <c r="E19" t="s">
         <v>53</v>
@@ -1792,7 +1792,7 @@
         <v>62</v>
       </c>
       <c r="D20">
-        <v>4.6709362145693351E-3</v>
+        <v>4.6560148543866612E-3</v>
       </c>
       <c r="E20" t="s">
         <v>53</v>
@@ -1830,7 +1830,7 @@
         <v>63</v>
       </c>
       <c r="D21">
-        <v>0.15922480708816919</v>
+        <v>0.15943932150390072</v>
       </c>
       <c r="E21" t="s">
         <v>53</v>
@@ -1868,7 +1868,7 @@
         <v>64</v>
       </c>
       <c r="D22">
-        <v>2.6690735927857134E-3</v>
+        <v>2.7068965561922089E-3</v>
       </c>
       <c r="E22" t="s">
         <v>53</v>
@@ -1918,7 +1918,7 @@
         <v>52</v>
       </c>
       <c r="I23">
-        <v>0.12016366394252097</v>
+        <v>0.12028698100353262</v>
       </c>
       <c r="J23" t="s">
         <v>53</v>
@@ -1944,7 +1944,7 @@
         <v>54</v>
       </c>
       <c r="D24">
-        <v>9.4995821623184082E-2</v>
+        <v>9.4966769772519791E-2</v>
       </c>
       <c r="E24" t="s">
         <v>53</v>
@@ -1956,7 +1956,7 @@
         <v>54</v>
       </c>
       <c r="I24">
-        <v>0.14054511196594263</v>
+        <v>0.14058366070657766</v>
       </c>
       <c r="J24" t="s">
         <v>53</v>
@@ -1994,7 +1994,7 @@
         <v>55</v>
       </c>
       <c r="I25">
-        <v>9.3006859593748173E-2</v>
+        <v>9.3051421931707831E-2</v>
       </c>
       <c r="J25" t="s">
         <v>53</v>
@@ -2020,7 +2020,7 @@
         <v>56</v>
       </c>
       <c r="D26">
-        <v>2.2548527558590492E-2</v>
+        <v>2.2641780960886679E-2</v>
       </c>
       <c r="E26" t="s">
         <v>53</v>
@@ -2032,7 +2032,7 @@
         <v>56</v>
       </c>
       <c r="I26">
-        <v>9.3904482175375587E-2</v>
+        <v>9.4011763813938609E-2</v>
       </c>
       <c r="J26" t="s">
         <v>53</v>
@@ -2058,7 +2058,7 @@
         <v>57</v>
       </c>
       <c r="D27">
-        <v>0.27719708187656278</v>
+        <v>0.27796467326299434</v>
       </c>
       <c r="E27" t="s">
         <v>53</v>
@@ -2070,7 +2070,7 @@
         <v>57</v>
       </c>
       <c r="I27">
-        <v>9.2844340144986784E-2</v>
+        <v>9.287290533844017E-2</v>
       </c>
       <c r="J27" t="s">
         <v>53</v>
@@ -2096,7 +2096,7 @@
         <v>58</v>
       </c>
       <c r="D28">
-        <v>1.5075418626712835E-2</v>
+        <v>1.4759379434962781E-2</v>
       </c>
       <c r="E28" t="s">
         <v>53</v>
@@ -2108,7 +2108,7 @@
         <v>58</v>
       </c>
       <c r="I28">
-        <v>7.2486209538346696E-2</v>
+        <v>7.2448382586309451E-2</v>
       </c>
       <c r="J28" t="s">
         <v>53</v>
@@ -2134,7 +2134,7 @@
         <v>59</v>
       </c>
       <c r="D29">
-        <v>4.0368469876971957E-2</v>
+        <v>4.0390707014552905E-2</v>
       </c>
       <c r="E29" t="s">
         <v>53</v>
@@ -2146,7 +2146,7 @@
         <v>59</v>
       </c>
       <c r="I29">
-        <v>4.3723827803047746E-2</v>
+        <v>4.3667571279931101E-2</v>
       </c>
       <c r="J29" t="s">
         <v>53</v>
@@ -2172,7 +2172,7 @@
         <v>60</v>
       </c>
       <c r="D30">
-        <v>0.34010808445139595</v>
+        <v>0.33937194756746619</v>
       </c>
       <c r="E30" t="s">
         <v>53</v>
@@ -2184,7 +2184,7 @@
         <v>60</v>
       </c>
       <c r="I30">
-        <v>4.5998210748753404E-2</v>
+        <v>4.5895070240746294E-2</v>
       </c>
       <c r="J30" t="s">
         <v>53</v>
@@ -2210,7 +2210,7 @@
         <v>61</v>
       </c>
       <c r="D31">
-        <v>3.2328829103209417E-2</v>
+        <v>3.1779238761971758E-2</v>
       </c>
       <c r="E31" t="s">
         <v>53</v>
@@ -2222,7 +2222,7 @@
         <v>61</v>
       </c>
       <c r="I31">
-        <v>3.7032659101216794E-2</v>
+        <v>3.6966006967352472E-2</v>
       </c>
       <c r="J31" t="s">
         <v>53</v>
@@ -2248,7 +2248,7 @@
         <v>62</v>
       </c>
       <c r="D32">
-        <v>5.710920181118689E-3</v>
+        <v>5.8707470701483948E-3</v>
       </c>
       <c r="E32" t="s">
         <v>53</v>
@@ -2260,7 +2260,7 @@
         <v>62</v>
       </c>
       <c r="I32">
-        <v>8.5031987474594103E-2</v>
+        <v>8.5166707657702581E-2</v>
       </c>
       <c r="J32" t="s">
         <v>53</v>
@@ -2286,7 +2286,7 @@
         <v>63</v>
       </c>
       <c r="D33">
-        <v>0.16979762604745402</v>
+        <v>0.17044650179855803</v>
       </c>
       <c r="E33" t="s">
         <v>53</v>
@@ -2298,7 +2298,7 @@
         <v>63</v>
       </c>
       <c r="I33">
-        <v>9.7760717923624368E-2</v>
+        <v>9.7678085086069497E-2</v>
       </c>
       <c r="J33" t="s">
         <v>53</v>
@@ -2324,7 +2324,7 @@
         <v>64</v>
       </c>
       <c r="D34">
-        <v>1.8692206547992276E-3</v>
+        <v>1.8082543559404111E-3</v>
       </c>
       <c r="E34" t="s">
         <v>53</v>
@@ -2336,7 +2336,7 @@
         <v>64</v>
       </c>
       <c r="I34">
-        <v>7.7501929587843688E-2</v>
+        <v>7.7371443387692279E-2</v>
       </c>
       <c r="J34" t="s">
         <v>53</v>
@@ -2400,7 +2400,7 @@
         <v>54</v>
       </c>
       <c r="D36">
-        <v>8.280472830165303E-2</v>
+        <v>8.3506570320454679E-2</v>
       </c>
       <c r="E36" t="s">
         <v>53</v>
@@ -2476,7 +2476,7 @@
         <v>56</v>
       </c>
       <c r="D38">
-        <v>2.4075113071422894E-2</v>
+        <v>2.5153837798531281E-2</v>
       </c>
       <c r="E38" t="s">
         <v>53</v>
@@ -2514,7 +2514,7 @@
         <v>57</v>
       </c>
       <c r="D39">
-        <v>0.28332331636313668</v>
+        <v>0.27733733689009155</v>
       </c>
       <c r="E39" t="s">
         <v>53</v>
@@ -2552,7 +2552,7 @@
         <v>58</v>
       </c>
       <c r="D40">
-        <v>1.6363353011479322E-2</v>
+        <v>1.519930147966481E-2</v>
       </c>
       <c r="E40" t="s">
         <v>53</v>
@@ -2590,7 +2590,7 @@
         <v>59</v>
       </c>
       <c r="D41">
-        <v>4.1752385353169913E-2</v>
+        <v>4.2199836061550138E-2</v>
       </c>
       <c r="E41" t="s">
         <v>53</v>
@@ -2628,7 +2628,7 @@
         <v>60</v>
       </c>
       <c r="D42">
-        <v>0.34518969365821262</v>
+        <v>0.34374080780077321</v>
       </c>
       <c r="E42" t="s">
         <v>53</v>
@@ -2666,7 +2666,7 @@
         <v>61</v>
       </c>
       <c r="D43">
-        <v>3.4445554055259703E-2</v>
+        <v>3.3564037331640748E-2</v>
       </c>
       <c r="E43" t="s">
         <v>53</v>
@@ -2704,7 +2704,7 @@
         <v>62</v>
       </c>
       <c r="D44">
-        <v>5.8042797919892457E-3</v>
+        <v>6.1437800952329454E-3</v>
       </c>
       <c r="E44" t="s">
         <v>53</v>
@@ -2742,7 +2742,7 @@
         <v>63</v>
       </c>
       <c r="D45">
-        <v>0.16441705490842451</v>
+        <v>0.17151187864862305</v>
       </c>
       <c r="E45" t="s">
         <v>53</v>
@@ -2780,7 +2780,7 @@
         <v>64</v>
       </c>
       <c r="D46">
-        <v>1.8245214852518651E-3</v>
+        <v>1.642613573432891E-3</v>
       </c>
       <c r="E46" t="s">
         <v>53</v>
@@ -2856,7 +2856,7 @@
         <v>54</v>
       </c>
       <c r="D48">
-        <v>6.9867283242606146E-2</v>
+        <v>6.9991526406045793E-2</v>
       </c>
       <c r="E48" t="s">
         <v>53</v>
@@ -2932,7 +2932,7 @@
         <v>56</v>
       </c>
       <c r="D50">
-        <v>2.3628726284712218E-2</v>
+        <v>2.3594205000005801E-2</v>
       </c>
       <c r="E50" t="s">
         <v>53</v>
@@ -2970,7 +2970,7 @@
         <v>57</v>
       </c>
       <c r="D51">
-        <v>0.30491682287182276</v>
+        <v>0.30361429091556336</v>
       </c>
       <c r="E51" t="s">
         <v>53</v>
@@ -3008,7 +3008,7 @@
         <v>58</v>
       </c>
       <c r="D52">
-        <v>1.751918802536577E-2</v>
+        <v>1.7398193806901743E-2</v>
       </c>
       <c r="E52" t="s">
         <v>53</v>
@@ -3046,7 +3046,7 @@
         <v>59</v>
       </c>
       <c r="D53">
-        <v>4.0866833997016114E-2</v>
+        <v>4.0913028067759469E-2</v>
       </c>
       <c r="E53" t="s">
         <v>53</v>
@@ -3084,7 +3084,7 @@
         <v>60</v>
       </c>
       <c r="D54">
-        <v>0.34859898222384256</v>
+        <v>0.34988275542982011</v>
       </c>
       <c r="E54" t="s">
         <v>53</v>
@@ -3122,7 +3122,7 @@
         <v>61</v>
       </c>
       <c r="D55">
-        <v>3.8238959072857182E-2</v>
+        <v>3.8230938688920434E-2</v>
       </c>
       <c r="E55" t="s">
         <v>53</v>
@@ -3160,7 +3160,7 @@
         <v>62</v>
       </c>
       <c r="D56">
-        <v>4.5193207908486559E-3</v>
+        <v>4.4982586168002244E-3</v>
       </c>
       <c r="E56" t="s">
         <v>53</v>
@@ -3198,7 +3198,7 @@
         <v>63</v>
       </c>
       <c r="D57">
-        <v>0.14935044464685165</v>
+        <v>0.14936181093255585</v>
       </c>
       <c r="E57" t="s">
         <v>53</v>
@@ -3236,7 +3236,7 @@
         <v>64</v>
       </c>
       <c r="D58">
-        <v>2.4934388440782285E-3</v>
+        <v>2.5149921356278138E-3</v>
       </c>
       <c r="E58" t="s">
         <v>53</v>
@@ -3312,7 +3312,7 @@
         <v>54</v>
       </c>
       <c r="D60">
-        <v>6.7595644603375152E-2</v>
+        <v>6.602182303432752E-2</v>
       </c>
       <c r="E60" t="s">
         <v>53</v>
@@ -3388,7 +3388,7 @@
         <v>56</v>
       </c>
       <c r="D62">
-        <v>2.4734275734393255E-2</v>
+        <v>2.4908913869458458E-2</v>
       </c>
       <c r="E62" t="s">
         <v>53</v>
@@ -3426,7 +3426,7 @@
         <v>57</v>
       </c>
       <c r="D63">
-        <v>0.30722769791585508</v>
+        <v>0.30890981807924567</v>
       </c>
       <c r="E63" t="s">
         <v>53</v>
@@ -3464,7 +3464,7 @@
         <v>58</v>
       </c>
       <c r="D64">
-        <v>1.6952283168290609E-2</v>
+        <v>1.6652814883034887E-2</v>
       </c>
       <c r="E64" t="s">
         <v>53</v>
@@ -3502,7 +3502,7 @@
         <v>59</v>
       </c>
       <c r="D65">
-        <v>4.3872161669475378E-2</v>
+        <v>4.4459372229074479E-2</v>
       </c>
       <c r="E65" t="s">
         <v>53</v>
@@ -3540,7 +3540,7 @@
         <v>60</v>
       </c>
       <c r="D66">
-        <v>0.34313640982054133</v>
+        <v>0.34258865842626712</v>
       </c>
       <c r="E66" t="s">
         <v>53</v>
@@ -3578,7 +3578,7 @@
         <v>61</v>
       </c>
       <c r="D67">
-        <v>3.6126061933050339E-2</v>
+        <v>3.6156350387245843E-2</v>
       </c>
       <c r="E67" t="s">
         <v>53</v>
@@ -3616,7 +3616,7 @@
         <v>62</v>
       </c>
       <c r="D68">
-        <v>6.169059873976976E-3</v>
+        <v>6.3170543478899398E-3</v>
       </c>
       <c r="E68" t="s">
         <v>53</v>
@@ -3654,7 +3654,7 @@
         <v>63</v>
       </c>
       <c r="D69">
-        <v>0.15215705333250182</v>
+        <v>0.15193679850536507</v>
       </c>
       <c r="E69" t="s">
         <v>53</v>
@@ -3692,7 +3692,7 @@
         <v>64</v>
       </c>
       <c r="D70">
-        <v>2.0293519485407386E-3</v>
+        <v>2.0483962380915904E-3</v>
       </c>
       <c r="E70" t="s">
         <v>53</v>
@@ -3742,7 +3742,7 @@
         <v>52</v>
       </c>
       <c r="I71">
-        <v>0.1118413608413153</v>
+        <v>0.11181117145098084</v>
       </c>
       <c r="J71" t="s">
         <v>53</v>
@@ -3768,7 +3768,7 @@
         <v>54</v>
       </c>
       <c r="D72">
-        <v>6.5212648746955662E-2</v>
+        <v>6.4248124226036804E-2</v>
       </c>
       <c r="E72" t="s">
         <v>53</v>
@@ -3780,7 +3780,7 @@
         <v>54</v>
       </c>
       <c r="I72">
-        <v>0.13450556943571101</v>
+        <v>0.1344819947089593</v>
       </c>
       <c r="J72" t="s">
         <v>53</v>
@@ -3818,7 +3818,7 @@
         <v>55</v>
       </c>
       <c r="I73">
-        <v>8.7891874267657891E-2</v>
+        <v>8.7872089671120757E-2</v>
       </c>
       <c r="J73" t="s">
         <v>53</v>
@@ -3844,7 +3844,7 @@
         <v>56</v>
       </c>
       <c r="D74">
-        <v>3.2556989388570046E-2</v>
+        <v>3.3088389192868148E-2</v>
       </c>
       <c r="E74" t="s">
         <v>53</v>
@@ -3856,7 +3856,7 @@
         <v>56</v>
       </c>
       <c r="I74">
-        <v>9.6378804374966487E-2</v>
+        <v>9.6347592933583637E-2</v>
       </c>
       <c r="J74" t="s">
         <v>53</v>
@@ -3882,7 +3882,7 @@
         <v>57</v>
       </c>
       <c r="D75">
-        <v>0.32441550201824931</v>
+        <v>0.32737228670463264</v>
       </c>
       <c r="E75" t="s">
         <v>53</v>
@@ -3894,7 +3894,7 @@
         <v>57</v>
       </c>
       <c r="I75">
-        <v>9.2387997887262402E-2</v>
+        <v>9.2412770605103431E-2</v>
       </c>
       <c r="J75" t="s">
         <v>53</v>
@@ -3920,7 +3920,7 @@
         <v>58</v>
       </c>
       <c r="D76">
-        <v>1.4934971252471955E-2</v>
+        <v>1.518376224965446E-2</v>
       </c>
       <c r="E76" t="s">
         <v>53</v>
@@ -3932,7 +3932,7 @@
         <v>58</v>
       </c>
       <c r="I76">
-        <v>7.126564662413129E-2</v>
+        <v>7.126240288472542E-2</v>
       </c>
       <c r="J76" t="s">
         <v>53</v>
@@ -3958,7 +3958,7 @@
         <v>59</v>
       </c>
       <c r="D77">
-        <v>5.0806198079624526E-2</v>
+        <v>5.0294394215110963E-2</v>
       </c>
       <c r="E77" t="s">
         <v>53</v>
@@ -3970,7 +3970,7 @@
         <v>59</v>
       </c>
       <c r="I77">
-        <v>4.778710352914483E-2</v>
+        <v>4.7765903589307185E-2</v>
       </c>
       <c r="J77" t="s">
         <v>53</v>
@@ -3996,7 +3996,7 @@
         <v>60</v>
       </c>
       <c r="D78">
-        <v>0.33197392587686264</v>
+        <v>0.33104905424242803</v>
       </c>
       <c r="E78" t="s">
         <v>53</v>
@@ -4008,7 +4008,7 @@
         <v>60</v>
       </c>
       <c r="I78">
-        <v>5.3039071481964788E-2</v>
+        <v>5.3116832270882625E-2</v>
       </c>
       <c r="J78" t="s">
         <v>53</v>
@@ -4034,7 +4034,7 @@
         <v>61</v>
       </c>
       <c r="D79">
-        <v>3.1590449059095096E-2</v>
+        <v>3.1843008274051142E-2</v>
       </c>
       <c r="E79" t="s">
         <v>53</v>
@@ -4046,7 +4046,7 @@
         <v>61</v>
       </c>
       <c r="I79">
-        <v>4.0648387873400249E-2</v>
+        <v>4.0663371691761784E-2</v>
       </c>
       <c r="J79" t="s">
         <v>53</v>
@@ -4072,7 +4072,7 @@
         <v>62</v>
       </c>
       <c r="D80">
-        <v>6.8948938360899412E-3</v>
+        <v>6.7972205772218325E-3</v>
       </c>
       <c r="E80" t="s">
         <v>53</v>
@@ -4084,7 +4084,7 @@
         <v>62</v>
       </c>
       <c r="I80">
-        <v>8.6945403884589087E-2</v>
+        <v>8.695485991953332E-2</v>
       </c>
       <c r="J80" t="s">
         <v>53</v>
@@ -4110,7 +4110,7 @@
         <v>63</v>
       </c>
       <c r="D81">
-        <v>0.14001535044124738</v>
+        <v>0.13855147659898992</v>
       </c>
       <c r="E81" t="s">
         <v>53</v>
@@ -4122,7 +4122,7 @@
         <v>63</v>
       </c>
       <c r="I81">
-        <v>0.10210016791423143</v>
+        <v>0.10213326612298475</v>
       </c>
       <c r="J81" t="s">
         <v>53</v>
@@ -4148,7 +4148,7 @@
         <v>64</v>
       </c>
       <c r="D82">
-        <v>1.5990713008328576E-3</v>
+        <v>1.5722837190106386E-3</v>
       </c>
       <c r="E82" t="s">
         <v>53</v>
@@ -4160,7 +4160,7 @@
         <v>64</v>
       </c>
       <c r="I82">
-        <v>7.5208611885625345E-2</v>
+        <v>7.5177744151055478E-2</v>
       </c>
       <c r="J82" t="s">
         <v>53</v>
@@ -4224,7 +4224,7 @@
         <v>54</v>
       </c>
       <c r="D84">
-        <v>6.3768170709060906E-2</v>
+        <v>6.3471303714747268E-2</v>
       </c>
       <c r="E84" t="s">
         <v>53</v>
@@ -4300,7 +4300,7 @@
         <v>56</v>
       </c>
       <c r="D86">
-        <v>2.6126015912640164E-2</v>
+        <v>2.6329078386994748E-2</v>
       </c>
       <c r="E86" t="s">
         <v>53</v>
@@ -4338,7 +4338,7 @@
         <v>57</v>
       </c>
       <c r="D87">
-        <v>0.32374515999200631</v>
+        <v>0.32441234122016477</v>
       </c>
       <c r="E87" t="s">
         <v>53</v>
@@ -4376,7 +4376,7 @@
         <v>58</v>
       </c>
       <c r="D88">
-        <v>2.030110701795261E-2</v>
+        <v>2.0333091742336652E-2</v>
       </c>
       <c r="E88" t="s">
         <v>53</v>
@@ -4414,7 +4414,7 @@
         <v>59</v>
       </c>
       <c r="D89">
-        <v>4.2451921343291101E-2</v>
+        <v>4.2490497122031061E-2</v>
       </c>
       <c r="E89" t="s">
         <v>53</v>
@@ -4452,7 +4452,7 @@
         <v>60</v>
       </c>
       <c r="D90">
-        <v>0.32868758963077438</v>
+        <v>0.32810801648410276</v>
       </c>
       <c r="E90" t="s">
         <v>53</v>
@@ -4490,7 +4490,7 @@
         <v>61</v>
       </c>
       <c r="D91">
-        <v>3.9762824753706474E-2</v>
+        <v>3.9740164184994986E-2</v>
       </c>
       <c r="E91" t="s">
         <v>53</v>
@@ -4528,7 +4528,7 @@
         <v>62</v>
       </c>
       <c r="D92">
-        <v>6.1521509869286589E-3</v>
+        <v>6.2064180724714074E-3</v>
       </c>
       <c r="E92" t="s">
         <v>53</v>
@@ -4566,7 +4566,7 @@
         <v>63</v>
       </c>
       <c r="D93">
-        <v>0.14661560561579987</v>
+        <v>0.14653943449050996</v>
       </c>
       <c r="E93" t="s">
         <v>53</v>
@@ -4604,7 +4604,7 @@
         <v>64</v>
       </c>
       <c r="D94">
-        <v>2.3894540378369186E-3</v>
+        <v>2.3696545816451042E-3</v>
       </c>
       <c r="E94" t="s">
         <v>53</v>
@@ -4680,7 +4680,7 @@
         <v>54</v>
       </c>
       <c r="D96">
-        <v>6.7739063581526468E-2</v>
+        <v>6.7498255518484346E-2</v>
       </c>
       <c r="E96" t="s">
         <v>53</v>
@@ -4756,7 +4756,7 @@
         <v>56</v>
       </c>
       <c r="D98">
-        <v>2.8443123155421343E-2</v>
+        <v>2.858609268020057E-2</v>
       </c>
       <c r="E98" t="s">
         <v>53</v>
@@ -4794,7 +4794,7 @@
         <v>57</v>
       </c>
       <c r="D99">
-        <v>0.33007842409135169</v>
+        <v>0.33069572277488829</v>
       </c>
       <c r="E99" t="s">
         <v>53</v>
@@ -4832,7 +4832,7 @@
         <v>58</v>
       </c>
       <c r="D100">
-        <v>1.6503047726622699E-2</v>
+        <v>1.646859269463203E-2</v>
       </c>
       <c r="E100" t="s">
         <v>53</v>
@@ -4870,7 +4870,7 @@
         <v>59</v>
       </c>
       <c r="D101">
-        <v>4.6284205872743761E-2</v>
+        <v>4.6122825350897484E-2</v>
       </c>
       <c r="E101" t="s">
         <v>53</v>
@@ -4908,7 +4908,7 @@
         <v>60</v>
       </c>
       <c r="D102">
-        <v>0.32309931141224002</v>
+        <v>0.32274429194802406</v>
       </c>
       <c r="E102" t="s">
         <v>53</v>
@@ -4946,7 +4946,7 @@
         <v>61</v>
       </c>
       <c r="D103">
-        <v>3.2621078529167638E-2</v>
+        <v>3.2507131701169104E-2</v>
       </c>
       <c r="E103" t="s">
         <v>53</v>
@@ -4984,7 +4984,7 @@
         <v>62</v>
       </c>
       <c r="D104">
-        <v>6.9457584131582912E-3</v>
+        <v>6.8059940168163757E-3</v>
       </c>
       <c r="E104" t="s">
         <v>53</v>
@@ -5022,7 +5022,7 @@
         <v>63</v>
       </c>
       <c r="D105">
-        <v>0.14645952077857746</v>
+        <v>0.1467464036587485</v>
       </c>
       <c r="E105" t="s">
         <v>53</v>
@@ -5060,7 +5060,7 @@
         <v>64</v>
       </c>
       <c r="D106">
-        <v>1.8264664391915853E-3</v>
+        <v>1.8246896561366255E-3</v>
       </c>
       <c r="E106" t="s">
         <v>53</v>
@@ -5098,7 +5098,7 @@
         <v>52</v>
       </c>
       <c r="D107">
-        <v>7.5305688489668419E-5</v>
+        <v>6.909293116429943E-5</v>
       </c>
       <c r="E107" t="s">
         <v>53</v>
@@ -5136,7 +5136,7 @@
         <v>54</v>
       </c>
       <c r="D108">
-        <v>7.8994389254252381E-2</v>
+        <v>7.8860656810920013E-2</v>
       </c>
       <c r="E108" t="s">
         <v>53</v>
@@ -5212,7 +5212,7 @@
         <v>56</v>
       </c>
       <c r="D110">
-        <v>3.7356933240119926E-2</v>
+        <v>3.7246141548471848E-2</v>
       </c>
       <c r="E110" t="s">
         <v>53</v>
@@ -5250,7 +5250,7 @@
         <v>57</v>
       </c>
       <c r="D111">
-        <v>0.30266016238585158</v>
+        <v>0.30219415220134288</v>
       </c>
       <c r="E111" t="s">
         <v>53</v>
@@ -5288,7 +5288,7 @@
         <v>58</v>
       </c>
       <c r="D112">
-        <v>1.1759327746171371E-2</v>
+        <v>1.1785547006504585E-2</v>
       </c>
       <c r="E112" t="s">
         <v>53</v>
@@ -5326,7 +5326,7 @@
         <v>59</v>
       </c>
       <c r="D113">
-        <v>5.8450188931177843E-2</v>
+        <v>5.8376899012120259E-2</v>
       </c>
       <c r="E113" t="s">
         <v>53</v>
@@ -5364,7 +5364,7 @@
         <v>60</v>
       </c>
       <c r="D114">
-        <v>0.33214496677253047</v>
+        <v>0.33277745862771962</v>
       </c>
       <c r="E114" t="s">
         <v>53</v>
@@ -5402,7 +5402,7 @@
         <v>61</v>
       </c>
       <c r="D115">
-        <v>2.5637210113257501E-2</v>
+        <v>2.5717665765975829E-2</v>
       </c>
       <c r="E115" t="s">
         <v>53</v>
@@ -5440,7 +5440,7 @@
         <v>62</v>
       </c>
       <c r="D116">
-        <v>8.675200631446698E-3</v>
+        <v>8.6314551423522443E-3</v>
       </c>
       <c r="E116" t="s">
         <v>53</v>
@@ -5478,7 +5478,7 @@
         <v>63</v>
       </c>
       <c r="D117">
-        <v>0.14306776459894274</v>
+        <v>0.1431598782096615</v>
       </c>
       <c r="E117" t="s">
         <v>53</v>
@@ -5516,7 +5516,7 @@
         <v>64</v>
       </c>
       <c r="D118">
-        <v>1.1785506377571676E-3</v>
+        <v>1.1810527437642777E-3</v>
       </c>
       <c r="E118" t="s">
         <v>53</v>
@@ -5554,7 +5554,7 @@
         <v>52</v>
       </c>
       <c r="D119">
-        <v>1.0952563202185512E-9</v>
+        <v>9.8986351088130496E-10</v>
       </c>
       <c r="E119" t="s">
         <v>53</v>
@@ -5592,7 +5592,7 @@
         <v>54</v>
       </c>
       <c r="D120">
-        <v>6.7236042940641394E-2</v>
+        <v>6.7146303666324306E-2</v>
       </c>
       <c r="E120" t="s">
         <v>53</v>
@@ -5668,7 +5668,7 @@
         <v>56</v>
       </c>
       <c r="D122">
-        <v>3.8357232026099593E-2</v>
+        <v>3.8352877993905632E-2</v>
       </c>
       <c r="E122" t="s">
         <v>53</v>
@@ -5706,7 +5706,7 @@
         <v>57</v>
       </c>
       <c r="D123">
-        <v>0.32824900282029945</v>
+        <v>0.32823616702802322</v>
       </c>
       <c r="E123" t="s">
         <v>53</v>
@@ -5744,7 +5744,7 @@
         <v>58</v>
       </c>
       <c r="D124">
-        <v>1.3777198236998647E-2</v>
+        <v>1.3801317612708077E-2</v>
       </c>
       <c r="E124" t="s">
         <v>53</v>
@@ -5782,7 +5782,7 @@
         <v>59</v>
       </c>
       <c r="D125">
-        <v>5.3304614681459792E-2</v>
+        <v>5.3278493237931594E-2</v>
       </c>
       <c r="E125" t="s">
         <v>53</v>
@@ -5820,7 +5820,7 @@
         <v>60</v>
       </c>
       <c r="D126">
-        <v>0.33220251987022542</v>
+        <v>0.33228415042105552</v>
       </c>
       <c r="E126" t="s">
         <v>53</v>
@@ -5858,7 +5858,7 @@
         <v>61</v>
       </c>
       <c r="D127">
-        <v>3.0243659495511725E-2</v>
+        <v>3.0277327022408283E-2</v>
       </c>
       <c r="E127" t="s">
         <v>53</v>
@@ -5896,7 +5896,7 @@
         <v>62</v>
       </c>
       <c r="D128">
-        <v>7.4730133993709865E-3</v>
+        <v>7.466303287726025E-3</v>
       </c>
       <c r="E128" t="s">
         <v>53</v>
@@ -5934,7 +5934,7 @@
         <v>63</v>
       </c>
       <c r="D129">
-        <v>0.1277680276448688</v>
+        <v>0.12776551560394095</v>
       </c>
       <c r="E129" t="s">
         <v>53</v>
@@ -5972,7 +5972,7 @@
         <v>64</v>
       </c>
       <c r="D130">
-        <v>1.3886877892669916E-3</v>
+        <v>1.3915431361112719E-3</v>
       </c>
       <c r="E130" t="s">
         <v>53</v>
@@ -6010,7 +6010,7 @@
         <v>52</v>
       </c>
       <c r="D131">
-        <v>2.6259624073628452E-5</v>
+        <v>2.7426333151613858E-5</v>
       </c>
       <c r="E131" t="s">
         <v>53</v>
@@ -6036,7 +6036,7 @@
         <v>54</v>
       </c>
       <c r="D132">
-        <v>7.1760707792765166E-2</v>
+        <v>7.1676840098715958E-2</v>
       </c>
       <c r="E132" t="s">
         <v>53</v>
@@ -6088,7 +6088,7 @@
         <v>56</v>
       </c>
       <c r="D134">
-        <v>3.7312589518224491E-2</v>
+        <v>3.7416109776342181E-2</v>
       </c>
       <c r="E134" t="s">
         <v>53</v>
@@ -6114,7 +6114,7 @@
         <v>57</v>
       </c>
       <c r="D135">
-        <v>0.3162382876270442</v>
+        <v>0.31668354981034408</v>
       </c>
       <c r="E135" t="s">
         <v>53</v>
@@ -6140,7 +6140,7 @@
         <v>58</v>
       </c>
       <c r="D136">
-        <v>1.2026660232155225E-2</v>
+        <v>1.2023700730970486E-2</v>
       </c>
       <c r="E136" t="s">
         <v>53</v>
@@ -6166,7 +6166,7 @@
         <v>59</v>
       </c>
       <c r="D137">
-        <v>5.7219825873404837E-2</v>
+        <v>5.7197311995085758E-2</v>
       </c>
       <c r="E137" t="s">
         <v>53</v>
@@ -6192,7 +6192,7 @@
         <v>60</v>
       </c>
       <c r="D138">
-        <v>0.33389180722874684</v>
+        <v>0.3336905852335964</v>
       </c>
       <c r="E138" t="s">
         <v>53</v>
@@ -6218,7 +6218,7 @@
         <v>61</v>
       </c>
       <c r="D139">
-        <v>2.7499637324350901E-2</v>
+        <v>2.7519719712929908E-2</v>
       </c>
       <c r="E139" t="s">
         <v>53</v>
@@ -6244,7 +6244,7 @@
         <v>62</v>
       </c>
       <c r="D140">
-        <v>8.0331290805462589E-3</v>
+        <v>8.0458277304882916E-3</v>
       </c>
       <c r="E140" t="s">
         <v>53</v>
@@ -6270,7 +6270,7 @@
         <v>63</v>
       </c>
       <c r="D141">
-        <v>0.13471709059840725</v>
+        <v>0.13444295395221376</v>
       </c>
       <c r="E141" t="s">
         <v>53</v>
@@ -6296,7 +6296,7 @@
         <v>64</v>
       </c>
       <c r="D142">
-        <v>1.274005100279089E-3</v>
+        <v>1.2759746261611143E-3</v>
       </c>
       <c r="E142" t="s">
         <v>53</v>
@@ -6322,7 +6322,7 @@
         <v>52</v>
       </c>
       <c r="D143">
-        <v>2.7202112365036024E-4</v>
+        <v>2.7374471485977481E-4</v>
       </c>
       <c r="E143" t="s">
         <v>53</v>
@@ -6348,7 +6348,7 @@
         <v>54</v>
       </c>
       <c r="D144">
-        <v>0.10284106313282161</v>
+        <v>0.10319133496901212</v>
       </c>
       <c r="E144" t="s">
         <v>53</v>
@@ -6400,7 +6400,7 @@
         <v>56</v>
       </c>
       <c r="D146">
-        <v>3.1456295542101297E-2</v>
+        <v>3.1545820481490863E-2</v>
       </c>
       <c r="E146" t="s">
         <v>53</v>
@@ -6426,7 +6426,7 @@
         <v>57</v>
       </c>
       <c r="D147">
-        <v>0.28024175510001059</v>
+        <v>0.28024918962929524</v>
       </c>
       <c r="E147" t="s">
         <v>53</v>
@@ -6452,7 +6452,7 @@
         <v>58</v>
       </c>
       <c r="D148">
-        <v>9.897835039593704E-3</v>
+        <v>9.8613481806807315E-3</v>
       </c>
       <c r="E148" t="s">
         <v>53</v>
@@ -6478,7 +6478,7 @@
         <v>59</v>
       </c>
       <c r="D149">
-        <v>4.8486031393620288E-2</v>
+        <v>4.8467284020236492E-2</v>
       </c>
       <c r="E149" t="s">
         <v>53</v>
@@ -6504,7 +6504,7 @@
         <v>60</v>
       </c>
       <c r="D150">
-        <v>0.32177982010285683</v>
+        <v>0.32137054201735693</v>
       </c>
       <c r="E150" t="s">
         <v>53</v>
@@ -6530,7 +6530,7 @@
         <v>61</v>
       </c>
       <c r="D151">
-        <v>2.1791635147382183E-2</v>
+        <v>2.1731335841149894E-2</v>
       </c>
       <c r="E151" t="s">
         <v>53</v>
@@ -6556,7 +6556,7 @@
         <v>62</v>
       </c>
       <c r="D152">
-        <v>1.014367230297774E-2</v>
+        <v>1.0168266198019273E-2</v>
       </c>
       <c r="E152" t="s">
         <v>53</v>
@@ -6582,7 +6582,7 @@
         <v>63</v>
       </c>
       <c r="D153">
-        <v>0.17163215731628889</v>
+        <v>0.17169019076236747</v>
       </c>
       <c r="E153" t="s">
         <v>53</v>
@@ -6608,7 +6608,7 @@
         <v>64</v>
       </c>
       <c r="D154">
-        <v>1.4577137986977763E-3</v>
+        <v>1.4509431855343599E-3</v>
       </c>
       <c r="E154" t="s">
         <v>53</v>
@@ -6634,7 +6634,7 @@
         <v>52</v>
       </c>
       <c r="D155">
-        <v>2.5934410797523184E-4</v>
+        <v>2.6618482647272173E-4</v>
       </c>
       <c r="E155" t="s">
         <v>53</v>
@@ -6660,7 +6660,7 @@
         <v>54</v>
       </c>
       <c r="D156">
-        <v>9.0291121801969312E-2</v>
+        <v>9.0769590571773279E-2</v>
       </c>
       <c r="E156" t="s">
         <v>53</v>
@@ -6712,7 +6712,7 @@
         <v>56</v>
       </c>
       <c r="D158">
-        <v>3.5545818149973311E-2</v>
+        <v>3.5529920245665231E-2</v>
       </c>
       <c r="E158" t="s">
         <v>53</v>
@@ -6738,7 +6738,7 @@
         <v>57</v>
       </c>
       <c r="D159">
-        <v>0.28977482222795808</v>
+        <v>0.28943400833968952</v>
       </c>
       <c r="E159" t="s">
         <v>53</v>
@@ -6764,7 +6764,7 @@
         <v>58</v>
       </c>
       <c r="D160">
-        <v>1.0282711267951803E-2</v>
+        <v>1.0258271119955857E-2</v>
       </c>
       <c r="E160" t="s">
         <v>53</v>
@@ -6790,7 +6790,7 @@
         <v>59</v>
       </c>
       <c r="D161">
-        <v>5.3145746829119468E-2</v>
+        <v>5.301176325386555E-2</v>
       </c>
       <c r="E161" t="s">
         <v>53</v>
@@ -6816,7 +6816,7 @@
         <v>60</v>
       </c>
       <c r="D162">
-        <v>0.32758190427776612</v>
+        <v>0.32725291998150757</v>
       </c>
       <c r="E162" t="s">
         <v>53</v>
@@ -6842,7 +6842,7 @@
         <v>61</v>
       </c>
       <c r="D163">
-        <v>2.1944346549929973E-2</v>
+        <v>2.1893358661718456E-2</v>
       </c>
       <c r="E163" t="s">
         <v>53</v>
@@ -6868,7 +6868,7 @@
         <v>62</v>
       </c>
       <c r="D164">
-        <v>1.0245680574323403E-2</v>
+        <v>1.0278018430461264E-2</v>
       </c>
       <c r="E164" t="s">
         <v>53</v>
@@ -6894,7 +6894,7 @@
         <v>63</v>
       </c>
       <c r="D165">
-        <v>0.15965017651868013</v>
+        <v>0.16002598863393791</v>
       </c>
       <c r="E165" t="s">
         <v>53</v>
@@ -6920,7 +6920,7 @@
         <v>64</v>
       </c>
       <c r="D166">
-        <v>1.2783276943538209E-3</v>
+        <v>1.2799759349548375E-3</v>
       </c>
       <c r="E166" t="s">
         <v>53</v>
@@ -6972,7 +6972,7 @@
         <v>54</v>
       </c>
       <c r="D168">
-        <v>0.10608333145946781</v>
+        <v>0.10705847798053528</v>
       </c>
       <c r="E168" t="s">
         <v>53</v>
@@ -7024,7 +7024,7 @@
         <v>56</v>
       </c>
       <c r="D170">
-        <v>2.6241656946795082E-2</v>
+        <v>2.5809028998462751E-2</v>
       </c>
       <c r="E170" t="s">
         <v>53</v>
@@ -7050,7 +7050,7 @@
         <v>57</v>
       </c>
       <c r="D171">
-        <v>0.27716762301031733</v>
+        <v>0.2771799889854657</v>
       </c>
       <c r="E171" t="s">
         <v>53</v>
@@ -7076,7 +7076,7 @@
         <v>58</v>
       </c>
       <c r="D172">
-        <v>1.2475849418897384E-2</v>
+        <v>1.2582862744573726E-2</v>
       </c>
       <c r="E172" t="s">
         <v>53</v>
@@ -7102,7 +7102,7 @@
         <v>59</v>
       </c>
       <c r="D173">
-        <v>4.3882439511982507E-2</v>
+        <v>4.3318247551879803E-2</v>
       </c>
       <c r="E173" t="s">
         <v>53</v>
@@ -7128,7 +7128,7 @@
         <v>60</v>
       </c>
       <c r="D174">
-        <v>0.32322749546093588</v>
+        <v>0.32240532009455702</v>
       </c>
       <c r="E174" t="s">
         <v>53</v>
@@ -7154,7 +7154,7 @@
         <v>61</v>
       </c>
       <c r="D175">
-        <v>2.5387052432841721E-2</v>
+        <v>2.5577248808938535E-2</v>
       </c>
       <c r="E175" t="s">
         <v>53</v>
@@ -7180,7 +7180,7 @@
         <v>62</v>
       </c>
       <c r="D176">
-        <v>8.1928845914691541E-3</v>
+        <v>8.0786885488166975E-3</v>
       </c>
       <c r="E176" t="s">
         <v>53</v>
@@ -7206,7 +7206,7 @@
         <v>63</v>
       </c>
       <c r="D177">
-        <v>0.1754704666371571</v>
+        <v>0.17610033220094812</v>
       </c>
       <c r="E177" t="s">
         <v>53</v>
@@ -7232,7 +7232,7 @@
         <v>64</v>
       </c>
       <c r="D178">
-        <v>1.871200530133039E-3</v>
+        <v>1.889804085824029E-3</v>
       </c>
       <c r="E178" t="s">
         <v>53</v>
@@ -7284,7 +7284,7 @@
         <v>54</v>
       </c>
       <c r="D180">
-        <v>9.3610809445157372E-2</v>
+        <v>9.5617031192836113E-2</v>
       </c>
       <c r="E180" t="s">
         <v>53</v>
@@ -7336,7 +7336,7 @@
         <v>56</v>
       </c>
       <c r="D182">
-        <v>2.5762803635527038E-2</v>
+        <v>2.5650479799733412E-2</v>
       </c>
       <c r="E182" t="s">
         <v>53</v>
@@ -7362,7 +7362,7 @@
         <v>57</v>
       </c>
       <c r="D183">
-        <v>0.27626963040979052</v>
+        <v>0.27558178265075378</v>
       </c>
       <c r="E183" t="s">
         <v>53</v>
@@ -7388,7 +7388,7 @@
         <v>58</v>
       </c>
       <c r="D184">
-        <v>1.3240018654179174E-2</v>
+        <v>1.3092913262449418E-2</v>
       </c>
       <c r="E184" t="s">
         <v>53</v>
@@ -7414,7 +7414,7 @@
         <v>59</v>
       </c>
       <c r="D185">
-        <v>4.2997079126519594E-2</v>
+        <v>4.2950366060061702E-2</v>
       </c>
       <c r="E185" t="s">
         <v>53</v>
@@ -7440,7 +7440,7 @@
         <v>60</v>
       </c>
       <c r="D186">
-        <v>0.3356097926156843</v>
+        <v>0.33484357884868055</v>
       </c>
       <c r="E186" t="s">
         <v>53</v>
@@ -7466,7 +7466,7 @@
         <v>61</v>
       </c>
       <c r="D187">
-        <v>2.9007157117531018E-2</v>
+        <v>2.8770059230015587E-2</v>
       </c>
       <c r="E187" t="s">
         <v>53</v>
@@ -7492,7 +7492,7 @@
         <v>62</v>
       </c>
       <c r="D188">
-        <v>7.4339398676949173E-3</v>
+        <v>7.5736190219616124E-3</v>
       </c>
       <c r="E188" t="s">
         <v>53</v>
@@ -7518,7 +7518,7 @@
         <v>63</v>
       </c>
       <c r="D189">
-        <v>0.1741773648124384</v>
+        <v>0.17400914650982008</v>
       </c>
       <c r="E189" t="s">
         <v>53</v>
@@ -7544,7 +7544,7 @@
         <v>64</v>
       </c>
       <c r="D190">
-        <v>1.8914043154779194E-3</v>
+        <v>1.9110234236870563E-3</v>
       </c>
       <c r="E190" t="s">
         <v>53</v>
@@ -7596,7 +7596,7 @@
         <v>54</v>
       </c>
       <c r="D192">
-        <v>7.5286649485648505E-2</v>
+        <v>7.4713730804062725E-2</v>
       </c>
       <c r="E192" t="s">
         <v>53</v>
@@ -7648,7 +7648,7 @@
         <v>56</v>
       </c>
       <c r="D194">
-        <v>2.6211473820748874E-2</v>
+        <v>2.5658328520294729E-2</v>
       </c>
       <c r="E194" t="s">
         <v>53</v>
@@ -7674,7 +7674,7 @@
         <v>57</v>
       </c>
       <c r="D195">
-        <v>0.29148654724938716</v>
+        <v>0.29178237507188232</v>
       </c>
       <c r="E195" t="s">
         <v>53</v>
@@ -7700,7 +7700,7 @@
         <v>58</v>
       </c>
       <c r="D196">
-        <v>1.467842229614855E-2</v>
+        <v>1.524260478099655E-2</v>
       </c>
       <c r="E196" t="s">
         <v>53</v>
@@ -7726,7 +7726,7 @@
         <v>59</v>
       </c>
       <c r="D197">
-        <v>4.6419715127242182E-2</v>
+        <v>4.5673558870242138E-2</v>
       </c>
       <c r="E197" t="s">
         <v>53</v>
@@ -7752,7 +7752,7 @@
         <v>60</v>
       </c>
       <c r="D198">
-        <v>0.34166072239329776</v>
+        <v>0.34159743333899667</v>
       </c>
       <c r="E198" t="s">
         <v>53</v>
@@ -7778,7 +7778,7 @@
         <v>61</v>
       </c>
       <c r="D199">
-        <v>3.1710072103519685E-2</v>
+        <v>3.2385063485723932E-2</v>
       </c>
       <c r="E199" t="s">
         <v>53</v>
@@ -7804,7 +7804,7 @@
         <v>62</v>
       </c>
       <c r="D200">
-        <v>7.5576519710684829E-3</v>
+        <v>7.4508083843738034E-3</v>
       </c>
       <c r="E200" t="s">
         <v>53</v>
@@ -7830,7 +7830,7 @@
         <v>63</v>
       </c>
       <c r="D201">
-        <v>0.16318440871859141</v>
+        <v>0.16372681905730638</v>
       </c>
       <c r="E201" t="s">
         <v>53</v>
@@ -7856,7 +7856,7 @@
         <v>64</v>
       </c>
       <c r="D202">
-        <v>1.8043368343473682E-3</v>
+        <v>1.7692776861207326E-3</v>
       </c>
       <c r="E202" t="s">
         <v>53</v>
@@ -7908,7 +7908,7 @@
         <v>54</v>
       </c>
       <c r="D204">
-        <v>7.0264071859403768E-2</v>
+        <v>6.9290311571817226E-2</v>
       </c>
       <c r="E204" t="s">
         <v>53</v>
@@ -7960,7 +7960,7 @@
         <v>56</v>
       </c>
       <c r="D206">
-        <v>2.6742234814587117E-2</v>
+        <v>2.6592506299167526E-2</v>
       </c>
       <c r="E206" t="s">
         <v>53</v>
@@ -7986,7 +7986,7 @@
         <v>57</v>
       </c>
       <c r="D207">
-        <v>0.30603056003747814</v>
+        <v>0.3087826866244428</v>
       </c>
       <c r="E207" t="s">
         <v>53</v>
@@ -8012,7 +8012,7 @@
         <v>58</v>
       </c>
       <c r="D208">
-        <v>1.5259472810283368E-2</v>
+        <v>1.5746147793704215E-2</v>
       </c>
       <c r="E208" t="s">
         <v>53</v>
@@ -8038,7 +8038,7 @@
         <v>59</v>
       </c>
       <c r="D209">
-        <v>4.8561663633186543E-2</v>
+        <v>4.8419220350748457E-2</v>
       </c>
       <c r="E209" t="s">
         <v>53</v>
@@ -8064,7 +8064,7 @@
         <v>60</v>
       </c>
       <c r="D210">
-        <v>0.33707562067582925</v>
+        <v>0.33616788432608413</v>
       </c>
       <c r="E210" t="s">
         <v>53</v>
@@ -8090,7 +8090,7 @@
         <v>61</v>
       </c>
       <c r="D211">
-        <v>3.2308706970093602E-2</v>
+        <v>3.2556016059058619E-2</v>
       </c>
       <c r="E211" t="s">
         <v>53</v>
@@ -8116,7 +8116,7 @@
         <v>62</v>
       </c>
       <c r="D212">
-        <v>7.6949915964270414E-3</v>
+        <v>7.6858836059066349E-3</v>
       </c>
       <c r="E212" t="s">
         <v>53</v>
@@ -8142,7 +8142,7 @@
         <v>63</v>
       </c>
       <c r="D213">
-        <v>0.15416756887418701</v>
+        <v>0.15289116966572439</v>
       </c>
       <c r="E213" t="s">
         <v>53</v>
@@ -8168,7 +8168,7 @@
         <v>64</v>
       </c>
       <c r="D214">
-        <v>1.8951087285247162E-3</v>
+        <v>1.8681737033404248E-3</v>
       </c>
       <c r="E214" t="s">
         <v>53</v>
@@ -8220,7 +8220,7 @@
         <v>54</v>
       </c>
       <c r="D216">
-        <v>7.4316314556685442E-2</v>
+        <v>7.4197015545942185E-2</v>
       </c>
       <c r="E216" t="s">
         <v>53</v>
@@ -8272,7 +8272,7 @@
         <v>56</v>
       </c>
       <c r="D218">
-        <v>3.1255390829928009E-2</v>
+        <v>3.180388419121298E-2</v>
       </c>
       <c r="E218" t="s">
         <v>53</v>
@@ -8298,7 +8298,7 @@
         <v>57</v>
       </c>
       <c r="D219">
-        <v>0.29287957717616603</v>
+        <v>0.29269398862776186</v>
       </c>
       <c r="E219" t="s">
         <v>53</v>
@@ -8324,7 +8324,7 @@
         <v>58</v>
       </c>
       <c r="D220">
-        <v>1.252604884419658E-2</v>
+        <v>1.2468801906355659E-2</v>
       </c>
       <c r="E220" t="s">
         <v>53</v>
@@ -8350,7 +8350,7 @@
         <v>59</v>
       </c>
       <c r="D221">
-        <v>5.5003528410841045E-2</v>
+        <v>5.5672888220839843E-2</v>
       </c>
       <c r="E221" t="s">
         <v>53</v>
@@ -8376,7 +8376,7 @@
         <v>60</v>
       </c>
       <c r="D222">
-        <v>0.3459253600070602</v>
+        <v>0.34645858014738035</v>
       </c>
       <c r="E222" t="s">
         <v>53</v>
@@ -8402,7 +8402,7 @@
         <v>61</v>
       </c>
       <c r="D223">
-        <v>2.8360968011254487E-2</v>
+        <v>2.8141464963918037E-2</v>
       </c>
       <c r="E223" t="s">
         <v>53</v>
@@ -8428,7 +8428,7 @@
         <v>62</v>
       </c>
       <c r="D224">
-        <v>8.0688060148930447E-3</v>
+        <v>8.074847398495566E-3</v>
       </c>
       <c r="E224" t="s">
         <v>53</v>
@@ -8454,7 +8454,7 @@
         <v>63</v>
       </c>
       <c r="D225">
-        <v>0.15019530927408686</v>
+        <v>0.14907703111113613</v>
       </c>
       <c r="E225" t="s">
         <v>53</v>
@@ -8480,7 +8480,7 @@
         <v>64</v>
       </c>
       <c r="D226">
-        <v>1.4686968748873403E-3</v>
+        <v>1.4114978869565786E-3</v>
       </c>
       <c r="E226" t="s">
         <v>53</v>
@@ -8518,7 +8518,7 @@
         <v>52</v>
       </c>
       <c r="I227">
-        <v>0.1177473917069823</v>
+        <v>0.11780111144854107</v>
       </c>
       <c r="J227" t="s">
         <v>53</v>
@@ -8532,7 +8532,7 @@
         <v>54</v>
       </c>
       <c r="D228">
-        <v>8.6070343353117335E-2</v>
+        <v>8.321854373268596E-2</v>
       </c>
       <c r="E228" t="s">
         <v>53</v>
@@ -8544,7 +8544,7 @@
         <v>54</v>
       </c>
       <c r="I228">
-        <v>0.14829078664323189</v>
+        <v>0.14846328704855094</v>
       </c>
       <c r="J228" t="s">
         <v>53</v>
@@ -8570,7 +8570,7 @@
         <v>55</v>
       </c>
       <c r="I229">
-        <v>9.4157669781299816E-2</v>
+        <v>9.4257511244969783E-2</v>
       </c>
       <c r="J229" t="s">
         <v>53</v>
@@ -8584,7 +8584,7 @@
         <v>56</v>
       </c>
       <c r="D230">
-        <v>2.9432809428413753E-2</v>
+        <v>2.9398588479047957E-2</v>
       </c>
       <c r="E230" t="s">
         <v>53</v>
@@ -8596,7 +8596,7 @@
         <v>56</v>
       </c>
       <c r="I230">
-        <v>8.554600248084758E-2</v>
+        <v>8.526509407615783E-2</v>
       </c>
       <c r="J230" t="s">
         <v>53</v>
@@ -8610,7 +8610,7 @@
         <v>57</v>
       </c>
       <c r="D231">
-        <v>0.28304346680082537</v>
+        <v>0.28512021926632009</v>
       </c>
       <c r="E231" t="s">
         <v>53</v>
@@ -8622,7 +8622,7 @@
         <v>57</v>
       </c>
       <c r="I231">
-        <v>8.7940245694804339E-2</v>
+        <v>8.8027308165610801E-2</v>
       </c>
       <c r="J231" t="s">
         <v>53</v>
@@ -8636,7 +8636,7 @@
         <v>58</v>
       </c>
       <c r="D232">
-        <v>1.164427714205833E-2</v>
+        <v>1.1564921215812887E-2</v>
       </c>
       <c r="E232" t="s">
         <v>53</v>
@@ -8648,7 +8648,7 @@
         <v>58</v>
       </c>
       <c r="I232">
-        <v>6.8346012935486852E-2</v>
+        <v>6.8291768476023598E-2</v>
       </c>
       <c r="J232" t="s">
         <v>53</v>
@@ -8662,7 +8662,7 @@
         <v>59</v>
       </c>
       <c r="D233">
-        <v>5.1187887391172547E-2</v>
+        <v>5.1485503641778382E-2</v>
       </c>
       <c r="E233" t="s">
         <v>53</v>
@@ -8674,7 +8674,7 @@
         <v>59</v>
       </c>
       <c r="I233">
-        <v>4.3899787023785886E-2</v>
+        <v>4.3632434481278834E-2</v>
       </c>
       <c r="J233" t="s">
         <v>53</v>
@@ -8688,7 +8688,7 @@
         <v>60</v>
       </c>
       <c r="D234">
-        <v>0.34168833149125177</v>
+        <v>0.34343605361075236</v>
       </c>
       <c r="E234" t="s">
         <v>53</v>
@@ -8700,7 +8700,7 @@
         <v>60</v>
       </c>
       <c r="I234">
-        <v>4.9671398622610892E-2</v>
+        <v>4.978325752533113E-2</v>
       </c>
       <c r="J234" t="s">
         <v>53</v>
@@ -8714,7 +8714,7 @@
         <v>61</v>
       </c>
       <c r="D235">
-        <v>2.67121224223918E-2</v>
+        <v>2.713441281217964E-2</v>
       </c>
       <c r="E235" t="s">
         <v>53</v>
@@ -8726,7 +8726,7 @@
         <v>61</v>
       </c>
       <c r="I235">
-        <v>3.4125280528430182E-2</v>
+        <v>3.4025512374897399E-2</v>
       </c>
       <c r="J235" t="s">
         <v>53</v>
@@ -8740,7 +8740,7 @@
         <v>62</v>
       </c>
       <c r="D236">
-        <v>8.4283043148226378E-3</v>
+        <v>8.3569529411364526E-3</v>
       </c>
       <c r="E236" t="s">
         <v>53</v>
@@ -8752,7 +8752,7 @@
         <v>62</v>
       </c>
       <c r="I236">
-        <v>8.5293482154232769E-2</v>
+        <v>8.5116608903684651E-2</v>
       </c>
       <c r="J236" t="s">
         <v>53</v>
@@ -8766,7 +8766,7 @@
         <v>63</v>
       </c>
       <c r="D237">
-        <v>0.16014204396457113</v>
+        <v>0.15864949403816986</v>
       </c>
       <c r="E237" t="s">
         <v>53</v>
@@ -8778,7 +8778,7 @@
         <v>63</v>
       </c>
       <c r="I237">
-        <v>0.10747167378146327</v>
+        <v>0.10774000315209203</v>
       </c>
       <c r="J237" t="s">
         <v>53</v>
@@ -8792,7 +8792,7 @@
         <v>64</v>
       </c>
       <c r="D238">
-        <v>1.6504136913743184E-3</v>
+        <v>1.6353102621146697E-3</v>
       </c>
       <c r="E238" t="s">
         <v>53</v>
@@ -8804,7 +8804,7 @@
         <v>64</v>
       </c>
       <c r="I238">
-        <v>7.7510268646826169E-2</v>
+        <v>7.7596103102857014E-2</v>
       </c>
       <c r="J238" t="s">
         <v>53</v>
@@ -8818,7 +8818,7 @@
         <v>52</v>
       </c>
       <c r="D239">
-        <v>1.5590618465953662E-6</v>
+        <v>1.0014058758320814E-6</v>
       </c>
       <c r="E239" t="s">
         <v>53</v>
@@ -8844,7 +8844,7 @@
         <v>54</v>
       </c>
       <c r="D240">
-        <v>7.852999556817912E-2</v>
+        <v>7.7903491980841483E-2</v>
       </c>
       <c r="E240" t="s">
         <v>53</v>
@@ -8896,7 +8896,7 @@
         <v>56</v>
       </c>
       <c r="D242">
-        <v>3.3444535761481986E-2</v>
+        <v>3.3474777401878257E-2</v>
       </c>
       <c r="E242" t="s">
         <v>53</v>
@@ -8922,7 +8922,7 @@
         <v>57</v>
       </c>
       <c r="D243">
-        <v>0.28986965095942574</v>
+        <v>0.29004195469655208</v>
       </c>
       <c r="E243" t="s">
         <v>53</v>
@@ -8948,7 +8948,7 @@
         <v>58</v>
       </c>
       <c r="D244">
-        <v>1.1486953682149642E-2</v>
+        <v>1.1531790549441005E-2</v>
       </c>
       <c r="E244" t="s">
         <v>53</v>
@@ -8974,7 +8974,7 @@
         <v>59</v>
       </c>
       <c r="D245">
-        <v>5.5523274243279505E-2</v>
+        <v>5.5738581110043664E-2</v>
       </c>
       <c r="E245" t="s">
         <v>53</v>
@@ -9000,7 +9000,7 @@
         <v>60</v>
       </c>
       <c r="D246">
-        <v>0.3412540255313794</v>
+        <v>0.34188896846152861</v>
       </c>
       <c r="E246" t="s">
         <v>53</v>
@@ -9026,7 +9026,7 @@
         <v>61</v>
       </c>
       <c r="D247">
-        <v>2.6575648477166935E-2</v>
+        <v>2.672089285204806E-2</v>
       </c>
       <c r="E247" t="s">
         <v>53</v>
@@ -9052,7 +9052,7 @@
         <v>62</v>
       </c>
       <c r="D248">
-        <v>8.7279156451866933E-3</v>
+        <v>8.6898793499387197E-3</v>
       </c>
       <c r="E248" t="s">
         <v>53</v>
@@ -9078,7 +9078,7 @@
         <v>63</v>
       </c>
       <c r="D249">
-        <v>0.153266993383707</v>
+        <v>0.15269715368404937</v>
       </c>
       <c r="E249" t="s">
         <v>53</v>
@@ -9104,7 +9104,7 @@
         <v>64</v>
       </c>
       <c r="D250">
-        <v>1.319447686195139E-3</v>
+        <v>1.3115085078021552E-3</v>
       </c>
       <c r="E250" t="s">
         <v>53</v>
@@ -9128,7 +9128,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1667E3F7-CEA9-40E1-AECA-394F8A704A69}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BD24A6C-4731-41EA-9BF1-A37DFD51D55B}">
   <dimension ref="B9:BL60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9344,37 +9344,37 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0.39420543044789591</v>
+        <v>0.39544519403841022</v>
       </c>
       <c r="F11">
         <v>0.99814814814814812</v>
       </c>
       <c r="G11">
-        <v>0.81276477316440376</v>
+        <v>0.8136273260668464</v>
       </c>
       <c r="H11">
-        <v>0.22993963328998498</v>
+        <v>0.2305444914590988</v>
       </c>
       <c r="I11">
-        <v>0.74309409650789993</v>
+        <v>0.74291359138670532</v>
       </c>
       <c r="J11">
-        <v>0.70645257406417217</v>
+        <v>0.70721519747608341</v>
       </c>
       <c r="K11">
-        <v>0.15359919108810818</v>
+        <v>0.15399121798097593</v>
       </c>
       <c r="L11">
-        <v>0.60723798648131633</v>
+        <v>0.60707522706323924</v>
       </c>
       <c r="M11">
-        <v>0.93899538863181353</v>
+        <v>0.94060139918867824</v>
       </c>
       <c r="N11">
-        <v>0.34862045472821318</v>
+        <v>0.35006920908769917</v>
       </c>
       <c r="O11">
-        <v>0.94732031757626389</v>
+        <v>0.9472406970146543</v>
       </c>
       <c r="Q11" t="s">
         <v>164</v>
@@ -9383,40 +9383,40 @@
         <v>165</v>
       </c>
       <c r="S11">
-        <v>0.98884116886885132</v>
+        <v>0.98883359192158815</v>
       </c>
       <c r="T11">
-        <v>0.15647641040776328</v>
+        <v>0.15847022884052397</v>
       </c>
       <c r="U11">
         <v>0</v>
       </c>
       <c r="V11">
-        <v>0.58938259936395077</v>
+        <v>0.58709614448333969</v>
       </c>
       <c r="W11">
-        <v>3.6027498980354671E-2</v>
+        <v>3.6310405707246599E-2</v>
       </c>
       <c r="X11">
-        <v>0.41120264014647845</v>
+        <v>0.3824672684708742</v>
       </c>
       <c r="Y11">
-        <v>0.45222475395727041</v>
+        <v>0.45095590042037886</v>
       </c>
       <c r="Z11">
-        <v>1.8738485132465996E-2</v>
+        <v>2.075021814417265E-2</v>
       </c>
       <c r="AA11">
-        <v>0.33944345029722189</v>
+        <v>0.34253886358823954</v>
       </c>
       <c r="AB11">
-        <v>0.79361701402063012</v>
+        <v>0.79382698866501922</v>
       </c>
       <c r="AC11">
-        <v>8.2179784570201919E-2</v>
+        <v>8.3006789270481621E-2</v>
       </c>
       <c r="AD11">
-        <v>0.20713287795546761</v>
+        <v>0.1445966715721517</v>
       </c>
       <c r="AF11" t="s">
         <v>164</v>
@@ -9428,7 +9428,7 @@
         <v>0</v>
       </c>
       <c r="AI11">
-        <v>4.9613659209719503E-2</v>
+        <v>5.1369827423705494E-2</v>
       </c>
       <c r="AJ11">
         <v>0</v>
@@ -9437,25 +9437,25 @@
         <v>0</v>
       </c>
       <c r="AL11">
-        <v>5.8127361084810376E-2</v>
+        <v>5.7259671076132231E-2</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1.4787684026820239E-2</v>
       </c>
       <c r="AN11">
         <v>0</v>
       </c>
       <c r="AO11">
-        <v>3.8328485617460079E-2</v>
+        <v>3.7422175068833954E-2</v>
       </c>
       <c r="AP11">
-        <v>7.3563027138581691E-3</v>
+        <v>1.4964910169038531E-2</v>
       </c>
       <c r="AQ11">
         <v>0</v>
       </c>
       <c r="AR11">
-        <v>9.2725030358223368E-2</v>
+        <v>9.7303119009853375E-2</v>
       </c>
       <c r="AS11">
         <v>0</v>
@@ -9467,37 +9467,37 @@
         <v>0</v>
       </c>
       <c r="AW11">
-        <v>0.10502998642390585</v>
+        <v>0.10467062169014847</v>
       </c>
       <c r="AX11">
-        <v>7.4926220915236703E-6</v>
+        <v>9.3916664944300607E-6</v>
       </c>
       <c r="AY11">
-        <v>3.5197116876812776E-2</v>
+        <v>3.5025945899982293E-2</v>
       </c>
       <c r="AZ11">
-        <v>0.36553803179913902</v>
+        <v>0.36436503269838871</v>
       </c>
       <c r="BA11">
-        <v>3.7323289171703113E-2</v>
+        <v>3.716450542411176E-2</v>
       </c>
       <c r="BB11">
-        <v>6.302087868337479E-2</v>
+        <v>6.2765373653355744E-2</v>
       </c>
       <c r="BC11">
-        <v>0.44274789968507355</v>
+        <v>0.44300759202112644</v>
       </c>
       <c r="BD11">
-        <v>7.7847152094713615E-2</v>
+        <v>7.8133604862046471E-2</v>
       </c>
       <c r="BE11">
-        <v>7.498373934796583E-3</v>
+        <v>7.4657560655551616E-3</v>
       </c>
       <c r="BF11">
-        <v>0.20448613954845429</v>
+        <v>0.20452427560178818</v>
       </c>
       <c r="BG11">
-        <v>5.7129765679587059E-3</v>
+        <v>5.7872179006423462E-3</v>
       </c>
       <c r="BI11" t="s">
         <v>114</v>
@@ -9509,7 +9509,7 @@
         <v>172</v>
       </c>
       <c r="BL11">
-        <v>0.43173263538053652</v>
+        <v>0.43135317373905929</v>
       </c>
     </row>
     <row r="12" spans="2:64" x14ac:dyDescent="0.45">
@@ -9523,37 +9523,37 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0.35572280231896081</v>
+        <v>0.36084222540115024</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>0.80695567446271532</v>
+        <v>0.80914285836258271</v>
       </c>
       <c r="H12">
-        <v>0.23558134484111884</v>
+        <v>0.24085238498065492</v>
       </c>
       <c r="I12">
-        <v>0.76570375450271377</v>
+        <v>0.77290512447454751</v>
       </c>
       <c r="J12">
-        <v>0.71106216656395915</v>
+        <v>0.71540981808517701</v>
       </c>
       <c r="K12">
-        <v>0.15454971425439146</v>
+        <v>0.15821924917494098</v>
       </c>
       <c r="L12">
-        <v>0.61899788749790252</v>
+        <v>0.6230572063849491</v>
       </c>
       <c r="M12">
-        <v>0.92736446372468362</v>
+        <v>0.92845432130920358</v>
       </c>
       <c r="N12">
-        <v>0.31479322623285744</v>
+        <v>0.31806852562279769</v>
       </c>
       <c r="O12">
-        <v>0.95427968614821645</v>
+        <v>0.95653643622598727</v>
       </c>
       <c r="Q12" t="s">
         <v>166</v>
@@ -9562,40 +9562,40 @@
         <v>165</v>
       </c>
       <c r="S12">
-        <v>7.2620212432003917E-3</v>
+        <v>7.2629862853960409E-3</v>
       </c>
       <c r="T12">
-        <v>3.6165530492050435E-3</v>
+        <v>3.6125214914444976E-3</v>
       </c>
       <c r="U12">
-        <v>2.1976913971970321E-3</v>
+        <v>2.1928008079755059E-3</v>
       </c>
       <c r="V12">
-        <v>3.6241584803671724E-3</v>
+        <v>3.6381601091061426E-3</v>
       </c>
       <c r="W12">
-        <v>1.0746110988398361E-2</v>
+        <v>1.0756564456254867E-2</v>
       </c>
       <c r="X12">
-        <v>1.3365428840526952E-2</v>
+        <v>1.3366369503412643E-2</v>
       </c>
       <c r="Y12">
-        <v>1.4714416327011018E-2</v>
+        <v>1.4729176799122869E-2</v>
       </c>
       <c r="Z12">
-        <v>1.0652156008859113E-2</v>
+        <v>1.0635937213483599E-2</v>
       </c>
       <c r="AA12">
-        <v>2.8608747415901453E-2</v>
+        <v>2.8598442605334458E-2</v>
       </c>
       <c r="AB12">
-        <v>2.6796307363722012E-3</v>
+        <v>2.69937043862311E-3</v>
       </c>
       <c r="AC12">
-        <v>5.3176251967690753E-3</v>
+        <v>5.31487770795334E-3</v>
       </c>
       <c r="AD12">
-        <v>7.7411077384112814E-3</v>
+        <v>7.7437083716019187E-3</v>
       </c>
       <c r="AF12" t="s">
         <v>166</v>
@@ -9604,40 +9604,40 @@
         <v>168</v>
       </c>
       <c r="AH12">
-        <v>1.2574776411188569E-2</v>
+        <v>1.2579301293804423E-2</v>
       </c>
       <c r="AI12">
-        <v>1.3700757979640661E-2</v>
+        <v>1.3709629490760326E-2</v>
       </c>
       <c r="AJ12">
-        <v>1.9565751748914294E-2</v>
+        <v>1.9587147339175479E-2</v>
       </c>
       <c r="AK12">
-        <v>2.1465458102578938E-2</v>
+        <v>2.1496879203823198E-2</v>
       </c>
       <c r="AL12">
-        <v>9.7534131622723976E-3</v>
+        <v>9.7700962873435698E-3</v>
       </c>
       <c r="AM12">
-        <v>2.9718674939691062E-2</v>
+        <v>2.9692222591396304E-2</v>
       </c>
       <c r="AN12">
-        <v>4.4590727716454046E-2</v>
+        <v>4.4595698882237966E-2</v>
       </c>
       <c r="AO12">
-        <v>1.3176256814683299E-2</v>
+        <v>1.3188231206923093E-2</v>
       </c>
       <c r="AP12">
-        <v>3.8198713177930478E-2</v>
+        <v>3.814313203752856E-2</v>
       </c>
       <c r="AQ12">
-        <v>1.9117693487945578E-2</v>
+        <v>1.9128878096509982E-2</v>
       </c>
       <c r="AR12">
-        <v>2.4978303459330647E-2</v>
+        <v>2.5003472282736514E-2</v>
       </c>
       <c r="AS12">
-        <v>6.7113150029632015E-3</v>
+        <v>6.7077210336660515E-3</v>
       </c>
       <c r="AU12" t="s">
         <v>115</v>
@@ -9646,37 +9646,37 @@
         <v>0</v>
       </c>
       <c r="AW12">
-        <v>0.12877361455454453</v>
+        <v>0.1288838895644597</v>
       </c>
       <c r="AX12">
         <v>0</v>
       </c>
       <c r="AY12">
-        <v>3.7377070968256328E-2</v>
+        <v>3.7575281932171009E-2</v>
       </c>
       <c r="AZ12">
-        <v>0.36759171877887353</v>
+        <v>0.36903814176397837</v>
       </c>
       <c r="BA12">
-        <v>3.3319248329197283E-2</v>
+        <v>3.2658670232738024E-2</v>
       </c>
       <c r="BB12">
-        <v>6.6915906573094958E-2</v>
+        <v>6.7030601794679137E-2</v>
       </c>
       <c r="BC12">
-        <v>0.451018151012684</v>
+        <v>0.4505651435016132</v>
       </c>
       <c r="BD12">
-        <v>7.1452230399315309E-2</v>
+        <v>7.031919489217324E-2</v>
       </c>
       <c r="BE12">
-        <v>9.5706096468801873E-3</v>
+        <v>9.8498919902715362E-3</v>
       </c>
       <c r="BF12">
-        <v>0.2276434264642502</v>
+        <v>0.22877901061310513</v>
       </c>
       <c r="BG12">
-        <v>4.1766955618618307E-3</v>
+        <v>4.0451660601577358E-3</v>
       </c>
       <c r="BI12" t="s">
         <v>115</v>
@@ -9688,7 +9688,7 @@
         <v>172</v>
       </c>
       <c r="BL12">
-        <v>0.43397183718912347</v>
+        <v>0.43296462352234361</v>
       </c>
     </row>
     <row r="13" spans="2:64" x14ac:dyDescent="0.45">
@@ -9702,37 +9702,37 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0.37905104827601954</v>
+        <v>0.38290247170238317</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0.80490139359527246</v>
+        <v>0.81341215135589506</v>
       </c>
       <c r="H13">
-        <v>0.2297023432648731</v>
+        <v>0.24423667139338875</v>
       </c>
       <c r="I13">
-        <v>0.75799347891321278</v>
+        <v>0.78470548588109035</v>
       </c>
       <c r="J13">
-        <v>0.70619993702772865</v>
+        <v>0.71562827124881934</v>
       </c>
       <c r="K13">
-        <v>0.14926477908868963</v>
+        <v>0.1568858353248227</v>
       </c>
       <c r="L13">
-        <v>0.61320053418888476</v>
+        <v>0.62016352168734479</v>
       </c>
       <c r="M13">
-        <v>0.92528988922630107</v>
+        <v>0.92698251921593955</v>
       </c>
       <c r="N13">
-        <v>0.32036377228093688</v>
+        <v>0.3223221787338415</v>
       </c>
       <c r="O13">
-        <v>0.95535496952907017</v>
+        <v>0.9634496634639611</v>
       </c>
       <c r="Q13" t="s">
         <v>167</v>
@@ -9825,37 +9825,37 @@
         <v>0</v>
       </c>
       <c r="AW13">
-        <v>0.10964322949823535</v>
+        <v>0.1108291840704221</v>
       </c>
       <c r="AX13">
         <v>0</v>
       </c>
       <c r="AY13">
-        <v>3.8981604701003786E-2</v>
+        <v>4.0822767159765891E-2</v>
       </c>
       <c r="AZ13">
-        <v>0.36699798628667396</v>
+        <v>0.36007793702907076</v>
       </c>
       <c r="BA13">
-        <v>3.5326646609944924E-2</v>
+        <v>3.288974829024148E-2</v>
       </c>
       <c r="BB13">
-        <v>6.760404307688081E-2</v>
+        <v>6.848712691554136E-2</v>
       </c>
       <c r="BC13">
-        <v>0.44713553436282172</v>
+        <v>0.4462921665489995</v>
       </c>
       <c r="BD13">
-        <v>7.4364093626793082E-2</v>
+        <v>7.2629175815668925E-2</v>
       </c>
       <c r="BE13">
-        <v>9.5013682767031375E-3</v>
+        <v>1.0080458392701464E-2</v>
       </c>
       <c r="BF13">
-        <v>0.21531518750173406</v>
+        <v>0.22512763539997169</v>
       </c>
       <c r="BG13">
-        <v>3.9822225854930521E-3</v>
+        <v>3.5935092132447399E-3</v>
       </c>
       <c r="BI13" t="s">
         <v>116</v>
@@ -9867,7 +9867,7 @@
         <v>172</v>
       </c>
       <c r="BL13">
-        <v>0.43905120074913467</v>
+        <v>0.43756700088855605</v>
       </c>
     </row>
     <row r="14" spans="2:64" x14ac:dyDescent="0.45">
@@ -9881,37 +9881,37 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0.4183669765275102</v>
+        <v>0.4222438294562621</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>0.8092884213725311</v>
+        <v>0.81185980047185302</v>
       </c>
       <c r="H14">
-        <v>0.21279227157529471</v>
+        <v>0.21952741987982863</v>
       </c>
       <c r="I14">
-        <v>0.73886940602624007</v>
+        <v>0.74269579074414571</v>
       </c>
       <c r="J14">
-        <v>0.71486324081778907</v>
+        <v>0.71666275508567867</v>
       </c>
       <c r="K14">
-        <v>0.15076693424286414</v>
+        <v>0.1538463532744179</v>
       </c>
       <c r="L14">
-        <v>0.60541757425102016</v>
+        <v>0.60661661201174877</v>
       </c>
       <c r="M14">
-        <v>0.9430398909202764</v>
+        <v>0.9437128785504505</v>
       </c>
       <c r="N14">
-        <v>0.36825577229343309</v>
+        <v>0.37244844623818185</v>
       </c>
       <c r="O14">
-        <v>0.94742021947057919</v>
+        <v>0.9488175771581383</v>
       </c>
       <c r="AU14" t="s">
         <v>117</v>
@@ -9920,37 +9920,37 @@
         <v>0</v>
       </c>
       <c r="AW14">
-        <v>9.2351973060126824E-2</v>
+        <v>9.1971471620870174E-2</v>
       </c>
       <c r="AX14">
         <v>0</v>
       </c>
       <c r="AY14">
-        <v>3.8192433288555976E-2</v>
+        <v>3.7912088921391036E-2</v>
       </c>
       <c r="AZ14">
-        <v>0.39428330670960215</v>
+        <v>0.39028742845942366</v>
       </c>
       <c r="BA14">
-        <v>3.7756326028252532E-2</v>
+        <v>3.7274795268792571E-2</v>
       </c>
       <c r="BB14">
-        <v>6.6055351961792755E-2</v>
+        <v>6.5740649373347518E-2</v>
       </c>
       <c r="BC14">
-        <v>0.45076804268223886</v>
+        <v>0.44976420730135702</v>
       </c>
       <c r="BD14">
-        <v>8.24103607795863E-2</v>
+        <v>8.1907951387342443E-2</v>
       </c>
       <c r="BE14">
-        <v>7.3851041059812749E-3</v>
+        <v>7.3074057299556778E-3</v>
       </c>
       <c r="BF14">
-        <v>0.19524501721144225</v>
+        <v>0.19411020059518078</v>
       </c>
       <c r="BG14">
-        <v>5.4327648770299457E-3</v>
+        <v>5.4474614907025643E-3</v>
       </c>
       <c r="BI14" t="s">
         <v>117</v>
@@ -9962,7 +9962,7 @@
         <v>172</v>
       </c>
       <c r="BL14">
-        <v>0.43806050506124011</v>
+        <v>0.43796829473155113</v>
       </c>
     </row>
     <row r="15" spans="2:64" x14ac:dyDescent="0.45">
@@ -9976,37 +9976,37 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0.4196698018667035</v>
+        <v>0.43577733279195696</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>0.79946800363600778</v>
+        <v>0.80672382873222781</v>
       </c>
       <c r="H15">
-        <v>0.20847708159176515</v>
+        <v>0.21565599468012689</v>
       </c>
       <c r="I15">
-        <v>0.75434989816466946</v>
+        <v>0.76194797963844096</v>
       </c>
       <c r="J15">
-        <v>0.69500424770763003</v>
+        <v>0.69686070707160497</v>
       </c>
       <c r="K15">
-        <v>0.14398481829803289</v>
+        <v>0.1497470196523592</v>
       </c>
       <c r="L15">
-        <v>0.60008760059659427</v>
+        <v>0.60370808500785622</v>
       </c>
       <c r="M15">
-        <v>0.92706275608489574</v>
+        <v>0.92880617414586009</v>
       </c>
       <c r="N15">
-        <v>0.36117513870497386</v>
+        <v>0.37455002640511331</v>
       </c>
       <c r="O15">
-        <v>0.95287968797135558</v>
+        <v>0.95696724741418537</v>
       </c>
       <c r="AU15" t="s">
         <v>118</v>
@@ -10015,37 +10015,37 @@
         <v>0</v>
       </c>
       <c r="AW15">
-        <v>9.0580417767396615E-2</v>
+        <v>8.8580712995026803E-2</v>
       </c>
       <c r="AX15">
         <v>0</v>
       </c>
       <c r="AY15">
-        <v>4.0530270150733384E-2</v>
+        <v>4.0866848283219334E-2</v>
       </c>
       <c r="AZ15">
-        <v>0.40274546068888051</v>
+        <v>0.40545069880771561</v>
       </c>
       <c r="BA15">
-        <v>3.7037975095003152E-2</v>
+        <v>3.6428622186157132E-2</v>
       </c>
       <c r="BB15">
-        <v>7.1890140776911901E-2</v>
+        <v>7.2942338199680906E-2</v>
       </c>
       <c r="BC15">
-        <v>0.44981826960846599</v>
+        <v>0.44965489224720795</v>
       </c>
       <c r="BD15">
-        <v>7.8929555911363525E-2</v>
+        <v>7.9093296667167162E-2</v>
       </c>
       <c r="BE15">
-        <v>1.0219878223081324E-2</v>
+        <v>1.0477976085814794E-2</v>
       </c>
       <c r="BF15">
-        <v>0.20165491502530525</v>
+        <v>0.20161170743465173</v>
       </c>
       <c r="BG15">
-        <v>4.4825262864542914E-3</v>
+        <v>4.530180389992664E-3</v>
       </c>
       <c r="BI15" t="s">
         <v>118</v>
@@ -10057,7 +10057,7 @@
         <v>172</v>
       </c>
       <c r="BL15">
-        <v>0.43455383759311039</v>
+        <v>0.43172842712377812</v>
       </c>
     </row>
     <row r="16" spans="2:64" x14ac:dyDescent="0.45">
@@ -10071,37 +10071,37 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0.42194652112654851</v>
+        <v>0.42812307789683124</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>0.77150180776867705</v>
+        <v>0.77416046422088136</v>
       </c>
       <c r="H16">
-        <v>0.18950023765579299</v>
+        <v>0.18973022685836502</v>
       </c>
       <c r="I16">
-        <v>0.79269015696651801</v>
+        <v>0.79518121173594625</v>
       </c>
       <c r="J16">
-        <v>0.65208907631274593</v>
+        <v>0.65228153627862007</v>
       </c>
       <c r="K16">
-        <v>0.14521904607098998</v>
+        <v>0.14799255606898976</v>
       </c>
       <c r="L16">
-        <v>0.62246721871503774</v>
+        <v>0.62491865249164957</v>
       </c>
       <c r="M16">
-        <v>0.91304008613096388</v>
+        <v>0.91539037187306416</v>
       </c>
       <c r="N16">
-        <v>0.37067066120956815</v>
+        <v>0.37868322355410911</v>
       </c>
       <c r="O16">
-        <v>0.96889842916373126</v>
+        <v>0.96889607652488119</v>
       </c>
       <c r="AU16" t="s">
         <v>119</v>
@@ -10110,37 +10110,37 @@
         <v>0</v>
       </c>
       <c r="AW16">
-        <v>8.8902925630838903E-2</v>
+        <v>8.745070630653691E-2</v>
       </c>
       <c r="AX16">
         <v>0</v>
       </c>
       <c r="AY16">
-        <v>5.4274164394090794E-2</v>
+        <v>5.5073564917256672E-2</v>
       </c>
       <c r="AZ16">
-        <v>0.43265377098317265</v>
+        <v>0.43591264062680762</v>
       </c>
       <c r="BA16">
-        <v>3.3196479985841222E-2</v>
+        <v>3.3696569958736468E-2</v>
       </c>
       <c r="BB16">
-        <v>8.4696527492199844E-2</v>
+        <v>8.3711889649104851E-2</v>
       </c>
       <c r="BC16">
-        <v>0.44273399392188501</v>
+        <v>0.44080844125338103</v>
       </c>
       <c r="BD16">
-        <v>7.0217189722438428E-2</v>
+        <v>7.0667607827408316E-2</v>
       </c>
       <c r="BE16">
-        <v>1.1620449464566852E-2</v>
+        <v>1.1437875433018781E-2</v>
       </c>
       <c r="BF16">
-        <v>0.18878217332945274</v>
+        <v>0.18651559264804995</v>
       </c>
       <c r="BG16">
-        <v>3.5933697570616719E-3</v>
+        <v>3.5276350814472568E-3</v>
       </c>
       <c r="BI16" t="s">
         <v>119</v>
@@ -10152,7 +10152,7 @@
         <v>172</v>
       </c>
       <c r="BL16">
-        <v>0.42543225574923688</v>
+        <v>0.42791988365721229</v>
       </c>
     </row>
     <row r="17" spans="2:64" x14ac:dyDescent="0.45">
@@ -10166,37 +10166,37 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0.44201964249763748</v>
+        <v>0.44100780756625074</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>0.78725858672527149</v>
+        <v>0.78664375763885797</v>
       </c>
       <c r="H17">
-        <v>0.17267358736907945</v>
+        <v>0.17022617269197454</v>
       </c>
       <c r="I17">
-        <v>0.74911738653999171</v>
+        <v>0.74795329064420646</v>
       </c>
       <c r="J17">
-        <v>0.68941460088364481</v>
+        <v>0.68829067905034913</v>
       </c>
       <c r="K17">
-        <v>0.13779736961755898</v>
+        <v>0.13704182877637042</v>
       </c>
       <c r="L17">
-        <v>0.59529011023941691</v>
+        <v>0.59527556355523659</v>
       </c>
       <c r="M17">
-        <v>0.9299062147511753</v>
+        <v>0.92969825430563047</v>
       </c>
       <c r="N17">
-        <v>0.36460708151904497</v>
+        <v>0.36297039939000053</v>
       </c>
       <c r="O17">
-        <v>0.94924383594082173</v>
+        <v>0.94871659575146738</v>
       </c>
       <c r="AU17" t="s">
         <v>120</v>
@@ -10205,37 +10205,37 @@
         <v>0</v>
       </c>
       <c r="AW17">
-        <v>8.9752654548138938E-2</v>
+        <v>8.9379136160535846E-2</v>
       </c>
       <c r="AX17">
         <v>0</v>
       </c>
       <c r="AY17">
-        <v>4.4965686228681315E-2</v>
+        <v>4.5337658472937595E-2</v>
       </c>
       <c r="AZ17">
-        <v>0.44576022095161283</v>
+        <v>0.44690044108527538</v>
       </c>
       <c r="BA17">
-        <v>4.6587187847113735E-2</v>
+        <v>4.6683734010141288E-2</v>
       </c>
       <c r="BB17">
-        <v>7.3064327194394083E-2</v>
+        <v>7.3166998804467753E-2</v>
       </c>
       <c r="BC17">
-        <v>0.45256538377742755</v>
+        <v>0.45199148940775868</v>
       </c>
       <c r="BD17">
-        <v>9.1248136591499426E-2</v>
+        <v>9.1241375283267645E-2</v>
       </c>
       <c r="BE17">
-        <v>1.0704871515513172E-2</v>
+        <v>1.0804654674337113E-2</v>
       </c>
       <c r="BF17">
-        <v>0.20409137859210211</v>
+        <v>0.20408653975346902</v>
       </c>
       <c r="BG17">
-        <v>5.543600066950042E-3</v>
+        <v>5.5003920464633581E-3</v>
       </c>
       <c r="BI17" t="s">
         <v>120</v>
@@ -10247,7 +10247,7 @@
         <v>172</v>
       </c>
       <c r="BL17">
-        <v>0.43745777073717351</v>
+        <v>0.43633791241229603</v>
       </c>
     </row>
     <row r="18" spans="2:64" x14ac:dyDescent="0.45">
@@ -10261,37 +10261,37 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0.43064183120730581</v>
+        <v>0.43124774696147583</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>0.78422478371802884</v>
+        <v>0.78519809220877035</v>
       </c>
       <c r="H18">
-        <v>0.17677685065790336</v>
+        <v>0.17309691600829283</v>
       </c>
       <c r="I18">
-        <v>0.77464072741299461</v>
+        <v>0.77833800488438265</v>
       </c>
       <c r="J18">
-        <v>0.67703551906557169</v>
+        <v>0.67574145200913083</v>
       </c>
       <c r="K18">
-        <v>0.14627632010113745</v>
+        <v>0.14807356846101793</v>
       </c>
       <c r="L18">
-        <v>0.61421949257323494</v>
+        <v>0.61782629023966951</v>
       </c>
       <c r="M18">
-        <v>0.92086648483392408</v>
+        <v>0.92054466423895753</v>
       </c>
       <c r="N18">
-        <v>0.36430228002206705</v>
+        <v>0.36463045023189206</v>
       </c>
       <c r="O18">
-        <v>0.96496727503783664</v>
+        <v>0.96607834552902527</v>
       </c>
       <c r="AU18" t="s">
         <v>121</v>
@@ -10300,37 +10300,37 @@
         <v>0</v>
       </c>
       <c r="AW18">
-        <v>9.4464611440271601E-2</v>
+        <v>9.4919259758213761E-2</v>
       </c>
       <c r="AX18">
         <v>0</v>
       </c>
       <c r="AY18">
-        <v>4.8503371828504907E-2</v>
+        <v>4.915653773937384E-2</v>
       </c>
       <c r="AZ18">
-        <v>0.45029981971493099</v>
+        <v>0.45493049948984493</v>
       </c>
       <c r="BA18">
-        <v>3.7522998948417735E-2</v>
+        <v>3.7759106959903484E-2</v>
       </c>
       <c r="BB18">
-        <v>7.8927339834158436E-2</v>
+        <v>7.9312637455285578E-2</v>
       </c>
       <c r="BC18">
-        <v>0.44077876971044966</v>
+        <v>0.44399189899217018</v>
       </c>
       <c r="BD18">
-        <v>7.4170584465534109E-2</v>
+        <v>7.4532188974726424E-2</v>
       </c>
       <c r="BE18">
-        <v>1.1974592898889793E-2</v>
+        <v>1.1832172349366548E-2</v>
       </c>
       <c r="BF18">
-        <v>0.20199874895360689</v>
+        <v>0.20409406596007842</v>
       </c>
       <c r="BG18">
-        <v>4.1984744745072085E-3</v>
+        <v>4.2296133755372811E-3</v>
       </c>
       <c r="BI18" t="s">
         <v>121</v>
@@ -10342,7 +10342,7 @@
         <v>172</v>
       </c>
       <c r="BL18">
-        <v>0.4421280453817929</v>
+        <v>0.44707338003928465</v>
       </c>
     </row>
     <row r="19" spans="2:64" x14ac:dyDescent="0.45">
@@ -10353,79 +10353,79 @@
         <v>31</v>
       </c>
       <c r="D19">
-        <v>0.99583333333333346</v>
+        <v>0.99583333333333313</v>
       </c>
       <c r="E19">
-        <v>0.40420485892583369</v>
+        <v>0.40499352818832818</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>0.76494218434532335</v>
+        <v>0.76501756251108832</v>
       </c>
       <c r="H19">
-        <v>0.23110469758317895</v>
+        <v>0.23107152185393973</v>
       </c>
       <c r="I19">
-        <v>0.82142493600359345</v>
+        <v>0.82130357878466675</v>
       </c>
       <c r="J19">
-        <v>0.63721771277110473</v>
+        <v>0.63813266969992988</v>
       </c>
       <c r="K19">
-        <v>0.1453509373542447</v>
+        <v>0.14450048454305067</v>
       </c>
       <c r="L19">
-        <v>0.65484626672426516</v>
+        <v>0.65419831092591574</v>
       </c>
       <c r="M19">
-        <v>0.89698575781263379</v>
+        <v>0.89689513120871167</v>
       </c>
       <c r="N19">
-        <v>0.35881066366452202</v>
+        <v>0.35838153910654935</v>
       </c>
       <c r="O19">
-        <v>0.97487081615833926</v>
+        <v>0.97488050186871533</v>
       </c>
       <c r="AU19" t="s">
         <v>122</v>
       </c>
       <c r="AV19">
-        <v>1.2771453234299937E-4</v>
+        <v>1.1714474019124044E-4</v>
       </c>
       <c r="AW19">
-        <v>0.10717630164379228</v>
+        <v>0.10696447231579219</v>
       </c>
       <c r="AX19">
         <v>0</v>
       </c>
       <c r="AY19">
-        <v>6.1978124829790503E-2</v>
+        <v>6.1776762913608015E-2</v>
       </c>
       <c r="AZ19">
-        <v>0.40170983425822038</v>
+        <v>0.40097740529984266</v>
       </c>
       <c r="BA19">
-        <v>2.6012880599948971E-2</v>
+        <v>2.6063476213789211E-2</v>
       </c>
       <c r="BB19">
-        <v>9.6973514464265748E-2</v>
+        <v>9.6824414556072394E-2</v>
       </c>
       <c r="BC19">
-        <v>0.44084394358381074</v>
+        <v>0.44155798823636472</v>
       </c>
       <c r="BD19">
-        <v>5.6712228792934326E-2</v>
+        <v>5.6874048323404078E-2</v>
       </c>
       <c r="BE19">
-        <v>1.4551011321477911E-2</v>
+        <v>1.447352484999964E-2</v>
       </c>
       <c r="BF19">
-        <v>0.19197533298506225</v>
+        <v>0.19204437913357805</v>
       </c>
       <c r="BG19">
-        <v>2.6357282713479228E-3</v>
+        <v>2.6405738783884165E-3</v>
       </c>
       <c r="BI19" t="s">
         <v>122</v>
@@ -10437,7 +10437,7 @@
         <v>172</v>
       </c>
       <c r="BL19">
-        <v>0.41350968790892051</v>
+        <v>0.41446094143084472</v>
       </c>
     </row>
     <row r="20" spans="2:64" x14ac:dyDescent="0.45">
@@ -10451,76 +10451,76 @@
         <v>0.99861111111111123</v>
       </c>
       <c r="E20">
-        <v>0.44041827567980024</v>
+        <v>0.44061062011635516</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>0.75517317789983596</v>
+        <v>0.75523660574461493</v>
       </c>
       <c r="H20">
-        <v>0.19978230450221604</v>
+        <v>0.19987551546594151</v>
       </c>
       <c r="I20">
-        <v>0.80963131098358732</v>
+        <v>0.80960854416323325</v>
       </c>
       <c r="J20">
-        <v>0.64798245685865175</v>
+        <v>0.64816471015904731</v>
       </c>
       <c r="K20">
-        <v>0.14612287761527795</v>
+        <v>0.14617948228482194</v>
       </c>
       <c r="L20">
-        <v>0.62866951147628769</v>
+        <v>0.62882676301938278</v>
       </c>
       <c r="M20">
-        <v>0.91425841568059563</v>
+        <v>0.9142954538177166</v>
       </c>
       <c r="N20">
-        <v>0.41531356116031248</v>
+        <v>0.41538142067417111</v>
       </c>
       <c r="O20">
-        <v>0.97195510156195475</v>
+        <v>0.97194153391101579</v>
       </c>
       <c r="AU20" t="s">
         <v>123</v>
       </c>
       <c r="AV20">
-        <v>1.8288398343306126E-9</v>
+        <v>1.6525181282250773E-9</v>
       </c>
       <c r="AW20">
-        <v>8.9815654189932023E-2</v>
+        <v>8.9677401243422314E-2</v>
       </c>
       <c r="AX20">
         <v>0</v>
       </c>
       <c r="AY20">
-        <v>6.2655881780650138E-2</v>
+        <v>6.2635934049892913E-2</v>
       </c>
       <c r="AZ20">
-        <v>0.42895130078897575</v>
+        <v>0.42884664695095542</v>
       </c>
       <c r="BA20">
-        <v>3.0006423244812602E-2</v>
+        <v>3.0052796209229227E-2</v>
       </c>
       <c r="BB20">
-        <v>8.7072175426321272E-2</v>
+        <v>8.7011675871078845E-2</v>
       </c>
       <c r="BC20">
-        <v>0.43411770271765282</v>
+        <v>0.43413541241739734</v>
       </c>
       <c r="BD20">
-        <v>6.5869999958135125E-2</v>
+        <v>6.5929816579743367E-2</v>
       </c>
       <c r="BE20">
-        <v>1.2341182729083307E-2</v>
+        <v>1.2327575233771279E-2</v>
       </c>
       <c r="BF20">
-        <v>0.16880029426765009</v>
+        <v>0.16876239233178664</v>
       </c>
       <c r="BG20">
-        <v>3.0577668998395765E-3</v>
+        <v>3.0634263553424167E-3</v>
       </c>
       <c r="BI20" t="s">
         <v>123</v>
@@ -10532,7 +10532,7 @@
         <v>172</v>
       </c>
       <c r="BL20">
-        <v>0.42391711599849091</v>
+        <v>0.42378123991787348</v>
       </c>
     </row>
     <row r="21" spans="2:64" x14ac:dyDescent="0.45">
@@ -10543,79 +10543,79 @@
         <v>31</v>
       </c>
       <c r="D21">
-        <v>0.9972222222222219</v>
+        <v>0.99722222222222234</v>
       </c>
       <c r="E21">
-        <v>0.42256374150109444</v>
+        <v>0.42260720900920046</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>0.7539022488924817</v>
+        <v>0.75328432163460191</v>
       </c>
       <c r="H21">
-        <v>0.21346136179552924</v>
+        <v>0.21287939344872281</v>
       </c>
       <c r="I21">
-        <v>0.81162254706340409</v>
+        <v>0.81144772277808197</v>
       </c>
       <c r="J21">
-        <v>0.63440402254023243</v>
+        <v>0.63409093208876854</v>
       </c>
       <c r="K21">
-        <v>0.14100727543128425</v>
+        <v>0.14119789828399329</v>
       </c>
       <c r="L21">
-        <v>0.63580308104636063</v>
+        <v>0.63563175761077806</v>
       </c>
       <c r="M21">
-        <v>0.90331274919201843</v>
+        <v>0.9032215377821875</v>
       </c>
       <c r="N21">
-        <v>0.39257940645482847</v>
+        <v>0.39322524196480607</v>
       </c>
       <c r="O21">
-        <v>0.9734522679101385</v>
+        <v>0.97354080748558947</v>
       </c>
       <c r="AU21" t="s">
         <v>124</v>
       </c>
       <c r="AV21">
-        <v>4.4218896604554777E-5</v>
+        <v>4.6157730419427035E-5</v>
       </c>
       <c r="AW21">
-        <v>9.6670974702784282E-2</v>
+        <v>9.6504049427350566E-2</v>
       </c>
       <c r="AX21">
         <v>0</v>
       </c>
       <c r="AY21">
-        <v>6.146522409872366E-2</v>
+        <v>6.1601319153972468E-2</v>
       </c>
       <c r="AZ21">
-        <v>0.416752789738145</v>
+        <v>0.41710641836986984</v>
       </c>
       <c r="BA21">
-        <v>2.6415440503178265E-2</v>
+        <v>2.639418619654527E-2</v>
       </c>
       <c r="BB21">
-        <v>9.4258518789776341E-2</v>
+        <v>9.4168792320211872E-2</v>
       </c>
       <c r="BC21">
-        <v>0.44001737796341162</v>
+        <v>0.4395065197857172</v>
       </c>
       <c r="BD21">
-        <v>6.0400395419684616E-2</v>
+        <v>6.0410735632238366E-2</v>
       </c>
       <c r="BE21">
-        <v>1.3378433353268722E-2</v>
+        <v>1.3392095757056551E-2</v>
       </c>
       <c r="BF21">
-        <v>0.17948708156393747</v>
+        <v>0.17902177113407547</v>
       </c>
       <c r="BG21">
-        <v>2.8289835181135848E-3</v>
+        <v>2.8317740075181432E-3</v>
       </c>
       <c r="BI21" t="s">
         <v>124</v>
@@ -10627,7 +10627,7 @@
         <v>172</v>
       </c>
       <c r="BL21">
-        <v>0.40557670957801439</v>
+        <v>0.40587417769260387</v>
       </c>
     </row>
     <row r="22" spans="2:64" x14ac:dyDescent="0.45">
@@ -10638,79 +10638,79 @@
         <v>31</v>
       </c>
       <c r="D22">
-        <v>0.99583130218692373</v>
+        <v>0.99583128995168069</v>
       </c>
       <c r="E22">
-        <v>0.37961263360123404</v>
+        <v>0.38002172071903084</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>0.77542111109967782</v>
+        <v>0.7753207946711389</v>
       </c>
       <c r="H22">
-        <v>0.24457605768483617</v>
+        <v>0.24424040987028164</v>
       </c>
       <c r="I22">
-        <v>0.81774116302663502</v>
+        <v>0.81787362038951772</v>
       </c>
       <c r="J22">
-        <v>0.68740818127103231</v>
+        <v>0.68707406039412222</v>
       </c>
       <c r="K22">
-        <v>0.160684322634219</v>
+        <v>0.16071195214857378</v>
       </c>
       <c r="L22">
-        <v>0.70115467900486672</v>
+        <v>0.70142915188288246</v>
       </c>
       <c r="M22">
-        <v>0.89665644503402231</v>
+        <v>0.89675543616831521</v>
       </c>
       <c r="N22">
-        <v>0.30991034503539105</v>
+        <v>0.3092679182175056</v>
       </c>
       <c r="O22">
-        <v>0.96985394697653193</v>
+        <v>0.96992078780821422</v>
       </c>
       <c r="AU22" t="s">
         <v>125</v>
       </c>
       <c r="AV22">
-        <v>4.754901616073163E-4</v>
+        <v>4.7910120188393433E-4</v>
       </c>
       <c r="AW22">
-        <v>0.14381210715605044</v>
+        <v>0.1444823294812802</v>
       </c>
       <c r="AX22">
         <v>0</v>
       </c>
       <c r="AY22">
-        <v>5.3789952864643914E-2</v>
+        <v>5.4010478749672068E-2</v>
       </c>
       <c r="AZ22">
-        <v>0.3833684936577294</v>
+        <v>0.38385796077085943</v>
       </c>
       <c r="BA22">
-        <v>2.2566932779447105E-2</v>
+        <v>2.2511852208473709E-2</v>
       </c>
       <c r="BB22">
-        <v>8.2910631983535224E-2</v>
+        <v>8.2982188247892677E-2</v>
       </c>
       <c r="BC22">
-        <v>0.44019223644336469</v>
+        <v>0.4401819718864699</v>
       </c>
       <c r="BD22">
-        <v>4.9684639474997488E-2</v>
+        <v>4.9609101289728882E-2</v>
       </c>
       <c r="BE22">
-        <v>1.7536189619357441E-2</v>
+        <v>1.7600683831549419E-2</v>
       </c>
       <c r="BF22">
-        <v>0.23737155267480717</v>
+        <v>0.23774867461085786</v>
       </c>
       <c r="BG22">
-        <v>3.3600908784896955E-3</v>
+        <v>3.3486655795991402E-3</v>
       </c>
       <c r="BI22" t="s">
         <v>125</v>
@@ -10722,7 +10722,7 @@
         <v>172</v>
       </c>
       <c r="BL22">
-        <v>0.41875919121629362</v>
+        <v>0.41893814297811888</v>
       </c>
     </row>
     <row r="23" spans="2:64" x14ac:dyDescent="0.45">
@@ -10733,79 +10733,79 @@
         <v>31</v>
       </c>
       <c r="D23">
-        <v>0.99428649084783793</v>
+        <v>0.99427653766545587</v>
       </c>
       <c r="E23">
-        <v>0.39444619810756915</v>
+        <v>0.39446374716391103</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>0.76219016869336476</v>
+        <v>0.76204903976570582</v>
       </c>
       <c r="H23">
-        <v>0.23242489647866499</v>
+        <v>0.23245997671078439</v>
       </c>
       <c r="I23">
-        <v>0.82364961830128947</v>
+        <v>0.82368257999825656</v>
       </c>
       <c r="J23">
-        <v>0.65992777134515979</v>
+        <v>0.66036771693135021</v>
       </c>
       <c r="K23">
-        <v>0.14527208350668985</v>
+        <v>0.14597994079456836</v>
       </c>
       <c r="L23">
-        <v>0.69484337366854643</v>
+        <v>0.69577850771058392</v>
       </c>
       <c r="M23">
-        <v>0.88787104847012788</v>
+        <v>0.88787107072137816</v>
       </c>
       <c r="N23">
-        <v>0.31763214422334579</v>
+        <v>0.31641125850313834</v>
       </c>
       <c r="O23">
-        <v>0.97445425461278112</v>
+        <v>0.97455687820763404</v>
       </c>
       <c r="AU23" t="s">
         <v>126</v>
       </c>
       <c r="AV23">
-        <v>4.5087953053218102E-4</v>
+        <v>4.6302791287833648E-4</v>
       </c>
       <c r="AW23">
-        <v>0.12557962138298162</v>
+        <v>0.12631480053075486</v>
       </c>
       <c r="AX23">
         <v>0</v>
       </c>
       <c r="AY23">
-        <v>6.0454318582128637E-2</v>
+        <v>6.0460647207285306E-2</v>
       </c>
       <c r="AZ23">
-        <v>0.39426611245546633</v>
+        <v>0.39401985362241665</v>
       </c>
       <c r="BA23">
-        <v>2.3317672241425825E-2</v>
+        <v>2.3275095350694972E-2</v>
       </c>
       <c r="BB23">
-        <v>9.0387282592204271E-2</v>
+        <v>9.0209195342033768E-2</v>
       </c>
       <c r="BC23">
-        <v>0.44570623119475583</v>
+        <v>0.44550448086006822</v>
       </c>
       <c r="BD23">
-        <v>4.9762272524204967E-2</v>
+        <v>4.9674063440102709E-2</v>
       </c>
       <c r="BE23">
-        <v>1.7616761002833076E-2</v>
+        <v>1.768212214765192E-2</v>
       </c>
       <c r="BF23">
-        <v>0.21960622202789551</v>
+        <v>0.22024471716749469</v>
       </c>
       <c r="BG23">
-        <v>2.9306650493829941E-3</v>
+        <v>2.9360641166458366E-3</v>
       </c>
       <c r="BI23" t="s">
         <v>126</v>
@@ -10817,7 +10817,7 @@
         <v>172</v>
       </c>
       <c r="BL23">
-        <v>0.41290635362151873</v>
+        <v>0.41229154487757458</v>
       </c>
     </row>
     <row r="24" spans="2:64" x14ac:dyDescent="0.45">
@@ -10831,37 +10831,37 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0.363134406560224</v>
+        <v>0.36280658365197155</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>0.79617252400939709</v>
+        <v>0.79724454148408752</v>
       </c>
       <c r="H24">
-        <v>0.22948933404367811</v>
+        <v>0.22877105032573589</v>
       </c>
       <c r="I24">
-        <v>0.80486883111552232</v>
+        <v>0.80480364925891634</v>
       </c>
       <c r="J24">
-        <v>0.69903041643794295</v>
+        <v>0.70126014388395574</v>
       </c>
       <c r="K24">
-        <v>0.16420775170492766</v>
+        <v>0.16692157741283187</v>
       </c>
       <c r="L24">
-        <v>0.6559219576098444</v>
+        <v>0.6560670265965165</v>
       </c>
       <c r="M24">
-        <v>0.90231422629180591</v>
+        <v>0.90332361575172526</v>
       </c>
       <c r="N24">
-        <v>0.30547405054878263</v>
+        <v>0.30718557767138999</v>
       </c>
       <c r="O24">
-        <v>0.96279986321406286</v>
+        <v>0.96267520903253911</v>
       </c>
       <c r="AU24" t="s">
         <v>127</v>
@@ -10870,37 +10870,37 @@
         <v>0</v>
       </c>
       <c r="AW24">
-        <v>0.14651246024797274</v>
+        <v>0.14797419012962226</v>
       </c>
       <c r="AX24">
         <v>0</v>
       </c>
       <c r="AY24">
-        <v>4.4318327248472199E-2</v>
+        <v>4.3621567508205852E-2</v>
       </c>
       <c r="AZ24">
-        <v>0.37447651858744768</v>
+        <v>0.37478436254764691</v>
       </c>
       <c r="BA24">
-        <v>2.8093184225898418E-2</v>
+        <v>2.8356184790555482E-2</v>
       </c>
       <c r="BB24">
-        <v>7.4111033411358093E-2</v>
+        <v>7.3215069812740632E-2</v>
       </c>
       <c r="BC24">
-        <v>0.43670723837555026</v>
+        <v>0.43593505005855465</v>
       </c>
       <c r="BD24">
-        <v>5.716669999784256E-2</v>
+        <v>5.763976039340056E-2</v>
       </c>
       <c r="BE24">
-        <v>1.3988636291848487E-2</v>
+        <v>1.3804379892988368E-2</v>
       </c>
       <c r="BF24">
-        <v>0.23968042125763331</v>
+        <v>0.24072777360274966</v>
       </c>
       <c r="BG24">
-        <v>4.2598823980181466E-3</v>
+        <v>4.3055789507415523E-3</v>
       </c>
       <c r="BI24" t="s">
         <v>127</v>
@@ -10912,7 +10912,7 @@
         <v>172</v>
       </c>
       <c r="BL24">
-        <v>0.40839397833532526</v>
+        <v>0.41065881893662243</v>
       </c>
     </row>
     <row r="25" spans="2:64" x14ac:dyDescent="0.45">
@@ -10926,37 +10926,37 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0.3619029088049065</v>
+        <v>0.35723063417980433</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>0.80263001299878456</v>
+        <v>0.80189607036360089</v>
       </c>
       <c r="H25">
-        <v>0.24047809460306499</v>
+        <v>0.23822643176152739</v>
       </c>
       <c r="I25">
-        <v>0.78583247144666957</v>
+        <v>0.78732141796542177</v>
       </c>
       <c r="J25">
-        <v>0.70080579449546032</v>
+        <v>0.6991311127810822</v>
       </c>
       <c r="K25">
-        <v>0.15125843039547371</v>
+        <v>0.15025271260338266</v>
       </c>
       <c r="L25">
-        <v>0.63620404497571859</v>
+        <v>0.63784733011712702</v>
       </c>
       <c r="M25">
-        <v>0.91499513787657794</v>
+        <v>0.91454104239374345</v>
       </c>
       <c r="N25">
-        <v>0.30531029791362163</v>
+        <v>0.3030214864379368</v>
       </c>
       <c r="O25">
-        <v>0.9599712168480028</v>
+        <v>0.95939279736908756</v>
       </c>
       <c r="AU25" t="s">
         <v>128</v>
@@ -10965,37 +10965,37 @@
         <v>0</v>
       </c>
       <c r="AW25">
-        <v>0.1274594114144294</v>
+        <v>0.1306056579219968</v>
       </c>
       <c r="AX25">
         <v>0</v>
       </c>
       <c r="AY25">
-        <v>4.2894709061179578E-2</v>
+        <v>4.2843695528701153E-2</v>
       </c>
       <c r="AZ25">
-        <v>0.3679880679609161</v>
+        <v>0.36824081518407475</v>
       </c>
       <c r="BA25">
-        <v>2.9392595421430617E-2</v>
+        <v>2.9158585922742647E-2</v>
       </c>
       <c r="BB25">
-        <v>7.1589537602546119E-2</v>
+        <v>7.1739492621212805E-2</v>
       </c>
       <c r="BC25">
-        <v>0.44702850251843218</v>
+        <v>0.44742824162166678</v>
       </c>
       <c r="BD25">
-        <v>6.4395349866998949E-2</v>
+        <v>6.4072389944471744E-2</v>
       </c>
       <c r="BE25">
-        <v>1.2513421745175278E-2</v>
+        <v>1.278913939840007E-2</v>
       </c>
       <c r="BF25">
-        <v>0.23455178418462189</v>
+        <v>0.23507147374141996</v>
       </c>
       <c r="BG25">
-        <v>4.2450240045787194E-3</v>
+        <v>4.3027153224494295E-3</v>
       </c>
       <c r="BI25" t="s">
         <v>128</v>
@@ -11007,7 +11007,7 @@
         <v>172</v>
       </c>
       <c r="BL25">
-        <v>0.42349266654301337</v>
+        <v>0.42646985123233772</v>
       </c>
     </row>
     <row r="26" spans="2:64" x14ac:dyDescent="0.45">
@@ -11021,37 +11021,37 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>0.3962969433739546</v>
+        <v>0.40215696322767686</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>0.80154355548049139</v>
+        <v>0.8063792133371156</v>
       </c>
       <c r="H26">
-        <v>0.23019349714873358</v>
+        <v>0.2322262245457542</v>
       </c>
       <c r="I26">
-        <v>0.78005306879691771</v>
+        <v>0.78071627397539967</v>
       </c>
       <c r="J26">
-        <v>0.6996329875370545</v>
+        <v>0.70760312371706013</v>
       </c>
       <c r="K26">
-        <v>0.14378712210438391</v>
+        <v>0.14889628537397503</v>
       </c>
       <c r="L26">
-        <v>0.61939345778768462</v>
+        <v>0.61878334335419072</v>
       </c>
       <c r="M26">
-        <v>0.92158301941122156</v>
+        <v>0.92427478533450336</v>
       </c>
       <c r="N26">
-        <v>0.32874275257632662</v>
+        <v>0.33399474568637055</v>
       </c>
       <c r="O26">
-        <v>0.96360980986239952</v>
+        <v>0.96382730611427014</v>
       </c>
       <c r="AU26" t="s">
         <v>129</v>
@@ -11060,37 +11060,37 @@
         <v>0</v>
       </c>
       <c r="AW26">
-        <v>0.10128732788153046</v>
+        <v>0.10046088143153165</v>
       </c>
       <c r="AX26">
         <v>0</v>
       </c>
       <c r="AY26">
-        <v>4.3121442476392879E-2</v>
+        <v>4.2188066070458843E-2</v>
       </c>
       <c r="AZ26">
-        <v>0.38362803910421894</v>
+        <v>0.3838047083383927</v>
       </c>
       <c r="BA26">
-        <v>3.2197337039808302E-2</v>
+        <v>3.3416363141916657E-2</v>
       </c>
       <c r="BB26">
-        <v>7.6366750275804571E-2</v>
+        <v>7.5097608862817439E-2</v>
       </c>
       <c r="BC26">
-        <v>0.44966271756799675</v>
+        <v>0.44933044101624781</v>
       </c>
       <c r="BD26">
-        <v>6.9556513532216563E-2</v>
+        <v>7.0997776125651363E-2</v>
       </c>
       <c r="BE26">
-        <v>1.2569996677718024E-2</v>
+        <v>1.2385429903369799E-2</v>
       </c>
       <c r="BF26">
-        <v>0.21712854556419342</v>
+        <v>0.21772961387533044</v>
       </c>
       <c r="BG26">
-        <v>4.0013323538499587E-3</v>
+        <v>3.9214115892895959E-3</v>
       </c>
       <c r="BI26" t="s">
         <v>129</v>
@@ -11102,7 +11102,7 @@
         <v>172</v>
       </c>
       <c r="BL26">
-        <v>0.430283254169329</v>
+        <v>0.43090706014716301</v>
       </c>
     </row>
     <row r="27" spans="2:64" x14ac:dyDescent="0.45">
@@ -11116,37 +11116,37 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0.42333150833762823</v>
+        <v>0.43347085008066244</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
       <c r="G27">
-        <v>0.79749371314510387</v>
+        <v>0.79774260480659254</v>
       </c>
       <c r="H27">
-        <v>0.21604009359109538</v>
+        <v>0.21853699380265168</v>
       </c>
       <c r="I27">
-        <v>0.7810303829760552</v>
+        <v>0.78174676842907065</v>
       </c>
       <c r="J27">
-        <v>0.69392768651764658</v>
+        <v>0.6956619664663346</v>
       </c>
       <c r="K27">
-        <v>0.14588052892078901</v>
+        <v>0.15016901185930115</v>
       </c>
       <c r="L27">
-        <v>0.61511907797208976</v>
+        <v>0.61633648127058249</v>
       </c>
       <c r="M27">
-        <v>0.91941505376416677</v>
+        <v>0.92119885628344456</v>
       </c>
       <c r="N27">
-        <v>0.34846086127695236</v>
+        <v>0.36018021001240813</v>
       </c>
       <c r="O27">
-        <v>0.96712493786441822</v>
+        <v>0.96877799529237341</v>
       </c>
       <c r="AU27" t="s">
         <v>130</v>
@@ -11155,37 +11155,37 @@
         <v>0</v>
       </c>
       <c r="AW27">
-        <v>9.4600995577649213E-2</v>
+        <v>9.2854448582609356E-2</v>
       </c>
       <c r="AX27">
         <v>0</v>
       </c>
       <c r="AY27">
-        <v>4.4027577072963203E-2</v>
+        <v>4.3576682772447729E-2</v>
       </c>
       <c r="AZ27">
-        <v>0.40307129638642175</v>
+        <v>0.40479750285376337</v>
       </c>
       <c r="BA27">
-        <v>3.3496956900105165E-2</v>
+        <v>3.4403922146333213E-2</v>
       </c>
       <c r="BB27">
-        <v>7.9950400676131558E-2</v>
+        <v>7.9343743744073589E-2</v>
       </c>
       <c r="BC27">
-        <v>0.44396058808448874</v>
+        <v>0.44069802488744769</v>
       </c>
       <c r="BD27">
-        <v>7.0922723106530139E-2</v>
+        <v>7.1131978218727132E-2</v>
       </c>
       <c r="BE27">
-        <v>1.280801044364931E-2</v>
+        <v>1.2733128868795086E-2</v>
       </c>
       <c r="BF27">
-        <v>0.20528467717931786</v>
+        <v>0.20263465501958641</v>
       </c>
       <c r="BG27">
-        <v>4.2057784525830772E-3</v>
+        <v>4.1266470208919702E-3</v>
       </c>
       <c r="BI27" t="s">
         <v>130</v>
@@ -11197,7 +11197,7 @@
         <v>172</v>
       </c>
       <c r="BL27">
-        <v>0.43539137939866707</v>
+        <v>0.43364240856259056</v>
       </c>
     </row>
     <row r="28" spans="2:64" x14ac:dyDescent="0.45">
@@ -11211,37 +11211,37 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>0.41801791653994608</v>
+        <v>0.4241863045242722</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
       <c r="G28">
-        <v>0.7861612418174081</v>
+        <v>0.78557388799580996</v>
       </c>
       <c r="H28">
-        <v>0.23584565464448154</v>
+        <v>0.23854895404663234</v>
       </c>
       <c r="I28">
-        <v>0.80391054127003692</v>
+        <v>0.80733577120915911</v>
       </c>
       <c r="J28">
-        <v>0.66972612786482144</v>
+        <v>0.66874253130390293</v>
       </c>
       <c r="K28">
-        <v>0.13716066630976043</v>
+        <v>0.13889864904080479</v>
       </c>
       <c r="L28">
-        <v>0.63147935712510184</v>
+        <v>0.63430425669109158</v>
       </c>
       <c r="M28">
-        <v>0.90529265834947648</v>
+        <v>0.90493565000789944</v>
       </c>
       <c r="N28">
-        <v>0.34158271220764108</v>
+        <v>0.34676224288871477</v>
       </c>
       <c r="O28">
-        <v>0.97084766527198296</v>
+        <v>0.97273812584223218</v>
       </c>
       <c r="AU28" t="s">
         <v>131</v>
@@ -11250,37 +11250,37 @@
         <v>0</v>
       </c>
       <c r="AW28">
-        <v>0.10009040614590581</v>
+        <v>9.9787696396035769E-2</v>
       </c>
       <c r="AX28">
         <v>0</v>
       </c>
       <c r="AY28">
-        <v>5.1475185009081173E-2</v>
+        <v>5.2304062075443129E-2</v>
       </c>
       <c r="AZ28">
-        <v>0.38587981196738302</v>
+        <v>0.38508716629084466</v>
       </c>
       <c r="BA28">
-        <v>2.7505897470990668E-2</v>
+        <v>2.7341272111939759E-2</v>
       </c>
       <c r="BB28">
-        <v>9.058651086804588E-2</v>
+        <v>9.1558571396966035E-2</v>
       </c>
       <c r="BC28">
-        <v>0.4557696175380046</v>
+        <v>0.45582334468706504</v>
       </c>
       <c r="BD28">
-        <v>6.2277729234389491E-2</v>
+        <v>6.1707889577980027E-2</v>
       </c>
       <c r="BE28">
-        <v>1.3434722240351773E-2</v>
+        <v>1.3425671416407218E-2</v>
       </c>
       <c r="BF28">
-        <v>0.20006253794444065</v>
+        <v>0.1982907303788328</v>
       </c>
       <c r="BG28">
-        <v>3.2605459482628958E-3</v>
+        <v>3.1291087661937771E-3</v>
       </c>
       <c r="BI28" t="s">
         <v>131</v>
@@ -11292,7 +11292,7 @@
         <v>172</v>
       </c>
       <c r="BL28">
-        <v>0.41669860616105853</v>
+        <v>0.41643841136848625</v>
       </c>
     </row>
     <row r="29" spans="2:64" x14ac:dyDescent="0.45">
@@ -11306,37 +11306,37 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0.38968388752004235</v>
+        <v>0.39695253978356732</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="G29">
-        <v>0.79257051203487738</v>
+        <v>0.7940530400604956</v>
       </c>
       <c r="H29">
-        <v>0.24104091819915441</v>
+        <v>0.24496044546517001</v>
       </c>
       <c r="I29">
-        <v>0.80930128852625471</v>
+        <v>0.81065734968083492</v>
       </c>
       <c r="J29">
-        <v>0.68528247085084704</v>
+        <v>0.68557383525277649</v>
       </c>
       <c r="K29">
-        <v>0.14420644608796651</v>
+        <v>0.14533231451151593</v>
       </c>
       <c r="L29">
-        <v>0.63887284838656178</v>
+        <v>0.63778285932874812</v>
       </c>
       <c r="M29">
-        <v>0.91000894159978851</v>
+        <v>0.91228996371360538</v>
       </c>
       <c r="N29">
-        <v>0.32165620283834889</v>
+        <v>0.32790210526079178</v>
       </c>
       <c r="O29">
-        <v>0.96765328154556629</v>
+        <v>0.96882896201225777</v>
       </c>
       <c r="AU29" t="s">
         <v>132</v>
@@ -11345,37 +11345,37 @@
         <v>0</v>
       </c>
       <c r="AW29">
-        <v>0.11564059075211301</v>
+        <v>0.11138089063617343</v>
       </c>
       <c r="AX29">
         <v>0</v>
       </c>
       <c r="AY29">
-        <v>4.8356312966860993E-2</v>
+        <v>4.8115139445701047E-2</v>
       </c>
       <c r="AZ29">
-        <v>0.37201853930078421</v>
+        <v>0.373313136950502</v>
       </c>
       <c r="BA29">
-        <v>2.5507784031456159E-2</v>
+        <v>2.5236939402672687E-2</v>
       </c>
       <c r="BB29">
-        <v>8.4098580831037523E-2</v>
+        <v>8.4263643777381061E-2</v>
       </c>
       <c r="BC29">
-        <v>0.44909849152938291</v>
+        <v>0.44966712934369396</v>
       </c>
       <c r="BD29">
-        <v>5.8515186598499656E-2</v>
+        <v>5.9212641321910613E-2</v>
       </c>
       <c r="BE29">
-        <v>1.3999357501462415E-2</v>
+        <v>1.3827690852366039E-2</v>
       </c>
       <c r="BF29">
-        <v>0.21279589732252044</v>
+        <v>0.21000536180075946</v>
       </c>
       <c r="BG29">
-        <v>3.6551015764382804E-3</v>
+        <v>3.6077846254088976E-3</v>
       </c>
       <c r="BI29" t="s">
         <v>132</v>
@@ -11387,7 +11387,7 @@
         <v>172</v>
       </c>
       <c r="BL29">
-        <v>0.40759494855981887</v>
+        <v>0.41046080911221178</v>
       </c>
     </row>
     <row r="30" spans="2:64" x14ac:dyDescent="0.45">
@@ -11398,79 +11398,79 @@
         <v>31</v>
       </c>
       <c r="D30">
-        <v>0.99861111111111134</v>
+        <v>0.99861111111111089</v>
       </c>
       <c r="E30">
-        <v>0.41251406263375995</v>
+        <v>0.4164094891167161</v>
       </c>
       <c r="F30">
         <v>0</v>
       </c>
       <c r="G30">
-        <v>0.77961740209406993</v>
+        <v>0.78092531384546715</v>
       </c>
       <c r="H30">
-        <v>0.24007386361454713</v>
+        <v>0.24131722118320337</v>
       </c>
       <c r="I30">
-        <v>0.81495980405605473</v>
+        <v>0.8152512811797985</v>
       </c>
       <c r="J30">
-        <v>0.66178013783464762</v>
+        <v>0.66227383895638769</v>
       </c>
       <c r="K30">
-        <v>0.14024679088277187</v>
+        <v>0.14124621804685528</v>
       </c>
       <c r="L30">
-        <v>0.64369490791059236</v>
+        <v>0.64322032018579178</v>
       </c>
       <c r="M30">
-        <v>0.90000126277419579</v>
+        <v>0.90051497361633048</v>
       </c>
       <c r="N30">
-        <v>0.32615259238446087</v>
+        <v>0.32977395750697058</v>
       </c>
       <c r="O30">
-        <v>0.97113181256797232</v>
+        <v>0.97154920056287408</v>
       </c>
       <c r="AU30" t="s">
         <v>133</v>
       </c>
       <c r="AV30">
-        <v>2.623781721411995E-6</v>
+        <v>1.6830842551847836E-6</v>
       </c>
       <c r="AW30">
-        <v>0.10572797604113505</v>
+        <v>0.10474725099284686</v>
       </c>
       <c r="AX30">
         <v>0</v>
       </c>
       <c r="AY30">
-        <v>5.5061014963235733E-2</v>
+        <v>5.5038691685513667E-2</v>
       </c>
       <c r="AZ30">
-        <v>0.38177877074308947</v>
+        <v>0.38150586105493378</v>
       </c>
       <c r="BA30">
-        <v>2.5215213354454442E-2</v>
+        <v>2.5280513225936746E-2</v>
       </c>
       <c r="BB30">
-        <v>9.1410084317510229E-2</v>
+        <v>9.1644480376187873E-2</v>
       </c>
       <c r="BC30">
-        <v>0.44945561547158047</v>
+        <v>0.44970268330510982</v>
       </c>
       <c r="BD30">
-        <v>5.8336671751891618E-2</v>
+        <v>5.8578750824414237E-2</v>
       </c>
       <c r="BE30">
-        <v>1.4527002655078858E-2</v>
+        <v>1.4444768495230255E-2</v>
       </c>
       <c r="BF30">
-        <v>0.20408171759074689</v>
+        <v>0.20305690756106926</v>
       </c>
       <c r="BG30">
-        <v>2.9281706835568209E-3</v>
+        <v>2.9067433523283009E-3</v>
       </c>
       <c r="BI30" t="s">
         <v>133</v>
@@ -11482,7 +11482,7 @@
         <v>172</v>
       </c>
       <c r="BL30">
-        <v>0.40670943215406347</v>
+        <v>0.40932530368051301</v>
       </c>
     </row>
     <row r="31" spans="2:64" x14ac:dyDescent="0.45">
@@ -11672,7 +11672,7 @@
         <v>172</v>
       </c>
       <c r="BL32">
-        <v>0.41596796755877696</v>
+        <v>0.41690589547843648</v>
       </c>
     </row>
     <row r="33" spans="2:64" x14ac:dyDescent="0.45">
@@ -12052,7 +12052,7 @@
         <v>172</v>
       </c>
       <c r="BL36">
-        <v>0.44567320393920529</v>
+        <v>0.44557068063962091</v>
       </c>
     </row>
     <row r="37" spans="2:64" x14ac:dyDescent="0.45">
@@ -12538,79 +12538,79 @@
         <v>31</v>
       </c>
       <c r="D42">
-        <v>0.32798490450093198</v>
+        <v>0.3274544830409517</v>
       </c>
       <c r="E42">
-        <v>0.37318328075181872</v>
+        <v>0.37277054029728179</v>
       </c>
       <c r="F42">
-        <v>0.32589859513310193</v>
+        <v>0.32611394760069645</v>
       </c>
       <c r="G42">
-        <v>0.35772620275855305</v>
+        <v>0.35684849103118377</v>
       </c>
       <c r="H42">
-        <v>0.4297430886219239</v>
+        <v>0.4289883131060504</v>
       </c>
       <c r="I42">
-        <v>0.33273980974359202</v>
+        <v>0.3325692445125677</v>
       </c>
       <c r="J42">
-        <v>0.34264246293893896</v>
+        <v>0.34139316938028397</v>
       </c>
       <c r="K42">
-        <v>0.46000420988796403</v>
+        <v>0.45877659784725294</v>
       </c>
       <c r="L42">
-        <v>0.35709408606164278</v>
+        <v>0.35661915592984866</v>
       </c>
       <c r="M42">
-        <v>0.37462712951174176</v>
+        <v>0.3743903423212715</v>
       </c>
       <c r="N42">
-        <v>0.43701540483134621</v>
+        <v>0.43671213701049066</v>
       </c>
       <c r="O42">
-        <v>0.34033515746553761</v>
+        <v>0.340138115907756</v>
       </c>
       <c r="AU42" t="s">
         <v>145</v>
       </c>
       <c r="AV42">
-        <v>0.40313864022234419</v>
+        <v>0.40427175512337199</v>
       </c>
       <c r="AW42">
-        <v>0.37721330038637663</v>
+        <v>0.377989390248959</v>
       </c>
       <c r="AX42">
-        <v>0.41603989844949352</v>
+        <v>0.41698124875711112</v>
       </c>
       <c r="AY42">
-        <v>0.30819264409541947</v>
+        <v>0.30909477085190828</v>
       </c>
       <c r="AZ42">
-        <v>0.24377062321807991</v>
+        <v>0.24428031752068863</v>
       </c>
       <c r="BA42">
-        <v>0.31719773200113616</v>
+        <v>0.31759736307647857</v>
       </c>
       <c r="BB42">
-        <v>0.14350073381404285</v>
+        <v>0.14357158498954242</v>
       </c>
       <c r="BC42">
-        <v>0.12077217074977138</v>
+        <v>0.12071617971020297</v>
       </c>
       <c r="BD42">
-        <v>0.16205393483381089</v>
+        <v>0.16205063408160117</v>
       </c>
       <c r="BE42">
-        <v>0.28214003231493895</v>
+        <v>0.28309079683966942</v>
       </c>
       <c r="BF42">
-        <v>0.25949963474480975</v>
+        <v>0.2597424998690796</v>
       </c>
       <c r="BG42">
-        <v>0.34287327342419371</v>
+        <v>0.34290619208136441</v>
       </c>
       <c r="BI42" t="s">
         <v>155</v>
@@ -12918,79 +12918,79 @@
         <v>31</v>
       </c>
       <c r="D46">
-        <v>0.34204977769144651</v>
+        <v>0.3418831326877706</v>
       </c>
       <c r="E46">
-        <v>0.37876673094606989</v>
+        <v>0.37817692431065386</v>
       </c>
       <c r="F46">
-        <v>0.34664385607840059</v>
+        <v>0.34612845884592164</v>
       </c>
       <c r="G46">
-        <v>0.29884706071104589</v>
+        <v>0.29874713675008241</v>
       </c>
       <c r="H46">
-        <v>0.36447422051194528</v>
+        <v>0.36421989706593938</v>
       </c>
       <c r="I46">
-        <v>0.33603303902870324</v>
+        <v>0.33541916799721927</v>
       </c>
       <c r="J46">
-        <v>0.36632094523025543</v>
+        <v>0.36562249030014649</v>
       </c>
       <c r="K46">
-        <v>0.44389474799755263</v>
+        <v>0.4433217471495417</v>
       </c>
       <c r="L46">
-        <v>0.36230279769903462</v>
+        <v>0.3615159162847586</v>
       </c>
       <c r="M46">
-        <v>0.35745206702502652</v>
+        <v>0.35699923621859309</v>
       </c>
       <c r="N46">
-        <v>0.39187385308495293</v>
+        <v>0.39156952760055047</v>
       </c>
       <c r="O46">
-        <v>0.33581055635922596</v>
+        <v>0.33537029185363437</v>
       </c>
       <c r="AU46" t="s">
         <v>149</v>
       </c>
       <c r="AV46">
-        <v>0.42542085697423909</v>
+        <v>0.42530760052429001</v>
       </c>
       <c r="AW46">
-        <v>0.4093045663014504</v>
+        <v>0.40923434566438227</v>
       </c>
       <c r="AX46">
-        <v>0.44576277435287287</v>
+        <v>0.44566408557203574</v>
       </c>
       <c r="AY46">
-        <v>0.3586349015153627</v>
+        <v>0.35852009057068218</v>
       </c>
       <c r="AZ46">
-        <v>0.27502777805453682</v>
+        <v>0.27510254384927707</v>
       </c>
       <c r="BA46">
-        <v>0.35358186652794116</v>
+        <v>0.35356708432599432</v>
       </c>
       <c r="BB46">
-        <v>0.17782045833648844</v>
+        <v>0.17774223060075695</v>
       </c>
       <c r="BC46">
-        <v>0.15789083336951146</v>
+        <v>0.15812290426154813</v>
       </c>
       <c r="BD46">
-        <v>0.20167547109243375</v>
+        <v>0.20175056110831821</v>
       </c>
       <c r="BE46">
-        <v>0.32708760114002616</v>
+        <v>0.32712438804057969</v>
       </c>
       <c r="BF46">
-        <v>0.30727971814026295</v>
+        <v>0.30738047037264543</v>
       </c>
       <c r="BG46">
-        <v>0.37724523432956641</v>
+        <v>0.37709180100177331</v>
       </c>
       <c r="BI46" t="s">
         <v>159</v>
@@ -13287,7 +13287,7 @@
         <v>172</v>
       </c>
       <c r="BL49">
-        <v>0.3810195723859946</v>
+        <v>0.37763666337061891</v>
       </c>
     </row>
     <row r="50" spans="2:64" x14ac:dyDescent="0.45">
@@ -14153,79 +14153,79 @@
         <v>31</v>
       </c>
       <c r="D59">
-        <v>0.35512232269809157</v>
+        <v>0.3568165549974977</v>
       </c>
       <c r="E59">
-        <v>0.39203528373331126</v>
+        <v>0.39334156717944579</v>
       </c>
       <c r="F59">
-        <v>0.34943469119930498</v>
+        <v>0.35062766372994481</v>
       </c>
       <c r="G59">
-        <v>0.35208019521735995</v>
+        <v>0.35511402983587875</v>
       </c>
       <c r="H59">
-        <v>0.41889765024371078</v>
+        <v>0.42093538464533509</v>
       </c>
       <c r="I59">
-        <v>0.34718621889895723</v>
+        <v>0.34844397739208011</v>
       </c>
       <c r="J59">
-        <v>0.38254167601786088</v>
+        <v>0.38469584005607976</v>
       </c>
       <c r="K59">
-        <v>0.49239232981471248</v>
+        <v>0.49319414570436715</v>
       </c>
       <c r="L59">
-        <v>0.37696099111068415</v>
+        <v>0.37842510167170518</v>
       </c>
       <c r="M59">
-        <v>0.38088641635442994</v>
+        <v>0.38302758742886212</v>
       </c>
       <c r="N59">
-        <v>0.42483983587551882</v>
+        <v>0.42602152004287702</v>
       </c>
       <c r="O59">
-        <v>0.34515854288357539</v>
+        <v>0.34699594844597798</v>
       </c>
       <c r="AU59" t="s">
         <v>162</v>
       </c>
       <c r="AV59">
-        <v>0.35735976785948609</v>
+        <v>0.35397322866648684</v>
       </c>
       <c r="AW59">
-        <v>0.36004643718920526</v>
+        <v>0.35688647354042147</v>
       </c>
       <c r="AX59">
-        <v>0.38102090163740648</v>
+        <v>0.37763803947383845</v>
       </c>
       <c r="AY59">
-        <v>0.25398540662762054</v>
+        <v>0.25063804064404066</v>
       </c>
       <c r="AZ59">
-        <v>0.20887511667634795</v>
+        <v>0.20700608877148657</v>
       </c>
       <c r="BA59">
-        <v>0.27055836444151993</v>
+        <v>0.26765958924385075</v>
       </c>
       <c r="BB59">
-        <v>0.13033812141716952</v>
+        <v>0.12825820466637075</v>
       </c>
       <c r="BC59">
-        <v>0.11797919258472367</v>
+        <v>0.11707091403083993</v>
       </c>
       <c r="BD59">
-        <v>0.13509025163757851</v>
+        <v>0.13335801472580169</v>
       </c>
       <c r="BE59">
-        <v>0.25601848539347949</v>
+        <v>0.25295103398225172</v>
       </c>
       <c r="BF59">
-        <v>0.25807116275992636</v>
+        <v>0.25614690763266973</v>
       </c>
       <c r="BG59">
-        <v>0.3102083313629822</v>
+        <v>0.30746861692718597</v>
       </c>
       <c r="BI59" t="s">
         <v>142</v>
@@ -14341,7 +14341,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABFBBD69-FF2E-47FA-88EF-0E498BEBD702}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8485496B-0012-4A2A-9B07-AC69FB1E6A71}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14572,7 +14572,7 @@
         <v>45</v>
       </c>
       <c r="R14">
-        <v>0.19109999999999996</v>
+        <v>0.19110000000000002</v>
       </c>
       <c r="S14" t="s">
         <v>186</v>
@@ -14859,7 +14859,7 @@
         <v>43</v>
       </c>
       <c r="R21">
-        <v>0.12036666666666668</v>
+        <v>0.12036666666666666</v>
       </c>
       <c r="S21" t="s">
         <v>186</v>
@@ -15196,7 +15196,7 @@
         <v>45</v>
       </c>
       <c r="R38">
-        <v>0.20659999999999998</v>
+        <v>0.20660000000000001</v>
       </c>
       <c r="S38" t="s">
         <v>186</v>
@@ -15252,7 +15252,7 @@
         <v>45</v>
       </c>
       <c r="R42">
-        <v>0.29533333333333339</v>
+        <v>0.29533333333333334</v>
       </c>
       <c r="S42" t="s">
         <v>186</v>
@@ -15308,7 +15308,7 @@
         <v>45</v>
       </c>
       <c r="R46">
-        <v>0.22879999999999998</v>
+        <v>0.2288</v>
       </c>
       <c r="S46" t="s">
         <v>186</v>
@@ -15518,7 +15518,7 @@
         <v>43</v>
       </c>
       <c r="R61">
-        <v>0.20516666666666669</v>
+        <v>0.20516666666666664</v>
       </c>
       <c r="S61" t="s">
         <v>186</v>
@@ -15588,7 +15588,7 @@
         <v>45</v>
       </c>
       <c r="R66">
-        <v>0.19193333333333332</v>
+        <v>0.19193333333333337</v>
       </c>
       <c r="S66" t="s">
         <v>186</v>
@@ -15644,7 +15644,7 @@
         <v>45</v>
       </c>
       <c r="R70">
-        <v>0.27233333333333337</v>
+        <v>0.27233333333333332</v>
       </c>
       <c r="S70" t="s">
         <v>186</v>
@@ -15686,7 +15686,7 @@
         <v>43</v>
       </c>
       <c r="R73">
-        <v>0.19603333333333336</v>
+        <v>0.19603333333333331</v>
       </c>
       <c r="S73" t="s">
         <v>186</v>
@@ -15742,7 +15742,7 @@
         <v>43</v>
       </c>
       <c r="R77">
-        <v>0.21279999999999999</v>
+        <v>0.21280000000000002</v>
       </c>
       <c r="S77" t="s">
         <v>186</v>
@@ -16134,7 +16134,7 @@
         <v>43</v>
       </c>
       <c r="R105">
-        <v>0.19526666666666667</v>
+        <v>0.1952666666666667</v>
       </c>
       <c r="S105" t="s">
         <v>186</v>
@@ -16148,7 +16148,7 @@
         <v>45</v>
       </c>
       <c r="R106">
-        <v>0.17756666666666665</v>
+        <v>0.17756666666666668</v>
       </c>
       <c r="S106" t="s">
         <v>186</v>
@@ -16372,7 +16372,7 @@
         <v>45</v>
       </c>
       <c r="R122">
-        <v>0.23020000000000004</v>
+        <v>0.23019999999999999</v>
       </c>
       <c r="S122" t="s">
         <v>186</v>
@@ -16414,7 +16414,7 @@
         <v>43</v>
       </c>
       <c r="R125">
-        <v>0.17353333333333334</v>
+        <v>0.17353333333333332</v>
       </c>
       <c r="S125" t="s">
         <v>186</v>
@@ -16428,7 +16428,7 @@
         <v>45</v>
       </c>
       <c r="R126">
-        <v>0.21530000000000002</v>
+        <v>0.21529999999999996</v>
       </c>
       <c r="S126" t="s">
         <v>186</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AD3A05E-BC24-4A2B-B17E-EF00FA63AB80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BD2EF9-403D-4637-8375-1EEDA4AFB20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -19,9 +19,6 @@
     <sheet name="firmness" sheetId="9" r:id="rId4"/>
     <sheet name="load_demand_peak_hydro" sheetId="10" r:id="rId5"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId6"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2590" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2591" uniqueCount="187">
   <si>
     <t>share of charging at night</t>
   </si>
@@ -573,13 +570,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S1aH2,S3aH2,S4aH2,S2aH2</t>
+    <t>S2aH2,S3aH2,S4aH2,S1aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S1aH1,S4aH3,S1aH3,S2aH1,S3aH1,S2aH3,S3aH3,S4aH1</t>
+    <t>S2aH3,S3aH3,S4aH1,S3aH1,S1aH1,S4aH3,S2aH1,S1aH3</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -740,19 +737,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Veda"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1076,9 +1060,8 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" t="str">
-        <f>IFERROR([1]Veda!D5,"ts_12")</f>
-        <v>ts_12</v>
+      <c r="A10" t="s">
+        <v>46</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
@@ -1174,7 +1157,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S1aH1,S4aH3,S1aH3,S2aH1,S3aH1,S2aH3,S3aH3,S4aH1</v>
+        <v>S2aH3,S3aH3,S4aH1,S3aH1,S1aH1,S4aH3,S2aH1,S1aH3</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1206,7 +1189,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S1aH2,S3aH2,S4aH2,S2aH2</v>
+        <v>S2aH2,S3aH2,S4aH2,S1aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1302,7 +1285,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60C02DEA-6F20-4F91-9E58-8547DC0A0A1C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{504A9C75-27C5-4CEB-A515-0E5230C506BF}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1333,10 +1316,6 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A11" t="str">
-        <f>IFERROR(IF([1]Veda!D5=A10,"ok","x"),"")</f>
-        <v/>
-      </c>
       <c r="C11" t="s">
         <v>37</v>
       </c>
@@ -1386,7 +1365,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53A9ED8E-0288-4406-9C3D-383F82C6453F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6641CDA7-5BE8-42F8-B433-4CEF34667E46}">
   <dimension ref="B9:O250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9128,7 +9107,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BD24A6C-4731-41EA-9BF1-A37DFD51D55B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{837650F7-4BF8-4F72-B510-2E6FBB69F1DD}">
   <dimension ref="B9:BL60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14341,7 +14320,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8485496B-0012-4A2A-9B07-AC69FB1E6A71}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86012BD0-C704-4684-A08C-4B05A3EFE943}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14411,10 +14390,6 @@
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A11" t="str">
-        <f>IFERROR(IF([1]Veda!D5=A10,"ok","x"),"")</f>
-        <v/>
-      </c>
       <c r="C11">
         <v>8.2191780821917804E-2</v>
       </c>
@@ -14490,7 +14465,7 @@
         <v>41</v>
       </c>
       <c r="R12">
-        <v>0.17526666666666665</v>
+        <v>0.17526666666666668</v>
       </c>
       <c r="S12" t="s">
         <v>186</v>
@@ -14572,7 +14547,7 @@
         <v>45</v>
       </c>
       <c r="R14">
-        <v>0.19110000000000002</v>
+        <v>0.19109999999999996</v>
       </c>
       <c r="S14" t="s">
         <v>186</v>
@@ -14613,7 +14588,7 @@
         <v>37</v>
       </c>
       <c r="R15">
-        <v>0.20653333333333332</v>
+        <v>0.20653333333333335</v>
       </c>
       <c r="S15" t="s">
         <v>186</v>
@@ -14777,7 +14752,7 @@
         <v>37</v>
       </c>
       <c r="R19">
-        <v>0.23840000000000003</v>
+        <v>0.23839999999999997</v>
       </c>
       <c r="S19" t="s">
         <v>186</v>
@@ -14818,7 +14793,7 @@
         <v>41</v>
       </c>
       <c r="R20">
-        <v>0.23150000000000001</v>
+        <v>0.23149999999999996</v>
       </c>
       <c r="S20" t="s">
         <v>186</v>
@@ -15168,7 +15143,7 @@
         <v>41</v>
       </c>
       <c r="R36">
-        <v>0.32773333333333338</v>
+        <v>0.32773333333333332</v>
       </c>
       <c r="S36" t="s">
         <v>186</v>
@@ -15280,7 +15255,7 @@
         <v>41</v>
       </c>
       <c r="R44">
-        <v>0.34233333333333338</v>
+        <v>0.34233333333333332</v>
       </c>
       <c r="S44" t="s">
         <v>186</v>
@@ -15364,7 +15339,7 @@
         <v>45</v>
       </c>
       <c r="R50">
-        <v>0.24779999999999999</v>
+        <v>0.24780000000000002</v>
       </c>
       <c r="S50" t="s">
         <v>186</v>
@@ -15378,7 +15353,7 @@
         <v>37</v>
       </c>
       <c r="R51">
-        <v>0.31676666666666664</v>
+        <v>0.3167666666666667</v>
       </c>
       <c r="S51" t="s">
         <v>186</v>
@@ -15392,7 +15367,7 @@
         <v>41</v>
       </c>
       <c r="R52">
-        <v>0.32276666666666665</v>
+        <v>0.3227666666666667</v>
       </c>
       <c r="S52" t="s">
         <v>186</v>
@@ -15420,7 +15395,7 @@
         <v>45</v>
       </c>
       <c r="R54">
-        <v>0.22766666666666668</v>
+        <v>0.22766666666666666</v>
       </c>
       <c r="S54" t="s">
         <v>186</v>
@@ -15448,7 +15423,7 @@
         <v>41</v>
       </c>
       <c r="R56">
-        <v>0.35000000000000003</v>
+        <v>0.34999999999999992</v>
       </c>
       <c r="S56" t="s">
         <v>186</v>
@@ -15616,7 +15591,7 @@
         <v>41</v>
       </c>
       <c r="R68">
-        <v>0.38203333333333328</v>
+        <v>0.38203333333333339</v>
       </c>
       <c r="S68" t="s">
         <v>186</v>
@@ -15770,7 +15745,7 @@
         <v>37</v>
       </c>
       <c r="R79">
-        <v>0.3242666666666667</v>
+        <v>0.32426666666666665</v>
       </c>
       <c r="S79" t="s">
         <v>186</v>
@@ -15826,7 +15801,7 @@
         <v>37</v>
       </c>
       <c r="R83">
-        <v>0.30743333333333334</v>
+        <v>0.30743333333333328</v>
       </c>
       <c r="S83" t="s">
         <v>186</v>
@@ -15840,7 +15815,7 @@
         <v>41</v>
       </c>
       <c r="R84">
-        <v>0.3323666666666667</v>
+        <v>0.33236666666666664</v>
       </c>
       <c r="S84" t="s">
         <v>186</v>
@@ -15938,7 +15913,7 @@
         <v>37</v>
       </c>
       <c r="R91">
-        <v>0.3143333333333333</v>
+        <v>0.31433333333333335</v>
       </c>
       <c r="S91" t="s">
         <v>186</v>
@@ -15952,7 +15927,7 @@
         <v>41</v>
       </c>
       <c r="R92">
-        <v>0.31546666666666667</v>
+        <v>0.31546666666666673</v>
       </c>
       <c r="S92" t="s">
         <v>186</v>
@@ -15980,7 +15955,7 @@
         <v>45</v>
       </c>
       <c r="R94">
-        <v>0.21929999999999997</v>
+        <v>0.21930000000000002</v>
       </c>
       <c r="S94" t="s">
         <v>186</v>
@@ -16106,7 +16081,7 @@
         <v>37</v>
       </c>
       <c r="R103">
-        <v>0.28610000000000002</v>
+        <v>0.28609999999999997</v>
       </c>
       <c r="S103" t="s">
         <v>186</v>
@@ -16120,7 +16095,7 @@
         <v>41</v>
       </c>
       <c r="R104">
-        <v>0.32653333333333329</v>
+        <v>0.32653333333333334</v>
       </c>
       <c r="S104" t="s">
         <v>186</v>
@@ -16162,7 +16137,7 @@
         <v>37</v>
       </c>
       <c r="R107">
-        <v>0.32646666666666663</v>
+        <v>0.32646666666666668</v>
       </c>
       <c r="S107" t="s">
         <v>186</v>
@@ -16176,7 +16151,7 @@
         <v>41</v>
       </c>
       <c r="R108">
-        <v>0.32569999999999999</v>
+        <v>0.32569999999999993</v>
       </c>
       <c r="S108" t="s">
         <v>186</v>
@@ -16218,7 +16193,7 @@
         <v>37</v>
       </c>
       <c r="R111">
-        <v>0.31429999999999997</v>
+        <v>0.31430000000000002</v>
       </c>
       <c r="S111" t="s">
         <v>186</v>
@@ -16288,7 +16263,7 @@
         <v>41</v>
       </c>
       <c r="R116">
-        <v>0.32293333333333335</v>
+        <v>0.32293333333333329</v>
       </c>
       <c r="S116" t="s">
         <v>186</v>
@@ -16372,7 +16347,7 @@
         <v>45</v>
       </c>
       <c r="R122">
-        <v>0.23019999999999999</v>
+        <v>0.23020000000000004</v>
       </c>
       <c r="S122" t="s">
         <v>186</v>
@@ -16386,7 +16361,7 @@
         <v>37</v>
       </c>
       <c r="R123">
-        <v>0.30760000000000004</v>
+        <v>0.30759999999999998</v>
       </c>
       <c r="S123" t="s">
         <v>186</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BD2EF9-403D-4637-8375-1EEDA4AFB20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B459409-9444-4071-8E4F-B8D6D85AA0A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -570,13 +570,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S2aH2,S3aH2,S4aH2,S1aH2</t>
+    <t>S4aH2,S2aH2,S3aH2,S1aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S2aH3,S3aH3,S4aH1,S3aH1,S1aH1,S4aH3,S2aH1,S1aH3</t>
+    <t>S2aH1,S1aH1,S4aH3,S2aH3,S3aH3,S4aH1,S3aH1,S1aH3</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S2aH3,S3aH3,S4aH1,S3aH1,S1aH1,S4aH3,S2aH1,S1aH3</v>
+        <v>S2aH1,S1aH1,S4aH3,S2aH3,S3aH3,S4aH1,S3aH1,S1aH3</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S2aH2,S3aH2,S4aH2,S1aH2</v>
+        <v>S4aH2,S2aH2,S3aH2,S1aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1285,7 +1285,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{504A9C75-27C5-4CEB-A515-0E5230C506BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76231011-E1A4-40A7-B4E5-E90490E88F2D}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1365,7 +1365,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6641CDA7-5BE8-42F8-B433-4CEF34667E46}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26C0A2B0-752E-45E6-8683-CBEAC822A5DA}">
   <dimension ref="B9:O250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9107,7 +9107,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{837650F7-4BF8-4F72-B510-2E6FBB69F1DD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80993A5A-058C-4A97-B552-334C1DE380C5}">
   <dimension ref="B9:BL60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14320,7 +14320,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86012BD0-C704-4684-A08C-4B05A3EFE943}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95515D2A-60CA-45AE-AEEA-2A1C976205F2}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B459409-9444-4071-8E4F-B8D6D85AA0A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{256DFBD3-B7A8-4881-8CCA-591B4F914D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -570,13 +570,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S4aH2,S2aH2,S3aH2,S1aH2</t>
+    <t>S1aH2,S2aH2,S3aH2,S4aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S2aH1,S1aH1,S4aH3,S2aH3,S3aH3,S4aH1,S3aH1,S1aH3</t>
+    <t>S1aH3,S1aH1,S4aH3,S2aH3,S3aH3,S4aH1,S3aH1,S2aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S2aH1,S1aH1,S4aH3,S2aH3,S3aH3,S4aH1,S3aH1,S1aH3</v>
+        <v>S1aH3,S1aH1,S4aH3,S2aH3,S3aH3,S4aH1,S3aH1,S2aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S4aH2,S2aH2,S3aH2,S1aH2</v>
+        <v>S1aH2,S2aH2,S3aH2,S4aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1285,7 +1285,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76231011-E1A4-40A7-B4E5-E90490E88F2D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3394833B-1444-454A-B9EB-1A1D8EF6913F}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1365,7 +1365,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26C0A2B0-752E-45E6-8683-CBEAC822A5DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20E5D90C-B1FF-4A14-A2C2-F24B051F0FB1}">
   <dimension ref="B9:O250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9107,7 +9107,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80993A5A-058C-4A97-B552-334C1DE380C5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41E449AC-6AE7-4A22-A16A-617D02556348}">
   <dimension ref="B9:BL60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14320,7 +14320,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95515D2A-60CA-45AE-AEEA-2A1C976205F2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6DB782-F84F-4F80-AF55-3B9594E680D9}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14465,7 +14465,7 @@
         <v>41</v>
       </c>
       <c r="R12">
-        <v>0.17526666666666668</v>
+        <v>0.17526666666666665</v>
       </c>
       <c r="S12" t="s">
         <v>186</v>
@@ -14547,7 +14547,7 @@
         <v>45</v>
       </c>
       <c r="R14">
-        <v>0.19109999999999996</v>
+        <v>0.19110000000000002</v>
       </c>
       <c r="S14" t="s">
         <v>186</v>
@@ -14752,7 +14752,7 @@
         <v>37</v>
       </c>
       <c r="R19">
-        <v>0.23839999999999997</v>
+        <v>0.23840000000000003</v>
       </c>
       <c r="S19" t="s">
         <v>186</v>
@@ -14793,7 +14793,7 @@
         <v>41</v>
       </c>
       <c r="R20">
-        <v>0.23149999999999996</v>
+        <v>0.23150000000000001</v>
       </c>
       <c r="S20" t="s">
         <v>186</v>
@@ -15143,7 +15143,7 @@
         <v>41</v>
       </c>
       <c r="R36">
-        <v>0.32773333333333332</v>
+        <v>0.32773333333333338</v>
       </c>
       <c r="S36" t="s">
         <v>186</v>
@@ -15255,7 +15255,7 @@
         <v>41</v>
       </c>
       <c r="R44">
-        <v>0.34233333333333332</v>
+        <v>0.34233333333333338</v>
       </c>
       <c r="S44" t="s">
         <v>186</v>
@@ -15297,7 +15297,7 @@
         <v>37</v>
       </c>
       <c r="R47">
-        <v>0.30259999999999998</v>
+        <v>0.30260000000000004</v>
       </c>
       <c r="S47" t="s">
         <v>186</v>
@@ -15339,7 +15339,7 @@
         <v>45</v>
       </c>
       <c r="R50">
-        <v>0.24780000000000002</v>
+        <v>0.24779999999999999</v>
       </c>
       <c r="S50" t="s">
         <v>186</v>
@@ -15353,7 +15353,7 @@
         <v>37</v>
       </c>
       <c r="R51">
-        <v>0.3167666666666667</v>
+        <v>0.31676666666666664</v>
       </c>
       <c r="S51" t="s">
         <v>186</v>
@@ -15367,7 +15367,7 @@
         <v>41</v>
       </c>
       <c r="R52">
-        <v>0.3227666666666667</v>
+        <v>0.32276666666666665</v>
       </c>
       <c r="S52" t="s">
         <v>186</v>
@@ -15395,7 +15395,7 @@
         <v>45</v>
       </c>
       <c r="R54">
-        <v>0.22766666666666666</v>
+        <v>0.22766666666666668</v>
       </c>
       <c r="S54" t="s">
         <v>186</v>
@@ -15423,7 +15423,7 @@
         <v>41</v>
       </c>
       <c r="R56">
-        <v>0.34999999999999992</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="S56" t="s">
         <v>186</v>
@@ -15465,7 +15465,7 @@
         <v>37</v>
       </c>
       <c r="R59">
-        <v>0.29860000000000003</v>
+        <v>0.29859999999999998</v>
       </c>
       <c r="S59" t="s">
         <v>186</v>
@@ -15577,7 +15577,7 @@
         <v>37</v>
       </c>
       <c r="R67">
-        <v>0.37280000000000002</v>
+        <v>0.37279999999999996</v>
       </c>
       <c r="S67" t="s">
         <v>186</v>
@@ -15591,7 +15591,7 @@
         <v>41</v>
       </c>
       <c r="R68">
-        <v>0.38203333333333339</v>
+        <v>0.38203333333333328</v>
       </c>
       <c r="S68" t="s">
         <v>186</v>
@@ -15815,7 +15815,7 @@
         <v>41</v>
       </c>
       <c r="R84">
-        <v>0.33236666666666664</v>
+        <v>0.3323666666666667</v>
       </c>
       <c r="S84" t="s">
         <v>186</v>
@@ -15927,7 +15927,7 @@
         <v>41</v>
       </c>
       <c r="R92">
-        <v>0.31546666666666673</v>
+        <v>0.31546666666666667</v>
       </c>
       <c r="S92" t="s">
         <v>186</v>
@@ -15955,7 +15955,7 @@
         <v>45</v>
       </c>
       <c r="R94">
-        <v>0.21930000000000002</v>
+        <v>0.21929999999999997</v>
       </c>
       <c r="S94" t="s">
         <v>186</v>
@@ -16081,7 +16081,7 @@
         <v>37</v>
       </c>
       <c r="R103">
-        <v>0.28609999999999997</v>
+        <v>0.28610000000000002</v>
       </c>
       <c r="S103" t="s">
         <v>186</v>
@@ -16095,7 +16095,7 @@
         <v>41</v>
       </c>
       <c r="R104">
-        <v>0.32653333333333334</v>
+        <v>0.32653333333333329</v>
       </c>
       <c r="S104" t="s">
         <v>186</v>
@@ -16137,7 +16137,7 @@
         <v>37</v>
       </c>
       <c r="R107">
-        <v>0.32646666666666668</v>
+        <v>0.32646666666666663</v>
       </c>
       <c r="S107" t="s">
         <v>186</v>
@@ -16151,7 +16151,7 @@
         <v>41</v>
       </c>
       <c r="R108">
-        <v>0.32569999999999993</v>
+        <v>0.32569999999999999</v>
       </c>
       <c r="S108" t="s">
         <v>186</v>
@@ -16263,7 +16263,7 @@
         <v>41</v>
       </c>
       <c r="R116">
-        <v>0.32293333333333329</v>
+        <v>0.32293333333333335</v>
       </c>
       <c r="S116" t="s">
         <v>186</v>
@@ -16305,7 +16305,7 @@
         <v>37</v>
       </c>
       <c r="R119">
-        <v>0.31936666666666663</v>
+        <v>0.31936666666666669</v>
       </c>
       <c r="S119" t="s">
         <v>186</v>
@@ -16347,7 +16347,7 @@
         <v>45</v>
       </c>
       <c r="R122">
-        <v>0.23020000000000004</v>
+        <v>0.23019999999999999</v>
       </c>
       <c r="S122" t="s">
         <v>186</v>
@@ -16361,7 +16361,7 @@
         <v>37</v>
       </c>
       <c r="R123">
-        <v>0.30759999999999998</v>
+        <v>0.30760000000000004</v>
       </c>
       <c r="S123" t="s">
         <v>186</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{256DFBD3-B7A8-4881-8CCA-591B4F914D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A4D0F37-38EF-495F-957D-37CB0B040341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -570,13 +570,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S1aH2,S2aH2,S3aH2,S4aH2</t>
+    <t>S1aH2,S3aH2,S2aH2,S4aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S1aH3,S1aH1,S4aH3,S2aH3,S3aH3,S4aH1,S3aH1,S2aH1</t>
+    <t>S1aH3,S1aH1,S4aH3,S2aH3,S3aH1,S3aH3,S4aH1,S2aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S1aH3,S1aH1,S4aH3,S2aH3,S3aH3,S4aH1,S3aH1,S2aH1</v>
+        <v>S1aH3,S1aH1,S4aH3,S2aH3,S3aH1,S3aH3,S4aH1,S2aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S1aH2,S2aH2,S3aH2,S4aH2</v>
+        <v>S1aH2,S3aH2,S2aH2,S4aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1285,7 +1285,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3394833B-1444-454A-B9EB-1A1D8EF6913F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA83EB0-63CB-4F33-B994-93666BAECBF2}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1365,7 +1365,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20E5D90C-B1FF-4A14-A2C2-F24B051F0FB1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA22F32E-BF7A-49C0-BB56-FBE4FF1833C8}">
   <dimension ref="B9:O250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9107,7 +9107,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41E449AC-6AE7-4A22-A16A-617D02556348}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B60304CB-8546-45B4-86A2-704DE8650152}">
   <dimension ref="B9:BL60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14320,7 +14320,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6DB782-F84F-4F80-AF55-3B9594E680D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2541CE67-0FAA-464D-946A-22849528A9B8}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14588,7 +14588,7 @@
         <v>37</v>
       </c>
       <c r="R15">
-        <v>0.20653333333333335</v>
+        <v>0.20653333333333332</v>
       </c>
       <c r="S15" t="s">
         <v>186</v>
@@ -15297,7 +15297,7 @@
         <v>37</v>
       </c>
       <c r="R47">
-        <v>0.30260000000000004</v>
+        <v>0.30259999999999998</v>
       </c>
       <c r="S47" t="s">
         <v>186</v>
@@ -15465,7 +15465,7 @@
         <v>37</v>
       </c>
       <c r="R59">
-        <v>0.29859999999999998</v>
+        <v>0.29860000000000003</v>
       </c>
       <c r="S59" t="s">
         <v>186</v>
@@ -15577,7 +15577,7 @@
         <v>37</v>
       </c>
       <c r="R67">
-        <v>0.37279999999999996</v>
+        <v>0.37280000000000002</v>
       </c>
       <c r="S67" t="s">
         <v>186</v>
@@ -15745,7 +15745,7 @@
         <v>37</v>
       </c>
       <c r="R79">
-        <v>0.32426666666666665</v>
+        <v>0.3242666666666667</v>
       </c>
       <c r="S79" t="s">
         <v>186</v>
@@ -15801,7 +15801,7 @@
         <v>37</v>
       </c>
       <c r="R83">
-        <v>0.30743333333333328</v>
+        <v>0.30743333333333334</v>
       </c>
       <c r="S83" t="s">
         <v>186</v>
@@ -15913,7 +15913,7 @@
         <v>37</v>
       </c>
       <c r="R91">
-        <v>0.31433333333333335</v>
+        <v>0.3143333333333333</v>
       </c>
       <c r="S91" t="s">
         <v>186</v>
@@ -16193,7 +16193,7 @@
         <v>37</v>
       </c>
       <c r="R111">
-        <v>0.31430000000000002</v>
+        <v>0.31429999999999997</v>
       </c>
       <c r="S111" t="s">
         <v>186</v>
@@ -16305,7 +16305,7 @@
         <v>37</v>
       </c>
       <c r="R119">
-        <v>0.31936666666666669</v>
+        <v>0.31936666666666663</v>
       </c>
       <c r="S119" t="s">
         <v>186</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A4D0F37-38EF-495F-957D-37CB0B040341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908D8DFF-C2B3-4AFE-B399-2737035D6228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -570,13 +570,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S1aH2,S3aH2,S2aH2,S4aH2</t>
+    <t>S2aH2,S4aH2,S3aH2,S1aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S1aH3,S1aH1,S4aH3,S2aH3,S3aH1,S3aH3,S4aH1,S2aH1</t>
+    <t>S3aH3,S4aH1,S1aH1,S4aH3,S2aH3,S2aH1,S3aH1,S1aH3</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S1aH3,S1aH1,S4aH3,S2aH3,S3aH1,S3aH3,S4aH1,S2aH1</v>
+        <v>S3aH3,S4aH1,S1aH1,S4aH3,S2aH3,S2aH1,S3aH1,S1aH3</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S1aH2,S3aH2,S2aH2,S4aH2</v>
+        <v>S2aH2,S4aH2,S3aH2,S1aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1285,7 +1285,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA83EB0-63CB-4F33-B994-93666BAECBF2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76E52C18-944E-4A1D-9961-CA0412B9309D}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1365,7 +1365,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA22F32E-BF7A-49C0-BB56-FBE4FF1833C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36011ED2-F0D4-46B0-AB5D-325801C923DF}">
   <dimension ref="B9:O250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9107,7 +9107,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B60304CB-8546-45B4-86A2-704DE8650152}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2288C63-C23D-40C5-AD61-BB0D1288B206}">
   <dimension ref="B9:BL60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14320,7 +14320,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2541CE67-0FAA-464D-946A-22849528A9B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA2EF383-423E-4404-9E37-BD7299E45855}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14465,7 +14465,7 @@
         <v>41</v>
       </c>
       <c r="R12">
-        <v>0.17526666666666665</v>
+        <v>0.17526666666666668</v>
       </c>
       <c r="S12" t="s">
         <v>186</v>
@@ -14547,7 +14547,7 @@
         <v>45</v>
       </c>
       <c r="R14">
-        <v>0.19110000000000002</v>
+        <v>0.19109999999999996</v>
       </c>
       <c r="S14" t="s">
         <v>186</v>
@@ -14588,7 +14588,7 @@
         <v>37</v>
       </c>
       <c r="R15">
-        <v>0.20653333333333332</v>
+        <v>0.20653333333333335</v>
       </c>
       <c r="S15" t="s">
         <v>186</v>
@@ -14834,7 +14834,7 @@
         <v>43</v>
       </c>
       <c r="R21">
-        <v>0.12036666666666666</v>
+        <v>0.12036666666666668</v>
       </c>
       <c r="S21" t="s">
         <v>186</v>
@@ -15171,7 +15171,7 @@
         <v>45</v>
       </c>
       <c r="R38">
-        <v>0.20660000000000001</v>
+        <v>0.20659999999999998</v>
       </c>
       <c r="S38" t="s">
         <v>186</v>
@@ -15227,7 +15227,7 @@
         <v>45</v>
       </c>
       <c r="R42">
-        <v>0.29533333333333334</v>
+        <v>0.29533333333333339</v>
       </c>
       <c r="S42" t="s">
         <v>186</v>
@@ -15283,7 +15283,7 @@
         <v>45</v>
       </c>
       <c r="R46">
-        <v>0.2288</v>
+        <v>0.22879999999999998</v>
       </c>
       <c r="S46" t="s">
         <v>186</v>
@@ -15297,7 +15297,7 @@
         <v>37</v>
       </c>
       <c r="R47">
-        <v>0.30259999999999998</v>
+        <v>0.30260000000000004</v>
       </c>
       <c r="S47" t="s">
         <v>186</v>
@@ -15367,7 +15367,7 @@
         <v>41</v>
       </c>
       <c r="R52">
-        <v>0.32276666666666665</v>
+        <v>0.3227666666666667</v>
       </c>
       <c r="S52" t="s">
         <v>186</v>
@@ -15465,7 +15465,7 @@
         <v>37</v>
       </c>
       <c r="R59">
-        <v>0.29860000000000003</v>
+        <v>0.29859999999999998</v>
       </c>
       <c r="S59" t="s">
         <v>186</v>
@@ -15493,7 +15493,7 @@
         <v>43</v>
       </c>
       <c r="R61">
-        <v>0.20516666666666664</v>
+        <v>0.20516666666666669</v>
       </c>
       <c r="S61" t="s">
         <v>186</v>
@@ -15535,7 +15535,7 @@
         <v>41</v>
       </c>
       <c r="R64">
-        <v>0.3297666666666666</v>
+        <v>0.32976666666666665</v>
       </c>
       <c r="S64" t="s">
         <v>186</v>
@@ -15563,7 +15563,7 @@
         <v>45</v>
       </c>
       <c r="R66">
-        <v>0.19193333333333337</v>
+        <v>0.19193333333333332</v>
       </c>
       <c r="S66" t="s">
         <v>186</v>
@@ -15577,7 +15577,7 @@
         <v>37</v>
       </c>
       <c r="R67">
-        <v>0.37280000000000002</v>
+        <v>0.37279999999999996</v>
       </c>
       <c r="S67" t="s">
         <v>186</v>
@@ -15619,7 +15619,7 @@
         <v>45</v>
       </c>
       <c r="R70">
-        <v>0.27233333333333332</v>
+        <v>0.27233333333333337</v>
       </c>
       <c r="S70" t="s">
         <v>186</v>
@@ -15661,7 +15661,7 @@
         <v>43</v>
       </c>
       <c r="R73">
-        <v>0.19603333333333331</v>
+        <v>0.19603333333333336</v>
       </c>
       <c r="S73" t="s">
         <v>186</v>
@@ -15717,7 +15717,7 @@
         <v>43</v>
       </c>
       <c r="R77">
-        <v>0.21280000000000002</v>
+        <v>0.21279999999999999</v>
       </c>
       <c r="S77" t="s">
         <v>186</v>
@@ -15745,7 +15745,7 @@
         <v>37</v>
       </c>
       <c r="R79">
-        <v>0.3242666666666667</v>
+        <v>0.32426666666666665</v>
       </c>
       <c r="S79" t="s">
         <v>186</v>
@@ -15801,7 +15801,7 @@
         <v>37</v>
       </c>
       <c r="R83">
-        <v>0.30743333333333334</v>
+        <v>0.30743333333333328</v>
       </c>
       <c r="S83" t="s">
         <v>186</v>
@@ -15913,7 +15913,7 @@
         <v>37</v>
       </c>
       <c r="R91">
-        <v>0.3143333333333333</v>
+        <v>0.31433333333333335</v>
       </c>
       <c r="S91" t="s">
         <v>186</v>
@@ -15927,7 +15927,7 @@
         <v>41</v>
       </c>
       <c r="R92">
-        <v>0.31546666666666667</v>
+        <v>0.31546666666666673</v>
       </c>
       <c r="S92" t="s">
         <v>186</v>
@@ -16109,7 +16109,7 @@
         <v>43</v>
       </c>
       <c r="R105">
-        <v>0.1952666666666667</v>
+        <v>0.19526666666666667</v>
       </c>
       <c r="S105" t="s">
         <v>186</v>
@@ -16123,7 +16123,7 @@
         <v>45</v>
       </c>
       <c r="R106">
-        <v>0.17756666666666668</v>
+        <v>0.17756666666666665</v>
       </c>
       <c r="S106" t="s">
         <v>186</v>
@@ -16151,7 +16151,7 @@
         <v>41</v>
       </c>
       <c r="R108">
-        <v>0.32569999999999999</v>
+        <v>0.32569999999999993</v>
       </c>
       <c r="S108" t="s">
         <v>186</v>
@@ -16193,7 +16193,7 @@
         <v>37</v>
       </c>
       <c r="R111">
-        <v>0.31429999999999997</v>
+        <v>0.31430000000000002</v>
       </c>
       <c r="S111" t="s">
         <v>186</v>
@@ -16305,7 +16305,7 @@
         <v>37</v>
       </c>
       <c r="R119">
-        <v>0.31936666666666663</v>
+        <v>0.31936666666666669</v>
       </c>
       <c r="S119" t="s">
         <v>186</v>
@@ -16347,7 +16347,7 @@
         <v>45</v>
       </c>
       <c r="R122">
-        <v>0.23019999999999999</v>
+        <v>0.23020000000000004</v>
       </c>
       <c r="S122" t="s">
         <v>186</v>
@@ -16375,7 +16375,7 @@
         <v>41</v>
       </c>
       <c r="R124">
-        <v>0.3557333333333334</v>
+        <v>0.35573333333333329</v>
       </c>
       <c r="S124" t="s">
         <v>186</v>
@@ -16389,7 +16389,7 @@
         <v>43</v>
       </c>
       <c r="R125">
-        <v>0.17353333333333332</v>
+        <v>0.17353333333333334</v>
       </c>
       <c r="S125" t="s">
         <v>186</v>
@@ -16403,7 +16403,7 @@
         <v>45</v>
       </c>
       <c r="R126">
-        <v>0.21529999999999996</v>
+        <v>0.21530000000000002</v>
       </c>
       <c r="S126" t="s">
         <v>186</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908D8DFF-C2B3-4AFE-B399-2737035D6228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09DD32A-1CD6-41D8-A166-67D1EE10EE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -570,13 +570,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S2aH2,S4aH2,S3aH2,S1aH2</t>
+    <t>S3aH2,S1aH2,S4aH2,S2aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S3aH3,S4aH1,S1aH1,S4aH3,S2aH3,S2aH1,S3aH1,S1aH3</t>
+    <t>S1aH1,S4aH3,S3aH1,S2aH3,S1aH3,S2aH1,S3aH3,S4aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S3aH3,S4aH1,S1aH1,S4aH3,S2aH3,S2aH1,S3aH1,S1aH3</v>
+        <v>S1aH1,S4aH3,S3aH1,S2aH3,S1aH3,S2aH1,S3aH3,S4aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S2aH2,S4aH2,S3aH2,S1aH2</v>
+        <v>S3aH2,S1aH2,S4aH2,S2aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1285,7 +1285,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76E52C18-944E-4A1D-9961-CA0412B9309D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E4B3976-B0BC-438E-ACB2-592513A1623C}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1365,7 +1365,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36011ED2-F0D4-46B0-AB5D-325801C923DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55AA4384-7309-4A9E-8127-7690E399AA05}">
   <dimension ref="B9:O250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9107,7 +9107,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2288C63-C23D-40C5-AD61-BB0D1288B206}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C383DAE4-F7EC-4061-998C-C36A74961138}">
   <dimension ref="B9:BL60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14320,7 +14320,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA2EF383-423E-4404-9E37-BD7299E45855}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44CFEB89-AAB7-4491-9E4A-F8C687C7499B}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14588,7 +14588,7 @@
         <v>37</v>
       </c>
       <c r="R15">
-        <v>0.20653333333333335</v>
+        <v>0.20653333333333332</v>
       </c>
       <c r="S15" t="s">
         <v>186</v>
@@ -14793,7 +14793,7 @@
         <v>41</v>
       </c>
       <c r="R20">
-        <v>0.23150000000000001</v>
+        <v>0.23149999999999996</v>
       </c>
       <c r="S20" t="s">
         <v>186</v>
@@ -14834,7 +14834,7 @@
         <v>43</v>
       </c>
       <c r="R21">
-        <v>0.12036666666666668</v>
+        <v>0.12036666666666666</v>
       </c>
       <c r="S21" t="s">
         <v>186</v>
@@ -15143,7 +15143,7 @@
         <v>41</v>
       </c>
       <c r="R36">
-        <v>0.32773333333333338</v>
+        <v>0.32773333333333332</v>
       </c>
       <c r="S36" t="s">
         <v>186</v>
@@ -15255,7 +15255,7 @@
         <v>41</v>
       </c>
       <c r="R44">
-        <v>0.34233333333333338</v>
+        <v>0.34233333333333332</v>
       </c>
       <c r="S44" t="s">
         <v>186</v>
@@ -15297,7 +15297,7 @@
         <v>37</v>
       </c>
       <c r="R47">
-        <v>0.30260000000000004</v>
+        <v>0.30259999999999998</v>
       </c>
       <c r="S47" t="s">
         <v>186</v>
@@ -15423,7 +15423,7 @@
         <v>41</v>
       </c>
       <c r="R56">
-        <v>0.35000000000000003</v>
+        <v>0.34999999999999992</v>
       </c>
       <c r="S56" t="s">
         <v>186</v>
@@ -15465,7 +15465,7 @@
         <v>37</v>
       </c>
       <c r="R59">
-        <v>0.29859999999999998</v>
+        <v>0.29860000000000003</v>
       </c>
       <c r="S59" t="s">
         <v>186</v>
@@ -15493,7 +15493,7 @@
         <v>43</v>
       </c>
       <c r="R61">
-        <v>0.20516666666666669</v>
+        <v>0.20516666666666664</v>
       </c>
       <c r="S61" t="s">
         <v>186</v>
@@ -15535,7 +15535,7 @@
         <v>41</v>
       </c>
       <c r="R64">
-        <v>0.32976666666666665</v>
+        <v>0.3297666666666666</v>
       </c>
       <c r="S64" t="s">
         <v>186</v>
@@ -15577,7 +15577,7 @@
         <v>37</v>
       </c>
       <c r="R67">
-        <v>0.37279999999999996</v>
+        <v>0.37280000000000002</v>
       </c>
       <c r="S67" t="s">
         <v>186</v>
@@ -15591,7 +15591,7 @@
         <v>41</v>
       </c>
       <c r="R68">
-        <v>0.38203333333333328</v>
+        <v>0.38203333333333339</v>
       </c>
       <c r="S68" t="s">
         <v>186</v>
@@ -15661,7 +15661,7 @@
         <v>43</v>
       </c>
       <c r="R73">
-        <v>0.19603333333333336</v>
+        <v>0.19603333333333331</v>
       </c>
       <c r="S73" t="s">
         <v>186</v>
@@ -15717,7 +15717,7 @@
         <v>43</v>
       </c>
       <c r="R77">
-        <v>0.21279999999999999</v>
+        <v>0.21280000000000002</v>
       </c>
       <c r="S77" t="s">
         <v>186</v>
@@ -15745,7 +15745,7 @@
         <v>37</v>
       </c>
       <c r="R79">
-        <v>0.32426666666666665</v>
+        <v>0.3242666666666667</v>
       </c>
       <c r="S79" t="s">
         <v>186</v>
@@ -15801,7 +15801,7 @@
         <v>37</v>
       </c>
       <c r="R83">
-        <v>0.30743333333333328</v>
+        <v>0.30743333333333334</v>
       </c>
       <c r="S83" t="s">
         <v>186</v>
@@ -15815,7 +15815,7 @@
         <v>41</v>
       </c>
       <c r="R84">
-        <v>0.3323666666666667</v>
+        <v>0.33236666666666664</v>
       </c>
       <c r="S84" t="s">
         <v>186</v>
@@ -15913,7 +15913,7 @@
         <v>37</v>
       </c>
       <c r="R91">
-        <v>0.31433333333333335</v>
+        <v>0.3143333333333333</v>
       </c>
       <c r="S91" t="s">
         <v>186</v>
@@ -16095,7 +16095,7 @@
         <v>41</v>
       </c>
       <c r="R104">
-        <v>0.32653333333333329</v>
+        <v>0.32653333333333334</v>
       </c>
       <c r="S104" t="s">
         <v>186</v>
@@ -16109,7 +16109,7 @@
         <v>43</v>
       </c>
       <c r="R105">
-        <v>0.19526666666666667</v>
+        <v>0.1952666666666667</v>
       </c>
       <c r="S105" t="s">
         <v>186</v>
@@ -16193,7 +16193,7 @@
         <v>37</v>
       </c>
       <c r="R111">
-        <v>0.31430000000000002</v>
+        <v>0.31429999999999997</v>
       </c>
       <c r="S111" t="s">
         <v>186</v>
@@ -16263,7 +16263,7 @@
         <v>41</v>
       </c>
       <c r="R116">
-        <v>0.32293333333333335</v>
+        <v>0.32293333333333329</v>
       </c>
       <c r="S116" t="s">
         <v>186</v>
@@ -16305,7 +16305,7 @@
         <v>37</v>
       </c>
       <c r="R119">
-        <v>0.31936666666666669</v>
+        <v>0.31936666666666663</v>
       </c>
       <c r="S119" t="s">
         <v>186</v>
@@ -16375,7 +16375,7 @@
         <v>41</v>
       </c>
       <c r="R124">
-        <v>0.35573333333333329</v>
+        <v>0.3557333333333334</v>
       </c>
       <c r="S124" t="s">
         <v>186</v>
@@ -16389,7 +16389,7 @@
         <v>43</v>
       </c>
       <c r="R125">
-        <v>0.17353333333333334</v>
+        <v>0.17353333333333332</v>
       </c>
       <c r="S125" t="s">
         <v>186</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09DD32A-1CD6-41D8-A166-67D1EE10EE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C94FAA-366D-4252-A0B8-147A35820A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -570,13 +570,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S3aH2,S1aH2,S4aH2,S2aH2</t>
+    <t>S2aH2,S1aH2,S3aH2,S4aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S1aH1,S4aH3,S3aH1,S2aH3,S1aH3,S2aH1,S3aH3,S4aH1</t>
+    <t>S1aH1,S4aH3,S3aH3,S4aH1,S1aH3,S3aH1,S2aH1,S2aH3</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S1aH1,S4aH3,S3aH1,S2aH3,S1aH3,S2aH1,S3aH3,S4aH1</v>
+        <v>S1aH1,S4aH3,S3aH3,S4aH1,S1aH3,S3aH1,S2aH1,S2aH3</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S3aH2,S1aH2,S4aH2,S2aH2</v>
+        <v>S2aH2,S1aH2,S3aH2,S4aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1285,7 +1285,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E4B3976-B0BC-438E-ACB2-592513A1623C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{390E3143-BC0C-4790-9DAB-BC5D4A2476AC}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1365,7 +1365,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55AA4384-7309-4A9E-8127-7690E399AA05}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B34951F-BFDC-4CB1-95C5-69C687C8560E}">
   <dimension ref="B9:O250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9107,7 +9107,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C383DAE4-F7EC-4061-998C-C36A74961138}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F76B5BC-B89F-4A0A-A24F-516845E06B7C}">
   <dimension ref="B9:BL60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14320,7 +14320,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44CFEB89-AAB7-4491-9E4A-F8C687C7499B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0D9206B-AA2B-4163-8B15-2CDFB34D26FD}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14588,7 +14588,7 @@
         <v>37</v>
       </c>
       <c r="R15">
-        <v>0.20653333333333332</v>
+        <v>0.20653333333333335</v>
       </c>
       <c r="S15" t="s">
         <v>186</v>
@@ -14752,7 +14752,7 @@
         <v>37</v>
       </c>
       <c r="R19">
-        <v>0.23840000000000003</v>
+        <v>0.23839999999999997</v>
       </c>
       <c r="S19" t="s">
         <v>186</v>
@@ -14793,7 +14793,7 @@
         <v>41</v>
       </c>
       <c r="R20">
-        <v>0.23149999999999996</v>
+        <v>0.23150000000000001</v>
       </c>
       <c r="S20" t="s">
         <v>186</v>
@@ -14834,7 +14834,7 @@
         <v>43</v>
       </c>
       <c r="R21">
-        <v>0.12036666666666666</v>
+        <v>0.12036666666666668</v>
       </c>
       <c r="S21" t="s">
         <v>186</v>
@@ -14935,7 +14935,7 @@
         <v>43</v>
       </c>
       <c r="R25">
-        <v>0.24466666666666667</v>
+        <v>0.2446666666666667</v>
       </c>
       <c r="S25" t="s">
         <v>186</v>
@@ -15143,7 +15143,7 @@
         <v>41</v>
       </c>
       <c r="R36">
-        <v>0.32773333333333332</v>
+        <v>0.32773333333333338</v>
       </c>
       <c r="S36" t="s">
         <v>186</v>
@@ -15255,7 +15255,7 @@
         <v>41</v>
       </c>
       <c r="R44">
-        <v>0.34233333333333332</v>
+        <v>0.34233333333333338</v>
       </c>
       <c r="S44" t="s">
         <v>186</v>
@@ -15353,7 +15353,7 @@
         <v>37</v>
       </c>
       <c r="R51">
-        <v>0.31676666666666664</v>
+        <v>0.3167666666666667</v>
       </c>
       <c r="S51" t="s">
         <v>186</v>
@@ -15423,7 +15423,7 @@
         <v>41</v>
       </c>
       <c r="R56">
-        <v>0.34999999999999992</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="S56" t="s">
         <v>186</v>
@@ -15437,7 +15437,7 @@
         <v>43</v>
       </c>
       <c r="R57">
-        <v>0.18733333333333332</v>
+        <v>0.18733333333333335</v>
       </c>
       <c r="S57" t="s">
         <v>186</v>
@@ -15535,7 +15535,7 @@
         <v>41</v>
       </c>
       <c r="R64">
-        <v>0.3297666666666666</v>
+        <v>0.32976666666666665</v>
       </c>
       <c r="S64" t="s">
         <v>186</v>
@@ -15549,7 +15549,7 @@
         <v>43</v>
       </c>
       <c r="R65">
-        <v>0.20076666666666668</v>
+        <v>0.20076666666666665</v>
       </c>
       <c r="S65" t="s">
         <v>186</v>
@@ -15591,7 +15591,7 @@
         <v>41</v>
       </c>
       <c r="R68">
-        <v>0.38203333333333339</v>
+        <v>0.38203333333333328</v>
       </c>
       <c r="S68" t="s">
         <v>186</v>
@@ -15745,7 +15745,7 @@
         <v>37</v>
       </c>
       <c r="R79">
-        <v>0.3242666666666667</v>
+        <v>0.32426666666666665</v>
       </c>
       <c r="S79" t="s">
         <v>186</v>
@@ -15801,7 +15801,7 @@
         <v>37</v>
       </c>
       <c r="R83">
-        <v>0.30743333333333334</v>
+        <v>0.30743333333333328</v>
       </c>
       <c r="S83" t="s">
         <v>186</v>
@@ -15815,7 +15815,7 @@
         <v>41</v>
       </c>
       <c r="R84">
-        <v>0.33236666666666664</v>
+        <v>0.3323666666666667</v>
       </c>
       <c r="S84" t="s">
         <v>186</v>
@@ -15913,7 +15913,7 @@
         <v>37</v>
       </c>
       <c r="R91">
-        <v>0.3143333333333333</v>
+        <v>0.31433333333333335</v>
       </c>
       <c r="S91" t="s">
         <v>186</v>
@@ -16081,7 +16081,7 @@
         <v>37</v>
       </c>
       <c r="R103">
-        <v>0.28610000000000002</v>
+        <v>0.28609999999999997</v>
       </c>
       <c r="S103" t="s">
         <v>186</v>
@@ -16095,7 +16095,7 @@
         <v>41</v>
       </c>
       <c r="R104">
-        <v>0.32653333333333334</v>
+        <v>0.32653333333333329</v>
       </c>
       <c r="S104" t="s">
         <v>186</v>
@@ -16109,7 +16109,7 @@
         <v>43</v>
       </c>
       <c r="R105">
-        <v>0.1952666666666667</v>
+        <v>0.19526666666666667</v>
       </c>
       <c r="S105" t="s">
         <v>186</v>
@@ -16137,7 +16137,7 @@
         <v>37</v>
       </c>
       <c r="R107">
-        <v>0.32646666666666663</v>
+        <v>0.32646666666666668</v>
       </c>
       <c r="S107" t="s">
         <v>186</v>
@@ -16193,7 +16193,7 @@
         <v>37</v>
       </c>
       <c r="R111">
-        <v>0.31429999999999997</v>
+        <v>0.31430000000000002</v>
       </c>
       <c r="S111" t="s">
         <v>186</v>
@@ -16263,7 +16263,7 @@
         <v>41</v>
       </c>
       <c r="R116">
-        <v>0.32293333333333329</v>
+        <v>0.32293333333333335</v>
       </c>
       <c r="S116" t="s">
         <v>186</v>
@@ -16361,7 +16361,7 @@
         <v>37</v>
       </c>
       <c r="R123">
-        <v>0.30760000000000004</v>
+        <v>0.30759999999999998</v>
       </c>
       <c r="S123" t="s">
         <v>186</v>
@@ -16375,7 +16375,7 @@
         <v>41</v>
       </c>
       <c r="R124">
-        <v>0.3557333333333334</v>
+        <v>0.35573333333333329</v>
       </c>
       <c r="S124" t="s">
         <v>186</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF79C914-9F86-4363-A763-B182BF159281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE6D59F-594F-4744-9B67-EA3CC762F617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -594,13 +594,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S2aH2,S4aH2,S3aH2,S1aH2</t>
+    <t>S3aH2,S1aH2,S4aH2,S2aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S3aH3,S4aH1,S2aH1,S1aH3,S3aH1,S1aH1,S4aH3,S2aH3</t>
+    <t>S1aH3,S1aH1,S4aH3,S2aH3,S3aH1,S2aH1,S3aH3,S4aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S3aH3,S4aH1,S2aH1,S1aH3,S3aH1,S1aH1,S4aH3,S2aH3</v>
+        <v>S1aH3,S1aH1,S4aH3,S2aH3,S3aH1,S2aH1,S3aH3,S4aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S2aH2,S4aH2,S3aH2,S1aH2</v>
+        <v>S3aH2,S1aH2,S4aH2,S2aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1325,7 +1325,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{206A817C-3907-4C3F-B9BD-ABEFF72FC564}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAE442FE-9B0B-4697-8E03-3CF3B868E658}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1405,7 +1405,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{289BD77F-4C35-483D-A172-3A3939B84485}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{021842F2-F02F-4495-A77C-7AB109FA41C4}">
   <dimension ref="B9:O250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9147,7 +9147,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B81F3CC-A788-4517-A92B-A5F34DD74523}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36942EC1-6A1A-4CCC-A155-DAF4E0484501}">
   <dimension ref="B9:CI60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20500,7 +20500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AA8233A-1761-4C4F-B9F5-186834D17016}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD779FDB-BD70-4364-9B64-26326ACDF72D}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20645,7 +20645,7 @@
         <v>42</v>
       </c>
       <c r="R12">
-        <v>0.17526666666666665</v>
+        <v>0.17526666666666668</v>
       </c>
       <c r="S12" t="s">
         <v>194</v>
@@ -20932,7 +20932,7 @@
         <v>38</v>
       </c>
       <c r="R19">
-        <v>0.23839999999999997</v>
+        <v>0.23840000000000003</v>
       </c>
       <c r="S19" t="s">
         <v>194</v>
@@ -20973,7 +20973,7 @@
         <v>42</v>
       </c>
       <c r="R20">
-        <v>0.23150000000000001</v>
+        <v>0.23149999999999996</v>
       </c>
       <c r="S20" t="s">
         <v>194</v>
@@ -21323,7 +21323,7 @@
         <v>42</v>
       </c>
       <c r="R36">
-        <v>0.32773333333333338</v>
+        <v>0.32773333333333332</v>
       </c>
       <c r="S36" t="s">
         <v>194</v>
@@ -21351,7 +21351,7 @@
         <v>46</v>
       </c>
       <c r="R38">
-        <v>0.20659999999999998</v>
+        <v>0.20660000000000001</v>
       </c>
       <c r="S38" t="s">
         <v>194</v>
@@ -21407,7 +21407,7 @@
         <v>46</v>
       </c>
       <c r="R42">
-        <v>0.29533333333333339</v>
+        <v>0.29533333333333334</v>
       </c>
       <c r="S42" t="s">
         <v>194</v>
@@ -21435,7 +21435,7 @@
         <v>42</v>
       </c>
       <c r="R44">
-        <v>0.34233333333333338</v>
+        <v>0.34233333333333332</v>
       </c>
       <c r="S44" t="s">
         <v>194</v>
@@ -21463,7 +21463,7 @@
         <v>46</v>
       </c>
       <c r="R46">
-        <v>0.22879999999999998</v>
+        <v>0.2288</v>
       </c>
       <c r="S46" t="s">
         <v>194</v>
@@ -21477,7 +21477,7 @@
         <v>38</v>
       </c>
       <c r="R47">
-        <v>0.30259999999999998</v>
+        <v>0.30260000000000004</v>
       </c>
       <c r="S47" t="s">
         <v>194</v>
@@ -21519,7 +21519,7 @@
         <v>46</v>
       </c>
       <c r="R50">
-        <v>0.24779999999999999</v>
+        <v>0.24780000000000002</v>
       </c>
       <c r="S50" t="s">
         <v>194</v>
@@ -21533,7 +21533,7 @@
         <v>38</v>
       </c>
       <c r="R51">
-        <v>0.3167666666666667</v>
+        <v>0.31676666666666664</v>
       </c>
       <c r="S51" t="s">
         <v>194</v>
@@ -21547,7 +21547,7 @@
         <v>42</v>
       </c>
       <c r="R52">
-        <v>0.32276666666666665</v>
+        <v>0.3227666666666667</v>
       </c>
       <c r="S52" t="s">
         <v>194</v>
@@ -21575,7 +21575,7 @@
         <v>46</v>
       </c>
       <c r="R54">
-        <v>0.22766666666666668</v>
+        <v>0.22766666666666666</v>
       </c>
       <c r="S54" t="s">
         <v>194</v>
@@ -21603,7 +21603,7 @@
         <v>42</v>
       </c>
       <c r="R56">
-        <v>0.35000000000000003</v>
+        <v>0.34999999999999992</v>
       </c>
       <c r="S56" t="s">
         <v>194</v>
@@ -21645,7 +21645,7 @@
         <v>38</v>
       </c>
       <c r="R59">
-        <v>0.29860000000000003</v>
+        <v>0.29859999999999998</v>
       </c>
       <c r="S59" t="s">
         <v>194</v>
@@ -21743,7 +21743,7 @@
         <v>46</v>
       </c>
       <c r="R66">
-        <v>0.19193333333333332</v>
+        <v>0.19193333333333337</v>
       </c>
       <c r="S66" t="s">
         <v>194</v>
@@ -21757,7 +21757,7 @@
         <v>38</v>
       </c>
       <c r="R67">
-        <v>0.37280000000000002</v>
+        <v>0.37279999999999996</v>
       </c>
       <c r="S67" t="s">
         <v>194</v>
@@ -21771,7 +21771,7 @@
         <v>42</v>
       </c>
       <c r="R68">
-        <v>0.38203333333333328</v>
+        <v>0.38203333333333339</v>
       </c>
       <c r="S68" t="s">
         <v>194</v>
@@ -21799,7 +21799,7 @@
         <v>46</v>
       </c>
       <c r="R70">
-        <v>0.27233333333333337</v>
+        <v>0.27233333333333332</v>
       </c>
       <c r="S70" t="s">
         <v>194</v>
@@ -21995,7 +21995,7 @@
         <v>42</v>
       </c>
       <c r="R84">
-        <v>0.3323666666666667</v>
+        <v>0.33236666666666664</v>
       </c>
       <c r="S84" t="s">
         <v>194</v>
@@ -22107,7 +22107,7 @@
         <v>42</v>
       </c>
       <c r="R92">
-        <v>0.31546666666666667</v>
+        <v>0.31546666666666673</v>
       </c>
       <c r="S92" t="s">
         <v>194</v>
@@ -22135,7 +22135,7 @@
         <v>46</v>
       </c>
       <c r="R94">
-        <v>0.21929999999999997</v>
+        <v>0.21930000000000002</v>
       </c>
       <c r="S94" t="s">
         <v>194</v>
@@ -22261,7 +22261,7 @@
         <v>38</v>
       </c>
       <c r="R103">
-        <v>0.28609999999999997</v>
+        <v>0.28610000000000002</v>
       </c>
       <c r="S103" t="s">
         <v>194</v>
@@ -22275,7 +22275,7 @@
         <v>42</v>
       </c>
       <c r="R104">
-        <v>0.32653333333333329</v>
+        <v>0.32653333333333334</v>
       </c>
       <c r="S104" t="s">
         <v>194</v>
@@ -22303,7 +22303,7 @@
         <v>46</v>
       </c>
       <c r="R106">
-        <v>0.17756666666666665</v>
+        <v>0.17756666666666668</v>
       </c>
       <c r="S106" t="s">
         <v>194</v>
@@ -22317,7 +22317,7 @@
         <v>38</v>
       </c>
       <c r="R107">
-        <v>0.32646666666666668</v>
+        <v>0.32646666666666663</v>
       </c>
       <c r="S107" t="s">
         <v>194</v>
@@ -22331,7 +22331,7 @@
         <v>42</v>
       </c>
       <c r="R108">
-        <v>0.32569999999999999</v>
+        <v>0.32569999999999993</v>
       </c>
       <c r="S108" t="s">
         <v>194</v>
@@ -22443,7 +22443,7 @@
         <v>42</v>
       </c>
       <c r="R116">
-        <v>0.32293333333333335</v>
+        <v>0.32293333333333329</v>
       </c>
       <c r="S116" t="s">
         <v>194</v>
@@ -22485,7 +22485,7 @@
         <v>38</v>
       </c>
       <c r="R119">
-        <v>0.31936666666666663</v>
+        <v>0.31936666666666669</v>
       </c>
       <c r="S119" t="s">
         <v>194</v>
@@ -22541,7 +22541,7 @@
         <v>38</v>
       </c>
       <c r="R123">
-        <v>0.30759999999999998</v>
+        <v>0.30760000000000004</v>
       </c>
       <c r="S123" t="s">
         <v>194</v>
@@ -22583,7 +22583,7 @@
         <v>46</v>
       </c>
       <c r="R126">
-        <v>0.21530000000000002</v>
+        <v>0.21529999999999996</v>
       </c>
       <c r="S126" t="s">
         <v>194</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE6D59F-594F-4744-9B67-EA3CC762F617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B4CCFA-8F30-4EA4-8E4F-02D53ED2EC98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -594,13 +594,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S3aH2,S1aH2,S4aH2,S2aH2</t>
+    <t>S3aH2,S1aH2,S2aH2,S4aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S1aH3,S1aH1,S4aH3,S2aH3,S3aH1,S2aH1,S3aH3,S4aH1</t>
+    <t>S1aH1,S4aH3,S2aH3,S1aH3,S3aH1,S3aH3,S4aH1,S2aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S1aH3,S1aH1,S4aH3,S2aH3,S3aH1,S2aH1,S3aH3,S4aH1</v>
+        <v>S1aH1,S4aH3,S2aH3,S1aH3,S3aH1,S3aH3,S4aH1,S2aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S3aH2,S1aH2,S4aH2,S2aH2</v>
+        <v>S3aH2,S1aH2,S2aH2,S4aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1325,7 +1325,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAE442FE-9B0B-4697-8E03-3CF3B868E658}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94592F66-0178-4598-9C82-7EA90FA4EFA8}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1405,7 +1405,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{021842F2-F02F-4495-A77C-7AB109FA41C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E436C5A1-3817-4188-96F0-1DEAE69A97D3}">
   <dimension ref="B9:O250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9147,7 +9147,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36942EC1-6A1A-4CCC-A155-DAF4E0484501}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4F67433-6898-4873-A87A-FBA1951E84C6}">
   <dimension ref="B9:CI60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20500,7 +20500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD779FDB-BD70-4364-9B64-26326ACDF72D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5500476-3B65-4A01-B44A-16215238B331}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20768,7 +20768,7 @@
         <v>38</v>
       </c>
       <c r="R15">
-        <v>0.20653333333333335</v>
+        <v>0.20653333333333332</v>
       </c>
       <c r="S15" t="s">
         <v>194</v>
@@ -21477,7 +21477,7 @@
         <v>38</v>
       </c>
       <c r="R47">
-        <v>0.30260000000000004</v>
+        <v>0.30259999999999998</v>
       </c>
       <c r="S47" t="s">
         <v>194</v>
@@ -21645,7 +21645,7 @@
         <v>38</v>
       </c>
       <c r="R59">
-        <v>0.29859999999999998</v>
+        <v>0.29860000000000003</v>
       </c>
       <c r="S59" t="s">
         <v>194</v>
@@ -21757,7 +21757,7 @@
         <v>38</v>
       </c>
       <c r="R67">
-        <v>0.37279999999999996</v>
+        <v>0.37280000000000002</v>
       </c>
       <c r="S67" t="s">
         <v>194</v>
@@ -21925,7 +21925,7 @@
         <v>38</v>
       </c>
       <c r="R79">
-        <v>0.32426666666666665</v>
+        <v>0.3242666666666667</v>
       </c>
       <c r="S79" t="s">
         <v>194</v>
@@ -21981,7 +21981,7 @@
         <v>38</v>
       </c>
       <c r="R83">
-        <v>0.30743333333333328</v>
+        <v>0.30743333333333334</v>
       </c>
       <c r="S83" t="s">
         <v>194</v>
@@ -22093,7 +22093,7 @@
         <v>38</v>
       </c>
       <c r="R91">
-        <v>0.31433333333333335</v>
+        <v>0.3143333333333333</v>
       </c>
       <c r="S91" t="s">
         <v>194</v>
@@ -22373,7 +22373,7 @@
         <v>38</v>
       </c>
       <c r="R111">
-        <v>0.31430000000000002</v>
+        <v>0.31429999999999997</v>
       </c>
       <c r="S111" t="s">
         <v>194</v>
@@ -22485,7 +22485,7 @@
         <v>38</v>
       </c>
       <c r="R119">
-        <v>0.31936666666666669</v>
+        <v>0.31936666666666663</v>
       </c>
       <c r="S119" t="s">
         <v>194</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1BF8A86-8973-4B16-9963-02899B609CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9FF2D7A-3077-451E-8C67-D5CD170A8F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -600,7 +600,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>S1aH3,S1aH1,S4aH3,S2aH1,S3aH1,S2aH3,S3aH3,S4aH1</t>
+    <t>S1aH3,S2aH1,S2aH3,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S1aH3,S1aH1,S4aH3,S2aH1,S3aH1,S2aH3,S3aH3,S4aH1</v>
+        <v>S1aH3,S2aH1,S2aH3,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1325,7 +1325,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{287263F3-E9AD-4F32-B9FE-D0175FA3D009}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B111BBC9-9191-4101-8E93-F8B72F92EAFA}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1405,7 +1405,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69D42087-154E-4578-A692-1915C3E79C39}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F8213E1-F067-4FE7-BE6C-50374A7DB3DA}">
   <dimension ref="B9:O250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9147,7 +9147,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3353291F-01FA-4C7D-B00A-BEA8F7986DC3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80FEBD17-C0A0-4972-9CFD-F74C966EC983}">
   <dimension ref="B9:CI60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20500,7 +20500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2199973A-A16D-4BFF-80E8-F78BEB767599}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAFCD2ED-24B4-4B20-8030-77E92202B24F}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20727,7 +20727,7 @@
         <v>46</v>
       </c>
       <c r="R14">
-        <v>0.19110000000000002</v>
+        <v>0.19109999999999996</v>
       </c>
       <c r="S14" t="s">
         <v>194</v>
@@ -20932,7 +20932,7 @@
         <v>38</v>
       </c>
       <c r="R19">
-        <v>0.23840000000000003</v>
+        <v>0.23839999999999997</v>
       </c>
       <c r="S19" t="s">
         <v>194</v>
@@ -21115,7 +21115,7 @@
         <v>44</v>
       </c>
       <c r="R25">
-        <v>0.24466666666666667</v>
+        <v>0.2446666666666667</v>
       </c>
       <c r="S25" t="s">
         <v>194</v>
@@ -21477,7 +21477,7 @@
         <v>38</v>
       </c>
       <c r="R47">
-        <v>0.30260000000000004</v>
+        <v>0.30259999999999998</v>
       </c>
       <c r="S47" t="s">
         <v>194</v>
@@ -21519,7 +21519,7 @@
         <v>46</v>
       </c>
       <c r="R50">
-        <v>0.24779999999999999</v>
+        <v>0.24780000000000002</v>
       </c>
       <c r="S50" t="s">
         <v>194</v>
@@ -21533,7 +21533,7 @@
         <v>38</v>
       </c>
       <c r="R51">
-        <v>0.31676666666666664</v>
+        <v>0.3167666666666667</v>
       </c>
       <c r="S51" t="s">
         <v>194</v>
@@ -21575,7 +21575,7 @@
         <v>46</v>
       </c>
       <c r="R54">
-        <v>0.22766666666666668</v>
+        <v>0.22766666666666666</v>
       </c>
       <c r="S54" t="s">
         <v>194</v>
@@ -21617,7 +21617,7 @@
         <v>44</v>
       </c>
       <c r="R57">
-        <v>0.18733333333333332</v>
+        <v>0.18733333333333335</v>
       </c>
       <c r="S57" t="s">
         <v>194</v>
@@ -21645,7 +21645,7 @@
         <v>38</v>
       </c>
       <c r="R59">
-        <v>0.29859999999999998</v>
+        <v>0.29860000000000003</v>
       </c>
       <c r="S59" t="s">
         <v>194</v>
@@ -21673,7 +21673,7 @@
         <v>44</v>
       </c>
       <c r="R61">
-        <v>0.20516666666666669</v>
+        <v>0.20516666666666664</v>
       </c>
       <c r="S61" t="s">
         <v>194</v>
@@ -21729,7 +21729,7 @@
         <v>44</v>
       </c>
       <c r="R65">
-        <v>0.20076666666666668</v>
+        <v>0.20076666666666665</v>
       </c>
       <c r="S65" t="s">
         <v>194</v>
@@ -21757,7 +21757,7 @@
         <v>38</v>
       </c>
       <c r="R67">
-        <v>0.37279999999999996</v>
+        <v>0.37280000000000002</v>
       </c>
       <c r="S67" t="s">
         <v>194</v>
@@ -21841,7 +21841,7 @@
         <v>44</v>
       </c>
       <c r="R73">
-        <v>0.19603333333333336</v>
+        <v>0.19603333333333331</v>
       </c>
       <c r="S73" t="s">
         <v>194</v>
@@ -21897,7 +21897,7 @@
         <v>44</v>
       </c>
       <c r="R77">
-        <v>0.21279999999999999</v>
+        <v>0.21280000000000002</v>
       </c>
       <c r="S77" t="s">
         <v>194</v>
@@ -22135,7 +22135,7 @@
         <v>46</v>
       </c>
       <c r="R94">
-        <v>0.21929999999999997</v>
+        <v>0.21930000000000002</v>
       </c>
       <c r="S94" t="s">
         <v>194</v>
@@ -22261,7 +22261,7 @@
         <v>38</v>
       </c>
       <c r="R103">
-        <v>0.28610000000000002</v>
+        <v>0.28609999999999997</v>
       </c>
       <c r="S103" t="s">
         <v>194</v>
@@ -22317,7 +22317,7 @@
         <v>38</v>
       </c>
       <c r="R107">
-        <v>0.32646666666666663</v>
+        <v>0.32646666666666668</v>
       </c>
       <c r="S107" t="s">
         <v>194</v>
@@ -22485,7 +22485,7 @@
         <v>38</v>
       </c>
       <c r="R119">
-        <v>0.31936666666666669</v>
+        <v>0.31936666666666663</v>
       </c>
       <c r="S119" t="s">
         <v>194</v>
@@ -22527,7 +22527,7 @@
         <v>46</v>
       </c>
       <c r="R122">
-        <v>0.23019999999999999</v>
+        <v>0.23020000000000004</v>
       </c>
       <c r="S122" t="s">
         <v>194</v>
@@ -22541,7 +22541,7 @@
         <v>38</v>
       </c>
       <c r="R123">
-        <v>0.30760000000000004</v>
+        <v>0.30759999999999998</v>
       </c>
       <c r="S123" t="s">
         <v>194</v>
@@ -22569,7 +22569,7 @@
         <v>44</v>
       </c>
       <c r="R125">
-        <v>0.17353333333333334</v>
+        <v>0.17353333333333332</v>
       </c>
       <c r="S125" t="s">
         <v>194</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7506259A-9DCF-4F33-8A4E-8B537ED4E372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAE6ACEF-A546-451D-95A5-7822994DAF44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -912,13 +912,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S3aH2,S2aH2,S4aH2,S1aH2</t>
+    <t>S2aH2,S3aH2,S4aH2,S1aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S2aH3,S3aH3,S4aH1,S2aH1,S1aH3,S1aH1,S4aH3,S3aH1</t>
+    <t>S3aH3,S4aH1,S1aH1,S4aH3,S2aH3,S2aH1,S3aH1,S1aH3</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S2aH3,S3aH3,S4aH1,S2aH1,S1aH3,S1aH1,S4aH3,S3aH1</v>
+        <v>S3aH3,S4aH1,S1aH1,S4aH3,S2aH3,S2aH1,S3aH1,S1aH3</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S3aH2,S2aH2,S4aH2,S1aH2</v>
+        <v>S2aH2,S3aH2,S4aH2,S1aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1623,7 +1623,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B266EE-444D-4455-9010-B80A45C31304}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3098460B-EA6E-48E6-8D56-BF9BF49F9D73}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1703,7 +1703,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A8E746-5E10-4A11-9EDE-1E70A68A5504}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF218D65-0BCC-4FAE-A10D-B52B0E028F98}">
   <dimension ref="B9:O586"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1779,7 +1779,7 @@
         <v>53</v>
       </c>
       <c r="I11">
-        <v>0.10714372538390542</v>
+        <v>0.10714372538390521</v>
       </c>
       <c r="J11" t="s">
         <v>54</v>
@@ -1791,7 +1791,7 @@
         <v>53</v>
       </c>
       <c r="N11">
-        <v>0.11316736557219671</v>
+        <v>0.11316736557219696</v>
       </c>
       <c r="O11" t="s">
         <v>54</v>
@@ -1805,7 +1805,7 @@
         <v>55</v>
       </c>
       <c r="D12">
-        <v>8.7226451367884608E-2</v>
+        <v>8.7226451367884636E-2</v>
       </c>
       <c r="E12" t="s">
         <v>54</v>
@@ -1817,7 +1817,7 @@
         <v>55</v>
       </c>
       <c r="I12">
-        <v>0.13360949822805118</v>
+        <v>0.1336094982280509</v>
       </c>
       <c r="J12" t="s">
         <v>54</v>
@@ -1829,7 +1829,7 @@
         <v>55</v>
       </c>
       <c r="N12">
-        <v>0.13685199178007687</v>
+        <v>0.13685199178007718</v>
       </c>
       <c r="O12" t="s">
         <v>54</v>
@@ -1855,7 +1855,7 @@
         <v>56</v>
       </c>
       <c r="I13">
-        <v>8.535627839065571E-2</v>
+        <v>8.5356278390655543E-2</v>
       </c>
       <c r="J13" t="s">
         <v>54</v>
@@ -1867,7 +1867,7 @@
         <v>56</v>
       </c>
       <c r="N13">
-        <v>8.7975477806498559E-2</v>
+        <v>8.7975477806498753E-2</v>
       </c>
       <c r="O13" t="s">
         <v>54</v>
@@ -1881,7 +1881,7 @@
         <v>57</v>
       </c>
       <c r="D14">
-        <v>9.4836848073850608E-3</v>
+        <v>9.4836848073850642E-3</v>
       </c>
       <c r="E14" t="s">
         <v>54</v>
@@ -1893,7 +1893,7 @@
         <v>57</v>
       </c>
       <c r="I14">
-        <v>9.3017310932357739E-2</v>
+        <v>9.3017310932357558E-2</v>
       </c>
       <c r="J14" t="s">
         <v>54</v>
@@ -1905,7 +1905,7 @@
         <v>57</v>
       </c>
       <c r="N14">
-        <v>8.6011780176409175E-2</v>
+        <v>8.6011780176409369E-2</v>
       </c>
       <c r="O14" t="s">
         <v>54</v>
@@ -1919,7 +1919,7 @@
         <v>58</v>
       </c>
       <c r="D15">
-        <v>0.34373239392579291</v>
+        <v>0.34373239392579302</v>
       </c>
       <c r="E15" t="s">
         <v>54</v>
@@ -1931,7 +1931,7 @@
         <v>58</v>
       </c>
       <c r="I15">
-        <v>9.0754003174934941E-2</v>
+        <v>9.0754003174934761E-2</v>
       </c>
       <c r="J15" t="s">
         <v>54</v>
@@ -1943,7 +1943,7 @@
         <v>58</v>
       </c>
       <c r="N15">
-        <v>8.9874798980809967E-2</v>
+        <v>8.9874798980810161E-2</v>
       </c>
       <c r="O15" t="s">
         <v>54</v>
@@ -1957,7 +1957,7 @@
         <v>59</v>
       </c>
       <c r="D16">
-        <v>5.2407251282421173E-3</v>
+        <v>5.2407251282421191E-3</v>
       </c>
       <c r="E16" t="s">
         <v>54</v>
@@ -1969,7 +1969,7 @@
         <v>59</v>
       </c>
       <c r="I16">
-        <v>6.9389680850120608E-2</v>
+        <v>6.9389680850120469E-2</v>
       </c>
       <c r="J16" t="s">
         <v>54</v>
@@ -1981,7 +1981,7 @@
         <v>59</v>
       </c>
       <c r="N16">
-        <v>6.4562630642842761E-2</v>
+        <v>6.45626306428429E-2</v>
       </c>
       <c r="O16" t="s">
         <v>54</v>
@@ -1995,7 +1995,7 @@
         <v>60</v>
       </c>
       <c r="D17">
-        <v>1.58755656110212E-2</v>
+        <v>1.5875565611021207E-2</v>
       </c>
       <c r="E17" t="s">
         <v>54</v>
@@ -2007,7 +2007,7 @@
         <v>60</v>
       </c>
       <c r="I17">
-        <v>4.8583435357519439E-2</v>
+        <v>4.8583435357519342E-2</v>
       </c>
       <c r="J17" t="s">
         <v>54</v>
@@ -2019,7 +2019,7 @@
         <v>60</v>
       </c>
       <c r="N17">
-        <v>5.0123164328323346E-2</v>
+        <v>5.0123164328323457E-2</v>
       </c>
       <c r="O17" t="s">
         <v>54</v>
@@ -2033,7 +2033,7 @@
         <v>61</v>
       </c>
       <c r="D18">
-        <v>0.35114363204589444</v>
+        <v>0.35114363204589455</v>
       </c>
       <c r="E18" t="s">
         <v>54</v>
@@ -2045,7 +2045,7 @@
         <v>61</v>
       </c>
       <c r="I18">
-        <v>6.1287559511608337E-2</v>
+        <v>6.1287559511608213E-2</v>
       </c>
       <c r="J18" t="s">
         <v>54</v>
@@ -2057,7 +2057,7 @@
         <v>61</v>
       </c>
       <c r="N18">
-        <v>6.2477899327997327E-2</v>
+        <v>6.2477899327997466E-2</v>
       </c>
       <c r="O18" t="s">
         <v>54</v>
@@ -2071,7 +2071,7 @@
         <v>62</v>
       </c>
       <c r="D19">
-        <v>1.1209438702951106E-2</v>
+        <v>1.1209438702951109E-2</v>
       </c>
       <c r="E19" t="s">
         <v>54</v>
@@ -2083,7 +2083,7 @@
         <v>62</v>
       </c>
       <c r="I19">
-        <v>4.2561771691295956E-2</v>
+        <v>4.2561771691295873E-2</v>
       </c>
       <c r="J19" t="s">
         <v>54</v>
@@ -2095,7 +2095,7 @@
         <v>62</v>
       </c>
       <c r="N19">
-        <v>3.9357246787282203E-2</v>
+        <v>3.9357246787282293E-2</v>
       </c>
       <c r="O19" t="s">
         <v>54</v>
@@ -2109,7 +2109,7 @@
         <v>63</v>
       </c>
       <c r="D20">
-        <v>2.142374198970782E-3</v>
+        <v>2.1423741989707828E-3</v>
       </c>
       <c r="E20" t="s">
         <v>54</v>
@@ -2121,7 +2121,7 @@
         <v>63</v>
       </c>
       <c r="I20">
-        <v>8.7696093316174686E-2</v>
+        <v>8.7696093316174506E-2</v>
       </c>
       <c r="J20" t="s">
         <v>54</v>
@@ -2133,7 +2133,7 @@
         <v>63</v>
       </c>
       <c r="N20">
-        <v>8.9262852143591101E-2</v>
+        <v>8.9262852143591295E-2</v>
       </c>
       <c r="O20" t="s">
         <v>54</v>
@@ -2147,7 +2147,7 @@
         <v>64</v>
       </c>
       <c r="D21">
-        <v>0.1735489177190733</v>
+        <v>0.17354891771907335</v>
       </c>
       <c r="E21" t="s">
         <v>54</v>
@@ -2159,7 +2159,7 @@
         <v>64</v>
       </c>
       <c r="I21">
-        <v>0.10660016419207244</v>
+        <v>0.10660016419207223</v>
       </c>
       <c r="J21" t="s">
         <v>54</v>
@@ -2171,7 +2171,7 @@
         <v>64</v>
       </c>
       <c r="N21">
-        <v>0.10746402963035086</v>
+        <v>0.10746402963035109</v>
       </c>
       <c r="O21" t="s">
         <v>54</v>
@@ -2185,7 +2185,7 @@
         <v>65</v>
       </c>
       <c r="D22">
-        <v>3.968164927841816E-4</v>
+        <v>3.9681649278418171E-4</v>
       </c>
       <c r="E22" t="s">
         <v>54</v>
@@ -2197,7 +2197,7 @@
         <v>65</v>
       </c>
       <c r="I22">
-        <v>7.4000478971305628E-2</v>
+        <v>7.4000478971305475E-2</v>
       </c>
       <c r="J22" t="s">
         <v>54</v>
@@ -2209,7 +2209,7 @@
         <v>65</v>
       </c>
       <c r="N22">
-        <v>7.2870762823618859E-2</v>
+        <v>7.2870762823619026E-2</v>
       </c>
       <c r="O22" t="s">
         <v>54</v>
@@ -2223,7 +2223,7 @@
         <v>53</v>
       </c>
       <c r="D23">
-        <v>7.8107946792281937E-6</v>
+        <v>7.8107946792282141E-6</v>
       </c>
       <c r="E23" t="s">
         <v>54</v>
@@ -2235,7 +2235,7 @@
         <v>53</v>
       </c>
       <c r="I23">
-        <v>0.11488827803169852</v>
+        <v>0.11488827803169828</v>
       </c>
       <c r="J23" t="s">
         <v>54</v>
@@ -2247,7 +2247,7 @@
         <v>53</v>
       </c>
       <c r="N23">
-        <v>0.10441755323655447</v>
+        <v>0.10441755323655473</v>
       </c>
       <c r="O23" t="s">
         <v>54</v>
@@ -2261,7 +2261,7 @@
         <v>55</v>
       </c>
       <c r="D24">
-        <v>9.8347614830307267E-2</v>
+        <v>9.8347614830307531E-2</v>
       </c>
       <c r="E24" t="s">
         <v>54</v>
@@ -2273,7 +2273,7 @@
         <v>55</v>
       </c>
       <c r="I24">
-        <v>0.13720834116746886</v>
+        <v>0.13720834116746858</v>
       </c>
       <c r="J24" t="s">
         <v>54</v>
@@ -2285,7 +2285,7 @@
         <v>55</v>
       </c>
       <c r="N24">
-        <v>0.1296343962763894</v>
+        <v>0.12963439627638973</v>
       </c>
       <c r="O24" t="s">
         <v>54</v>
@@ -2311,7 +2311,7 @@
         <v>56</v>
       </c>
       <c r="I25">
-        <v>8.7926739901540818E-2</v>
+        <v>8.7926739901540638E-2</v>
       </c>
       <c r="J25" t="s">
         <v>54</v>
@@ -2323,7 +2323,7 @@
         <v>56</v>
       </c>
       <c r="N25">
-        <v>8.2040141999297572E-2</v>
+        <v>8.204014199929778E-2</v>
       </c>
       <c r="O25" t="s">
         <v>54</v>
@@ -2337,7 +2337,7 @@
         <v>57</v>
       </c>
       <c r="D26">
-        <v>1.584151789848012E-2</v>
+        <v>1.5841517898480161E-2</v>
       </c>
       <c r="E26" t="s">
         <v>54</v>
@@ -2349,7 +2349,7 @@
         <v>57</v>
       </c>
       <c r="I26">
-        <v>9.1314408325792282E-2</v>
+        <v>9.1314408325792101E-2</v>
       </c>
       <c r="J26" t="s">
         <v>54</v>
@@ -2361,7 +2361,7 @@
         <v>57</v>
       </c>
       <c r="N26">
-        <v>8.9625256795971192E-2</v>
+        <v>8.9625256795971414E-2</v>
       </c>
       <c r="O26" t="s">
         <v>54</v>
@@ -2375,7 +2375,7 @@
         <v>58</v>
       </c>
       <c r="D27">
-        <v>0.33906617873957257</v>
+        <v>0.33906617873957345</v>
       </c>
       <c r="E27" t="s">
         <v>54</v>
@@ -2387,7 +2387,7 @@
         <v>58</v>
       </c>
       <c r="I27">
-        <v>0.10051823100450309</v>
+        <v>0.1005182310045029</v>
       </c>
       <c r="J27" t="s">
         <v>54</v>
@@ -2399,7 +2399,7 @@
         <v>58</v>
       </c>
       <c r="N27">
-        <v>9.6551166886462036E-2</v>
+        <v>9.6551166886462286E-2</v>
       </c>
       <c r="O27" t="s">
         <v>54</v>
@@ -2413,7 +2413,7 @@
         <v>59</v>
       </c>
       <c r="D28">
-        <v>2.6946764071012269E-3</v>
+        <v>2.6946764071012342E-3</v>
       </c>
       <c r="E28" t="s">
         <v>54</v>
@@ -2425,7 +2425,7 @@
         <v>59</v>
       </c>
       <c r="I28">
-        <v>7.224006395474003E-2</v>
+        <v>7.2240063954739892E-2</v>
       </c>
       <c r="J28" t="s">
         <v>54</v>
@@ -2437,7 +2437,7 @@
         <v>59</v>
       </c>
       <c r="N28">
-        <v>6.7194169763368186E-2</v>
+        <v>6.7194169763368353E-2</v>
       </c>
       <c r="O28" t="s">
         <v>54</v>
@@ -2451,7 +2451,7 @@
         <v>60</v>
       </c>
       <c r="D29">
-        <v>2.3312287070074503E-2</v>
+        <v>2.3312287070074565E-2</v>
       </c>
       <c r="E29" t="s">
         <v>54</v>
@@ -2463,7 +2463,7 @@
         <v>60</v>
       </c>
       <c r="I29">
-        <v>4.770202486975627E-2</v>
+        <v>4.7702024869756172E-2</v>
       </c>
       <c r="J29" t="s">
         <v>54</v>
@@ -2475,7 +2475,7 @@
         <v>60</v>
       </c>
       <c r="N29">
-        <v>5.6874566424566717E-2</v>
+        <v>5.6874566424566862E-2</v>
       </c>
       <c r="O29" t="s">
         <v>54</v>
@@ -2489,7 +2489,7 @@
         <v>61</v>
       </c>
       <c r="D30">
-        <v>0.34963305659180627</v>
+        <v>0.34963305659180721</v>
       </c>
       <c r="E30" t="s">
         <v>54</v>
@@ -2501,7 +2501,7 @@
         <v>61</v>
       </c>
       <c r="I30">
-        <v>5.3442969848545331E-2</v>
+        <v>5.3442969848545227E-2</v>
       </c>
       <c r="J30" t="s">
         <v>54</v>
@@ -2513,7 +2513,7 @@
         <v>61</v>
       </c>
       <c r="N30">
-        <v>6.7537927631627859E-2</v>
+        <v>6.7537927631628025E-2</v>
       </c>
       <c r="O30" t="s">
         <v>54</v>
@@ -2527,7 +2527,7 @@
         <v>62</v>
       </c>
       <c r="D31">
-        <v>7.0609718014996428E-3</v>
+        <v>7.0609718014996619E-3</v>
       </c>
       <c r="E31" t="s">
         <v>54</v>
@@ -2539,7 +2539,7 @@
         <v>62</v>
       </c>
       <c r="I31">
-        <v>3.8597402446914085E-2</v>
+        <v>3.8597402446914009E-2</v>
       </c>
       <c r="J31" t="s">
         <v>54</v>
@@ -2551,7 +2551,7 @@
         <v>62</v>
       </c>
       <c r="N31">
-        <v>4.3563909328004996E-2</v>
+        <v>4.3563909328005107E-2</v>
       </c>
       <c r="O31" t="s">
         <v>54</v>
@@ -2565,7 +2565,7 @@
         <v>63</v>
       </c>
       <c r="D32">
-        <v>3.5152030476355276E-3</v>
+        <v>3.5152030476355372E-3</v>
       </c>
       <c r="E32" t="s">
         <v>54</v>
@@ -2577,7 +2577,7 @@
         <v>63</v>
       </c>
       <c r="I32">
-        <v>8.7332692786988686E-2</v>
+        <v>8.7332692786988506E-2</v>
       </c>
       <c r="J32" t="s">
         <v>54</v>
@@ -2589,7 +2589,7 @@
         <v>63</v>
       </c>
       <c r="N32">
-        <v>8.6209586614654027E-2</v>
+        <v>8.6209586614654249E-2</v>
       </c>
       <c r="O32" t="s">
         <v>54</v>
@@ -2603,7 +2603,7 @@
         <v>64</v>
       </c>
       <c r="D33">
-        <v>0.16043471826457165</v>
+        <v>0.16043471826457206</v>
       </c>
       <c r="E33" t="s">
         <v>54</v>
@@ -2615,7 +2615,7 @@
         <v>64</v>
       </c>
       <c r="I33">
-        <v>9.8749025237946583E-2</v>
+        <v>9.8749025237946389E-2</v>
       </c>
       <c r="J33" t="s">
         <v>54</v>
@@ -2627,7 +2627,7 @@
         <v>64</v>
       </c>
       <c r="N33">
-        <v>0.10709840230405178</v>
+        <v>0.10709840230405206</v>
       </c>
       <c r="O33" t="s">
         <v>54</v>
@@ -2641,7 +2641,7 @@
         <v>65</v>
       </c>
       <c r="D34">
-        <v>8.5964554269332585E-5</v>
+        <v>8.5964554269332816E-5</v>
       </c>
       <c r="E34" t="s">
         <v>54</v>
@@ -2653,7 +2653,7 @@
         <v>65</v>
       </c>
       <c r="I34">
-        <v>7.0079822424107513E-2</v>
+        <v>7.0079822424107374E-2</v>
       </c>
       <c r="J34" t="s">
         <v>54</v>
@@ -2665,7 +2665,7 @@
         <v>65</v>
       </c>
       <c r="N34">
-        <v>6.9252922739049261E-2</v>
+        <v>6.9252922739049441E-2</v>
       </c>
       <c r="O34" t="s">
         <v>54</v>
@@ -2691,7 +2691,7 @@
         <v>53</v>
       </c>
       <c r="I35">
-        <v>0.10184522285948037</v>
+        <v>0.1018452228594799</v>
       </c>
       <c r="J35" t="s">
         <v>54</v>
@@ -2703,7 +2703,7 @@
         <v>53</v>
       </c>
       <c r="N35">
-        <v>9.4466736333631326E-2</v>
+        <v>9.4466736333631465E-2</v>
       </c>
       <c r="O35" t="s">
         <v>54</v>
@@ -2717,7 +2717,7 @@
         <v>55</v>
       </c>
       <c r="D36">
-        <v>8.8543349849711808E-2</v>
+        <v>8.854334984971203E-2</v>
       </c>
       <c r="E36" t="s">
         <v>54</v>
@@ -2729,7 +2729,7 @@
         <v>55</v>
       </c>
       <c r="I36">
-        <v>0.12889799278387748</v>
+        <v>0.12889799278387687</v>
       </c>
       <c r="J36" t="s">
         <v>54</v>
@@ -2741,7 +2741,7 @@
         <v>55</v>
       </c>
       <c r="N36">
-        <v>0.12377282528277489</v>
+        <v>0.12377282528277507</v>
       </c>
       <c r="O36" t="s">
         <v>54</v>
@@ -2767,7 +2767,7 @@
         <v>56</v>
       </c>
       <c r="I37">
-        <v>8.1117962651637246E-2</v>
+        <v>8.1117962651636871E-2</v>
       </c>
       <c r="J37" t="s">
         <v>54</v>
@@ -2779,7 +2779,7 @@
         <v>56</v>
       </c>
       <c r="N37">
-        <v>7.6240944181044074E-2</v>
+        <v>7.6240944181044185E-2</v>
       </c>
       <c r="O37" t="s">
         <v>54</v>
@@ -2793,7 +2793,7 @@
         <v>57</v>
       </c>
       <c r="D38">
-        <v>7.8362935653910407E-3</v>
+        <v>7.8362935653910597E-3</v>
       </c>
       <c r="E38" t="s">
         <v>54</v>
@@ -2805,7 +2805,7 @@
         <v>57</v>
       </c>
       <c r="I38">
-        <v>8.7122782633802381E-2</v>
+        <v>8.7122782633801979E-2</v>
       </c>
       <c r="J38" t="s">
         <v>54</v>
@@ -2817,7 +2817,7 @@
         <v>57</v>
       </c>
       <c r="N38">
-        <v>8.7049363323775927E-2</v>
+        <v>8.7049363323776052E-2</v>
       </c>
       <c r="O38" t="s">
         <v>54</v>
@@ -2831,7 +2831,7 @@
         <v>58</v>
       </c>
       <c r="D39">
-        <v>0.3339118524816686</v>
+        <v>0.33391185248166944</v>
       </c>
       <c r="E39" t="s">
         <v>54</v>
@@ -2843,7 +2843,7 @@
         <v>58</v>
       </c>
       <c r="I39">
-        <v>8.5743324066586052E-2</v>
+        <v>8.5743324066585649E-2</v>
       </c>
       <c r="J39" t="s">
         <v>54</v>
@@ -2855,7 +2855,7 @@
         <v>58</v>
       </c>
       <c r="N39">
-        <v>0.10340103332586482</v>
+        <v>0.10340103332586498</v>
       </c>
       <c r="O39" t="s">
         <v>54</v>
@@ -2869,7 +2869,7 @@
         <v>59</v>
       </c>
       <c r="D40">
-        <v>6.3679322044681097E-3</v>
+        <v>6.3679322044681253E-3</v>
       </c>
       <c r="E40" t="s">
         <v>54</v>
@@ -2881,7 +2881,7 @@
         <v>59</v>
       </c>
       <c r="I40">
-        <v>6.4629709387893503E-2</v>
+        <v>6.4629709387893197E-2</v>
       </c>
       <c r="J40" t="s">
         <v>54</v>
@@ -2893,7 +2893,7 @@
         <v>59</v>
       </c>
       <c r="N40">
-        <v>6.8676174292099726E-2</v>
+        <v>6.8676174292099823E-2</v>
       </c>
       <c r="O40" t="s">
         <v>54</v>
@@ -2907,7 +2907,7 @@
         <v>60</v>
       </c>
       <c r="D41">
-        <v>1.2782671251977391E-2</v>
+        <v>1.2782671251977422E-2</v>
       </c>
       <c r="E41" t="s">
         <v>54</v>
@@ -2919,7 +2919,7 @@
         <v>60</v>
       </c>
       <c r="I41">
-        <v>5.7519114846736621E-2</v>
+        <v>5.7519114846736351E-2</v>
       </c>
       <c r="J41" t="s">
         <v>54</v>
@@ -2931,7 +2931,7 @@
         <v>60</v>
       </c>
       <c r="N41">
-        <v>6.1288920276485706E-2</v>
+        <v>6.1288920276485796E-2</v>
       </c>
       <c r="O41" t="s">
         <v>54</v>
@@ -2945,7 +2945,7 @@
         <v>61</v>
       </c>
       <c r="D42">
-        <v>0.36270162738596284</v>
+        <v>0.36270162738596373</v>
       </c>
       <c r="E42" t="s">
         <v>54</v>
@@ -2957,7 +2957,7 @@
         <v>61</v>
       </c>
       <c r="I42">
-        <v>6.9247169654171103E-2</v>
+        <v>6.9247169654170784E-2</v>
       </c>
       <c r="J42" t="s">
         <v>54</v>
@@ -2969,7 +2969,7 @@
         <v>61</v>
       </c>
       <c r="N42">
-        <v>7.2910593155668418E-2</v>
+        <v>7.2910593155668529E-2</v>
       </c>
       <c r="O42" t="s">
         <v>54</v>
@@ -2983,7 +2983,7 @@
         <v>62</v>
       </c>
       <c r="D43">
-        <v>1.3203178133090047E-2</v>
+        <v>1.320317813309008E-2</v>
       </c>
       <c r="E43" t="s">
         <v>54</v>
@@ -2995,7 +2995,7 @@
         <v>62</v>
       </c>
       <c r="I43">
-        <v>4.2401860391636584E-2</v>
+        <v>4.240186039163639E-2</v>
       </c>
       <c r="J43" t="s">
         <v>54</v>
@@ -3007,7 +3007,7 @@
         <v>62</v>
       </c>
       <c r="N43">
-        <v>5.081653309163188E-2</v>
+        <v>5.0816533091631956E-2</v>
       </c>
       <c r="O43" t="s">
         <v>54</v>
@@ -3021,7 +3021,7 @@
         <v>63</v>
       </c>
       <c r="D44">
-        <v>1.2816650753870078E-3</v>
+        <v>1.2816650753870108E-3</v>
       </c>
       <c r="E44" t="s">
         <v>54</v>
@@ -3033,7 +3033,7 @@
         <v>63</v>
       </c>
       <c r="I44">
-        <v>9.2825045434777015E-2</v>
+        <v>9.2825045434776585E-2</v>
       </c>
       <c r="J44" t="s">
         <v>54</v>
@@ -3045,7 +3045,7 @@
         <v>63</v>
       </c>
       <c r="N44">
-        <v>8.5179506730593962E-2</v>
+        <v>8.5179506730594087E-2</v>
       </c>
       <c r="O44" t="s">
         <v>54</v>
@@ -3059,7 +3059,7 @@
         <v>64</v>
       </c>
       <c r="D45">
-        <v>0.17277667969030305</v>
+        <v>0.17277667969030347</v>
       </c>
       <c r="E45" t="s">
         <v>54</v>
@@ -3071,7 +3071,7 @@
         <v>64</v>
       </c>
       <c r="I45">
-        <v>0.11367885994751581</v>
+        <v>0.11367885994751528</v>
       </c>
       <c r="J45" t="s">
         <v>54</v>
@@ -3083,7 +3083,7 @@
         <v>64</v>
       </c>
       <c r="N45">
-        <v>0.10690624118644028</v>
+        <v>0.10690624118644043</v>
       </c>
       <c r="O45" t="s">
         <v>54</v>
@@ -3097,7 +3097,7 @@
         <v>65</v>
       </c>
       <c r="D46">
-        <v>5.9475036203763404E-4</v>
+        <v>5.9475036203763545E-4</v>
       </c>
       <c r="E46" t="s">
         <v>54</v>
@@ -3109,7 +3109,7 @@
         <v>65</v>
       </c>
       <c r="I46">
-        <v>7.4970955341890549E-2</v>
+        <v>7.4970955341890202E-2</v>
       </c>
       <c r="J46" t="s">
         <v>54</v>
@@ -3121,7 +3121,7 @@
         <v>65</v>
       </c>
       <c r="N46">
-        <v>6.9291128819987544E-2</v>
+        <v>6.9291128819987641E-2</v>
       </c>
       <c r="O46" t="s">
         <v>54</v>
@@ -3147,7 +3147,7 @@
         <v>53</v>
       </c>
       <c r="I47">
-        <v>0.10360867967416243</v>
+        <v>0.10360867967416251</v>
       </c>
       <c r="J47" t="s">
         <v>54</v>
@@ -3173,7 +3173,7 @@
         <v>55</v>
       </c>
       <c r="D48">
-        <v>0.11138635630551083</v>
+        <v>0.11138635630551093</v>
       </c>
       <c r="E48" t="s">
         <v>54</v>
@@ -3185,7 +3185,7 @@
         <v>55</v>
       </c>
       <c r="I48">
-        <v>0.13159358242077945</v>
+        <v>0.13159358242077956</v>
       </c>
       <c r="J48" t="s">
         <v>54</v>
@@ -3223,7 +3223,7 @@
         <v>56</v>
       </c>
       <c r="I49">
-        <v>8.4628168643463994E-2</v>
+        <v>8.4628168643464063E-2</v>
       </c>
       <c r="J49" t="s">
         <v>54</v>
@@ -3249,7 +3249,7 @@
         <v>57</v>
       </c>
       <c r="D50">
-        <v>7.946358310501337E-3</v>
+        <v>7.946358310501344E-3</v>
       </c>
       <c r="E50" t="s">
         <v>54</v>
@@ -3261,7 +3261,7 @@
         <v>57</v>
       </c>
       <c r="I50">
-        <v>8.6318877629566942E-2</v>
+        <v>8.6318877629567012E-2</v>
       </c>
       <c r="J50" t="s">
         <v>54</v>
@@ -3287,7 +3287,7 @@
         <v>58</v>
       </c>
       <c r="D51">
-        <v>0.30358552245091441</v>
+        <v>0.30358552245091469</v>
       </c>
       <c r="E51" t="s">
         <v>54</v>
@@ -3299,7 +3299,7 @@
         <v>58</v>
       </c>
       <c r="I51">
-        <v>8.997306480496628E-2</v>
+        <v>8.9973064804966349E-2</v>
       </c>
       <c r="J51" t="s">
         <v>54</v>
@@ -3325,7 +3325,7 @@
         <v>59</v>
       </c>
       <c r="D52">
-        <v>5.4802836553805188E-3</v>
+        <v>5.480283655380524E-3</v>
       </c>
       <c r="E52" t="s">
         <v>54</v>
@@ -3337,7 +3337,7 @@
         <v>59</v>
       </c>
       <c r="I52">
-        <v>6.6093018913556761E-2</v>
+        <v>6.6093018913556817E-2</v>
       </c>
       <c r="J52" t="s">
         <v>54</v>
@@ -3363,7 +3363,7 @@
         <v>60</v>
       </c>
       <c r="D53">
-        <v>1.331975844233891E-2</v>
+        <v>1.3319758442338922E-2</v>
       </c>
       <c r="E53" t="s">
         <v>54</v>
@@ -3375,7 +3375,7 @@
         <v>60</v>
       </c>
       <c r="I53">
-        <v>5.6735660505799181E-2</v>
+        <v>5.6735660505799222E-2</v>
       </c>
       <c r="J53" t="s">
         <v>54</v>
@@ -3401,7 +3401,7 @@
         <v>61</v>
       </c>
       <c r="D54">
-        <v>0.35672514918004056</v>
+        <v>0.35672514918004089</v>
       </c>
       <c r="E54" t="s">
         <v>54</v>
@@ -3413,7 +3413,7 @@
         <v>61</v>
       </c>
       <c r="I54">
-        <v>5.9085370426580949E-2</v>
+        <v>5.9085370426580998E-2</v>
       </c>
       <c r="J54" t="s">
         <v>54</v>
@@ -3439,7 +3439,7 @@
         <v>62</v>
       </c>
       <c r="D55">
-        <v>1.1490806393112476E-2</v>
+        <v>1.1490806393112486E-2</v>
       </c>
       <c r="E55" t="s">
         <v>54</v>
@@ -3451,7 +3451,7 @@
         <v>62</v>
       </c>
       <c r="I55">
-        <v>3.9955153307978025E-2</v>
+        <v>3.9955153307978053E-2</v>
       </c>
       <c r="J55" t="s">
         <v>54</v>
@@ -3477,7 +3477,7 @@
         <v>63</v>
       </c>
       <c r="D56">
-        <v>1.617332201459301E-3</v>
+        <v>1.6173322014593026E-3</v>
       </c>
       <c r="E56" t="s">
         <v>54</v>
@@ -3489,7 +3489,7 @@
         <v>63</v>
       </c>
       <c r="I56">
-        <v>9.4058262133539614E-2</v>
+        <v>9.4058262133539683E-2</v>
       </c>
       <c r="J56" t="s">
         <v>54</v>
@@ -3515,7 +3515,7 @@
         <v>64</v>
       </c>
       <c r="D57">
-        <v>0.18797581546035891</v>
+        <v>0.18797581546035907</v>
       </c>
       <c r="E57" t="s">
         <v>54</v>
@@ -3527,7 +3527,7 @@
         <v>64</v>
       </c>
       <c r="I57">
-        <v>0.11124126168993627</v>
+        <v>0.11124126168993635</v>
       </c>
       <c r="J57" t="s">
         <v>54</v>
@@ -3553,7 +3553,7 @@
         <v>65</v>
       </c>
       <c r="D58">
-        <v>4.7261760038191529E-4</v>
+        <v>4.7261760038191572E-4</v>
       </c>
       <c r="E58" t="s">
         <v>54</v>
@@ -3565,7 +3565,7 @@
         <v>65</v>
       </c>
       <c r="I58">
-        <v>7.670889984966929E-2</v>
+        <v>7.6708899849669346E-2</v>
       </c>
       <c r="J58" t="s">
         <v>54</v>
@@ -3629,7 +3629,7 @@
         <v>55</v>
       </c>
       <c r="D60">
-        <v>0.10760895809563159</v>
+        <v>0.10760895809563167</v>
       </c>
       <c r="E60" t="s">
         <v>54</v>
@@ -3705,7 +3705,7 @@
         <v>57</v>
       </c>
       <c r="D62">
-        <v>8.8298029730968543E-3</v>
+        <v>8.8298029730968612E-3</v>
       </c>
       <c r="E62" t="s">
         <v>54</v>
@@ -3743,7 +3743,7 @@
         <v>58</v>
       </c>
       <c r="D63">
-        <v>0.29796605061993309</v>
+        <v>0.29796605061993331</v>
       </c>
       <c r="E63" t="s">
         <v>54</v>
@@ -3781,7 +3781,7 @@
         <v>59</v>
       </c>
       <c r="D64">
-        <v>4.7303984856086872E-3</v>
+        <v>4.7303984856086907E-3</v>
       </c>
       <c r="E64" t="s">
         <v>54</v>
@@ -3819,7 +3819,7 @@
         <v>60</v>
       </c>
       <c r="D65">
-        <v>1.3927771217583741E-2</v>
+        <v>1.3927771217583752E-2</v>
       </c>
       <c r="E65" t="s">
         <v>54</v>
@@ -3857,7 +3857,7 @@
         <v>61</v>
       </c>
       <c r="D66">
-        <v>0.35438715693486916</v>
+        <v>0.35438715693486944</v>
       </c>
       <c r="E66" t="s">
         <v>54</v>
@@ -3895,7 +3895,7 @@
         <v>62</v>
       </c>
       <c r="D67">
-        <v>1.0206280519362721E-2</v>
+        <v>1.020628051936273E-2</v>
       </c>
       <c r="E67" t="s">
         <v>54</v>
@@ -3933,7 +3933,7 @@
         <v>63</v>
       </c>
       <c r="D68">
-        <v>1.9296336244798375E-3</v>
+        <v>1.929633624479839E-3</v>
       </c>
       <c r="E68" t="s">
         <v>54</v>
@@ -3971,7 +3971,7 @@
         <v>64</v>
       </c>
       <c r="D69">
-        <v>0.20005544931827585</v>
+        <v>0.20005544931827601</v>
       </c>
       <c r="E69" t="s">
         <v>54</v>
@@ -4009,7 +4009,7 @@
         <v>65</v>
       </c>
       <c r="D70">
-        <v>3.5849821115770624E-4</v>
+        <v>3.5849821115770651E-4</v>
       </c>
       <c r="E70" t="s">
         <v>54</v>
@@ -4059,7 +4059,7 @@
         <v>53</v>
       </c>
       <c r="I71">
-        <v>0.10550920225277827</v>
+        <v>0.10550920225277778</v>
       </c>
       <c r="J71" t="s">
         <v>54</v>
@@ -4071,7 +4071,7 @@
         <v>53</v>
       </c>
       <c r="N71">
-        <v>9.4653263361758277E-2</v>
+        <v>9.4653263361758527E-2</v>
       </c>
       <c r="O71" t="s">
         <v>54</v>
@@ -4085,7 +4085,7 @@
         <v>55</v>
       </c>
       <c r="D72">
-        <v>0.11540498450210401</v>
+        <v>0.11540498450210386</v>
       </c>
       <c r="E72" t="s">
         <v>54</v>
@@ -4097,7 +4097,7 @@
         <v>55</v>
       </c>
       <c r="I72">
-        <v>0.13624044631634541</v>
+        <v>0.13624044631634477</v>
       </c>
       <c r="J72" t="s">
         <v>54</v>
@@ -4109,7 +4109,7 @@
         <v>55</v>
       </c>
       <c r="N72">
-        <v>0.1225284577160347</v>
+        <v>0.12252845771603503</v>
       </c>
       <c r="O72" t="s">
         <v>54</v>
@@ -4135,7 +4135,7 @@
         <v>56</v>
       </c>
       <c r="I73">
-        <v>8.7966011165416316E-2</v>
+        <v>8.79660111654159E-2</v>
       </c>
       <c r="J73" t="s">
         <v>54</v>
@@ -4147,7 +4147,7 @@
         <v>56</v>
       </c>
       <c r="N73">
-        <v>7.4530905246973256E-2</v>
+        <v>7.453090524697345E-2</v>
       </c>
       <c r="O73" t="s">
         <v>54</v>
@@ -4161,7 +4161,7 @@
         <v>57</v>
       </c>
       <c r="D74">
-        <v>8.1384616158811859E-3</v>
+        <v>8.1384616158811755E-3</v>
       </c>
       <c r="E74" t="s">
         <v>54</v>
@@ -4173,7 +4173,7 @@
         <v>57</v>
       </c>
       <c r="I74">
-        <v>7.7802167073682219E-2</v>
+        <v>7.7802167073681858E-2</v>
       </c>
       <c r="J74" t="s">
         <v>54</v>
@@ -4185,7 +4185,7 @@
         <v>57</v>
       </c>
       <c r="N74">
-        <v>9.0922010355408908E-2</v>
+        <v>9.0922010355409144E-2</v>
       </c>
       <c r="O74" t="s">
         <v>54</v>
@@ -4199,7 +4199,7 @@
         <v>58</v>
       </c>
       <c r="D75">
-        <v>0.29573116515527348</v>
+        <v>0.29573116515527309</v>
       </c>
       <c r="E75" t="s">
         <v>54</v>
@@ -4211,7 +4211,7 @@
         <v>58</v>
       </c>
       <c r="I75">
-        <v>9.4800403182305717E-2</v>
+        <v>9.4800403182305273E-2</v>
       </c>
       <c r="J75" t="s">
         <v>54</v>
@@ -4223,7 +4223,7 @@
         <v>58</v>
       </c>
       <c r="N75">
-        <v>0.10697241966610174</v>
+        <v>0.10697241966610203</v>
       </c>
       <c r="O75" t="s">
         <v>54</v>
@@ -4237,7 +4237,7 @@
         <v>59</v>
       </c>
       <c r="D76">
-        <v>5.1197863695700094E-3</v>
+        <v>5.1197863695700025E-3</v>
       </c>
       <c r="E76" t="s">
         <v>54</v>
@@ -4249,7 +4249,7 @@
         <v>59</v>
       </c>
       <c r="I76">
-        <v>6.1423109786782032E-2</v>
+        <v>6.1423109786781747E-2</v>
       </c>
       <c r="J76" t="s">
         <v>54</v>
@@ -4261,7 +4261,7 @@
         <v>59</v>
       </c>
       <c r="N76">
-        <v>7.0682325778333235E-2</v>
+        <v>7.068232577833343E-2</v>
       </c>
       <c r="O76" t="s">
         <v>54</v>
@@ -4275,7 +4275,7 @@
         <v>60</v>
       </c>
       <c r="D77">
-        <v>1.3368087340455945E-2</v>
+        <v>1.3368087340455928E-2</v>
       </c>
       <c r="E77" t="s">
         <v>54</v>
@@ -4287,7 +4287,7 @@
         <v>60</v>
       </c>
       <c r="I77">
-        <v>5.2642492245260561E-2</v>
+        <v>5.2642492245260318E-2</v>
       </c>
       <c r="J77" t="s">
         <v>54</v>
@@ -4299,7 +4299,7 @@
         <v>60</v>
       </c>
       <c r="N77">
-        <v>6.2480353611197324E-2</v>
+        <v>6.2480353611197491E-2</v>
       </c>
       <c r="O77" t="s">
         <v>54</v>
@@ -4313,7 +4313,7 @@
         <v>61</v>
       </c>
       <c r="D78">
-        <v>0.35560217093760532</v>
+        <v>0.35560217093760482</v>
       </c>
       <c r="E78" t="s">
         <v>54</v>
@@ -4325,7 +4325,7 @@
         <v>61</v>
       </c>
       <c r="I78">
-        <v>5.919202961979917E-2</v>
+        <v>5.9192029619798893E-2</v>
       </c>
       <c r="J78" t="s">
         <v>54</v>
@@ -4337,7 +4337,7 @@
         <v>61</v>
       </c>
       <c r="N78">
-        <v>7.1904748750569472E-2</v>
+        <v>7.1904748750569666E-2</v>
       </c>
       <c r="O78" t="s">
         <v>54</v>
@@ -4351,7 +4351,7 @@
         <v>62</v>
       </c>
       <c r="D79">
-        <v>1.083876033283356E-2</v>
+        <v>1.0838760332833547E-2</v>
       </c>
       <c r="E79" t="s">
         <v>54</v>
@@ -4363,7 +4363,7 @@
         <v>62</v>
       </c>
       <c r="I79">
-        <v>3.725540920844498E-2</v>
+        <v>3.7255409208444806E-2</v>
       </c>
       <c r="J79" t="s">
         <v>54</v>
@@ -4375,7 +4375,7 @@
         <v>62</v>
       </c>
       <c r="N79">
-        <v>4.6280885921981388E-2</v>
+        <v>4.6280885921981513E-2</v>
       </c>
       <c r="O79" t="s">
         <v>54</v>
@@ -4389,7 +4389,7 @@
         <v>63</v>
       </c>
       <c r="D80">
-        <v>1.6182199375266867E-3</v>
+        <v>1.6182199375266845E-3</v>
       </c>
       <c r="E80" t="s">
         <v>54</v>
@@ -4401,7 +4401,7 @@
         <v>63</v>
       </c>
       <c r="I80">
-        <v>9.3488019642981701E-2</v>
+        <v>9.3488019642981271E-2</v>
       </c>
       <c r="J80" t="s">
         <v>54</v>
@@ -4413,7 +4413,7 @@
         <v>63</v>
       </c>
       <c r="N80">
-        <v>8.6060506200605014E-2</v>
+        <v>8.606050620060525E-2</v>
       </c>
       <c r="O80" t="s">
         <v>54</v>
@@ -4427,7 +4427,7 @@
         <v>64</v>
       </c>
       <c r="D81">
-        <v>0.19375049067920289</v>
+        <v>0.19375049067920264</v>
       </c>
       <c r="E81" t="s">
         <v>54</v>
@@ -4439,7 +4439,7 @@
         <v>64</v>
       </c>
       <c r="I81">
-        <v>0.11677158655610043</v>
+        <v>0.11677158655609989</v>
       </c>
       <c r="J81" t="s">
         <v>54</v>
@@ -4451,7 +4451,7 @@
         <v>64</v>
       </c>
       <c r="N81">
-        <v>0.10692569421629303</v>
+        <v>0.10692569421629332</v>
       </c>
       <c r="O81" t="s">
         <v>54</v>
@@ -4465,7 +4465,7 @@
         <v>65</v>
       </c>
       <c r="D82">
-        <v>4.2787312954827624E-4</v>
+        <v>4.2787312954827565E-4</v>
       </c>
       <c r="E82" t="s">
         <v>54</v>
@@ -4477,7 +4477,7 @@
         <v>65</v>
       </c>
       <c r="I82">
-        <v>7.6909122950107822E-2</v>
+        <v>7.6909122950107461E-2</v>
       </c>
       <c r="J82" t="s">
         <v>54</v>
@@ -4489,7 +4489,7 @@
         <v>65</v>
       </c>
       <c r="N82">
-        <v>6.6058429174740987E-2</v>
+        <v>6.6058429174741168E-2</v>
       </c>
       <c r="O82" t="s">
         <v>54</v>
@@ -4983,7 +4983,7 @@
         <v>53</v>
       </c>
       <c r="N95">
-        <v>9.6394837756669516E-2</v>
+        <v>9.6394837756669252E-2</v>
       </c>
       <c r="O95" t="s">
         <v>54</v>
@@ -5021,7 +5021,7 @@
         <v>55</v>
       </c>
       <c r="N96">
-        <v>0.12398996609727328</v>
+        <v>0.12398996609727295</v>
       </c>
       <c r="O96" t="s">
         <v>54</v>
@@ -5059,7 +5059,7 @@
         <v>56</v>
       </c>
       <c r="N97">
-        <v>7.5493463051599721E-2</v>
+        <v>7.5493463051599527E-2</v>
       </c>
       <c r="O97" t="s">
         <v>54</v>
@@ -5097,7 +5097,7 @@
         <v>57</v>
       </c>
       <c r="N98">
-        <v>9.0651671387978791E-2</v>
+        <v>9.0651671387978555E-2</v>
       </c>
       <c r="O98" t="s">
         <v>54</v>
@@ -5135,7 +5135,7 @@
         <v>58</v>
       </c>
       <c r="N99">
-        <v>0.10610469671630322</v>
+        <v>0.10610469671630295</v>
       </c>
       <c r="O99" t="s">
         <v>54</v>
@@ -5173,7 +5173,7 @@
         <v>59</v>
       </c>
       <c r="N100">
-        <v>7.0641888842209913E-2</v>
+        <v>7.0641888842209719E-2</v>
       </c>
       <c r="O100" t="s">
         <v>54</v>
@@ -5211,7 +5211,7 @@
         <v>60</v>
       </c>
       <c r="N101">
-        <v>6.0583011621085855E-2</v>
+        <v>6.0583011621085696E-2</v>
       </c>
       <c r="O101" t="s">
         <v>54</v>
@@ -5249,7 +5249,7 @@
         <v>61</v>
       </c>
       <c r="N102">
-        <v>7.2399173187371463E-2</v>
+        <v>7.2399173187371269E-2</v>
       </c>
       <c r="O102" t="s">
         <v>54</v>
@@ -5287,7 +5287,7 @@
         <v>62</v>
       </c>
       <c r="N103">
-        <v>4.3896737497909157E-2</v>
+        <v>4.3896737497909039E-2</v>
       </c>
       <c r="O103" t="s">
         <v>54</v>
@@ -5325,7 +5325,7 @@
         <v>63</v>
       </c>
       <c r="N104">
-        <v>8.5866886121659089E-2</v>
+        <v>8.5866886121658867E-2</v>
       </c>
       <c r="O104" t="s">
         <v>54</v>
@@ -5363,7 +5363,7 @@
         <v>64</v>
       </c>
       <c r="N105">
-        <v>0.10864287620579367</v>
+        <v>0.10864287620579338</v>
       </c>
       <c r="O105" t="s">
         <v>54</v>
@@ -5401,7 +5401,7 @@
         <v>65</v>
       </c>
       <c r="N106">
-        <v>6.5334791514148963E-2</v>
+        <v>6.5334791514148782E-2</v>
       </c>
       <c r="O106" t="s">
         <v>54</v>
@@ -5427,7 +5427,7 @@
         <v>53</v>
       </c>
       <c r="I107">
-        <v>0.11663700066651861</v>
+        <v>0.11663700066651846</v>
       </c>
       <c r="J107" t="s">
         <v>54</v>
@@ -5439,7 +5439,7 @@
         <v>53</v>
       </c>
       <c r="N107">
-        <v>9.7179472377289466E-2</v>
+        <v>9.7179472377289147E-2</v>
       </c>
       <c r="O107" t="s">
         <v>54</v>
@@ -5453,7 +5453,7 @@
         <v>55</v>
       </c>
       <c r="D108">
-        <v>8.5864111565030071E-2</v>
+        <v>8.5864111565030002E-2</v>
       </c>
       <c r="E108" t="s">
         <v>54</v>
@@ -5465,7 +5465,7 @@
         <v>55</v>
       </c>
       <c r="I108">
-        <v>0.1361766985966619</v>
+        <v>0.1361766985966617</v>
       </c>
       <c r="J108" t="s">
         <v>54</v>
@@ -5477,7 +5477,7 @@
         <v>55</v>
       </c>
       <c r="N108">
-        <v>0.12412054045252534</v>
+        <v>0.12412054045252492</v>
       </c>
       <c r="O108" t="s">
         <v>54</v>
@@ -5503,7 +5503,7 @@
         <v>56</v>
       </c>
       <c r="I109">
-        <v>8.8995405519363593E-2</v>
+        <v>8.8995405519363469E-2</v>
       </c>
       <c r="J109" t="s">
         <v>54</v>
@@ -5515,7 +5515,7 @@
         <v>56</v>
       </c>
       <c r="N109">
-        <v>7.5446572975437443E-2</v>
+        <v>7.5446572975437193E-2</v>
       </c>
       <c r="O109" t="s">
         <v>54</v>
@@ -5529,7 +5529,7 @@
         <v>57</v>
       </c>
       <c r="D110">
-        <v>1.2595345059638914E-2</v>
+        <v>1.2595345059638904E-2</v>
       </c>
       <c r="E110" t="s">
         <v>54</v>
@@ -5541,7 +5541,7 @@
         <v>57</v>
       </c>
       <c r="I110">
-        <v>8.9224205197277917E-2</v>
+        <v>8.9224205197277792E-2</v>
       </c>
       <c r="J110" t="s">
         <v>54</v>
@@ -5553,7 +5553,7 @@
         <v>57</v>
       </c>
       <c r="N110">
-        <v>9.0664784926800593E-2</v>
+        <v>9.0664784926800288E-2</v>
       </c>
       <c r="O110" t="s">
         <v>54</v>
@@ -5567,7 +5567,7 @@
         <v>58</v>
       </c>
       <c r="D111">
-        <v>0.35528482606980466</v>
+        <v>0.35528482606980433</v>
       </c>
       <c r="E111" t="s">
         <v>54</v>
@@ -5579,7 +5579,7 @@
         <v>58</v>
       </c>
       <c r="I111">
-        <v>9.3567454928639993E-2</v>
+        <v>9.3567454928639868E-2</v>
       </c>
       <c r="J111" t="s">
         <v>54</v>
@@ -5591,7 +5591,7 @@
         <v>58</v>
       </c>
       <c r="N111">
-        <v>0.10572458252298192</v>
+        <v>0.10572458252298157</v>
       </c>
       <c r="O111" t="s">
         <v>54</v>
@@ -5605,7 +5605,7 @@
         <v>59</v>
       </c>
       <c r="D112">
-        <v>3.863363321289193E-3</v>
+        <v>3.8633633212891896E-3</v>
       </c>
       <c r="E112" t="s">
         <v>54</v>
@@ -5617,7 +5617,7 @@
         <v>59</v>
       </c>
       <c r="I112">
-        <v>6.8214188243477844E-2</v>
+        <v>6.8214188243477747E-2</v>
       </c>
       <c r="J112" t="s">
         <v>54</v>
@@ -5629,7 +5629,7 @@
         <v>59</v>
       </c>
       <c r="N112">
-        <v>7.1538683927156746E-2</v>
+        <v>7.153868392715651E-2</v>
       </c>
       <c r="O112" t="s">
         <v>54</v>
@@ -5643,7 +5643,7 @@
         <v>60</v>
       </c>
       <c r="D113">
-        <v>1.9737473224077519E-2</v>
+        <v>1.9737473224077502E-2</v>
       </c>
       <c r="E113" t="s">
         <v>54</v>
@@ -5655,7 +5655,7 @@
         <v>60</v>
       </c>
       <c r="I113">
-        <v>4.8873214548184607E-2</v>
+        <v>4.8873214548184545E-2</v>
       </c>
       <c r="J113" t="s">
         <v>54</v>
@@ -5667,7 +5667,7 @@
         <v>60</v>
       </c>
       <c r="N113">
-        <v>5.9359165480432532E-2</v>
+        <v>5.9359165480432338E-2</v>
       </c>
       <c r="O113" t="s">
         <v>54</v>
@@ -5681,7 +5681,7 @@
         <v>61</v>
       </c>
       <c r="D114">
-        <v>0.34818323006086555</v>
+        <v>0.34818323006086521</v>
       </c>
       <c r="E114" t="s">
         <v>54</v>
@@ -5693,7 +5693,7 @@
         <v>61</v>
       </c>
       <c r="I114">
-        <v>5.8165955166169445E-2</v>
+        <v>5.8165955166169368E-2</v>
       </c>
       <c r="J114" t="s">
         <v>54</v>
@@ -5705,7 +5705,7 @@
         <v>61</v>
       </c>
       <c r="N114">
-        <v>7.1571647278896963E-2</v>
+        <v>7.1571647278896727E-2</v>
       </c>
       <c r="O114" t="s">
         <v>54</v>
@@ -5719,7 +5719,7 @@
         <v>62</v>
       </c>
       <c r="D115">
-        <v>9.094795142507394E-3</v>
+        <v>9.0947951425073854E-3</v>
       </c>
       <c r="E115" t="s">
         <v>54</v>
@@ -5731,7 +5731,7 @@
         <v>62</v>
       </c>
       <c r="I115">
-        <v>3.8130790282287733E-2</v>
+        <v>3.8130790282287684E-2</v>
       </c>
       <c r="J115" t="s">
         <v>54</v>
@@ -5743,7 +5743,7 @@
         <v>62</v>
       </c>
       <c r="N115">
-        <v>4.4746289518082613E-2</v>
+        <v>4.4746289518082467E-2</v>
       </c>
       <c r="O115" t="s">
         <v>54</v>
@@ -5757,7 +5757,7 @@
         <v>63</v>
       </c>
       <c r="D116">
-        <v>2.5097997690875862E-3</v>
+        <v>2.509799769087584E-3</v>
       </c>
       <c r="E116" t="s">
         <v>54</v>
@@ -5769,7 +5769,7 @@
         <v>63</v>
       </c>
       <c r="I116">
-        <v>8.8870989131419512E-2</v>
+        <v>8.8870989131419387E-2</v>
       </c>
       <c r="J116" t="s">
         <v>54</v>
@@ -5781,7 +5781,7 @@
         <v>63</v>
       </c>
       <c r="N116">
-        <v>8.4530420906013634E-2</v>
+        <v>8.4530420906013357E-2</v>
       </c>
       <c r="O116" t="s">
         <v>54</v>
@@ -5795,7 +5795,7 @@
         <v>64</v>
       </c>
       <c r="D117">
-        <v>0.16264806791195399</v>
+        <v>0.16264806791195385</v>
       </c>
       <c r="E117" t="s">
         <v>54</v>
@@ -5807,7 +5807,7 @@
         <v>64</v>
       </c>
       <c r="I117">
-        <v>0.10212396280896716</v>
+        <v>0.10212396280896702</v>
       </c>
       <c r="J117" t="s">
         <v>54</v>
@@ -5819,7 +5819,7 @@
         <v>64</v>
       </c>
       <c r="N117">
-        <v>0.10958867718958826</v>
+        <v>0.1095886771895879</v>
       </c>
       <c r="O117" t="s">
         <v>54</v>
@@ -5833,7 +5833,7 @@
         <v>65</v>
       </c>
       <c r="D118">
-        <v>2.1898787574592047E-4</v>
+        <v>2.1898787574592028E-4</v>
       </c>
       <c r="E118" t="s">
         <v>54</v>
@@ -5845,7 +5845,7 @@
         <v>65</v>
       </c>
       <c r="I118">
-        <v>7.1020134911032998E-2</v>
+        <v>7.1020134911032901E-2</v>
       </c>
       <c r="J118" t="s">
         <v>54</v>
@@ -5857,7 +5857,7 @@
         <v>65</v>
       </c>
       <c r="N118">
-        <v>6.5529162444797839E-2</v>
+        <v>6.5529162444797617E-2</v>
       </c>
       <c r="O118" t="s">
         <v>54</v>
@@ -5883,7 +5883,7 @@
         <v>53</v>
       </c>
       <c r="I119">
-        <v>0.10904158429480042</v>
+        <v>0.10904158429480039</v>
       </c>
       <c r="J119" t="s">
         <v>54</v>
@@ -5895,7 +5895,7 @@
         <v>53</v>
       </c>
       <c r="N119">
-        <v>9.9267641123149647E-2</v>
+        <v>9.9267641123149425E-2</v>
       </c>
       <c r="O119" t="s">
         <v>54</v>
@@ -5909,7 +5909,7 @@
         <v>55</v>
       </c>
       <c r="D120">
-        <v>0.11342614718300754</v>
+        <v>0.11342616691738447</v>
       </c>
       <c r="E120" t="s">
         <v>54</v>
@@ -5921,7 +5921,7 @@
         <v>55</v>
       </c>
       <c r="I120">
-        <v>0.14269415858926418</v>
+        <v>0.14269415858926415</v>
       </c>
       <c r="J120" t="s">
         <v>54</v>
@@ -5933,7 +5933,7 @@
         <v>55</v>
       </c>
       <c r="N120">
-        <v>0.12576893452988722</v>
+        <v>0.12576893452988694</v>
       </c>
       <c r="O120" t="s">
         <v>54</v>
@@ -5947,7 +5947,7 @@
         <v>56</v>
       </c>
       <c r="D121">
-        <v>1.7398434332650151E-7</v>
+        <v>0</v>
       </c>
       <c r="E121" t="s">
         <v>54</v>
@@ -5959,7 +5959,7 @@
         <v>56</v>
       </c>
       <c r="I121">
-        <v>8.8576660336305471E-2</v>
+        <v>8.8576660336305457E-2</v>
       </c>
       <c r="J121" t="s">
         <v>54</v>
@@ -5971,7 +5971,7 @@
         <v>56</v>
       </c>
       <c r="N121">
-        <v>7.8309357546654135E-2</v>
+        <v>7.8309357546653954E-2</v>
       </c>
       <c r="O121" t="s">
         <v>54</v>
@@ -5985,7 +5985,7 @@
         <v>57</v>
       </c>
       <c r="D122">
-        <v>7.0700605962896951E-3</v>
+        <v>7.0700618263697442E-3</v>
       </c>
       <c r="E122" t="s">
         <v>54</v>
@@ -5997,7 +5997,7 @@
         <v>57</v>
       </c>
       <c r="I122">
-        <v>7.7084091545317521E-2</v>
+        <v>7.7084091545317507E-2</v>
       </c>
       <c r="J122" t="s">
         <v>54</v>
@@ -6009,7 +6009,7 @@
         <v>57</v>
       </c>
       <c r="N122">
-        <v>9.0683286369398736E-2</v>
+        <v>9.0683286369398527E-2</v>
       </c>
       <c r="O122" t="s">
         <v>54</v>
@@ -6023,7 +6023,7 @@
         <v>58</v>
       </c>
       <c r="D123">
-        <v>0.30361918523211179</v>
+        <v>0.30361923805710489</v>
       </c>
       <c r="E123" t="s">
         <v>54</v>
@@ -6035,7 +6035,7 @@
         <v>58</v>
       </c>
       <c r="I123">
-        <v>8.8358512991240742E-2</v>
+        <v>8.8358512991240729E-2</v>
       </c>
       <c r="J123" t="s">
         <v>54</v>
@@ -6047,7 +6047,7 @@
         <v>58</v>
       </c>
       <c r="N123">
-        <v>0.10373489887533995</v>
+        <v>0.10373489887533971</v>
       </c>
       <c r="O123" t="s">
         <v>54</v>
@@ -6061,7 +6061,7 @@
         <v>59</v>
       </c>
       <c r="D124">
-        <v>6.1262474182497036E-3</v>
+        <v>6.1262484841210097E-3</v>
       </c>
       <c r="E124" t="s">
         <v>54</v>
@@ -6073,7 +6073,7 @@
         <v>59</v>
       </c>
       <c r="I124">
-        <v>6.1529538479701294E-2</v>
+        <v>6.152953847970128E-2</v>
       </c>
       <c r="J124" t="s">
         <v>54</v>
@@ -6085,7 +6085,7 @@
         <v>59</v>
       </c>
       <c r="N124">
-        <v>6.9594461993247037E-2</v>
+        <v>6.9594461993246884E-2</v>
       </c>
       <c r="O124" t="s">
         <v>54</v>
@@ -6099,7 +6099,7 @@
         <v>60</v>
       </c>
       <c r="D125">
-        <v>1.2209481458180509E-2</v>
+        <v>1.2209483582439465E-2</v>
       </c>
       <c r="E125" t="s">
         <v>54</v>
@@ -6111,7 +6111,7 @@
         <v>60</v>
       </c>
       <c r="I125">
-        <v>5.3487603098752598E-2</v>
+        <v>5.3487603098752584E-2</v>
       </c>
       <c r="J125" t="s">
         <v>54</v>
@@ -6123,7 +6123,7 @@
         <v>60</v>
       </c>
       <c r="N125">
-        <v>5.9214697759435615E-2</v>
+        <v>5.9214697759435483E-2</v>
       </c>
       <c r="O125" t="s">
         <v>54</v>
@@ -6137,7 +6137,7 @@
         <v>61</v>
       </c>
       <c r="D126">
-        <v>0.35600414316051288</v>
+        <v>0.35600420509966996</v>
       </c>
       <c r="E126" t="s">
         <v>54</v>
@@ -6149,7 +6149,7 @@
         <v>61</v>
       </c>
       <c r="I126">
-        <v>5.621875876888055E-2</v>
+        <v>5.6218758768880536E-2</v>
       </c>
       <c r="J126" t="s">
         <v>54</v>
@@ -6161,7 +6161,7 @@
         <v>61</v>
       </c>
       <c r="N126">
-        <v>7.1484397885433787E-2</v>
+        <v>7.1484397885433634E-2</v>
       </c>
       <c r="O126" t="s">
         <v>54</v>
@@ -6175,7 +6175,7 @@
         <v>62</v>
       </c>
       <c r="D127">
-        <v>1.2335002795008754E-2</v>
+        <v>1.2335004941106462E-2</v>
       </c>
       <c r="E127" t="s">
         <v>54</v>
@@ -6187,7 +6187,7 @@
         <v>62</v>
       </c>
       <c r="I127">
-        <v>3.5788980390782578E-2</v>
+        <v>3.5788980390782571E-2</v>
       </c>
       <c r="J127" t="s">
         <v>54</v>
@@ -6199,7 +6199,7 @@
         <v>62</v>
       </c>
       <c r="N127">
-        <v>4.3818701753445689E-2</v>
+        <v>4.3818701753445592E-2</v>
       </c>
       <c r="O127" t="s">
         <v>54</v>
@@ -6213,7 +6213,7 @@
         <v>63</v>
       </c>
       <c r="D128">
-        <v>1.3116480382326138E-3</v>
+        <v>1.3116482664388732E-3</v>
       </c>
       <c r="E128" t="s">
         <v>54</v>
@@ -6225,7 +6225,7 @@
         <v>63</v>
       </c>
       <c r="I128">
-        <v>9.7698626266245897E-2</v>
+        <v>9.7698626266245869E-2</v>
       </c>
       <c r="J128" t="s">
         <v>54</v>
@@ -6237,7 +6237,7 @@
         <v>63</v>
       </c>
       <c r="N128">
-        <v>8.4626825295831598E-2</v>
+        <v>8.4626825295831404E-2</v>
       </c>
       <c r="O128" t="s">
         <v>54</v>
@@ -6251,7 +6251,7 @@
         <v>64</v>
       </c>
       <c r="D129">
-        <v>0.18728764682049567</v>
+        <v>0.18728767940561919</v>
       </c>
       <c r="E129" t="s">
         <v>54</v>
@@ -6263,7 +6263,7 @@
         <v>64</v>
       </c>
       <c r="I129">
-        <v>0.11529587158910763</v>
+        <v>0.1152958715891076</v>
       </c>
       <c r="J129" t="s">
         <v>54</v>
@@ -6275,7 +6275,7 @@
         <v>64</v>
       </c>
       <c r="N129">
-        <v>0.10721679803687134</v>
+        <v>0.10721679803687111</v>
       </c>
       <c r="O129" t="s">
         <v>54</v>
@@ -6289,7 +6289,7 @@
         <v>65</v>
       </c>
       <c r="D130">
-        <v>6.1026331356961742E-4</v>
+        <v>6.1026341974589646E-4</v>
       </c>
       <c r="E130" t="s">
         <v>54</v>
@@ -6301,7 +6301,7 @@
         <v>65</v>
       </c>
       <c r="I130">
-        <v>7.4225613649601341E-2</v>
+        <v>7.4225613649601327E-2</v>
       </c>
       <c r="J130" t="s">
         <v>54</v>
@@ -6313,7 +6313,7 @@
         <v>65</v>
       </c>
       <c r="N130">
-        <v>6.6279998831307502E-2</v>
+        <v>6.6279998831307349E-2</v>
       </c>
       <c r="O130" t="s">
         <v>54</v>
@@ -6339,7 +6339,7 @@
         <v>53</v>
       </c>
       <c r="I131">
-        <v>0.11061959680870727</v>
+        <v>0.11061959680870724</v>
       </c>
       <c r="J131" t="s">
         <v>54</v>
@@ -6353,7 +6353,7 @@
         <v>55</v>
       </c>
       <c r="D132">
-        <v>8.5108947986660285E-2</v>
+        <v>8.5108947986660008E-2</v>
       </c>
       <c r="E132" t="s">
         <v>54</v>
@@ -6365,7 +6365,7 @@
         <v>55</v>
       </c>
       <c r="I132">
-        <v>0.13568223494034515</v>
+        <v>0.13568223494034512</v>
       </c>
       <c r="J132" t="s">
         <v>54</v>
@@ -6391,7 +6391,7 @@
         <v>56</v>
       </c>
       <c r="I133">
-        <v>8.6350183087020013E-2</v>
+        <v>8.6350183087019999E-2</v>
       </c>
       <c r="J133" t="s">
         <v>54</v>
@@ -6405,7 +6405,7 @@
         <v>57</v>
       </c>
       <c r="D134">
-        <v>1.0565518995855559E-2</v>
+        <v>1.0565518995855524E-2</v>
       </c>
       <c r="E134" t="s">
         <v>54</v>
@@ -6417,7 +6417,7 @@
         <v>57</v>
       </c>
       <c r="I134">
-        <v>8.6099784597888737E-2</v>
+        <v>8.6099784597888723E-2</v>
       </c>
       <c r="J134" t="s">
         <v>54</v>
@@ -6431,7 +6431,7 @@
         <v>58</v>
       </c>
       <c r="D135">
-        <v>0.35927151358380971</v>
+        <v>0.35927151358380849</v>
       </c>
       <c r="E135" t="s">
         <v>54</v>
@@ -6443,7 +6443,7 @@
         <v>58</v>
       </c>
       <c r="I135">
-        <v>9.1384255600792941E-2</v>
+        <v>9.1384255600792927E-2</v>
       </c>
       <c r="J135" t="s">
         <v>54</v>
@@ -6457,7 +6457,7 @@
         <v>59</v>
       </c>
       <c r="D136">
-        <v>4.8560448986575567E-3</v>
+        <v>4.8560448986575402E-3</v>
       </c>
       <c r="E136" t="s">
         <v>54</v>
@@ -6469,7 +6469,7 @@
         <v>59</v>
       </c>
       <c r="I136">
-        <v>6.5679828634954418E-2</v>
+        <v>6.5679828634954404E-2</v>
       </c>
       <c r="J136" t="s">
         <v>54</v>
@@ -6483,7 +6483,7 @@
         <v>60</v>
       </c>
       <c r="D137">
-        <v>1.6971249732627529E-2</v>
+        <v>1.6971249732627473E-2</v>
       </c>
       <c r="E137" t="s">
         <v>54</v>
@@ -6495,7 +6495,7 @@
         <v>60</v>
       </c>
       <c r="I137">
-        <v>5.0020408819282637E-2</v>
+        <v>5.0020408819282623E-2</v>
       </c>
       <c r="J137" t="s">
         <v>54</v>
@@ -6509,7 +6509,7 @@
         <v>61</v>
       </c>
       <c r="D138">
-        <v>0.33975337145757833</v>
+        <v>0.33975337145757722</v>
       </c>
       <c r="E138" t="s">
         <v>54</v>
@@ -6521,7 +6521,7 @@
         <v>61</v>
       </c>
       <c r="I138">
-        <v>6.5183968451317131E-2</v>
+        <v>6.5183968451317117E-2</v>
       </c>
       <c r="J138" t="s">
         <v>54</v>
@@ -6535,7 +6535,7 @@
         <v>62</v>
       </c>
       <c r="D139">
-        <v>1.0397642923827988E-2</v>
+        <v>1.0397642923827954E-2</v>
       </c>
       <c r="E139" t="s">
         <v>54</v>
@@ -6547,7 +6547,7 @@
         <v>62</v>
       </c>
       <c r="I139">
-        <v>4.0636904814461812E-2</v>
+        <v>4.0636904814461805E-2</v>
       </c>
       <c r="J139" t="s">
         <v>54</v>
@@ -6561,7 +6561,7 @@
         <v>63</v>
       </c>
       <c r="D140">
-        <v>2.1866088698228223E-3</v>
+        <v>2.1866088698228149E-3</v>
       </c>
       <c r="E140" t="s">
         <v>54</v>
@@ -6573,7 +6573,7 @@
         <v>63</v>
       </c>
       <c r="I140">
-        <v>8.8740732522584881E-2</v>
+        <v>8.8740732522584867E-2</v>
       </c>
       <c r="J140" t="s">
         <v>54</v>
@@ -6587,7 +6587,7 @@
         <v>64</v>
       </c>
       <c r="D141">
-        <v>0.17055546422989692</v>
+        <v>0.17055546422989637</v>
       </c>
       <c r="E141" t="s">
         <v>54</v>
@@ -6599,7 +6599,7 @@
         <v>64</v>
       </c>
       <c r="I141">
-        <v>0.10653785075652361</v>
+        <v>0.10653785075652358</v>
       </c>
       <c r="J141" t="s">
         <v>54</v>
@@ -6613,7 +6613,7 @@
         <v>65</v>
       </c>
       <c r="D142">
-        <v>3.33637321266626E-4</v>
+        <v>3.3363732126662492E-4</v>
       </c>
       <c r="E142" t="s">
         <v>54</v>
@@ -6625,7 +6625,7 @@
         <v>65</v>
       </c>
       <c r="I142">
-        <v>7.3064250966121694E-2</v>
+        <v>7.306425096612168E-2</v>
       </c>
       <c r="J142" t="s">
         <v>54</v>
@@ -6651,7 +6651,7 @@
         <v>53</v>
       </c>
       <c r="I143">
-        <v>0.11706686262419337</v>
+        <v>0.11706686262419319</v>
       </c>
       <c r="J143" t="s">
         <v>54</v>
@@ -6665,7 +6665,7 @@
         <v>55</v>
       </c>
       <c r="D144">
-        <v>9.6027294560829618E-2</v>
+        <v>9.6027294560829687E-2</v>
       </c>
       <c r="E144" t="s">
         <v>54</v>
@@ -6677,7 +6677,7 @@
         <v>55</v>
       </c>
       <c r="I144">
-        <v>0.13754614677977722</v>
+        <v>0.137546146779777</v>
       </c>
       <c r="J144" t="s">
         <v>54</v>
@@ -6703,7 +6703,7 @@
         <v>56</v>
       </c>
       <c r="I145">
-        <v>8.9795550341659369E-2</v>
+        <v>8.979555034165923E-2</v>
       </c>
       <c r="J145" t="s">
         <v>54</v>
@@ -6717,7 +6717,7 @@
         <v>57</v>
       </c>
       <c r="D146">
-        <v>1.3823359672206395E-2</v>
+        <v>1.3823359672206404E-2</v>
       </c>
       <c r="E146" t="s">
         <v>54</v>
@@ -6729,7 +6729,7 @@
         <v>57</v>
       </c>
       <c r="I146">
-        <v>9.2421865157536462E-2</v>
+        <v>9.2421865157536323E-2</v>
       </c>
       <c r="J146" t="s">
         <v>54</v>
@@ -6743,7 +6743,7 @@
         <v>58</v>
       </c>
       <c r="D147">
-        <v>0.32855386435382411</v>
+        <v>0.32855386435382433</v>
       </c>
       <c r="E147" t="s">
         <v>54</v>
@@ -6755,7 +6755,7 @@
         <v>58</v>
       </c>
       <c r="I147">
-        <v>9.9876850877049159E-2</v>
+        <v>9.9876850877049006E-2</v>
       </c>
       <c r="J147" t="s">
         <v>54</v>
@@ -6769,7 +6769,7 @@
         <v>59</v>
       </c>
       <c r="D148">
-        <v>3.1695762312463978E-3</v>
+        <v>3.1695762312464E-3</v>
       </c>
       <c r="E148" t="s">
         <v>54</v>
@@ -6781,7 +6781,7 @@
         <v>59</v>
       </c>
       <c r="I148">
-        <v>7.1895226680303875E-2</v>
+        <v>7.1895226680303764E-2</v>
       </c>
       <c r="J148" t="s">
         <v>54</v>
@@ -6795,7 +6795,7 @@
         <v>60</v>
       </c>
       <c r="D149">
-        <v>2.1472998036898835E-2</v>
+        <v>2.1472998036898849E-2</v>
       </c>
       <c r="E149" t="s">
         <v>54</v>
@@ -6807,7 +6807,7 @@
         <v>60</v>
       </c>
       <c r="I149">
-        <v>4.7468595388655617E-2</v>
+        <v>4.7468595388655541E-2</v>
       </c>
       <c r="J149" t="s">
         <v>54</v>
@@ -6821,7 +6821,7 @@
         <v>61</v>
       </c>
       <c r="D150">
-        <v>0.35917101542136964</v>
+        <v>0.35917101542136987</v>
       </c>
       <c r="E150" t="s">
         <v>54</v>
@@ -6833,7 +6833,7 @@
         <v>61</v>
       </c>
       <c r="I150">
-        <v>5.2585689392413523E-2</v>
+        <v>5.258568939241344E-2</v>
       </c>
       <c r="J150" t="s">
         <v>54</v>
@@ -6847,7 +6847,7 @@
         <v>62</v>
       </c>
       <c r="D151">
-        <v>7.8296793779152087E-3</v>
+        <v>7.8296793779152139E-3</v>
       </c>
       <c r="E151" t="s">
         <v>54</v>
@@ -6859,7 +6859,7 @@
         <v>62</v>
       </c>
       <c r="I151">
-        <v>3.9233559103067576E-2</v>
+        <v>3.9233559103067514E-2</v>
       </c>
       <c r="J151" t="s">
         <v>54</v>
@@ -6873,7 +6873,7 @@
         <v>63</v>
       </c>
       <c r="D152">
-        <v>3.0683284223914269E-3</v>
+        <v>3.0683284223914291E-3</v>
       </c>
       <c r="E152" t="s">
         <v>54</v>
@@ -6885,7 +6885,7 @@
         <v>63</v>
       </c>
       <c r="I152">
-        <v>8.6442104232027459E-2</v>
+        <v>8.644210423202732E-2</v>
       </c>
       <c r="J152" t="s">
         <v>54</v>
@@ -6899,7 +6899,7 @@
         <v>64</v>
       </c>
       <c r="D153">
-        <v>0.1667457407379106</v>
+        <v>0.16674574073791071</v>
       </c>
       <c r="E153" t="s">
         <v>54</v>
@@ -6911,7 +6911,7 @@
         <v>64</v>
       </c>
       <c r="I153">
-        <v>9.6193928888484229E-2</v>
+        <v>9.6193928888484076E-2</v>
       </c>
       <c r="J153" t="s">
         <v>54</v>
@@ -6925,7 +6925,7 @@
         <v>65</v>
       </c>
       <c r="D154">
-        <v>1.3814318540710647E-4</v>
+        <v>1.3814318540710655E-4</v>
       </c>
       <c r="E154" t="s">
         <v>54</v>
@@ -6937,7 +6937,7 @@
         <v>65</v>
       </c>
       <c r="I154">
-        <v>6.9473620534833774E-2</v>
+        <v>6.9473620534833663E-2</v>
       </c>
       <c r="J154" t="s">
         <v>54</v>
@@ -6963,7 +6963,7 @@
         <v>53</v>
       </c>
       <c r="I155">
-        <v>0.10774109433207457</v>
+        <v>0.10774109433207459</v>
       </c>
       <c r="J155" t="s">
         <v>54</v>
@@ -6977,7 +6977,7 @@
         <v>55</v>
       </c>
       <c r="D156">
-        <v>9.7347919308906489E-2</v>
+        <v>9.7347919308906544E-2</v>
       </c>
       <c r="E156" t="s">
         <v>54</v>
@@ -6989,7 +6989,7 @@
         <v>55</v>
       </c>
       <c r="I156">
-        <v>0.13522300241573157</v>
+        <v>0.1352230024157316</v>
       </c>
       <c r="J156" t="s">
         <v>54</v>
@@ -7015,7 +7015,7 @@
         <v>56</v>
       </c>
       <c r="I157">
-        <v>8.4262247630586082E-2</v>
+        <v>8.4262247630586096E-2</v>
       </c>
       <c r="J157" t="s">
         <v>54</v>
@@ -7029,7 +7029,7 @@
         <v>57</v>
       </c>
       <c r="D158">
-        <v>7.5004667604135914E-3</v>
+        <v>7.5004667604135957E-3</v>
       </c>
       <c r="E158" t="s">
         <v>54</v>
@@ -7041,7 +7041,7 @@
         <v>57</v>
       </c>
       <c r="I158">
-        <v>8.530722104707042E-2</v>
+        <v>8.5307221047070433E-2</v>
       </c>
       <c r="J158" t="s">
         <v>54</v>
@@ -7055,7 +7055,7 @@
         <v>58</v>
       </c>
       <c r="D159">
-        <v>0.32015034138842469</v>
+        <v>0.32015034138842485</v>
       </c>
       <c r="E159" t="s">
         <v>54</v>
@@ -7067,7 +7067,7 @@
         <v>58</v>
       </c>
       <c r="I159">
-        <v>8.214721891577699E-2</v>
+        <v>8.2147218915777004E-2</v>
       </c>
       <c r="J159" t="s">
         <v>54</v>
@@ -7081,7 +7081,7 @@
         <v>59</v>
       </c>
       <c r="D160">
-        <v>6.3726744288001942E-3</v>
+        <v>6.3726744288001977E-3</v>
       </c>
       <c r="E160" t="s">
         <v>54</v>
@@ -7093,7 +7093,7 @@
         <v>59</v>
       </c>
       <c r="I160">
-        <v>6.5265332156333067E-2</v>
+        <v>6.5265332156333081E-2</v>
       </c>
       <c r="J160" t="s">
         <v>54</v>
@@ -7107,7 +7107,7 @@
         <v>60</v>
       </c>
       <c r="D161">
-        <v>1.248186884661839E-2</v>
+        <v>1.2481868846618397E-2</v>
       </c>
       <c r="E161" t="s">
         <v>54</v>
@@ -7119,7 +7119,7 @@
         <v>60</v>
       </c>
       <c r="I161">
-        <v>5.7087854628301661E-2</v>
+        <v>5.7087854628301668E-2</v>
       </c>
       <c r="J161" t="s">
         <v>54</v>
@@ -7133,7 +7133,7 @@
         <v>61</v>
       </c>
       <c r="D162">
-        <v>0.3623655774169986</v>
+        <v>0.36236557741699882</v>
       </c>
       <c r="E162" t="s">
         <v>54</v>
@@ -7145,7 +7145,7 @@
         <v>61</v>
       </c>
       <c r="I162">
-        <v>6.1028939356306343E-2</v>
+        <v>6.102893935630635E-2</v>
       </c>
       <c r="J162" t="s">
         <v>54</v>
@@ -7159,7 +7159,7 @@
         <v>62</v>
       </c>
       <c r="D163">
-        <v>1.279987121400036E-2</v>
+        <v>1.2799871214000367E-2</v>
       </c>
       <c r="E163" t="s">
         <v>54</v>
@@ -7171,7 +7171,7 @@
         <v>62</v>
       </c>
       <c r="I163">
-        <v>4.1720483941838693E-2</v>
+        <v>4.17204839418387E-2</v>
       </c>
       <c r="J163" t="s">
         <v>54</v>
@@ -7185,7 +7185,7 @@
         <v>63</v>
       </c>
       <c r="D164">
-        <v>1.2807516889432008E-3</v>
+        <v>1.2807516889432014E-3</v>
       </c>
       <c r="E164" t="s">
         <v>54</v>
@@ -7197,7 +7197,7 @@
         <v>63</v>
       </c>
       <c r="I164">
-        <v>9.550239053725687E-2</v>
+        <v>9.5502390537256884E-2</v>
       </c>
       <c r="J164" t="s">
         <v>54</v>
@@ -7211,7 +7211,7 @@
         <v>64</v>
       </c>
       <c r="D165">
-        <v>0.17906959355627725</v>
+        <v>0.17906959355627736</v>
       </c>
       <c r="E165" t="s">
         <v>54</v>
@@ -7223,7 +7223,7 @@
         <v>64</v>
       </c>
       <c r="I165">
-        <v>0.10964754699284877</v>
+        <v>0.10964754699284879</v>
       </c>
       <c r="J165" t="s">
         <v>54</v>
@@ -7237,7 +7237,7 @@
         <v>65</v>
       </c>
       <c r="D166">
-        <v>6.3093539061667388E-4</v>
+        <v>6.3093539061667421E-4</v>
       </c>
       <c r="E166" t="s">
         <v>54</v>
@@ -7249,7 +7249,7 @@
         <v>65</v>
       </c>
       <c r="I166">
-        <v>7.5066668045874835E-2</v>
+        <v>7.5066668045874849E-2</v>
       </c>
       <c r="J166" t="s">
         <v>54</v>
@@ -7289,7 +7289,7 @@
         <v>55</v>
       </c>
       <c r="D168">
-        <v>8.3854723620839733E-2</v>
+        <v>8.3854723620839858E-2</v>
       </c>
       <c r="E168" t="s">
         <v>54</v>
@@ -7341,7 +7341,7 @@
         <v>57</v>
       </c>
       <c r="D170">
-        <v>7.5534212797875224E-3</v>
+        <v>7.5534212797875346E-3</v>
       </c>
       <c r="E170" t="s">
         <v>54</v>
@@ -7367,7 +7367,7 @@
         <v>58</v>
       </c>
       <c r="D171">
-        <v>0.34504640218879568</v>
+        <v>0.34504640218879623</v>
       </c>
       <c r="E171" t="s">
         <v>54</v>
@@ -7393,7 +7393,7 @@
         <v>59</v>
       </c>
       <c r="D172">
-        <v>6.9864323211573749E-3</v>
+        <v>6.9864323211573862E-3</v>
       </c>
       <c r="E172" t="s">
         <v>54</v>
@@ -7419,7 +7419,7 @@
         <v>60</v>
       </c>
       <c r="D173">
-        <v>1.2719705442364055E-2</v>
+        <v>1.2719705442364074E-2</v>
       </c>
       <c r="E173" t="s">
         <v>54</v>
@@ -7445,7 +7445,7 @@
         <v>61</v>
       </c>
       <c r="D174">
-        <v>0.35643549436844796</v>
+        <v>0.35643549436844851</v>
       </c>
       <c r="E174" t="s">
         <v>54</v>
@@ -7471,7 +7471,7 @@
         <v>62</v>
       </c>
       <c r="D175">
-        <v>1.3322968200966167E-2</v>
+        <v>1.3322968200966187E-2</v>
       </c>
       <c r="E175" t="s">
         <v>54</v>
@@ -7497,7 +7497,7 @@
         <v>63</v>
       </c>
       <c r="D176">
-        <v>1.2947091293127411E-3</v>
+        <v>1.294709129312743E-3</v>
       </c>
       <c r="E176" t="s">
         <v>54</v>
@@ -7523,7 +7523,7 @@
         <v>64</v>
       </c>
       <c r="D177">
-        <v>0.17217019965591371</v>
+        <v>0.17217019965591399</v>
       </c>
       <c r="E177" t="s">
         <v>54</v>
@@ -7549,7 +7549,7 @@
         <v>65</v>
       </c>
       <c r="D178">
-        <v>6.1594379241353267E-4</v>
+        <v>6.1594379241353364E-4</v>
       </c>
       <c r="E178" t="s">
         <v>54</v>
@@ -7575,7 +7575,7 @@
         <v>53</v>
       </c>
       <c r="D179">
-        <v>2.1217180041074595E-5</v>
+        <v>2.1217180041074629E-5</v>
       </c>
       <c r="E179" t="s">
         <v>54</v>
@@ -7587,7 +7587,7 @@
         <v>53</v>
       </c>
       <c r="I179">
-        <v>0.11910599565626406</v>
+        <v>0.11910599565626401</v>
       </c>
       <c r="J179" t="s">
         <v>54</v>
@@ -7601,7 +7601,7 @@
         <v>55</v>
       </c>
       <c r="D180">
-        <v>0.12916849545533177</v>
+        <v>0.12916849545533199</v>
       </c>
       <c r="E180" t="s">
         <v>54</v>
@@ -7613,7 +7613,7 @@
         <v>55</v>
       </c>
       <c r="I180">
-        <v>0.14428084553742915</v>
+        <v>0.14428084553742909</v>
       </c>
       <c r="J180" t="s">
         <v>54</v>
@@ -7639,7 +7639,7 @@
         <v>56</v>
       </c>
       <c r="I181">
-        <v>9.0762579281075992E-2</v>
+        <v>9.076257928107595E-2</v>
       </c>
       <c r="J181" t="s">
         <v>54</v>
@@ -7653,7 +7653,7 @@
         <v>57</v>
       </c>
       <c r="D182">
-        <v>1.2047068617370879E-2</v>
+        <v>1.20470686173709E-2</v>
       </c>
       <c r="E182" t="s">
         <v>54</v>
@@ -7665,7 +7665,7 @@
         <v>57</v>
       </c>
       <c r="I182">
-        <v>8.2766168159869119E-2</v>
+        <v>8.2766168159869077E-2</v>
       </c>
       <c r="J182" t="s">
         <v>54</v>
@@ -7679,7 +7679,7 @@
         <v>58</v>
       </c>
       <c r="D183">
-        <v>0.29627572480759085</v>
+        <v>0.29627572480759135</v>
       </c>
       <c r="E183" t="s">
         <v>54</v>
@@ -7691,7 +7691,7 @@
         <v>58</v>
       </c>
       <c r="I183">
-        <v>0.10124273129943859</v>
+        <v>0.10124273129943855</v>
       </c>
       <c r="J183" t="s">
         <v>54</v>
@@ -7705,7 +7705,7 @@
         <v>59</v>
       </c>
       <c r="D184">
-        <v>2.7184892626581246E-3</v>
+        <v>2.7184892626581289E-3</v>
       </c>
       <c r="E184" t="s">
         <v>54</v>
@@ -7717,7 +7717,7 @@
         <v>59</v>
       </c>
       <c r="I184">
-        <v>6.2323751813127631E-2</v>
+        <v>6.2323751813127604E-2</v>
       </c>
       <c r="J184" t="s">
         <v>54</v>
@@ -7731,7 +7731,7 @@
         <v>60</v>
       </c>
       <c r="D185">
-        <v>1.7878716481463653E-2</v>
+        <v>1.7878716481463684E-2</v>
       </c>
       <c r="E185" t="s">
         <v>54</v>
@@ -7743,7 +7743,7 @@
         <v>60</v>
       </c>
       <c r="I185">
-        <v>4.0007363420798324E-2</v>
+        <v>4.0007363420798303E-2</v>
       </c>
       <c r="J185" t="s">
         <v>54</v>
@@ -7757,7 +7757,7 @@
         <v>61</v>
       </c>
       <c r="D186">
-        <v>0.33575659229617016</v>
+        <v>0.33575659229617072</v>
       </c>
       <c r="E186" t="s">
         <v>54</v>
@@ -7769,7 +7769,7 @@
         <v>61</v>
       </c>
       <c r="I186">
-        <v>5.1428700972038437E-2</v>
+        <v>5.1428700972038416E-2</v>
       </c>
       <c r="J186" t="s">
         <v>54</v>
@@ -7783,7 +7783,7 @@
         <v>62</v>
       </c>
       <c r="D187">
-        <v>6.6001562289884292E-3</v>
+        <v>6.6001562289884404E-3</v>
       </c>
       <c r="E187" t="s">
         <v>54</v>
@@ -7795,7 +7795,7 @@
         <v>62</v>
       </c>
       <c r="I187">
-        <v>3.3304930069673895E-2</v>
+        <v>3.3304930069673881E-2</v>
       </c>
       <c r="J187" t="s">
         <v>54</v>
@@ -7809,7 +7809,7 @@
         <v>63</v>
       </c>
       <c r="D188">
-        <v>3.7308819080437909E-3</v>
+        <v>3.730881908043797E-3</v>
       </c>
       <c r="E188" t="s">
         <v>54</v>
@@ -7821,7 +7821,7 @@
         <v>63</v>
       </c>
       <c r="I188">
-        <v>8.7610954079918438E-2</v>
+        <v>8.7610954079918396E-2</v>
       </c>
       <c r="J188" t="s">
         <v>54</v>
@@ -7835,7 +7835,7 @@
         <v>64</v>
       </c>
       <c r="D189">
-        <v>0.19566323850884837</v>
+        <v>0.1956632385088487</v>
       </c>
       <c r="E189" t="s">
         <v>54</v>
@@ -7847,7 +7847,7 @@
         <v>64</v>
       </c>
       <c r="I189">
-        <v>0.11199564077722034</v>
+        <v>0.11199564077722028</v>
       </c>
       <c r="J189" t="s">
         <v>54</v>
@@ -7861,7 +7861,7 @@
         <v>65</v>
       </c>
       <c r="D190">
-        <v>1.3941925349116515E-4</v>
+        <v>1.394192534911654E-4</v>
       </c>
       <c r="E190" t="s">
         <v>54</v>
@@ -7873,7 +7873,7 @@
         <v>65</v>
       </c>
       <c r="I190">
-        <v>7.5170338933146424E-2</v>
+        <v>7.5170338933146397E-2</v>
       </c>
       <c r="J190" t="s">
         <v>54</v>
@@ -7887,7 +7887,7 @@
         <v>53</v>
       </c>
       <c r="D191">
-        <v>8.99059907758285E-8</v>
+        <v>0</v>
       </c>
       <c r="E191" t="s">
         <v>54</v>
@@ -7899,7 +7899,7 @@
         <v>53</v>
       </c>
       <c r="I191">
-        <v>0.1132984478589876</v>
+        <v>0.11329844785898699</v>
       </c>
       <c r="J191" t="s">
         <v>54</v>
@@ -7913,7 +7913,7 @@
         <v>55</v>
       </c>
       <c r="D192">
-        <v>9.1369981999621985E-2</v>
+        <v>9.1369990214331578E-2</v>
       </c>
       <c r="E192" t="s">
         <v>54</v>
@@ -7925,7 +7925,7 @@
         <v>55</v>
       </c>
       <c r="I192">
-        <v>0.13330159782039427</v>
+        <v>0.13330159782039355</v>
       </c>
       <c r="J192" t="s">
         <v>54</v>
@@ -7951,7 +7951,7 @@
         <v>56</v>
       </c>
       <c r="I193">
-        <v>8.8124836603834855E-2</v>
+        <v>8.8124836603834383E-2</v>
       </c>
       <c r="J193" t="s">
         <v>54</v>
@@ -7965,7 +7965,7 @@
         <v>57</v>
       </c>
       <c r="D194">
-        <v>1.5843281301596002E-2</v>
+        <v>1.584328272600205E-2</v>
       </c>
       <c r="E194" t="s">
         <v>54</v>
@@ -7977,7 +7977,7 @@
         <v>57</v>
       </c>
       <c r="I194">
-        <v>9.2674991731315118E-2</v>
+        <v>9.2674991731314618E-2</v>
       </c>
       <c r="J194" t="s">
         <v>54</v>
@@ -7991,7 +7991,7 @@
         <v>58</v>
       </c>
       <c r="D195">
-        <v>0.35892826689682517</v>
+        <v>0.35892829916662988</v>
       </c>
       <c r="E195" t="s">
         <v>54</v>
@@ -8003,7 +8003,7 @@
         <v>58</v>
       </c>
       <c r="I195">
-        <v>9.5047139274509349E-2</v>
+        <v>9.5047139274508849E-2</v>
       </c>
       <c r="J195" t="s">
         <v>54</v>
@@ -8017,7 +8017,7 @@
         <v>59</v>
       </c>
       <c r="D196">
-        <v>3.0285640115364529E-3</v>
+        <v>3.0285642838225285E-3</v>
       </c>
       <c r="E196" t="s">
         <v>54</v>
@@ -8029,7 +8029,7 @@
         <v>59</v>
       </c>
       <c r="I196">
-        <v>7.1890233501116216E-2</v>
+        <v>7.1890233501115827E-2</v>
       </c>
       <c r="J196" t="s">
         <v>54</v>
@@ -8043,7 +8043,7 @@
         <v>60</v>
       </c>
       <c r="D197">
-        <v>2.2385806429899884E-2</v>
+        <v>2.2385808442518192E-2</v>
       </c>
       <c r="E197" t="s">
         <v>54</v>
@@ -8055,7 +8055,7 @@
         <v>60</v>
       </c>
       <c r="I197">
-        <v>4.8544014893774176E-2</v>
+        <v>4.8544014893773919E-2</v>
       </c>
       <c r="J197" t="s">
         <v>54</v>
@@ -8069,7 +8069,7 @@
         <v>61</v>
       </c>
       <c r="D198">
-        <v>0.3500790867718499</v>
+        <v>0.35007911824606019</v>
       </c>
       <c r="E198" t="s">
         <v>54</v>
@@ -8081,7 +8081,7 @@
         <v>61</v>
       </c>
       <c r="I198">
-        <v>5.8355611063841871E-2</v>
+        <v>5.8355611063841559E-2</v>
       </c>
       <c r="J198" t="s">
         <v>54</v>
@@ -8095,7 +8095,7 @@
         <v>62</v>
       </c>
       <c r="D199">
-        <v>8.0245018049628705E-3</v>
+        <v>8.0245025264137279E-3</v>
       </c>
       <c r="E199" t="s">
         <v>54</v>
@@ -8107,7 +8107,7 @@
         <v>62</v>
       </c>
       <c r="I199">
-        <v>4.0823505671109026E-2</v>
+        <v>4.082350567110881E-2</v>
       </c>
       <c r="J199" t="s">
         <v>54</v>
@@ -8121,7 +8121,7 @@
         <v>63</v>
       </c>
       <c r="D200">
-        <v>3.0735232153737014E-3</v>
+        <v>3.0735234917018792E-3</v>
       </c>
       <c r="E200" t="s">
         <v>54</v>
@@ -8133,7 +8133,7 @@
         <v>63</v>
       </c>
       <c r="I200">
-        <v>8.7649702937428284E-2</v>
+        <v>8.7649702937427812E-2</v>
       </c>
       <c r="J200" t="s">
         <v>54</v>
@@ -8147,7 +8147,7 @@
         <v>64</v>
       </c>
       <c r="D201">
-        <v>0.14716469062242524</v>
+        <v>0.1471647038534139</v>
       </c>
       <c r="E201" t="s">
         <v>54</v>
@@ -8159,7 +8159,7 @@
         <v>64</v>
       </c>
       <c r="I201">
-        <v>0.10171419314692765</v>
+        <v>0.1017141931469271</v>
       </c>
       <c r="J201" t="s">
         <v>54</v>
@@ -8173,7 +8173,7 @@
         <v>65</v>
       </c>
       <c r="D202">
-        <v>1.0220703991695688E-4</v>
+        <v>1.02207049105983E-4</v>
       </c>
       <c r="E202" t="s">
         <v>54</v>
@@ -8185,7 +8185,7 @@
         <v>65</v>
       </c>
       <c r="I202">
-        <v>6.8575725496766826E-2</v>
+        <v>6.8575725496766465E-2</v>
       </c>
       <c r="J202" t="s">
         <v>54</v>
@@ -8211,7 +8211,7 @@
         <v>53</v>
       </c>
       <c r="I203">
-        <v>0.11643097113342614</v>
+        <v>0.11643097113342625</v>
       </c>
       <c r="J203" t="s">
         <v>54</v>
@@ -8225,7 +8225,7 @@
         <v>55</v>
       </c>
       <c r="D204">
-        <v>0.10318125301894192</v>
+        <v>0.10318125301894174</v>
       </c>
       <c r="E204" t="s">
         <v>54</v>
@@ -8237,7 +8237,7 @@
         <v>55</v>
       </c>
       <c r="I204">
-        <v>0.13951172921107921</v>
+        <v>0.13951172921107935</v>
       </c>
       <c r="J204" t="s">
         <v>54</v>
@@ -8263,7 +8263,7 @@
         <v>56</v>
       </c>
       <c r="I205">
-        <v>9.1350014489462464E-2</v>
+        <v>9.1350014489462561E-2</v>
       </c>
       <c r="J205" t="s">
         <v>54</v>
@@ -8277,7 +8277,7 @@
         <v>57</v>
       </c>
       <c r="D206">
-        <v>1.0745055882695765E-2</v>
+        <v>1.0745055882695746E-2</v>
       </c>
       <c r="E206" t="s">
         <v>54</v>
@@ -8289,7 +8289,7 @@
         <v>57</v>
       </c>
       <c r="I206">
-        <v>9.7433972762046975E-2</v>
+        <v>9.7433972762047072E-2</v>
       </c>
       <c r="J206" t="s">
         <v>54</v>
@@ -8303,7 +8303,7 @@
         <v>58</v>
       </c>
       <c r="D207">
-        <v>0.31237991763417294</v>
+        <v>0.31237991763417239</v>
       </c>
       <c r="E207" t="s">
         <v>54</v>
@@ -8315,7 +8315,7 @@
         <v>58</v>
       </c>
       <c r="I207">
-        <v>9.1432198905461379E-2</v>
+        <v>9.1432198905461476E-2</v>
       </c>
       <c r="J207" t="s">
         <v>54</v>
@@ -8329,7 +8329,7 @@
         <v>59</v>
       </c>
       <c r="D208">
-        <v>3.6789841182135381E-3</v>
+        <v>3.6789841182135316E-3</v>
       </c>
       <c r="E208" t="s">
         <v>54</v>
@@ -8341,7 +8341,7 @@
         <v>59</v>
       </c>
       <c r="I208">
-        <v>7.0296211366211531E-2</v>
+        <v>7.02962113662116E-2</v>
       </c>
       <c r="J208" t="s">
         <v>54</v>
@@ -8355,7 +8355,7 @@
         <v>60</v>
       </c>
       <c r="D209">
-        <v>1.7154362642004619E-2</v>
+        <v>1.7154362642004588E-2</v>
       </c>
       <c r="E209" t="s">
         <v>54</v>
@@ -8367,7 +8367,7 @@
         <v>60</v>
       </c>
       <c r="I209">
-        <v>5.0420856742190462E-2</v>
+        <v>5.042085674219051E-2</v>
       </c>
       <c r="J209" t="s">
         <v>54</v>
@@ -8381,7 +8381,7 @@
         <v>61</v>
       </c>
       <c r="D210">
-        <v>0.35604841788689584</v>
+        <v>0.35604841788689523</v>
       </c>
       <c r="E210" t="s">
         <v>54</v>
@@ -8393,7 +8393,7 @@
         <v>61</v>
       </c>
       <c r="I210">
-        <v>4.794857907272803E-2</v>
+        <v>4.7948579072728079E-2</v>
       </c>
       <c r="J210" t="s">
         <v>54</v>
@@ -8407,7 +8407,7 @@
         <v>62</v>
       </c>
       <c r="D211">
-        <v>8.584341977003293E-3</v>
+        <v>8.5843419770032774E-3</v>
       </c>
       <c r="E211" t="s">
         <v>54</v>
@@ -8419,7 +8419,7 @@
         <v>62</v>
       </c>
       <c r="I211">
-        <v>3.7329482780923989E-2</v>
+        <v>3.7329482780924024E-2</v>
       </c>
       <c r="J211" t="s">
         <v>54</v>
@@ -8433,7 +8433,7 @@
         <v>63</v>
       </c>
       <c r="D212">
-        <v>2.7654050146070112E-3</v>
+        <v>2.7654050146070064E-3</v>
       </c>
       <c r="E212" t="s">
         <v>54</v>
@@ -8445,7 +8445,7 @@
         <v>63</v>
       </c>
       <c r="I212">
-        <v>8.6407581309536421E-2</v>
+        <v>8.6407581309536505E-2</v>
       </c>
       <c r="J212" t="s">
         <v>54</v>
@@ -8459,7 +8459,7 @@
         <v>64</v>
       </c>
       <c r="D213">
-        <v>0.18521892997516259</v>
+        <v>0.18521892997516226</v>
       </c>
       <c r="E213" t="s">
         <v>54</v>
@@ -8471,7 +8471,7 @@
         <v>64</v>
       </c>
       <c r="I213">
-        <v>9.7398667318116319E-2</v>
+        <v>9.7398667318116416E-2</v>
       </c>
       <c r="J213" t="s">
         <v>54</v>
@@ -8485,7 +8485,7 @@
         <v>65</v>
       </c>
       <c r="D214">
-        <v>2.4333185030432178E-4</v>
+        <v>2.4333185030432134E-4</v>
       </c>
       <c r="E214" t="s">
         <v>54</v>
@@ -8497,7 +8497,7 @@
         <v>65</v>
       </c>
       <c r="I214">
-        <v>7.4039734908816074E-2</v>
+        <v>7.4039734908816143E-2</v>
       </c>
       <c r="J214" t="s">
         <v>54</v>
@@ -8523,7 +8523,7 @@
         <v>53</v>
       </c>
       <c r="I215">
-        <v>0.11323661549032892</v>
+        <v>0.11323661549032882</v>
       </c>
       <c r="J215" t="s">
         <v>54</v>
@@ -8537,7 +8537,7 @@
         <v>55</v>
       </c>
       <c r="D216">
-        <v>0.10139335697559988</v>
+        <v>0.1013933569755997</v>
       </c>
       <c r="E216" t="s">
         <v>54</v>
@@ -8549,7 +8549,7 @@
         <v>55</v>
       </c>
       <c r="I216">
-        <v>0.13629118931431061</v>
+        <v>0.1362911893143105</v>
       </c>
       <c r="J216" t="s">
         <v>54</v>
@@ -8575,7 +8575,7 @@
         <v>56</v>
       </c>
       <c r="I217">
-        <v>8.8969749583882596E-2</v>
+        <v>8.8969749583882513E-2</v>
       </c>
       <c r="J217" t="s">
         <v>54</v>
@@ -8589,7 +8589,7 @@
         <v>57</v>
       </c>
       <c r="D218">
-        <v>9.8832791413418671E-3</v>
+        <v>9.8832791413418497E-3</v>
       </c>
       <c r="E218" t="s">
         <v>54</v>
@@ -8601,7 +8601,7 @@
         <v>57</v>
       </c>
       <c r="I218">
-        <v>9.8128581252052094E-2</v>
+        <v>9.8128581252052011E-2</v>
       </c>
       <c r="J218" t="s">
         <v>54</v>
@@ -8615,7 +8615,7 @@
         <v>58</v>
       </c>
       <c r="D219">
-        <v>0.3104821640005791</v>
+        <v>0.31048216400057854</v>
       </c>
       <c r="E219" t="s">
         <v>54</v>
@@ -8627,7 +8627,7 @@
         <v>58</v>
       </c>
       <c r="I219">
-        <v>9.0560978804531525E-2</v>
+        <v>9.0560978804531442E-2</v>
       </c>
       <c r="J219" t="s">
         <v>54</v>
@@ -8641,7 +8641,7 @@
         <v>59</v>
       </c>
       <c r="D220">
-        <v>4.2740640203438761E-3</v>
+        <v>4.2740640203438682E-3</v>
       </c>
       <c r="E220" t="s">
         <v>54</v>
@@ -8653,7 +8653,7 @@
         <v>59</v>
       </c>
       <c r="I220">
-        <v>7.0224428139626524E-2</v>
+        <v>7.0224428139626469E-2</v>
       </c>
       <c r="J220" t="s">
         <v>54</v>
@@ -8667,7 +8667,7 @@
         <v>60</v>
       </c>
       <c r="D221">
-        <v>1.5365028847994696E-2</v>
+        <v>1.5365028847994669E-2</v>
       </c>
       <c r="E221" t="s">
         <v>54</v>
@@ -8679,7 +8679,7 @@
         <v>60</v>
       </c>
       <c r="I221">
-        <v>5.0739203341291735E-2</v>
+        <v>5.0739203341291693E-2</v>
       </c>
       <c r="J221" t="s">
         <v>54</v>
@@ -8693,7 +8693,7 @@
         <v>61</v>
       </c>
       <c r="D222">
-        <v>0.35328669614836361</v>
+        <v>0.353286696148363</v>
       </c>
       <c r="E222" t="s">
         <v>54</v>
@@ -8705,7 +8705,7 @@
         <v>61</v>
       </c>
       <c r="I222">
-        <v>5.0153277425107397E-2</v>
+        <v>5.0153277425107355E-2</v>
       </c>
       <c r="J222" t="s">
         <v>54</v>
@@ -8719,7 +8719,7 @@
         <v>62</v>
       </c>
       <c r="D223">
-        <v>9.3781716489368082E-3</v>
+        <v>9.3781716489367908E-3</v>
       </c>
       <c r="E223" t="s">
         <v>54</v>
@@ -8731,7 +8731,7 @@
         <v>62</v>
       </c>
       <c r="I223">
-        <v>3.859793074382533E-2</v>
+        <v>3.8597930743825296E-2</v>
       </c>
       <c r="J223" t="s">
         <v>54</v>
@@ -8745,7 +8745,7 @@
         <v>63</v>
       </c>
       <c r="D224">
-        <v>2.4210133069635926E-3</v>
+        <v>2.4210133069635883E-3</v>
       </c>
       <c r="E224" t="s">
         <v>54</v>
@@ -8757,7 +8757,7 @@
         <v>63</v>
       </c>
       <c r="I224">
-        <v>8.759672642035099E-2</v>
+        <v>8.7596726420350907E-2</v>
       </c>
       <c r="J224" t="s">
         <v>54</v>
@@ -8771,7 +8771,7 @@
         <v>64</v>
       </c>
       <c r="D225">
-        <v>0.19322192995762616</v>
+        <v>0.19322192995762583</v>
       </c>
       <c r="E225" t="s">
         <v>54</v>
@@ -8783,7 +8783,7 @@
         <v>64</v>
       </c>
       <c r="I225">
-        <v>0.10119508040812664</v>
+        <v>0.10119508040812655</v>
       </c>
       <c r="J225" t="s">
         <v>54</v>
@@ -8797,7 +8797,7 @@
         <v>65</v>
       </c>
       <c r="D226">
-        <v>2.9429595225215021E-4</v>
+        <v>2.9429595225214966E-4</v>
       </c>
       <c r="E226" t="s">
         <v>54</v>
@@ -8809,7 +8809,7 @@
         <v>65</v>
       </c>
       <c r="I226">
-        <v>7.4306239076566638E-2</v>
+        <v>7.4306239076566569E-2</v>
       </c>
       <c r="J226" t="s">
         <v>54</v>
@@ -8823,7 +8823,7 @@
         <v>53</v>
       </c>
       <c r="D227">
-        <v>5.8271482960546011E-5</v>
+        <v>5.8271482960545896E-5</v>
       </c>
       <c r="E227" t="s">
         <v>54</v>
@@ -8835,7 +8835,7 @@
         <v>53</v>
       </c>
       <c r="I227">
-        <v>0.11835072084920879</v>
+        <v>0.11835072084920842</v>
       </c>
       <c r="J227" t="s">
         <v>54</v>
@@ -8849,7 +8849,7 @@
         <v>55</v>
       </c>
       <c r="D228">
-        <v>0.11834405163737163</v>
+        <v>0.1183440516373714</v>
       </c>
       <c r="E228" t="s">
         <v>54</v>
@@ -8861,7 +8861,7 @@
         <v>55</v>
       </c>
       <c r="I228">
-        <v>0.13852144362308921</v>
+        <v>0.13852144362308877</v>
       </c>
       <c r="J228" t="s">
         <v>54</v>
@@ -8887,7 +8887,7 @@
         <v>56</v>
       </c>
       <c r="I229">
-        <v>9.1202289151863E-2</v>
+        <v>9.1202289151862723E-2</v>
       </c>
       <c r="J229" t="s">
         <v>54</v>
@@ -8901,7 +8901,7 @@
         <v>57</v>
       </c>
       <c r="D230">
-        <v>1.4439487484960756E-2</v>
+        <v>1.4439487484960727E-2</v>
       </c>
       <c r="E230" t="s">
         <v>54</v>
@@ -8913,7 +8913,7 @@
         <v>57</v>
       </c>
       <c r="I230">
-        <v>9.7210088840468153E-2</v>
+        <v>9.7210088840467848E-2</v>
       </c>
       <c r="J230" t="s">
         <v>54</v>
@@ -8927,7 +8927,7 @@
         <v>58</v>
       </c>
       <c r="D231">
-        <v>0.30693150403973163</v>
+        <v>0.30693150403973102</v>
       </c>
       <c r="E231" t="s">
         <v>54</v>
@@ -8939,7 +8939,7 @@
         <v>58</v>
       </c>
       <c r="I231">
-        <v>9.7060184032160629E-2</v>
+        <v>9.7060184032160324E-2</v>
       </c>
       <c r="J231" t="s">
         <v>54</v>
@@ -8953,7 +8953,7 @@
         <v>59</v>
       </c>
       <c r="D232">
-        <v>2.3414324465817564E-3</v>
+        <v>2.3414324465817517E-3</v>
       </c>
       <c r="E232" t="s">
         <v>54</v>
@@ -8965,7 +8965,7 @@
         <v>59</v>
       </c>
       <c r="I232">
-        <v>7.2689967108247946E-2</v>
+        <v>7.2689967108247724E-2</v>
       </c>
       <c r="J232" t="s">
         <v>54</v>
@@ -8979,7 +8979,7 @@
         <v>60</v>
       </c>
       <c r="D233">
-        <v>2.0689952479162516E-2</v>
+        <v>2.0689952479162475E-2</v>
       </c>
       <c r="E233" t="s">
         <v>54</v>
@@ -8991,7 +8991,7 @@
         <v>60</v>
       </c>
       <c r="I233">
-        <v>4.4872183659250046E-2</v>
+        <v>4.4872183659249908E-2</v>
       </c>
       <c r="J233" t="s">
         <v>54</v>
@@ -9005,7 +9005,7 @@
         <v>61</v>
       </c>
       <c r="D234">
-        <v>0.33948066763286483</v>
+        <v>0.33948066763286416</v>
       </c>
       <c r="E234" t="s">
         <v>54</v>
@@ -9017,7 +9017,7 @@
         <v>61</v>
       </c>
       <c r="I234">
-        <v>4.4121111894098168E-2</v>
+        <v>4.4121111894098029E-2</v>
       </c>
       <c r="J234" t="s">
         <v>54</v>
@@ -9031,7 +9031,7 @@
         <v>62</v>
       </c>
       <c r="D235">
-        <v>5.9319156493812071E-3</v>
+        <v>5.9319156493811949E-3</v>
       </c>
       <c r="E235" t="s">
         <v>54</v>
@@ -9043,7 +9043,7 @@
         <v>62</v>
       </c>
       <c r="I235">
-        <v>3.52960475580213E-2</v>
+        <v>3.5296047558021189E-2</v>
       </c>
       <c r="J235" t="s">
         <v>54</v>
@@ -9057,7 +9057,7 @@
         <v>63</v>
       </c>
       <c r="D236">
-        <v>4.1864171095308475E-3</v>
+        <v>4.1864171095308388E-3</v>
       </c>
       <c r="E236" t="s">
         <v>54</v>
@@ -9069,7 +9069,7 @@
         <v>63</v>
       </c>
       <c r="I236">
-        <v>9.1588554294632418E-2</v>
+        <v>9.1588554294632127E-2</v>
       </c>
       <c r="J236" t="s">
         <v>54</v>
@@ -9083,7 +9083,7 @@
         <v>64</v>
       </c>
       <c r="D237">
-        <v>0.18751121393821557</v>
+        <v>0.18751121393821518</v>
       </c>
       <c r="E237" t="s">
         <v>54</v>
@@ -9095,7 +9095,7 @@
         <v>64</v>
       </c>
       <c r="I237">
-        <v>9.7569299276720492E-2</v>
+        <v>9.7569299276720187E-2</v>
       </c>
       <c r="J237" t="s">
         <v>54</v>
@@ -9109,7 +9109,7 @@
         <v>65</v>
       </c>
       <c r="D238">
-        <v>8.5086099240675592E-5</v>
+        <v>8.5086099240675415E-5</v>
       </c>
       <c r="E238" t="s">
         <v>54</v>
@@ -9121,7 +9121,7 @@
         <v>65</v>
       </c>
       <c r="I238">
-        <v>7.1518109712242886E-2</v>
+        <v>7.1518109712242664E-2</v>
       </c>
       <c r="J238" t="s">
         <v>54</v>
@@ -9147,7 +9147,7 @@
         <v>53</v>
       </c>
       <c r="I239">
-        <v>0.10206334834946791</v>
+        <v>0.10206334834946787</v>
       </c>
       <c r="J239" t="s">
         <v>54</v>
@@ -9161,7 +9161,7 @@
         <v>55</v>
       </c>
       <c r="D240">
-        <v>8.4599035377141155E-2</v>
+        <v>8.4599035377141057E-2</v>
       </c>
       <c r="E240" t="s">
         <v>54</v>
@@ -9173,7 +9173,7 @@
         <v>55</v>
       </c>
       <c r="I240">
-        <v>0.13181729700366315</v>
+        <v>0.1318172970036631</v>
       </c>
       <c r="J240" t="s">
         <v>54</v>
@@ -9199,7 +9199,7 @@
         <v>56</v>
       </c>
       <c r="I241">
-        <v>8.1729400342874764E-2</v>
+        <v>8.1729400342874722E-2</v>
       </c>
       <c r="J241" t="s">
         <v>54</v>
@@ -9213,7 +9213,7 @@
         <v>57</v>
       </c>
       <c r="D242">
-        <v>8.7505029016424866E-3</v>
+        <v>8.7505029016424762E-3</v>
       </c>
       <c r="E242" t="s">
         <v>54</v>
@@ -9225,7 +9225,7 @@
         <v>57</v>
       </c>
       <c r="I242">
-        <v>8.7440229795553007E-2</v>
+        <v>8.7440229795552965E-2</v>
       </c>
       <c r="J242" t="s">
         <v>54</v>
@@ -9239,7 +9239,7 @@
         <v>58</v>
       </c>
       <c r="D243">
-        <v>0.35002223554763512</v>
+        <v>0.35002223554763473</v>
       </c>
       <c r="E243" t="s">
         <v>54</v>
@@ -9251,7 +9251,7 @@
         <v>58</v>
       </c>
       <c r="I243">
-        <v>9.2435035897746973E-2</v>
+        <v>9.2435035897746931E-2</v>
       </c>
       <c r="J243" t="s">
         <v>54</v>
@@ -9265,7 +9265,7 @@
         <v>59</v>
       </c>
       <c r="D244">
-        <v>6.0894413082139155E-3</v>
+        <v>6.0894413082139085E-3</v>
       </c>
       <c r="E244" t="s">
         <v>54</v>
@@ -9277,7 +9277,7 @@
         <v>59</v>
       </c>
       <c r="I244">
-        <v>6.4264240997440658E-2</v>
+        <v>6.426424099744063E-2</v>
       </c>
       <c r="J244" t="s">
         <v>54</v>
@@ -9291,7 +9291,7 @@
         <v>60</v>
       </c>
       <c r="D245">
-        <v>1.4419015167100004E-2</v>
+        <v>1.4419015167099989E-2</v>
       </c>
       <c r="E245" t="s">
         <v>54</v>
@@ -9303,7 +9303,7 @@
         <v>60</v>
       </c>
       <c r="I245">
-        <v>5.2658042281182489E-2</v>
+        <v>5.2658042281182468E-2</v>
       </c>
       <c r="J245" t="s">
         <v>54</v>
@@ -9317,7 +9317,7 @@
         <v>61</v>
       </c>
       <c r="D246">
-        <v>0.35121471040407765</v>
+        <v>0.35121471040407726</v>
       </c>
       <c r="E246" t="s">
         <v>54</v>
@@ -9329,7 +9329,7 @@
         <v>61</v>
       </c>
       <c r="I246">
-        <v>6.9598416136000679E-2</v>
+        <v>6.9598416136000651E-2</v>
       </c>
       <c r="J246" t="s">
         <v>54</v>
@@ -9343,7 +9343,7 @@
         <v>62</v>
       </c>
       <c r="D247">
-        <v>1.2475012097883117E-2</v>
+        <v>1.2475012097883103E-2</v>
       </c>
       <c r="E247" t="s">
         <v>54</v>
@@ -9355,7 +9355,7 @@
         <v>62</v>
       </c>
       <c r="I247">
-        <v>3.9900355615294411E-2</v>
+        <v>3.990035561529439E-2</v>
       </c>
       <c r="J247" t="s">
         <v>54</v>
@@ -9369,7 +9369,7 @@
         <v>63</v>
       </c>
       <c r="D248">
-        <v>1.651820698664694E-3</v>
+        <v>1.6518206986646923E-3</v>
       </c>
       <c r="E248" t="s">
         <v>54</v>
@@ -9381,7 +9381,7 @@
         <v>63</v>
       </c>
       <c r="I248">
-        <v>9.089440184877759E-2</v>
+        <v>9.0894401848777548E-2</v>
       </c>
       <c r="J248" t="s">
         <v>54</v>
@@ -9395,7 +9395,7 @@
         <v>64</v>
       </c>
       <c r="D249">
-        <v>0.17026736440709339</v>
+        <v>0.1702673644070932</v>
       </c>
       <c r="E249" t="s">
         <v>54</v>
@@ -9407,7 +9407,7 @@
         <v>64</v>
       </c>
       <c r="I249">
-        <v>0.1126880207773395</v>
+        <v>0.11268802077733944</v>
       </c>
       <c r="J249" t="s">
         <v>54</v>
@@ -9421,7 +9421,7 @@
         <v>65</v>
       </c>
       <c r="D250">
-        <v>5.1086209054958948E-4</v>
+        <v>5.1086209054958893E-4</v>
       </c>
       <c r="E250" t="s">
         <v>54</v>
@@ -9433,7 +9433,7 @@
         <v>65</v>
       </c>
       <c r="I250">
-        <v>7.4511210954659415E-2</v>
+        <v>7.4511210954659388E-2</v>
       </c>
       <c r="J250" t="s">
         <v>54</v>
@@ -9459,7 +9459,7 @@
         <v>53</v>
       </c>
       <c r="I251">
-        <v>0.10443286940657974</v>
+        <v>0.10443286940657998</v>
       </c>
       <c r="J251" t="s">
         <v>54</v>
@@ -9473,7 +9473,7 @@
         <v>55</v>
       </c>
       <c r="D252">
-        <v>9.9630862245262755E-2</v>
+        <v>9.9630862245262949E-2</v>
       </c>
       <c r="E252" t="s">
         <v>54</v>
@@ -9485,7 +9485,7 @@
         <v>55</v>
       </c>
       <c r="I252">
-        <v>0.13030414897723805</v>
+        <v>0.13030414897723833</v>
       </c>
       <c r="J252" t="s">
         <v>54</v>
@@ -9511,7 +9511,7 @@
         <v>56</v>
       </c>
       <c r="I253">
-        <v>8.3285178176460764E-2</v>
+        <v>8.3285178176460944E-2</v>
       </c>
       <c r="J253" t="s">
         <v>54</v>
@@ -9525,7 +9525,7 @@
         <v>57</v>
       </c>
       <c r="D254">
-        <v>7.9075898835810812E-3</v>
+        <v>7.9075898835810968E-3</v>
       </c>
       <c r="E254" t="s">
         <v>54</v>
@@ -9537,7 +9537,7 @@
         <v>57</v>
       </c>
       <c r="I254">
-        <v>9.0038720370996458E-2</v>
+        <v>9.0038720370996653E-2</v>
       </c>
       <c r="J254" t="s">
         <v>54</v>
@@ -9551,7 +9551,7 @@
         <v>58</v>
       </c>
       <c r="D255">
-        <v>0.31964370367012673</v>
+        <v>0.31964370367012734</v>
       </c>
       <c r="E255" t="s">
         <v>54</v>
@@ -9563,7 +9563,7 @@
         <v>58</v>
       </c>
       <c r="I255">
-        <v>8.5467493344801707E-2</v>
+        <v>8.5467493344801901E-2</v>
       </c>
       <c r="J255" t="s">
         <v>54</v>
@@ -9577,7 +9577,7 @@
         <v>59</v>
       </c>
       <c r="D256">
-        <v>5.9847878855547668E-3</v>
+        <v>5.984787885554778E-3</v>
       </c>
       <c r="E256" t="s">
         <v>54</v>
@@ -9589,7 +9589,7 @@
         <v>59</v>
       </c>
       <c r="I256">
-        <v>6.7791613874343612E-2</v>
+        <v>6.7791613874343765E-2</v>
       </c>
       <c r="J256" t="s">
         <v>54</v>
@@ -9603,7 +9603,7 @@
         <v>60</v>
       </c>
       <c r="D257">
-        <v>1.3338969894631373E-2</v>
+        <v>1.3338969894631399E-2</v>
       </c>
       <c r="E257" t="s">
         <v>54</v>
@@ -9615,7 +9615,7 @@
         <v>60</v>
       </c>
       <c r="I257">
-        <v>5.8193665317057254E-2</v>
+        <v>5.8193665317057386E-2</v>
       </c>
       <c r="J257" t="s">
         <v>54</v>
@@ -9629,7 +9629,7 @@
         <v>61</v>
       </c>
       <c r="D258">
-        <v>0.3599514621264962</v>
+        <v>0.35995146212649687</v>
       </c>
       <c r="E258" t="s">
         <v>54</v>
@@ -9641,7 +9641,7 @@
         <v>61</v>
       </c>
       <c r="I258">
-        <v>5.9657958646134011E-2</v>
+        <v>5.9657958646134143E-2</v>
       </c>
       <c r="J258" t="s">
         <v>54</v>
@@ -9655,7 +9655,7 @@
         <v>62</v>
       </c>
       <c r="D259">
-        <v>1.2004245505509733E-2</v>
+        <v>1.2004245505509756E-2</v>
       </c>
       <c r="E259" t="s">
         <v>54</v>
@@ -9667,7 +9667,7 @@
         <v>62</v>
       </c>
       <c r="I259">
-        <v>4.1388895154069495E-2</v>
+        <v>4.1388895154069585E-2</v>
       </c>
       <c r="J259" t="s">
         <v>54</v>
@@ -9681,7 +9681,7 @@
         <v>63</v>
       </c>
       <c r="D260">
-        <v>1.5229613297209445E-3</v>
+        <v>1.5229613297209474E-3</v>
       </c>
       <c r="E260" t="s">
         <v>54</v>
@@ -9693,7 +9693,7 @@
         <v>63</v>
       </c>
       <c r="I260">
-        <v>9.4408671096213162E-2</v>
+        <v>9.440867109621337E-2</v>
       </c>
       <c r="J260" t="s">
         <v>54</v>
@@ -9707,7 +9707,7 @@
         <v>64</v>
       </c>
       <c r="D261">
-        <v>0.17950552532054131</v>
+        <v>0.17950552532054165</v>
       </c>
       <c r="E261" t="s">
         <v>54</v>
@@ -9719,7 +9719,7 @@
         <v>64</v>
       </c>
       <c r="I261">
-        <v>0.10900641556849647</v>
+        <v>0.1090064155684967</v>
       </c>
       <c r="J261" t="s">
         <v>54</v>
@@ -9733,7 +9733,7 @@
         <v>65</v>
       </c>
       <c r="D262">
-        <v>5.0989213857322458E-4</v>
+        <v>5.0989213857322556E-4</v>
       </c>
       <c r="E262" t="s">
         <v>54</v>
@@ -9745,7 +9745,7 @@
         <v>65</v>
       </c>
       <c r="I262">
-        <v>7.6024370067607011E-2</v>
+        <v>7.6024370067607178E-2</v>
       </c>
       <c r="J262" t="s">
         <v>54</v>
@@ -10083,7 +10083,7 @@
         <v>53</v>
       </c>
       <c r="I275">
-        <v>0.11886695815061905</v>
+        <v>0.11886695815061937</v>
       </c>
       <c r="J275" t="s">
         <v>54</v>
@@ -10097,7 +10097,7 @@
         <v>55</v>
       </c>
       <c r="D276">
-        <v>0.12768499539561937</v>
+        <v>0.12768499539561914</v>
       </c>
       <c r="E276" t="s">
         <v>54</v>
@@ -10109,7 +10109,7 @@
         <v>55</v>
       </c>
       <c r="I276">
-        <v>0.14001371771380608</v>
+        <v>0.14001371771380644</v>
       </c>
       <c r="J276" t="s">
         <v>54</v>
@@ -10135,7 +10135,7 @@
         <v>56</v>
       </c>
       <c r="I277">
-        <v>8.9485335194685683E-2</v>
+        <v>8.9485335194685919E-2</v>
       </c>
       <c r="J277" t="s">
         <v>54</v>
@@ -10149,7 +10149,7 @@
         <v>57</v>
       </c>
       <c r="D278">
-        <v>1.1369293810103747E-2</v>
+        <v>1.1369293810103726E-2</v>
       </c>
       <c r="E278" t="s">
         <v>54</v>
@@ -10161,7 +10161,7 @@
         <v>57</v>
       </c>
       <c r="I278">
-        <v>9.800638818480148E-2</v>
+        <v>9.8006388184801743E-2</v>
       </c>
       <c r="J278" t="s">
         <v>54</v>
@@ -10175,7 +10175,7 @@
         <v>58</v>
       </c>
       <c r="D279">
-        <v>0.29647913268504306</v>
+        <v>0.29647913268504256</v>
       </c>
       <c r="E279" t="s">
         <v>54</v>
@@ -10187,7 +10187,7 @@
         <v>58</v>
       </c>
       <c r="I279">
-        <v>9.8346708044020903E-2</v>
+        <v>9.8346708044021167E-2</v>
       </c>
       <c r="J279" t="s">
         <v>54</v>
@@ -10201,7 +10201,7 @@
         <v>59</v>
       </c>
       <c r="D280">
-        <v>3.1804688258714525E-3</v>
+        <v>3.1804688258714468E-3</v>
       </c>
       <c r="E280" t="s">
         <v>54</v>
@@ -10213,7 +10213,7 @@
         <v>59</v>
       </c>
       <c r="I280">
-        <v>7.1246040347496653E-2</v>
+        <v>7.1246040347496847E-2</v>
       </c>
       <c r="J280" t="s">
         <v>54</v>
@@ -10227,7 +10227,7 @@
         <v>60</v>
       </c>
       <c r="D281">
-        <v>1.6977350753205164E-2</v>
+        <v>1.6977350753205132E-2</v>
       </c>
       <c r="E281" t="s">
         <v>54</v>
@@ -10239,7 +10239,7 @@
         <v>60</v>
       </c>
       <c r="I281">
-        <v>4.4983347977738279E-2</v>
+        <v>4.4983347977738397E-2</v>
       </c>
       <c r="J281" t="s">
         <v>54</v>
@@ -10253,7 +10253,7 @@
         <v>61</v>
       </c>
       <c r="D282">
-        <v>0.33862308002572183</v>
+        <v>0.33862308002572122</v>
       </c>
       <c r="E282" t="s">
         <v>54</v>
@@ -10265,7 +10265,7 @@
         <v>61</v>
       </c>
       <c r="I282">
-        <v>4.7598911707990542E-2</v>
+        <v>4.7598911707990667E-2</v>
       </c>
       <c r="J282" t="s">
         <v>54</v>
@@ -10279,7 +10279,7 @@
         <v>62</v>
       </c>
       <c r="D283">
-        <v>7.1725663879981267E-3</v>
+        <v>7.1725663879981137E-3</v>
       </c>
       <c r="E283" t="s">
         <v>54</v>
@@ -10291,7 +10291,7 @@
         <v>62</v>
       </c>
       <c r="I283">
-        <v>3.7146041831964606E-2</v>
+        <v>3.7146041831964703E-2</v>
       </c>
       <c r="J283" t="s">
         <v>54</v>
@@ -10305,7 +10305,7 @@
         <v>63</v>
       </c>
       <c r="D284">
-        <v>3.2781422705553814E-3</v>
+        <v>3.2781422705553758E-3</v>
       </c>
       <c r="E284" t="s">
         <v>54</v>
@@ -10317,7 +10317,7 @@
         <v>63</v>
       </c>
       <c r="I284">
-        <v>8.812911798988228E-2</v>
+        <v>8.8129117989882516E-2</v>
       </c>
       <c r="J284" t="s">
         <v>54</v>
@@ -10331,7 +10331,7 @@
         <v>64</v>
       </c>
       <c r="D285">
-        <v>0.19505167960506709</v>
+        <v>0.19505167960506675</v>
       </c>
       <c r="E285" t="s">
         <v>54</v>
@@ -10343,7 +10343,7 @@
         <v>64</v>
       </c>
       <c r="I285">
-        <v>9.5440053990017731E-2</v>
+        <v>9.5440053990017981E-2</v>
       </c>
       <c r="J285" t="s">
         <v>54</v>
@@ -10357,7 +10357,7 @@
         <v>65</v>
       </c>
       <c r="D286">
-        <v>1.8329024081662732E-4</v>
+        <v>1.8329024081662699E-4</v>
       </c>
       <c r="E286" t="s">
         <v>54</v>
@@ -10369,7 +10369,7 @@
         <v>65</v>
       </c>
       <c r="I286">
-        <v>7.0737378866974107E-2</v>
+        <v>7.0737378866974301E-2</v>
       </c>
       <c r="J286" t="s">
         <v>54</v>
@@ -10383,7 +10383,7 @@
         <v>53</v>
       </c>
       <c r="D287">
-        <v>2.2836978935702699E-5</v>
+        <v>2.2836978935702696E-5</v>
       </c>
       <c r="E287" t="s">
         <v>54</v>
@@ -10409,7 +10409,7 @@
         <v>55</v>
       </c>
       <c r="D288">
-        <v>0.10522509793388399</v>
+        <v>0.10522509793388396</v>
       </c>
       <c r="E288" t="s">
         <v>54</v>
@@ -10461,7 +10461,7 @@
         <v>57</v>
       </c>
       <c r="D290">
-        <v>1.51885549496208E-2</v>
+        <v>1.5188554949620797E-2</v>
       </c>
       <c r="E290" t="s">
         <v>54</v>
@@ -10487,7 +10487,7 @@
         <v>58</v>
       </c>
       <c r="D291">
-        <v>0.32355491405807624</v>
+        <v>0.32355491405807618</v>
       </c>
       <c r="E291" t="s">
         <v>54</v>
@@ -10513,7 +10513,7 @@
         <v>59</v>
       </c>
       <c r="D292">
-        <v>2.4321427795576107E-3</v>
+        <v>2.4321427795576103E-3</v>
       </c>
       <c r="E292" t="s">
         <v>54</v>
@@ -10539,7 +10539,7 @@
         <v>60</v>
       </c>
       <c r="D293">
-        <v>2.2654518080552209E-2</v>
+        <v>2.2654518080552206E-2</v>
       </c>
       <c r="E293" t="s">
         <v>54</v>
@@ -10565,7 +10565,7 @@
         <v>61</v>
       </c>
       <c r="D294">
-        <v>0.34508058273444542</v>
+        <v>0.34508058273444536</v>
       </c>
       <c r="E294" t="s">
         <v>54</v>
@@ -10591,7 +10591,7 @@
         <v>62</v>
       </c>
       <c r="D295">
-        <v>6.2892737929421136E-3</v>
+        <v>6.2892737929421119E-3</v>
       </c>
       <c r="E295" t="s">
         <v>54</v>
@@ -10617,7 +10617,7 @@
         <v>63</v>
       </c>
       <c r="D296">
-        <v>3.871014754722602E-3</v>
+        <v>3.8710147547226011E-3</v>
       </c>
       <c r="E296" t="s">
         <v>54</v>
@@ -10643,7 +10643,7 @@
         <v>64</v>
       </c>
       <c r="D297">
-        <v>0.17560438041655485</v>
+        <v>0.17560438041655482</v>
       </c>
       <c r="E297" t="s">
         <v>54</v>
@@ -10669,7 +10669,7 @@
         <v>65</v>
       </c>
       <c r="D298">
-        <v>7.6683520708674852E-5</v>
+        <v>7.6683520708674838E-5</v>
       </c>
       <c r="E298" t="s">
         <v>54</v>
@@ -10707,7 +10707,7 @@
         <v>53</v>
       </c>
       <c r="I299">
-        <v>0.11943034932678222</v>
+        <v>0.11943034932678225</v>
       </c>
       <c r="J299" t="s">
         <v>54</v>
@@ -10733,7 +10733,7 @@
         <v>55</v>
       </c>
       <c r="I300">
-        <v>0.14219083297235086</v>
+        <v>0.14219083297235088</v>
       </c>
       <c r="J300" t="s">
         <v>54</v>
@@ -10759,7 +10759,7 @@
         <v>56</v>
       </c>
       <c r="I301">
-        <v>9.421893568238103E-2</v>
+        <v>9.4218935682381058E-2</v>
       </c>
       <c r="J301" t="s">
         <v>54</v>
@@ -10785,7 +10785,7 @@
         <v>57</v>
       </c>
       <c r="I302">
-        <v>9.4136428641906786E-2</v>
+        <v>9.4136428641906814E-2</v>
       </c>
       <c r="J302" t="s">
         <v>54</v>
@@ -10811,7 +10811,7 @@
         <v>58</v>
       </c>
       <c r="I303">
-        <v>9.078900264560677E-2</v>
+        <v>9.0789002645606784E-2</v>
       </c>
       <c r="J303" t="s">
         <v>54</v>
@@ -10837,7 +10837,7 @@
         <v>59</v>
       </c>
       <c r="I304">
-        <v>6.9272839205482661E-2</v>
+        <v>6.9272839205482675E-2</v>
       </c>
       <c r="J304" t="s">
         <v>54</v>
@@ -10863,7 +10863,7 @@
         <v>60</v>
       </c>
       <c r="I305">
-        <v>4.9251033726047874E-2</v>
+        <v>4.9251033726047888E-2</v>
       </c>
       <c r="J305" t="s">
         <v>54</v>
@@ -10889,7 +10889,7 @@
         <v>61</v>
       </c>
       <c r="I306">
-        <v>4.6890347147085593E-2</v>
+        <v>4.6890347147085606E-2</v>
       </c>
       <c r="J306" t="s">
         <v>54</v>
@@ -10915,7 +10915,7 @@
         <v>62</v>
       </c>
       <c r="I307">
-        <v>3.6786951962998929E-2</v>
+        <v>3.6786951962998936E-2</v>
       </c>
       <c r="J307" t="s">
         <v>54</v>
@@ -10941,7 +10941,7 @@
         <v>63</v>
       </c>
       <c r="I308">
-        <v>8.592550000624305E-2</v>
+        <v>8.5925500006243063E-2</v>
       </c>
       <c r="J308" t="s">
         <v>54</v>
@@ -10967,7 +10967,7 @@
         <v>64</v>
       </c>
       <c r="I309">
-        <v>9.5893881095462846E-2</v>
+        <v>9.5893881095462874E-2</v>
       </c>
       <c r="J309" t="s">
         <v>54</v>
@@ -10993,7 +10993,7 @@
         <v>65</v>
       </c>
       <c r="I310">
-        <v>7.5213897587651152E-2</v>
+        <v>7.5213897587651166E-2</v>
       </c>
       <c r="J310" t="s">
         <v>54</v>
@@ -11033,7 +11033,7 @@
         <v>55</v>
       </c>
       <c r="D312">
-        <v>0.11493096580668372</v>
+        <v>0.11493096580668366</v>
       </c>
       <c r="E312" t="s">
         <v>54</v>
@@ -11085,7 +11085,7 @@
         <v>57</v>
       </c>
       <c r="D314">
-        <v>1.1322379727955103E-2</v>
+        <v>1.1322379727955098E-2</v>
       </c>
       <c r="E314" t="s">
         <v>54</v>
@@ -11111,7 +11111,7 @@
         <v>58</v>
       </c>
       <c r="D315">
-        <v>0.30241676101418324</v>
+        <v>0.30241676101418313</v>
       </c>
       <c r="E315" t="s">
         <v>54</v>
@@ -11137,7 +11137,7 @@
         <v>59</v>
       </c>
       <c r="D316">
-        <v>3.3380439303539807E-3</v>
+        <v>3.3380439303539794E-3</v>
       </c>
       <c r="E316" t="s">
         <v>54</v>
@@ -11163,7 +11163,7 @@
         <v>60</v>
       </c>
       <c r="D317">
-        <v>1.7751945170586814E-2</v>
+        <v>1.7751945170586807E-2</v>
       </c>
       <c r="E317" t="s">
         <v>54</v>
@@ -11189,7 +11189,7 @@
         <v>61</v>
       </c>
       <c r="D318">
-        <v>0.35233799586458181</v>
+        <v>0.35233799586458164</v>
       </c>
       <c r="E318" t="s">
         <v>54</v>
@@ -11215,7 +11215,7 @@
         <v>62</v>
       </c>
       <c r="D319">
-        <v>7.7699766509785242E-3</v>
+        <v>7.7699766509785207E-3</v>
       </c>
       <c r="E319" t="s">
         <v>54</v>
@@ -11241,7 +11241,7 @@
         <v>63</v>
       </c>
       <c r="D320">
-        <v>3.062386599628862E-3</v>
+        <v>3.0623865996288607E-3</v>
       </c>
       <c r="E320" t="s">
         <v>54</v>
@@ -11267,7 +11267,7 @@
         <v>64</v>
       </c>
       <c r="D321">
-        <v>0.18687081589692445</v>
+        <v>0.18687081589692436</v>
       </c>
       <c r="E321" t="s">
         <v>54</v>
@@ -11293,7 +11293,7 @@
         <v>65</v>
       </c>
       <c r="D322">
-        <v>1.9872933812383278E-4</v>
+        <v>1.987293381238327E-4</v>
       </c>
       <c r="E322" t="s">
         <v>54</v>
@@ -11331,7 +11331,7 @@
         <v>53</v>
       </c>
       <c r="I323">
-        <v>0.12330189836323177</v>
+        <v>0.12330189836323144</v>
       </c>
       <c r="J323" t="s">
         <v>54</v>
@@ -11357,7 +11357,7 @@
         <v>55</v>
       </c>
       <c r="I324">
-        <v>0.14190649517589263</v>
+        <v>0.14190649517589224</v>
       </c>
       <c r="J324" t="s">
         <v>54</v>
@@ -11383,7 +11383,7 @@
         <v>56</v>
       </c>
       <c r="I325">
-        <v>9.3614911168500944E-2</v>
+        <v>9.3614911168500695E-2</v>
       </c>
       <c r="J325" t="s">
         <v>54</v>
@@ -11409,7 +11409,7 @@
         <v>57</v>
       </c>
       <c r="I326">
-        <v>9.6144131202724012E-2</v>
+        <v>9.6144131202723762E-2</v>
       </c>
       <c r="J326" t="s">
         <v>54</v>
@@ -11435,7 +11435,7 @@
         <v>58</v>
       </c>
       <c r="I327">
-        <v>9.4184157474335228E-2</v>
+        <v>9.4184157474334979E-2</v>
       </c>
       <c r="J327" t="s">
         <v>54</v>
@@ -11461,7 +11461,7 @@
         <v>59</v>
       </c>
       <c r="I328">
-        <v>7.1054594622881148E-2</v>
+        <v>7.1054594622880954E-2</v>
       </c>
       <c r="J328" t="s">
         <v>54</v>
@@ -11487,7 +11487,7 @@
         <v>60</v>
       </c>
       <c r="I329">
-        <v>4.393417015844063E-2</v>
+        <v>4.3934170158440512E-2</v>
       </c>
       <c r="J329" t="s">
         <v>54</v>
@@ -11513,7 +11513,7 @@
         <v>61</v>
       </c>
       <c r="I330">
-        <v>4.5107369935740153E-2</v>
+        <v>4.5107369935740035E-2</v>
       </c>
       <c r="J330" t="s">
         <v>54</v>
@@ -11539,7 +11539,7 @@
         <v>62</v>
       </c>
       <c r="I331">
-        <v>3.7087931971210616E-2</v>
+        <v>3.7087931971210519E-2</v>
       </c>
       <c r="J331" t="s">
         <v>54</v>
@@ -11565,7 +11565,7 @@
         <v>63</v>
       </c>
       <c r="I332">
-        <v>8.6561111952391995E-2</v>
+        <v>8.6561111952391759E-2</v>
       </c>
       <c r="J332" t="s">
         <v>54</v>
@@ -11591,7 +11591,7 @@
         <v>64</v>
       </c>
       <c r="I333">
-        <v>9.5369029979268563E-2</v>
+        <v>9.5369029979268313E-2</v>
       </c>
       <c r="J333" t="s">
         <v>54</v>
@@ -11617,7 +11617,7 @@
         <v>65</v>
       </c>
       <c r="I334">
-        <v>7.1734197995384913E-2</v>
+        <v>7.1734197995384719E-2</v>
       </c>
       <c r="J334" t="s">
         <v>54</v>
@@ -11631,7 +11631,7 @@
         <v>53</v>
       </c>
       <c r="D335">
-        <v>3.4474088713245377E-5</v>
+        <v>3.4474088713245418E-5</v>
       </c>
       <c r="E335" t="s">
         <v>54</v>
@@ -11643,7 +11643,7 @@
         <v>53</v>
       </c>
       <c r="I335">
-        <v>0.11666485118944103</v>
+        <v>0.11666485118944062</v>
       </c>
       <c r="J335" t="s">
         <v>54</v>
@@ -11657,7 +11657,7 @@
         <v>55</v>
       </c>
       <c r="D336">
-        <v>0.11632784190304606</v>
+        <v>0.11632784190304619</v>
       </c>
       <c r="E336" t="s">
         <v>54</v>
@@ -11669,7 +11669,7 @@
         <v>55</v>
       </c>
       <c r="I336">
-        <v>0.14337426078157753</v>
+        <v>0.14337426078157703</v>
       </c>
       <c r="J336" t="s">
         <v>54</v>
@@ -11695,7 +11695,7 @@
         <v>56</v>
       </c>
       <c r="I337">
-        <v>9.1231826270163699E-2</v>
+        <v>9.123182627016338E-2</v>
       </c>
       <c r="J337" t="s">
         <v>54</v>
@@ -11709,7 +11709,7 @@
         <v>57</v>
       </c>
       <c r="D338">
-        <v>1.3164593097033678E-2</v>
+        <v>1.3164593097033694E-2</v>
       </c>
       <c r="E338" t="s">
         <v>54</v>
@@ -11721,7 +11721,7 @@
         <v>57</v>
       </c>
       <c r="I338">
-        <v>9.1558692129337246E-2</v>
+        <v>9.1558692129336927E-2</v>
       </c>
       <c r="J338" t="s">
         <v>54</v>
@@ -11735,7 +11735,7 @@
         <v>58</v>
       </c>
       <c r="D339">
-        <v>0.30506644137442773</v>
+        <v>0.30506644137442812</v>
       </c>
       <c r="E339" t="s">
         <v>54</v>
@@ -11747,7 +11747,7 @@
         <v>58</v>
       </c>
       <c r="I339">
-        <v>8.7636113203841251E-2</v>
+        <v>8.7636113203840946E-2</v>
       </c>
       <c r="J339" t="s">
         <v>54</v>
@@ -11761,7 +11761,7 @@
         <v>59</v>
       </c>
       <c r="D340">
-        <v>2.6480060790881827E-3</v>
+        <v>2.6480060790881857E-3</v>
       </c>
       <c r="E340" t="s">
         <v>54</v>
@@ -11773,7 +11773,7 @@
         <v>59</v>
       </c>
       <c r="I340">
-        <v>6.8176017348764578E-2</v>
+        <v>6.8176017348764342E-2</v>
       </c>
       <c r="J340" t="s">
         <v>54</v>
@@ -11787,7 +11787,7 @@
         <v>60</v>
       </c>
       <c r="D341">
-        <v>1.9693549240511966E-2</v>
+        <v>1.969354924051199E-2</v>
       </c>
       <c r="E341" t="s">
         <v>54</v>
@@ -11799,7 +11799,7 @@
         <v>60</v>
       </c>
       <c r="I341">
-        <v>5.1016659100689699E-2</v>
+        <v>5.1016659100689518E-2</v>
       </c>
       <c r="J341" t="s">
         <v>54</v>
@@ -11813,7 +11813,7 @@
         <v>61</v>
       </c>
       <c r="D342">
-        <v>0.34300508304778282</v>
+        <v>0.34300508304778327</v>
       </c>
       <c r="E342" t="s">
         <v>54</v>
@@ -11825,7 +11825,7 @@
         <v>61</v>
       </c>
       <c r="I342">
-        <v>4.8976831364956751E-2</v>
+        <v>4.8976831364956577E-2</v>
       </c>
       <c r="J342" t="s">
         <v>54</v>
@@ -11839,7 +11839,7 @@
         <v>62</v>
       </c>
       <c r="D343">
-        <v>6.530738701291304E-3</v>
+        <v>6.5307387012913118E-3</v>
       </c>
       <c r="E343" t="s">
         <v>54</v>
@@ -11851,7 +11851,7 @@
         <v>62</v>
       </c>
       <c r="I343">
-        <v>3.7155980925083515E-2</v>
+        <v>3.7155980925083383E-2</v>
       </c>
       <c r="J343" t="s">
         <v>54</v>
@@ -11865,7 +11865,7 @@
         <v>63</v>
       </c>
       <c r="D344">
-        <v>3.8557010894087044E-3</v>
+        <v>3.8557010894087092E-3</v>
       </c>
       <c r="E344" t="s">
         <v>54</v>
@@ -11877,7 +11877,7 @@
         <v>63</v>
       </c>
       <c r="I344">
-        <v>8.9251762249184546E-2</v>
+        <v>8.9251762249184227E-2</v>
       </c>
       <c r="J344" t="s">
         <v>54</v>
@@ -11891,7 +11891,7 @@
         <v>64</v>
       </c>
       <c r="D345">
-        <v>0.1895573799867537</v>
+        <v>0.18955737998675393</v>
       </c>
       <c r="E345" t="s">
         <v>54</v>
@@ -11903,7 +11903,7 @@
         <v>64</v>
       </c>
       <c r="I345">
-        <v>0.10114145512244362</v>
+        <v>0.10114145512244326</v>
       </c>
       <c r="J345" t="s">
         <v>54</v>
@@ -11917,7 +11917,7 @@
         <v>65</v>
       </c>
       <c r="D346">
-        <v>1.1619139194143212E-4</v>
+        <v>1.1619139194143226E-4</v>
       </c>
       <c r="E346" t="s">
         <v>54</v>
@@ -11929,7 +11929,7 @@
         <v>65</v>
       </c>
       <c r="I346">
-        <v>7.3815550314520001E-2</v>
+        <v>7.3815550314519737E-2</v>
       </c>
       <c r="J346" t="s">
         <v>54</v>
@@ -11955,7 +11955,7 @@
         <v>53</v>
       </c>
       <c r="I347">
-        <v>0.11131165029986612</v>
+        <v>0.1113116502998665</v>
       </c>
       <c r="J347" t="s">
         <v>54</v>
@@ -11969,7 +11969,7 @@
         <v>55</v>
       </c>
       <c r="D348">
-        <v>0.11341942412054302</v>
+        <v>0.11341942412054316</v>
       </c>
       <c r="E348" t="s">
         <v>54</v>
@@ -11981,7 +11981,7 @@
         <v>55</v>
       </c>
       <c r="I348">
-        <v>0.13539800958379067</v>
+        <v>0.13539800958379114</v>
       </c>
       <c r="J348" t="s">
         <v>54</v>
@@ -12007,7 +12007,7 @@
         <v>56</v>
       </c>
       <c r="I349">
-        <v>8.7341603346774002E-2</v>
+        <v>8.7341603346774307E-2</v>
       </c>
       <c r="J349" t="s">
         <v>54</v>
@@ -12021,7 +12021,7 @@
         <v>57</v>
       </c>
       <c r="D350">
-        <v>9.9098542314664251E-3</v>
+        <v>9.9098542314664372E-3</v>
       </c>
       <c r="E350" t="s">
         <v>54</v>
@@ -12033,7 +12033,7 @@
         <v>57</v>
       </c>
       <c r="I350">
-        <v>9.5220280040049385E-2</v>
+        <v>9.5220280040049718E-2</v>
       </c>
       <c r="J350" t="s">
         <v>54</v>
@@ -12047,7 +12047,7 @@
         <v>58</v>
       </c>
       <c r="D351">
-        <v>0.30127449332628869</v>
+        <v>0.30127449332628908</v>
       </c>
       <c r="E351" t="s">
         <v>54</v>
@@ -12059,7 +12059,7 @@
         <v>58</v>
       </c>
       <c r="I351">
-        <v>9.4569071542495206E-2</v>
+        <v>9.4569071542495539E-2</v>
       </c>
       <c r="J351" t="s">
         <v>54</v>
@@ -12073,7 +12073,7 @@
         <v>59</v>
       </c>
       <c r="D352">
-        <v>3.930446139096727E-3</v>
+        <v>3.9304461390967322E-3</v>
       </c>
       <c r="E352" t="s">
         <v>54</v>
@@ -12085,7 +12085,7 @@
         <v>59</v>
       </c>
       <c r="I352">
-        <v>6.9857825471507665E-2</v>
+        <v>6.9857825471507914E-2</v>
       </c>
       <c r="J352" t="s">
         <v>54</v>
@@ -12099,7 +12099,7 @@
         <v>60</v>
       </c>
       <c r="D353">
-        <v>1.5209481538288E-2</v>
+        <v>1.5209481538288019E-2</v>
       </c>
       <c r="E353" t="s">
         <v>54</v>
@@ -12111,7 +12111,7 @@
         <v>60</v>
       </c>
       <c r="I353">
-        <v>4.8434909842485004E-2</v>
+        <v>4.8434909842485177E-2</v>
       </c>
       <c r="J353" t="s">
         <v>54</v>
@@ -12125,7 +12125,7 @@
         <v>61</v>
       </c>
       <c r="D354">
-        <v>0.34900141063648915</v>
+        <v>0.3490014106364896</v>
       </c>
       <c r="E354" t="s">
         <v>54</v>
@@ -12137,7 +12137,7 @@
         <v>61</v>
       </c>
       <c r="I354">
-        <v>5.6377122065634874E-2</v>
+        <v>5.6377122065635075E-2</v>
       </c>
       <c r="J354" t="s">
         <v>54</v>
@@ -12151,7 +12151,7 @@
         <v>62</v>
       </c>
       <c r="D355">
-        <v>8.5926242416117394E-3</v>
+        <v>8.5926242416117498E-3</v>
       </c>
       <c r="E355" t="s">
         <v>54</v>
@@ -12163,7 +12163,7 @@
         <v>62</v>
       </c>
       <c r="I355">
-        <v>4.1762631836127745E-2</v>
+        <v>4.1762631836127891E-2</v>
       </c>
       <c r="J355" t="s">
         <v>54</v>
@@ -12177,7 +12177,7 @@
         <v>63</v>
       </c>
       <c r="D356">
-        <v>2.5143254028520772E-3</v>
+        <v>2.5143254028520802E-3</v>
       </c>
       <c r="E356" t="s">
         <v>54</v>
@@ -12189,7 +12189,7 @@
         <v>63</v>
       </c>
       <c r="I356">
-        <v>8.5561860534405204E-2</v>
+        <v>8.5561860534405509E-2</v>
       </c>
       <c r="J356" t="s">
         <v>54</v>
@@ -12203,7 +12203,7 @@
         <v>64</v>
       </c>
       <c r="D357">
-        <v>0.19587571377126722</v>
+        <v>0.19587571377126747</v>
       </c>
       <c r="E357" t="s">
         <v>54</v>
@@ -12215,7 +12215,7 @@
         <v>64</v>
       </c>
       <c r="I357">
-        <v>0.1011504360710505</v>
+        <v>0.10115043607105086</v>
       </c>
       <c r="J357" t="s">
         <v>54</v>
@@ -12229,7 +12229,7 @@
         <v>65</v>
       </c>
       <c r="D358">
-        <v>2.7222659209567293E-4</v>
+        <v>2.7222659209567325E-4</v>
       </c>
       <c r="E358" t="s">
         <v>54</v>
@@ -12241,7 +12241,7 @@
         <v>65</v>
       </c>
       <c r="I358">
-        <v>7.301459936581009E-2</v>
+        <v>7.3014599365810354E-2</v>
       </c>
       <c r="J358" t="s">
         <v>54</v>
@@ -12267,7 +12267,7 @@
         <v>53</v>
       </c>
       <c r="I359">
-        <v>0.1215216724634049</v>
+        <v>0.12152167246340519</v>
       </c>
       <c r="J359" t="s">
         <v>54</v>
@@ -12281,7 +12281,7 @@
         <v>55</v>
       </c>
       <c r="D360">
-        <v>9.1429129454693822E-2</v>
+        <v>9.142912945469335E-2</v>
       </c>
       <c r="E360" t="s">
         <v>54</v>
@@ -12293,7 +12293,7 @@
         <v>55</v>
       </c>
       <c r="I360">
-        <v>0.14095638274498234</v>
+        <v>0.14095638274498268</v>
       </c>
       <c r="J360" t="s">
         <v>54</v>
@@ -12319,7 +12319,7 @@
         <v>56</v>
       </c>
       <c r="I361">
-        <v>9.3751946835578748E-2</v>
+        <v>9.3751946835578984E-2</v>
       </c>
       <c r="J361" t="s">
         <v>54</v>
@@ -12333,7 +12333,7 @@
         <v>57</v>
       </c>
       <c r="D362">
-        <v>1.0164889371213006E-2</v>
+        <v>1.0164889371212954E-2</v>
       </c>
       <c r="E362" t="s">
         <v>54</v>
@@ -12345,7 +12345,7 @@
         <v>57</v>
       </c>
       <c r="I362">
-        <v>9.5785923011378685E-2</v>
+        <v>9.5785923011378921E-2</v>
       </c>
       <c r="J362" t="s">
         <v>54</v>
@@ -12359,7 +12359,7 @@
         <v>58</v>
       </c>
       <c r="D363">
-        <v>0.33615595849746827</v>
+        <v>0.33615595849746654</v>
       </c>
       <c r="E363" t="s">
         <v>54</v>
@@ -12371,7 +12371,7 @@
         <v>58</v>
       </c>
       <c r="I363">
-        <v>9.3556124804751076E-2</v>
+        <v>9.3556124804751298E-2</v>
       </c>
       <c r="J363" t="s">
         <v>54</v>
@@ -12385,7 +12385,7 @@
         <v>59</v>
       </c>
       <c r="D364">
-        <v>4.464915913226954E-3</v>
+        <v>4.4649159132269314E-3</v>
       </c>
       <c r="E364" t="s">
         <v>54</v>
@@ -12397,7 +12397,7 @@
         <v>59</v>
       </c>
       <c r="I364">
-        <v>7.1123837471441159E-2</v>
+        <v>7.112383747144134E-2</v>
       </c>
       <c r="J364" t="s">
         <v>54</v>
@@ -12411,7 +12411,7 @@
         <v>60</v>
       </c>
       <c r="D365">
-        <v>1.6504511489149283E-2</v>
+        <v>1.65045114891492E-2</v>
       </c>
       <c r="E365" t="s">
         <v>54</v>
@@ -12423,7 +12423,7 @@
         <v>60</v>
       </c>
       <c r="I365">
-        <v>4.6069649080721996E-2</v>
+        <v>4.6069649080722107E-2</v>
       </c>
       <c r="J365" t="s">
         <v>54</v>
@@ -12437,7 +12437,7 @@
         <v>61</v>
       </c>
       <c r="D366">
-        <v>0.35074634825400303</v>
+        <v>0.35074634825400125</v>
       </c>
       <c r="E366" t="s">
         <v>54</v>
@@ -12449,7 +12449,7 @@
         <v>61</v>
       </c>
       <c r="I366">
-        <v>4.6460108341818442E-2</v>
+        <v>4.6460108341818553E-2</v>
       </c>
       <c r="J366" t="s">
         <v>54</v>
@@ -12463,7 +12463,7 @@
         <v>62</v>
       </c>
       <c r="D367">
-        <v>1.0159273184387533E-2</v>
+        <v>1.0159273184387481E-2</v>
       </c>
       <c r="E367" t="s">
         <v>54</v>
@@ -12475,7 +12475,7 @@
         <v>62</v>
       </c>
       <c r="I367">
-        <v>3.6953020381641735E-2</v>
+        <v>3.6953020381641825E-2</v>
       </c>
       <c r="J367" t="s">
         <v>54</v>
@@ -12489,7 +12489,7 @@
         <v>63</v>
       </c>
       <c r="D368">
-        <v>2.4615208104867502E-3</v>
+        <v>2.4615208104867376E-3</v>
       </c>
       <c r="E368" t="s">
         <v>54</v>
@@ -12501,7 +12501,7 @@
         <v>63</v>
       </c>
       <c r="I368">
-        <v>8.6233853252788178E-2</v>
+        <v>8.6233853252788387E-2</v>
       </c>
       <c r="J368" t="s">
         <v>54</v>
@@ -12515,7 +12515,7 @@
         <v>64</v>
       </c>
       <c r="D369">
-        <v>0.17758687390943054</v>
+        <v>0.17758687390942962</v>
       </c>
       <c r="E369" t="s">
         <v>54</v>
@@ -12527,7 +12527,7 @@
         <v>64</v>
       </c>
       <c r="I369">
-        <v>9.3923857840914629E-2</v>
+        <v>9.3923857840914865E-2</v>
       </c>
       <c r="J369" t="s">
         <v>54</v>
@@ -12541,7 +12541,7 @@
         <v>65</v>
       </c>
       <c r="D370">
-        <v>3.2657911594605464E-4</v>
+        <v>3.2657911594605296E-4</v>
       </c>
       <c r="E370" t="s">
         <v>54</v>
@@ -12553,7 +12553,7 @@
         <v>65</v>
       </c>
       <c r="I370">
-        <v>7.3663623770575629E-2</v>
+        <v>7.3663623770575809E-2</v>
       </c>
       <c r="J370" t="s">
         <v>54</v>
@@ -12567,7 +12567,7 @@
         <v>53</v>
       </c>
       <c r="D371">
-        <v>1.0615133245152579E-6</v>
+        <v>1.0615133245152571E-6</v>
       </c>
       <c r="E371" t="s">
         <v>54</v>
@@ -12579,7 +12579,7 @@
         <v>53</v>
       </c>
       <c r="I371">
-        <v>0.1118879478976235</v>
+        <v>0.11188794789762309</v>
       </c>
       <c r="J371" t="s">
         <v>54</v>
@@ -12593,7 +12593,7 @@
         <v>55</v>
       </c>
       <c r="D372">
-        <v>0.11186798864370139</v>
+        <v>0.11186798864370129</v>
       </c>
       <c r="E372" t="s">
         <v>54</v>
@@ -12605,7 +12605,7 @@
         <v>55</v>
       </c>
       <c r="I372">
-        <v>0.13466857751657124</v>
+        <v>0.13466857751657074</v>
       </c>
       <c r="J372" t="s">
         <v>54</v>
@@ -12631,7 +12631,7 @@
         <v>56</v>
       </c>
       <c r="I373">
-        <v>8.8073211805208787E-2</v>
+        <v>8.8073211805208454E-2</v>
       </c>
       <c r="J373" t="s">
         <v>54</v>
@@ -12645,7 +12645,7 @@
         <v>57</v>
       </c>
       <c r="D374">
-        <v>1.2529244693139993E-2</v>
+        <v>1.2529244693139983E-2</v>
       </c>
       <c r="E374" t="s">
         <v>54</v>
@@ -12657,7 +12657,7 @@
         <v>57</v>
       </c>
       <c r="I374">
-        <v>9.6406527213545784E-2</v>
+        <v>9.6406527213545423E-2</v>
       </c>
       <c r="J374" t="s">
         <v>54</v>
@@ -12671,7 +12671,7 @@
         <v>58</v>
       </c>
       <c r="D375">
-        <v>0.30672920019771444</v>
+        <v>0.30672920019771416</v>
       </c>
       <c r="E375" t="s">
         <v>54</v>
@@ -12683,7 +12683,7 @@
         <v>58</v>
       </c>
       <c r="I375">
-        <v>9.0866934543664804E-2</v>
+        <v>9.0866934543664457E-2</v>
       </c>
       <c r="J375" t="s">
         <v>54</v>
@@ -12697,7 +12697,7 @@
         <v>59</v>
       </c>
       <c r="D376">
-        <v>2.9923679715431854E-3</v>
+        <v>2.9923679715431828E-3</v>
       </c>
       <c r="E376" t="s">
         <v>54</v>
@@ -12709,7 +12709,7 @@
         <v>59</v>
       </c>
       <c r="I376">
-        <v>6.9311972383179099E-2</v>
+        <v>6.9311972383178835E-2</v>
       </c>
       <c r="J376" t="s">
         <v>54</v>
@@ -12723,7 +12723,7 @@
         <v>60</v>
       </c>
       <c r="D377">
-        <v>1.949595393850849E-2</v>
+        <v>1.9495953938508472E-2</v>
       </c>
       <c r="E377" t="s">
         <v>54</v>
@@ -12735,7 +12735,7 @@
         <v>60</v>
       </c>
       <c r="I377">
-        <v>5.0065022803585768E-2</v>
+        <v>5.0065022803585581E-2</v>
       </c>
       <c r="J377" t="s">
         <v>54</v>
@@ -12749,7 +12749,7 @@
         <v>61</v>
       </c>
       <c r="D378">
-        <v>0.3501800102648342</v>
+        <v>0.35018001026483386</v>
       </c>
       <c r="E378" t="s">
         <v>54</v>
@@ -12761,7 +12761,7 @@
         <v>61</v>
       </c>
       <c r="I378">
-        <v>5.3726746054826587E-2</v>
+        <v>5.3726746054826385E-2</v>
       </c>
       <c r="J378" t="s">
         <v>54</v>
@@ -12775,7 +12775,7 @@
         <v>62</v>
       </c>
       <c r="D379">
-        <v>7.2200599674354252E-3</v>
+        <v>7.2200599674354191E-3</v>
       </c>
       <c r="E379" t="s">
         <v>54</v>
@@ -12787,7 +12787,7 @@
         <v>62</v>
       </c>
       <c r="I379">
-        <v>4.0350517945939052E-2</v>
+        <v>4.0350517945938899E-2</v>
       </c>
       <c r="J379" t="s">
         <v>54</v>
@@ -12801,7 +12801,7 @@
         <v>63</v>
       </c>
       <c r="D380">
-        <v>3.4566007111792169E-3</v>
+        <v>3.4566007111792138E-3</v>
       </c>
       <c r="E380" t="s">
         <v>54</v>
@@ -12813,7 +12813,7 @@
         <v>63</v>
       </c>
       <c r="I380">
-        <v>8.7115503334795577E-2</v>
+        <v>8.7115503334795244E-2</v>
       </c>
       <c r="J380" t="s">
         <v>54</v>
@@ -12827,7 +12827,7 @@
         <v>64</v>
       </c>
       <c r="D381">
-        <v>0.18537812972816181</v>
+        <v>0.18537812972816164</v>
       </c>
       <c r="E381" t="s">
         <v>54</v>
@@ -12839,7 +12839,7 @@
         <v>64</v>
       </c>
       <c r="I381">
-        <v>0.10269649022849731</v>
+        <v>0.10269649022849692</v>
       </c>
       <c r="J381" t="s">
         <v>54</v>
@@ -12853,7 +12853,7 @@
         <v>65</v>
       </c>
       <c r="D382">
-        <v>1.493823704581386E-4</v>
+        <v>1.4938237045813846E-4</v>
       </c>
       <c r="E382" t="s">
         <v>54</v>
@@ -12865,7 +12865,7 @@
         <v>65</v>
       </c>
       <c r="I382">
-        <v>7.4830548272566244E-2</v>
+        <v>7.4830548272565967E-2</v>
       </c>
       <c r="J382" t="s">
         <v>54</v>
@@ -13203,7 +13203,7 @@
         <v>53</v>
       </c>
       <c r="I395">
-        <v>0.11721569543964983</v>
+        <v>0.11721569543964909</v>
       </c>
       <c r="J395" t="s">
         <v>54</v>
@@ -13217,7 +13217,7 @@
         <v>55</v>
       </c>
       <c r="D396">
-        <v>9.5062280275083219E-2</v>
+        <v>9.5062280275083288E-2</v>
       </c>
       <c r="E396" t="s">
         <v>54</v>
@@ -13229,7 +13229,7 @@
         <v>55</v>
       </c>
       <c r="I396">
-        <v>0.13696529855315345</v>
+        <v>0.13696529855315259</v>
       </c>
       <c r="J396" t="s">
         <v>54</v>
@@ -13255,7 +13255,7 @@
         <v>56</v>
       </c>
       <c r="I397">
-        <v>9.1592208443818615E-2</v>
+        <v>9.1592208443818046E-2</v>
       </c>
       <c r="J397" t="s">
         <v>54</v>
@@ -13269,7 +13269,7 @@
         <v>57</v>
       </c>
       <c r="D398">
-        <v>9.5022356211700541E-3</v>
+        <v>9.5022356211700611E-3</v>
       </c>
       <c r="E398" t="s">
         <v>54</v>
@@ -13281,7 +13281,7 @@
         <v>57</v>
       </c>
       <c r="I398">
-        <v>9.6479505441785532E-2</v>
+        <v>9.6479505441784935E-2</v>
       </c>
       <c r="J398" t="s">
         <v>54</v>
@@ -13295,7 +13295,7 @@
         <v>58</v>
       </c>
       <c r="D399">
-        <v>0.32010021309416786</v>
+        <v>0.32010021309416808</v>
       </c>
       <c r="E399" t="s">
         <v>54</v>
@@ -13307,7 +13307,7 @@
         <v>58</v>
       </c>
       <c r="I399">
-        <v>9.8096806141933154E-2</v>
+        <v>9.8096806141932544E-2</v>
       </c>
       <c r="J399" t="s">
         <v>54</v>
@@ -13321,7 +13321,7 @@
         <v>59</v>
       </c>
       <c r="D400">
-        <v>4.7768419174705748E-3</v>
+        <v>4.7768419174705782E-3</v>
       </c>
       <c r="E400" t="s">
         <v>54</v>
@@ -13333,7 +13333,7 @@
         <v>59</v>
       </c>
       <c r="I400">
-        <v>7.1653950287266663E-2</v>
+        <v>7.1653950287266219E-2</v>
       </c>
       <c r="J400" t="s">
         <v>54</v>
@@ -13347,7 +13347,7 @@
         <v>60</v>
       </c>
       <c r="D401">
-        <v>1.5210266073167061E-2</v>
+        <v>1.5210266073167071E-2</v>
       </c>
       <c r="E401" t="s">
         <v>54</v>
@@ -13359,7 +13359,7 @@
         <v>60</v>
       </c>
       <c r="I401">
-        <v>4.7299313345171554E-2</v>
+        <v>4.7299313345171262E-2</v>
       </c>
       <c r="J401" t="s">
         <v>54</v>
@@ -13373,7 +13373,7 @@
         <v>61</v>
       </c>
       <c r="D402">
-        <v>0.35497159781231691</v>
+        <v>0.35497159781231713</v>
       </c>
       <c r="E402" t="s">
         <v>54</v>
@@ -13385,7 +13385,7 @@
         <v>61</v>
       </c>
       <c r="I402">
-        <v>4.8782112433773561E-2</v>
+        <v>4.8782112433773256E-2</v>
       </c>
       <c r="J402" t="s">
         <v>54</v>
@@ -13399,7 +13399,7 @@
         <v>62</v>
       </c>
       <c r="D403">
-        <v>1.0320344348460164E-2</v>
+        <v>1.0320344348460171E-2</v>
       </c>
       <c r="E403" t="s">
         <v>54</v>
@@ -13411,7 +13411,7 @@
         <v>62</v>
       </c>
       <c r="I403">
-        <v>3.8455964398908762E-2</v>
+        <v>3.8455964398908526E-2</v>
       </c>
       <c r="J403" t="s">
         <v>54</v>
@@ -13425,7 +13425,7 @@
         <v>63</v>
       </c>
       <c r="D404">
-        <v>2.3062975749886072E-3</v>
+        <v>2.3062975749886089E-3</v>
       </c>
       <c r="E404" t="s">
         <v>54</v>
@@ -13437,7 +13437,7 @@
         <v>63</v>
       </c>
       <c r="I404">
-        <v>8.7098572879119263E-2</v>
+        <v>8.7098572879118721E-2</v>
       </c>
       <c r="J404" t="s">
         <v>54</v>
@@ -13451,7 +13451,7 @@
         <v>64</v>
       </c>
       <c r="D405">
-        <v>0.18741368726922267</v>
+        <v>0.18741368726922278</v>
       </c>
       <c r="E405" t="s">
         <v>54</v>
@@ -13463,7 +13463,7 @@
         <v>64</v>
       </c>
       <c r="I405">
-        <v>9.4752890363993952E-2</v>
+        <v>9.475289036399337E-2</v>
       </c>
       <c r="J405" t="s">
         <v>54</v>
@@ -13477,7 +13477,7 @@
         <v>65</v>
       </c>
       <c r="D406">
-        <v>3.3623601395225348E-4</v>
+        <v>3.362360139522537E-4</v>
       </c>
       <c r="E406" t="s">
         <v>54</v>
@@ -13489,7 +13489,7 @@
         <v>65</v>
       </c>
       <c r="I406">
-        <v>7.1607682271431994E-2</v>
+        <v>7.160768227143155E-2</v>
       </c>
       <c r="J406" t="s">
         <v>54</v>
@@ -13827,7 +13827,7 @@
         <v>53</v>
       </c>
       <c r="I419">
-        <v>0.11552635941687146</v>
+        <v>0.11552635941687144</v>
       </c>
       <c r="J419" t="s">
         <v>54</v>
@@ -13841,7 +13841,7 @@
         <v>55</v>
       </c>
       <c r="D420">
-        <v>9.8876495181457955E-2</v>
+        <v>9.8876495181458246E-2</v>
       </c>
       <c r="E420" t="s">
         <v>54</v>
@@ -13853,7 +13853,7 @@
         <v>55</v>
       </c>
       <c r="I420">
-        <v>0.13410082938656448</v>
+        <v>0.13410082938656445</v>
       </c>
       <c r="J420" t="s">
         <v>54</v>
@@ -13879,7 +13879,7 @@
         <v>56</v>
       </c>
       <c r="I421">
-        <v>8.9162809850298314E-2</v>
+        <v>8.91628098502983E-2</v>
       </c>
       <c r="J421" t="s">
         <v>54</v>
@@ -13893,7 +13893,7 @@
         <v>57</v>
       </c>
       <c r="D422">
-        <v>1.2182954688135392E-2</v>
+        <v>1.2182954688135426E-2</v>
       </c>
       <c r="E422" t="s">
         <v>54</v>
@@ -13905,7 +13905,7 @@
         <v>57</v>
       </c>
       <c r="I422">
-        <v>9.0101522805534809E-2</v>
+        <v>9.0101522805534795E-2</v>
       </c>
       <c r="J422" t="s">
         <v>54</v>
@@ -13919,7 +13919,7 @@
         <v>58</v>
       </c>
       <c r="D423">
-        <v>0.31606032085832386</v>
+        <v>0.31606032085832475</v>
       </c>
       <c r="E423" t="s">
         <v>54</v>
@@ -13931,7 +13931,7 @@
         <v>58</v>
       </c>
       <c r="I423">
-        <v>9.6418901099027968E-2</v>
+        <v>9.641890109902794E-2</v>
       </c>
       <c r="J423" t="s">
         <v>54</v>
@@ -13945,7 +13945,7 @@
         <v>59</v>
       </c>
       <c r="D424">
-        <v>3.2356749895535919E-3</v>
+        <v>3.2356749895536014E-3</v>
       </c>
       <c r="E424" t="s">
         <v>54</v>
@@ -13957,7 +13957,7 @@
         <v>59</v>
       </c>
       <c r="I424">
-        <v>7.0787813430331456E-2</v>
+        <v>7.0787813430331442E-2</v>
       </c>
       <c r="J424" t="s">
         <v>54</v>
@@ -13971,7 +13971,7 @@
         <v>60</v>
       </c>
       <c r="D425">
-        <v>2.0146857326147845E-2</v>
+        <v>2.0146857326147904E-2</v>
       </c>
       <c r="E425" t="s">
         <v>54</v>
@@ -13983,7 +13983,7 @@
         <v>60</v>
       </c>
       <c r="I425">
-        <v>4.8386769883397358E-2</v>
+        <v>4.8386769883397344E-2</v>
       </c>
       <c r="J425" t="s">
         <v>54</v>
@@ -13997,7 +13997,7 @@
         <v>61</v>
       </c>
       <c r="D426">
-        <v>0.36187445047994349</v>
+        <v>0.36187445047994454</v>
       </c>
       <c r="E426" t="s">
         <v>54</v>
@@ -14009,7 +14009,7 @@
         <v>61</v>
       </c>
       <c r="I426">
-        <v>5.8025094790740431E-2</v>
+        <v>5.8025094790740417E-2</v>
       </c>
       <c r="J426" t="s">
         <v>54</v>
@@ -14023,7 +14023,7 @@
         <v>62</v>
       </c>
       <c r="D427">
-        <v>8.1137137573402528E-3</v>
+        <v>8.1137137573402771E-3</v>
       </c>
       <c r="E427" t="s">
         <v>54</v>
@@ -14035,7 +14035,7 @@
         <v>62</v>
       </c>
       <c r="I427">
-        <v>4.0134745133888761E-2</v>
+        <v>4.0134745133888754E-2</v>
       </c>
       <c r="J427" t="s">
         <v>54</v>
@@ -14049,7 +14049,7 @@
         <v>63</v>
       </c>
       <c r="D428">
-        <v>3.1126212109078861E-3</v>
+        <v>3.1126212109078952E-3</v>
       </c>
       <c r="E428" t="s">
         <v>54</v>
@@ -14061,7 +14061,7 @@
         <v>63</v>
       </c>
       <c r="I428">
-        <v>8.7543810911219822E-2</v>
+        <v>8.7543810911219808E-2</v>
       </c>
       <c r="J428" t="s">
         <v>54</v>
@@ -14075,7 +14075,7 @@
         <v>64</v>
       </c>
       <c r="D429">
-        <v>0.17622422925150524</v>
+        <v>0.17622422925150574</v>
       </c>
       <c r="E429" t="s">
         <v>54</v>
@@ -14087,7 +14087,7 @@
         <v>64</v>
       </c>
       <c r="I429">
-        <v>0.10018248589426694</v>
+        <v>0.10018248589426691</v>
       </c>
       <c r="J429" t="s">
         <v>54</v>
@@ -14101,7 +14101,7 @@
         <v>65</v>
       </c>
       <c r="D430">
-        <v>1.7268225668158312E-4</v>
+        <v>1.7268225668158361E-4</v>
       </c>
       <c r="E430" t="s">
         <v>54</v>
@@ -14113,7 +14113,7 @@
         <v>65</v>
       </c>
       <c r="I430">
-        <v>6.9628857397858471E-2</v>
+        <v>6.9628857397858457E-2</v>
       </c>
       <c r="J430" t="s">
         <v>54</v>
@@ -14139,7 +14139,7 @@
         <v>53</v>
       </c>
       <c r="I431">
-        <v>0.10555878701514913</v>
+        <v>0.10555878701514915</v>
       </c>
       <c r="J431" t="s">
         <v>54</v>
@@ -14165,7 +14165,7 @@
         <v>55</v>
       </c>
       <c r="I432">
-        <v>0.13054977148471003</v>
+        <v>0.13054977148471006</v>
       </c>
       <c r="J432" t="s">
         <v>54</v>
@@ -14191,7 +14191,7 @@
         <v>56</v>
       </c>
       <c r="I433">
-        <v>8.5178046489688228E-2</v>
+        <v>8.5178046489688242E-2</v>
       </c>
       <c r="J433" t="s">
         <v>54</v>
@@ -14217,7 +14217,7 @@
         <v>57</v>
       </c>
       <c r="I434">
-        <v>9.3403442117582558E-2</v>
+        <v>9.3403442117582572E-2</v>
       </c>
       <c r="J434" t="s">
         <v>54</v>
@@ -14243,7 +14243,7 @@
         <v>58</v>
       </c>
       <c r="I435">
-        <v>8.7487524527171512E-2</v>
+        <v>8.7487524527171526E-2</v>
       </c>
       <c r="J435" t="s">
         <v>54</v>
@@ -14269,7 +14269,7 @@
         <v>59</v>
       </c>
       <c r="I436">
-        <v>6.7591946873030329E-2</v>
+        <v>6.7591946873030342E-2</v>
       </c>
       <c r="J436" t="s">
         <v>54</v>
@@ -14295,7 +14295,7 @@
         <v>60</v>
       </c>
       <c r="I437">
-        <v>5.2983119650627443E-2</v>
+        <v>5.298311965062745E-2</v>
       </c>
       <c r="J437" t="s">
         <v>54</v>
@@ -14321,7 +14321,7 @@
         <v>61</v>
       </c>
       <c r="I438">
-        <v>6.0645378966110802E-2</v>
+        <v>6.0645378966110809E-2</v>
       </c>
       <c r="J438" t="s">
         <v>54</v>
@@ -14347,7 +14347,7 @@
         <v>62</v>
       </c>
       <c r="I439">
-        <v>4.2022956669992249E-2</v>
+        <v>4.2022956669992256E-2</v>
       </c>
       <c r="J439" t="s">
         <v>54</v>
@@ -14373,7 +14373,7 @@
         <v>63</v>
       </c>
       <c r="I440">
-        <v>8.9942056418397434E-2</v>
+        <v>8.9942056418397448E-2</v>
       </c>
       <c r="J440" t="s">
         <v>54</v>
@@ -14399,7 +14399,7 @@
         <v>64</v>
       </c>
       <c r="I441">
-        <v>0.10885363580062207</v>
+        <v>0.10885363580062209</v>
       </c>
       <c r="J441" t="s">
         <v>54</v>
@@ -14425,7 +14425,7 @@
         <v>65</v>
       </c>
       <c r="I442">
-        <v>7.5783333986918069E-2</v>
+        <v>7.5783333986918083E-2</v>
       </c>
       <c r="J442" t="s">
         <v>54</v>
@@ -14465,7 +14465,7 @@
         <v>55</v>
       </c>
       <c r="D444">
-        <v>8.7220264056828672E-2</v>
+        <v>8.7220264056828492E-2</v>
       </c>
       <c r="E444" t="s">
         <v>54</v>
@@ -14517,7 +14517,7 @@
         <v>57</v>
       </c>
       <c r="D446">
-        <v>1.4520895687120295E-2</v>
+        <v>1.4520895687120266E-2</v>
       </c>
       <c r="E446" t="s">
         <v>54</v>
@@ -14543,7 +14543,7 @@
         <v>58</v>
       </c>
       <c r="D447">
-        <v>0.35209049714328339</v>
+        <v>0.35209049714328267</v>
       </c>
       <c r="E447" t="s">
         <v>54</v>
@@ -14569,7 +14569,7 @@
         <v>59</v>
       </c>
       <c r="D448">
-        <v>3.2596505121816558E-3</v>
+        <v>3.2596505121816493E-3</v>
       </c>
       <c r="E448" t="s">
         <v>54</v>
@@ -14595,7 +14595,7 @@
         <v>60</v>
       </c>
       <c r="D449">
-        <v>2.1594465354442299E-2</v>
+        <v>2.1594465354442257E-2</v>
       </c>
       <c r="E449" t="s">
         <v>54</v>
@@ -14621,7 +14621,7 @@
         <v>61</v>
       </c>
       <c r="D450">
-        <v>0.35569086701387764</v>
+        <v>0.35569086701387692</v>
       </c>
       <c r="E450" t="s">
         <v>54</v>
@@ -14647,7 +14647,7 @@
         <v>62</v>
       </c>
       <c r="D451">
-        <v>8.3770904969941874E-3</v>
+        <v>8.37709049699417E-3</v>
       </c>
       <c r="E451" t="s">
         <v>54</v>
@@ -14673,7 +14673,7 @@
         <v>63</v>
       </c>
       <c r="D452">
-        <v>2.8704710941938913E-3</v>
+        <v>2.8704710941938856E-3</v>
       </c>
       <c r="E452" t="s">
         <v>54</v>
@@ -14699,7 +14699,7 @@
         <v>64</v>
       </c>
       <c r="D453">
-        <v>0.15423858500460885</v>
+        <v>0.15423858500460855</v>
       </c>
       <c r="E453" t="s">
         <v>54</v>
@@ -14725,7 +14725,7 @@
         <v>65</v>
       </c>
       <c r="D454">
-        <v>1.3721363647109492E-4</v>
+        <v>1.3721363647109465E-4</v>
       </c>
       <c r="E454" t="s">
         <v>54</v>
@@ -14777,7 +14777,7 @@
         <v>55</v>
       </c>
       <c r="D456">
-        <v>8.8261473090673392E-2</v>
+        <v>8.8261473090673351E-2</v>
       </c>
       <c r="E456" t="s">
         <v>54</v>
@@ -14829,7 +14829,7 @@
         <v>57</v>
       </c>
       <c r="D458">
-        <v>8.5148670811821189E-3</v>
+        <v>8.5148670811821155E-3</v>
       </c>
       <c r="E458" t="s">
         <v>54</v>
@@ -14855,7 +14855,7 @@
         <v>58</v>
       </c>
       <c r="D459">
-        <v>0.33046288910119426</v>
+        <v>0.33046288910119409</v>
       </c>
       <c r="E459" t="s">
         <v>54</v>
@@ -14881,7 +14881,7 @@
         <v>59</v>
       </c>
       <c r="D460">
-        <v>5.6206442761318719E-3</v>
+        <v>5.6206442761318693E-3</v>
       </c>
       <c r="E460" t="s">
         <v>54</v>
@@ -14907,7 +14907,7 @@
         <v>60</v>
       </c>
       <c r="D461">
-        <v>1.4285543893438762E-2</v>
+        <v>1.4285543893438755E-2</v>
       </c>
       <c r="E461" t="s">
         <v>54</v>
@@ -14933,7 +14933,7 @@
         <v>61</v>
       </c>
       <c r="D462">
-        <v>0.36134533642885691</v>
+        <v>0.36134533642885674</v>
       </c>
       <c r="E462" t="s">
         <v>54</v>
@@ -14959,7 +14959,7 @@
         <v>62</v>
       </c>
       <c r="D463">
-        <v>1.1924801548218884E-2</v>
+        <v>1.1924801548218879E-2</v>
       </c>
       <c r="E463" t="s">
         <v>54</v>
@@ -14985,7 +14985,7 @@
         <v>63</v>
       </c>
       <c r="D464">
-        <v>1.7406426523700177E-3</v>
+        <v>1.7406426523700169E-3</v>
       </c>
       <c r="E464" t="s">
         <v>54</v>
@@ -15011,7 +15011,7 @@
         <v>64</v>
       </c>
       <c r="D465">
-        <v>0.17739078535583885</v>
+        <v>0.17739078535583877</v>
       </c>
       <c r="E465" t="s">
         <v>54</v>
@@ -15037,7 +15037,7 @@
         <v>65</v>
       </c>
       <c r="D466">
-        <v>4.5301657209538987E-4</v>
+        <v>4.5301657209538966E-4</v>
       </c>
       <c r="E466" t="s">
         <v>54</v>
@@ -15089,7 +15089,7 @@
         <v>55</v>
       </c>
       <c r="D468">
-        <v>0.11739607428841389</v>
+        <v>0.11739607428841368</v>
       </c>
       <c r="E468" t="s">
         <v>54</v>
@@ -15141,7 +15141,7 @@
         <v>57</v>
       </c>
       <c r="D470">
-        <v>8.9399397488018114E-3</v>
+        <v>8.9399397488017958E-3</v>
       </c>
       <c r="E470" t="s">
         <v>54</v>
@@ -15167,7 +15167,7 @@
         <v>58</v>
       </c>
       <c r="D471">
-        <v>0.29218948641847642</v>
+        <v>0.29218948641847592</v>
       </c>
       <c r="E471" t="s">
         <v>54</v>
@@ -15193,7 +15193,7 @@
         <v>59</v>
       </c>
       <c r="D472">
-        <v>4.2858048486052666E-3</v>
+        <v>4.2858048486052588E-3</v>
       </c>
       <c r="E472" t="s">
         <v>54</v>
@@ -15219,7 +15219,7 @@
         <v>60</v>
       </c>
       <c r="D473">
-        <v>1.3810296194278695E-2</v>
+        <v>1.3810296194278671E-2</v>
       </c>
       <c r="E473" t="s">
         <v>54</v>
@@ -15245,7 +15245,7 @@
         <v>61</v>
       </c>
       <c r="D474">
-        <v>0.3479815867222999</v>
+        <v>0.34798158672229929</v>
       </c>
       <c r="E474" t="s">
         <v>54</v>
@@ -15271,7 +15271,7 @@
         <v>62</v>
       </c>
       <c r="D475">
-        <v>9.3844158442228705E-3</v>
+        <v>9.3844158442228532E-3</v>
       </c>
       <c r="E475" t="s">
         <v>54</v>
@@ -15297,7 +15297,7 @@
         <v>63</v>
       </c>
       <c r="D476">
-        <v>2.2096997287939842E-3</v>
+        <v>2.2096997287939803E-3</v>
       </c>
       <c r="E476" t="s">
         <v>54</v>
@@ -15323,7 +15323,7 @@
         <v>64</v>
       </c>
       <c r="D477">
-        <v>0.20346474715044788</v>
+        <v>0.20346474715044752</v>
       </c>
       <c r="E477" t="s">
         <v>54</v>
@@ -15349,7 +15349,7 @@
         <v>65</v>
       </c>
       <c r="D478">
-        <v>3.3794905566100877E-4</v>
+        <v>3.3794905566100818E-4</v>
       </c>
       <c r="E478" t="s">
         <v>54</v>
@@ -15387,7 +15387,7 @@
         <v>53</v>
       </c>
       <c r="I479">
-        <v>0.11352206300131859</v>
+        <v>0.1135220630013187</v>
       </c>
       <c r="J479" t="s">
         <v>54</v>
@@ -15413,7 +15413,7 @@
         <v>55</v>
       </c>
       <c r="I480">
-        <v>0.13632288991844044</v>
+        <v>0.13632288991844058</v>
       </c>
       <c r="J480" t="s">
         <v>54</v>
@@ -15439,7 +15439,7 @@
         <v>56</v>
       </c>
       <c r="I481">
-        <v>8.7468204625782905E-2</v>
+        <v>8.7468204625782989E-2</v>
       </c>
       <c r="J481" t="s">
         <v>54</v>
@@ -15465,7 +15465,7 @@
         <v>57</v>
       </c>
       <c r="I482">
-        <v>8.9770466593666345E-2</v>
+        <v>8.9770466593666429E-2</v>
       </c>
       <c r="J482" t="s">
         <v>54</v>
@@ -15491,7 +15491,7 @@
         <v>58</v>
       </c>
       <c r="I483">
-        <v>9.1680897607541861E-2</v>
+        <v>9.1680897607541958E-2</v>
       </c>
       <c r="J483" t="s">
         <v>54</v>
@@ -15517,7 +15517,7 @@
         <v>59</v>
       </c>
       <c r="I484">
-        <v>6.8419255679156743E-2</v>
+        <v>6.8419255679156812E-2</v>
       </c>
       <c r="J484" t="s">
         <v>54</v>
@@ -15543,7 +15543,7 @@
         <v>60</v>
       </c>
       <c r="I485">
-        <v>4.9066061341198397E-2</v>
+        <v>4.9066061341198446E-2</v>
       </c>
       <c r="J485" t="s">
         <v>54</v>
@@ -15569,7 +15569,7 @@
         <v>61</v>
       </c>
       <c r="I486">
-        <v>5.9169217980861243E-2</v>
+        <v>5.9169217980861305E-2</v>
       </c>
       <c r="J486" t="s">
         <v>54</v>
@@ -15595,7 +15595,7 @@
         <v>62</v>
       </c>
       <c r="I487">
-        <v>3.9753952686060592E-2</v>
+        <v>3.9753952686060634E-2</v>
       </c>
       <c r="J487" t="s">
         <v>54</v>
@@ -15621,7 +15621,7 @@
         <v>63</v>
       </c>
       <c r="I488">
-        <v>8.8540882320344211E-2</v>
+        <v>8.8540882320344294E-2</v>
       </c>
       <c r="J488" t="s">
         <v>54</v>
@@ -15647,7 +15647,7 @@
         <v>64</v>
       </c>
       <c r="I489">
-        <v>0.10364873220276064</v>
+        <v>0.10364873220276073</v>
       </c>
       <c r="J489" t="s">
         <v>54</v>
@@ -15673,7 +15673,7 @@
         <v>65</v>
       </c>
       <c r="I490">
-        <v>7.2637376042867088E-2</v>
+        <v>7.2637376042867158E-2</v>
       </c>
       <c r="J490" t="s">
         <v>54</v>
@@ -15699,7 +15699,7 @@
         <v>53</v>
       </c>
       <c r="I491">
-        <v>0.11464516703557691</v>
+        <v>0.11464516703557617</v>
       </c>
       <c r="J491" t="s">
         <v>54</v>
@@ -15725,7 +15725,7 @@
         <v>55</v>
       </c>
       <c r="I492">
-        <v>0.13585818222306217</v>
+        <v>0.13585818222306129</v>
       </c>
       <c r="J492" t="s">
         <v>54</v>
@@ -15751,7 +15751,7 @@
         <v>56</v>
       </c>
       <c r="I493">
-        <v>8.9000352632348956E-2</v>
+        <v>8.9000352632348387E-2</v>
       </c>
       <c r="J493" t="s">
         <v>54</v>
@@ -15777,7 +15777,7 @@
         <v>57</v>
       </c>
       <c r="I494">
-        <v>9.7006947938435562E-2</v>
+        <v>9.7006947938434937E-2</v>
       </c>
       <c r="J494" t="s">
         <v>54</v>
@@ -15803,7 +15803,7 @@
         <v>58</v>
       </c>
       <c r="I495">
-        <v>9.7348086499939229E-2</v>
+        <v>9.7348086499938605E-2</v>
       </c>
       <c r="J495" t="s">
         <v>54</v>
@@ -15829,7 +15829,7 @@
         <v>59</v>
       </c>
       <c r="I496">
-        <v>7.1578799001660684E-2</v>
+        <v>7.1578799001660226E-2</v>
       </c>
       <c r="J496" t="s">
         <v>54</v>
@@ -15855,7 +15855,7 @@
         <v>60</v>
       </c>
       <c r="I497">
-        <v>4.8121079569699285E-2</v>
+        <v>4.8121079569698973E-2</v>
       </c>
       <c r="J497" t="s">
         <v>54</v>
@@ -15881,7 +15881,7 @@
         <v>61</v>
       </c>
       <c r="I498">
-        <v>5.159873531196895E-2</v>
+        <v>5.1598735311968617E-2</v>
       </c>
       <c r="J498" t="s">
         <v>54</v>
@@ -15907,7 +15907,7 @@
         <v>62</v>
       </c>
       <c r="I499">
-        <v>4.0229799780873363E-2</v>
+        <v>4.0229799780873106E-2</v>
       </c>
       <c r="J499" t="s">
         <v>54</v>
@@ -15933,7 +15933,7 @@
         <v>63</v>
       </c>
       <c r="I500">
-        <v>8.5465417773332872E-2</v>
+        <v>8.5465417773332317E-2</v>
       </c>
       <c r="J500" t="s">
         <v>54</v>
@@ -15959,7 +15959,7 @@
         <v>64</v>
       </c>
       <c r="I501">
-        <v>9.6624590766253515E-2</v>
+        <v>9.6624590766252891E-2</v>
       </c>
       <c r="J501" t="s">
         <v>54</v>
@@ -15985,7 +15985,7 @@
         <v>65</v>
       </c>
       <c r="I502">
-        <v>7.2522841466855004E-2</v>
+        <v>7.2522841466854532E-2</v>
       </c>
       <c r="J502" t="s">
         <v>54</v>
@@ -16011,7 +16011,7 @@
         <v>53</v>
       </c>
       <c r="I503">
-        <v>0.10555021684222023</v>
+        <v>0.10555021684221999</v>
       </c>
       <c r="J503" t="s">
         <v>54</v>
@@ -16025,7 +16025,7 @@
         <v>55</v>
       </c>
       <c r="D504">
-        <v>0.13386017449316917</v>
+        <v>0.13386017449316884</v>
       </c>
       <c r="E504" t="s">
         <v>54</v>
@@ -16037,7 +16037,7 @@
         <v>55</v>
       </c>
       <c r="I504">
-        <v>0.12720937189882031</v>
+        <v>0.12720937189882003</v>
       </c>
       <c r="J504" t="s">
         <v>54</v>
@@ -16063,7 +16063,7 @@
         <v>56</v>
       </c>
       <c r="I505">
-        <v>8.5333603019770402E-2</v>
+        <v>8.5333603019770207E-2</v>
       </c>
       <c r="J505" t="s">
         <v>54</v>
@@ -16077,7 +16077,7 @@
         <v>57</v>
       </c>
       <c r="D506">
-        <v>9.7794660770292047E-3</v>
+        <v>9.7794660770291805E-3</v>
       </c>
       <c r="E506" t="s">
         <v>54</v>
@@ -16089,7 +16089,7 @@
         <v>57</v>
       </c>
       <c r="I506">
-        <v>9.3943978265127556E-2</v>
+        <v>9.3943978265127348E-2</v>
       </c>
       <c r="J506" t="s">
         <v>54</v>
@@ -16103,7 +16103,7 @@
         <v>58</v>
       </c>
       <c r="D507">
-        <v>0.29555846877992875</v>
+        <v>0.29555846877992803</v>
       </c>
       <c r="E507" t="s">
         <v>54</v>
@@ -16115,7 +16115,7 @@
         <v>58</v>
       </c>
       <c r="I507">
-        <v>8.8222482589221773E-2</v>
+        <v>8.8222482589221579E-2</v>
       </c>
       <c r="J507" t="s">
         <v>54</v>
@@ -16129,7 +16129,7 @@
         <v>59</v>
       </c>
       <c r="D508">
-        <v>3.7510040352699489E-3</v>
+        <v>3.7510040352699398E-3</v>
       </c>
       <c r="E508" t="s">
         <v>54</v>
@@ -16141,7 +16141,7 @@
         <v>59</v>
       </c>
       <c r="I508">
-        <v>6.7965315366588869E-2</v>
+        <v>6.7965315366588716E-2</v>
       </c>
       <c r="J508" t="s">
         <v>54</v>
@@ -16155,7 +16155,7 @@
         <v>60</v>
       </c>
       <c r="D509">
-        <v>1.4763481837044979E-2</v>
+        <v>1.4763481837044942E-2</v>
       </c>
       <c r="E509" t="s">
         <v>54</v>
@@ -16167,7 +16167,7 @@
         <v>60</v>
       </c>
       <c r="I509">
-        <v>5.5835882783186977E-2</v>
+        <v>5.5835882783186852E-2</v>
       </c>
       <c r="J509" t="s">
         <v>54</v>
@@ -16181,7 +16181,7 @@
         <v>61</v>
       </c>
       <c r="D510">
-        <v>0.33197930543323095</v>
+        <v>0.33197930543323012</v>
       </c>
       <c r="E510" t="s">
         <v>54</v>
@@ -16193,7 +16193,7 @@
         <v>61</v>
       </c>
       <c r="I510">
-        <v>5.8557377009233025E-2</v>
+        <v>5.8557377009232893E-2</v>
       </c>
       <c r="J510" t="s">
         <v>54</v>
@@ -16207,7 +16207,7 @@
         <v>62</v>
       </c>
       <c r="D511">
-        <v>7.9629707401194343E-3</v>
+        <v>7.9629707401194152E-3</v>
       </c>
       <c r="E511" t="s">
         <v>54</v>
@@ -16219,7 +16219,7 @@
         <v>62</v>
       </c>
       <c r="I511">
-        <v>4.2937075577245097E-2</v>
+        <v>4.2937075577245E-2</v>
       </c>
       <c r="J511" t="s">
         <v>54</v>
@@ -16233,7 +16233,7 @@
         <v>63</v>
       </c>
       <c r="D512">
-        <v>2.6479659681460919E-3</v>
+        <v>2.6479659681460854E-3</v>
       </c>
       <c r="E512" t="s">
         <v>54</v>
@@ -16245,7 +16245,7 @@
         <v>63</v>
       </c>
       <c r="I512">
-        <v>9.1586138024080221E-2</v>
+        <v>9.1586138024080013E-2</v>
       </c>
       <c r="J512" t="s">
         <v>54</v>
@@ -16259,7 +16259,7 @@
         <v>64</v>
       </c>
       <c r="D513">
-        <v>0.19942517939722129</v>
+        <v>0.19942517939722079</v>
       </c>
       <c r="E513" t="s">
         <v>54</v>
@@ -16271,7 +16271,7 @@
         <v>64</v>
       </c>
       <c r="I513">
-        <v>0.10662703736411645</v>
+        <v>0.10662703736411622</v>
       </c>
       <c r="J513" t="s">
         <v>54</v>
@@ -16285,7 +16285,7 @@
         <v>65</v>
       </c>
       <c r="D514">
-        <v>2.719832388425885E-4</v>
+        <v>2.7198323884258785E-4</v>
       </c>
       <c r="E514" t="s">
         <v>54</v>
@@ -16297,7 +16297,7 @@
         <v>65</v>
       </c>
       <c r="I514">
-        <v>7.6231521260391344E-2</v>
+        <v>7.6231521260391177E-2</v>
       </c>
       <c r="J514" t="s">
         <v>54</v>
@@ -16337,7 +16337,7 @@
         <v>55</v>
       </c>
       <c r="D516">
-        <v>8.7157492255883096E-2</v>
+        <v>8.7157492255883248E-2</v>
       </c>
       <c r="E516" t="s">
         <v>54</v>
@@ -16389,7 +16389,7 @@
         <v>57</v>
       </c>
       <c r="D518">
-        <v>1.0929021693013899E-2</v>
+        <v>1.0929021693013918E-2</v>
       </c>
       <c r="E518" t="s">
         <v>54</v>
@@ -16415,7 +16415,7 @@
         <v>58</v>
       </c>
       <c r="D519">
-        <v>0.35792184522688053</v>
+        <v>0.35792184522688114</v>
       </c>
       <c r="E519" t="s">
         <v>54</v>
@@ -16441,7 +16441,7 @@
         <v>59</v>
       </c>
       <c r="D520">
-        <v>4.4731266883965143E-3</v>
+        <v>4.4731266883965221E-3</v>
       </c>
       <c r="E520" t="s">
         <v>54</v>
@@ -16467,7 +16467,7 @@
         <v>60</v>
       </c>
       <c r="D521">
-        <v>1.7528682052228458E-2</v>
+        <v>1.7528682052228489E-2</v>
       </c>
       <c r="E521" t="s">
         <v>54</v>
@@ -16493,7 +16493,7 @@
         <v>61</v>
       </c>
       <c r="D522">
-        <v>0.33976287338505001</v>
+        <v>0.33976287338505062</v>
       </c>
       <c r="E522" t="s">
         <v>54</v>
@@ -16519,7 +16519,7 @@
         <v>62</v>
       </c>
       <c r="D523">
-        <v>9.9996452053920017E-3</v>
+        <v>9.9996452053920191E-3</v>
       </c>
       <c r="E523" t="s">
         <v>54</v>
@@ -16545,7 +16545,7 @@
         <v>63</v>
       </c>
       <c r="D524">
-        <v>2.3418568626361411E-3</v>
+        <v>2.3418568626361455E-3</v>
       </c>
       <c r="E524" t="s">
         <v>54</v>
@@ -16571,7 +16571,7 @@
         <v>64</v>
       </c>
       <c r="D525">
-        <v>0.16958568466806534</v>
+        <v>0.16958568466806564</v>
       </c>
       <c r="E525" t="s">
         <v>54</v>
@@ -16597,7 +16597,7 @@
         <v>65</v>
       </c>
       <c r="D526">
-        <v>2.997719624522132E-4</v>
+        <v>2.9977196245221374E-4</v>
       </c>
       <c r="E526" t="s">
         <v>54</v>
@@ -16649,7 +16649,7 @@
         <v>55</v>
       </c>
       <c r="D528">
-        <v>9.4516498750928643E-2</v>
+        <v>9.451649875092856E-2</v>
       </c>
       <c r="E528" t="s">
         <v>54</v>
@@ -16701,7 +16701,7 @@
         <v>57</v>
       </c>
       <c r="D530">
-        <v>1.105182550824544E-2</v>
+        <v>1.105182550824543E-2</v>
       </c>
       <c r="E530" t="s">
         <v>54</v>
@@ -16727,7 +16727,7 @@
         <v>58</v>
       </c>
       <c r="D531">
-        <v>0.32725948942512306</v>
+        <v>0.32725948942512278</v>
       </c>
       <c r="E531" t="s">
         <v>54</v>
@@ -16753,7 +16753,7 @@
         <v>59</v>
       </c>
       <c r="D532">
-        <v>3.7764683635622145E-3</v>
+        <v>3.776468363562211E-3</v>
       </c>
       <c r="E532" t="s">
         <v>54</v>
@@ -16779,7 +16779,7 @@
         <v>60</v>
       </c>
       <c r="D533">
-        <v>1.8387082683893736E-2</v>
+        <v>1.8387082683893718E-2</v>
       </c>
       <c r="E533" t="s">
         <v>54</v>
@@ -16805,7 +16805,7 @@
         <v>61</v>
       </c>
       <c r="D534">
-        <v>0.35495878944535969</v>
+        <v>0.35495878944535936</v>
       </c>
       <c r="E534" t="s">
         <v>54</v>
@@ -16831,7 +16831,7 @@
         <v>62</v>
       </c>
       <c r="D535">
-        <v>9.0056668901892806E-3</v>
+        <v>9.005666890189272E-3</v>
       </c>
       <c r="E535" t="s">
         <v>54</v>
@@ -16857,7 +16857,7 @@
         <v>63</v>
       </c>
       <c r="D536">
-        <v>2.728695865813517E-3</v>
+        <v>2.7286958658135144E-3</v>
       </c>
       <c r="E536" t="s">
         <v>54</v>
@@ -16883,7 +16883,7 @@
         <v>64</v>
       </c>
       <c r="D537">
-        <v>0.17806186308006883</v>
+        <v>0.17806186308006866</v>
       </c>
       <c r="E537" t="s">
         <v>54</v>
@@ -16909,7 +16909,7 @@
         <v>65</v>
       </c>
       <c r="D538">
-        <v>2.5361998681644427E-4</v>
+        <v>2.5361998681644406E-4</v>
       </c>
       <c r="E538" t="s">
         <v>54</v>
@@ -16947,7 +16947,7 @@
         <v>53</v>
       </c>
       <c r="I539">
-        <v>0.12072860367510714</v>
+        <v>0.12072860367510733</v>
       </c>
       <c r="J539" t="s">
         <v>54</v>
@@ -16961,7 +16961,7 @@
         <v>55</v>
       </c>
       <c r="D540">
-        <v>0.10465182157274405</v>
+        <v>0.10465182157274425</v>
       </c>
       <c r="E540" t="s">
         <v>54</v>
@@ -16973,7 +16973,7 @@
         <v>55</v>
       </c>
       <c r="I540">
-        <v>0.14029067626240008</v>
+        <v>0.1402906762624003</v>
       </c>
       <c r="J540" t="s">
         <v>54</v>
@@ -16999,7 +16999,7 @@
         <v>56</v>
       </c>
       <c r="I541">
-        <v>9.1457074871010416E-2</v>
+        <v>9.1457074871010569E-2</v>
       </c>
       <c r="J541" t="s">
         <v>54</v>
@@ -17013,7 +17013,7 @@
         <v>57</v>
       </c>
       <c r="D542">
-        <v>8.6835979108753174E-3</v>
+        <v>8.683597910875333E-3</v>
       </c>
       <c r="E542" t="s">
         <v>54</v>
@@ -17025,7 +17025,7 @@
         <v>57</v>
       </c>
       <c r="I542">
-        <v>9.6196775817514901E-2</v>
+        <v>9.6196775817515068E-2</v>
       </c>
       <c r="J542" t="s">
         <v>54</v>
@@ -17039,7 +17039,7 @@
         <v>58</v>
       </c>
       <c r="D543">
-        <v>0.30440845326879185</v>
+        <v>0.3044084532687924</v>
       </c>
       <c r="E543" t="s">
         <v>54</v>
@@ -17051,7 +17051,7 @@
         <v>58</v>
       </c>
       <c r="I543">
-        <v>9.8268486092539631E-2</v>
+        <v>9.8268486092539797E-2</v>
       </c>
       <c r="J543" t="s">
         <v>54</v>
@@ -17065,7 +17065,7 @@
         <v>59</v>
       </c>
       <c r="D544">
-        <v>4.9920096319561822E-3</v>
+        <v>4.9920096319561917E-3</v>
       </c>
       <c r="E544" t="s">
         <v>54</v>
@@ -17077,7 +17077,7 @@
         <v>59</v>
       </c>
       <c r="I544">
-        <v>7.0907528893050825E-2</v>
+        <v>7.090752889305095E-2</v>
       </c>
       <c r="J544" t="s">
         <v>54</v>
@@ -17091,7 +17091,7 @@
         <v>60</v>
       </c>
       <c r="D545">
-        <v>1.3950553444840164E-2</v>
+        <v>1.395055344484019E-2</v>
       </c>
       <c r="E545" t="s">
         <v>54</v>
@@ -17103,7 +17103,7 @@
         <v>60</v>
       </c>
       <c r="I545">
-        <v>4.5457947981830567E-2</v>
+        <v>4.5457947981830643E-2</v>
       </c>
       <c r="J545" t="s">
         <v>54</v>
@@ -17117,7 +17117,7 @@
         <v>61</v>
       </c>
       <c r="D546">
-        <v>0.3562099517802193</v>
+        <v>0.35620995178021997</v>
       </c>
       <c r="E546" t="s">
         <v>54</v>
@@ -17129,7 +17129,7 @@
         <v>61</v>
       </c>
       <c r="I546">
-        <v>4.7341451030656422E-2</v>
+        <v>4.7341451030656498E-2</v>
       </c>
       <c r="J546" t="s">
         <v>54</v>
@@ -17143,7 +17143,7 @@
         <v>62</v>
       </c>
       <c r="D547">
-        <v>1.0765213606611305E-2</v>
+        <v>1.0765213606611326E-2</v>
       </c>
       <c r="E547" t="s">
         <v>54</v>
@@ -17155,7 +17155,7 @@
         <v>62</v>
       </c>
       <c r="I547">
-        <v>3.8052304975077438E-2</v>
+        <v>3.80523049750775E-2</v>
       </c>
       <c r="J547" t="s">
         <v>54</v>
@@ -17169,7 +17169,7 @@
         <v>63</v>
       </c>
       <c r="D548">
-        <v>1.9196735925759798E-3</v>
+        <v>1.9196735925759835E-3</v>
       </c>
       <c r="E548" t="s">
         <v>54</v>
@@ -17181,7 +17181,7 @@
         <v>63</v>
       </c>
       <c r="I548">
-        <v>8.6886708171556873E-2</v>
+        <v>8.6886708171557012E-2</v>
       </c>
       <c r="J548" t="s">
         <v>54</v>
@@ -17195,7 +17195,7 @@
         <v>64</v>
       </c>
       <c r="D549">
-        <v>0.19403976900771297</v>
+        <v>0.19403976900771333</v>
       </c>
       <c r="E549" t="s">
         <v>54</v>
@@ -17207,7 +17207,7 @@
         <v>64</v>
       </c>
       <c r="I549">
-        <v>9.3844958035267975E-2</v>
+        <v>9.3844958035268128E-2</v>
       </c>
       <c r="J549" t="s">
         <v>54</v>
@@ -17221,7 +17221,7 @@
         <v>65</v>
       </c>
       <c r="D550">
-        <v>3.7895618367099021E-4</v>
+        <v>3.7895618367099091E-4</v>
       </c>
       <c r="E550" t="s">
         <v>54</v>
@@ -17233,7 +17233,7 @@
         <v>65</v>
       </c>
       <c r="I550">
-        <v>7.0567484193986035E-2</v>
+        <v>7.0567484193986146E-2</v>
       </c>
       <c r="J550" t="s">
         <v>54</v>
@@ -17261,7 +17261,7 @@
         <v>55</v>
       </c>
       <c r="D552">
-        <v>8.3116421992633069E-2</v>
+        <v>8.3116421992633083E-2</v>
       </c>
       <c r="E552" t="s">
         <v>54</v>
@@ -17289,7 +17289,7 @@
         <v>57</v>
       </c>
       <c r="D554">
-        <v>1.0304651438777042E-2</v>
+        <v>1.0304651438777044E-2</v>
       </c>
       <c r="E554" t="s">
         <v>54</v>
@@ -17303,7 +17303,7 @@
         <v>58</v>
       </c>
       <c r="D555">
-        <v>0.35962648615007131</v>
+        <v>0.35962648615007137</v>
       </c>
       <c r="E555" t="s">
         <v>54</v>
@@ -17317,7 +17317,7 @@
         <v>59</v>
       </c>
       <c r="D556">
-        <v>5.4505182634397532E-3</v>
+        <v>5.4505182634397541E-3</v>
       </c>
       <c r="E556" t="s">
         <v>54</v>
@@ -17331,7 +17331,7 @@
         <v>60</v>
       </c>
       <c r="D557">
-        <v>1.6537709752261039E-2</v>
+        <v>1.6537709752261043E-2</v>
       </c>
       <c r="E557" t="s">
         <v>54</v>
@@ -17345,7 +17345,7 @@
         <v>61</v>
       </c>
       <c r="D558">
-        <v>0.3422389390794276</v>
+        <v>0.34223893907942765</v>
       </c>
       <c r="E558" t="s">
         <v>54</v>
@@ -17359,7 +17359,7 @@
         <v>62</v>
       </c>
       <c r="D559">
-        <v>1.1237176858844504E-2</v>
+        <v>1.1237176858844506E-2</v>
       </c>
       <c r="E559" t="s">
         <v>54</v>
@@ -17373,7 +17373,7 @@
         <v>63</v>
       </c>
       <c r="D560">
-        <v>2.0432626750845951E-3</v>
+        <v>2.0432626750845955E-3</v>
       </c>
       <c r="E560" t="s">
         <v>54</v>
@@ -17387,7 +17387,7 @@
         <v>64</v>
       </c>
       <c r="D561">
-        <v>0.16906214861766791</v>
+        <v>0.16906214861766794</v>
       </c>
       <c r="E561" t="s">
         <v>54</v>
@@ -17401,7 +17401,7 @@
         <v>65</v>
       </c>
       <c r="D562">
-        <v>3.8268517179314358E-4</v>
+        <v>3.8268517179314363E-4</v>
       </c>
       <c r="E562" t="s">
         <v>54</v>
@@ -17583,7 +17583,7 @@
         <v>53</v>
       </c>
       <c r="D575">
-        <v>4.7896647289431011E-7</v>
+        <v>0</v>
       </c>
       <c r="E575" t="s">
         <v>54</v>
@@ -17597,7 +17597,7 @@
         <v>55</v>
       </c>
       <c r="D576">
-        <v>0.10270627725902087</v>
+        <v>0.10270632645190725</v>
       </c>
       <c r="E576" t="s">
         <v>54</v>
@@ -17625,7 +17625,7 @@
         <v>57</v>
       </c>
       <c r="D578">
-        <v>1.3562997996987547E-2</v>
+        <v>1.3563004493211898E-2</v>
       </c>
       <c r="E578" t="s">
         <v>54</v>
@@ -17639,7 +17639,7 @@
         <v>58</v>
       </c>
       <c r="D579">
-        <v>0.31383231500567543</v>
+        <v>0.31383246532090275</v>
       </c>
       <c r="E579" t="s">
         <v>54</v>
@@ -17653,7 +17653,7 @@
         <v>59</v>
       </c>
       <c r="D580">
-        <v>2.8696598766836173E-3</v>
+        <v>2.86966125115513E-3</v>
       </c>
       <c r="E580" t="s">
         <v>54</v>
@@ -17667,7 +17667,7 @@
         <v>60</v>
       </c>
       <c r="D581">
-        <v>2.1283151547305455E-2</v>
+        <v>2.1283161741226252E-2</v>
       </c>
       <c r="E581" t="s">
         <v>54</v>
@@ -17681,7 +17681,7 @@
         <v>61</v>
       </c>
       <c r="D582">
-        <v>0.35516189577243529</v>
+        <v>0.35516206588315541</v>
       </c>
       <c r="E582" t="s">
         <v>54</v>
@@ -17695,7 +17695,7 @@
         <v>62</v>
       </c>
       <c r="D583">
-        <v>7.3330702531825493E-3</v>
+        <v>7.3330737654789873E-3</v>
       </c>
       <c r="E583" t="s">
         <v>54</v>
@@ -17709,7 +17709,7 @@
         <v>63</v>
       </c>
       <c r="D584">
-        <v>3.5220295126088433E-3</v>
+        <v>3.5220311995436855E-3</v>
       </c>
       <c r="E584" t="s">
         <v>54</v>
@@ -17723,7 +17723,7 @@
         <v>64</v>
       </c>
       <c r="D585">
-        <v>0.17960387086050922</v>
+        <v>0.17960395688478201</v>
       </c>
       <c r="E585" t="s">
         <v>54</v>
@@ -17737,7 +17737,7 @@
         <v>65</v>
       </c>
       <c r="D586">
-        <v>1.2425294912362571E-4</v>
+        <v>1.2425300863665035E-4</v>
       </c>
       <c r="E586" t="s">
         <v>54</v>
@@ -17749,7 +17749,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E29355E8-F797-43A8-9EFA-A96D501226AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C5F9534-B2C1-4D64-974F-9B59489C60A5}">
   <dimension ref="B9:CI113"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20049,7 +20049,7 @@
         <v>0.41577106663881119</v>
       </c>
       <c r="F20">
-        <v>0.99814814814814823</v>
+        <v>0</v>
       </c>
       <c r="G20">
         <v>0.82259453210651012</v>
@@ -20091,7 +20091,7 @@
         <v>0.26337477785366648</v>
       </c>
       <c r="U20">
-        <v>0.99629972565157743</v>
+        <v>0</v>
       </c>
       <c r="V20">
         <v>0.7060895863064357</v>
@@ -20214,7 +20214,7 @@
         <v>0.12390298806088079</v>
       </c>
       <c r="BU20">
-        <v>3.1675794557878333E-7</v>
+        <v>0</v>
       </c>
       <c r="BV20">
         <v>9.4440098376753351E-3</v>
@@ -21369,7 +21369,7 @@
         <v>31</v>
       </c>
       <c r="D26">
-        <v>0.99722222222222223</v>
+        <v>0</v>
       </c>
       <c r="E26">
         <v>0.4559086725846806</v>
@@ -21411,7 +21411,7 @@
         <v>271</v>
       </c>
       <c r="S26">
-        <v>0.99445216049382701</v>
+        <v>0</v>
       </c>
       <c r="T26">
         <v>0.28174444089770867</v>
@@ -21534,7 +21534,7 @@
         <v>183</v>
       </c>
       <c r="BS26">
-        <v>1.2405366983881074E-7</v>
+        <v>0</v>
       </c>
       <c r="BT26">
         <v>0.10085896596965439</v>
@@ -28441,7 +28441,7 @@
         <v>31</v>
       </c>
       <c r="D58">
-        <v>0.99861111111111134</v>
+        <v>0</v>
       </c>
       <c r="E58">
         <v>0.43506408738051566</v>
@@ -28483,7 +28483,7 @@
         <v>271</v>
       </c>
       <c r="S58">
-        <v>0.99722415123456798</v>
+        <v>0</v>
       </c>
       <c r="T58">
         <v>0.26942509786613428</v>
@@ -28606,7 +28606,7 @@
         <v>215</v>
       </c>
       <c r="BS58">
-        <v>6.6635978727016594E-7</v>
+        <v>0</v>
       </c>
       <c r="BT58">
         <v>0.11431168891979429</v>
@@ -40815,7 +40815,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE2301E7-56ED-4C45-9760-C226FA563A69}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{412E9800-0AD2-429E-ADF2-B53D76AFABED}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41083,7 +41083,7 @@
         <v>38</v>
       </c>
       <c r="R15">
-        <v>0.20653333333333332</v>
+        <v>0.20653333333333335</v>
       </c>
       <c r="S15" t="s">
         <v>300</v>
@@ -41666,7 +41666,7 @@
         <v>46</v>
       </c>
       <c r="R38">
-        <v>0.20659999999999998</v>
+        <v>0.20660000000000001</v>
       </c>
       <c r="S38" t="s">
         <v>300</v>
@@ -41722,7 +41722,7 @@
         <v>46</v>
       </c>
       <c r="R42">
-        <v>0.29533333333333339</v>
+        <v>0.29533333333333334</v>
       </c>
       <c r="S42" t="s">
         <v>300</v>
@@ -41778,7 +41778,7 @@
         <v>46</v>
       </c>
       <c r="R46">
-        <v>0.22879999999999998</v>
+        <v>0.2288</v>
       </c>
       <c r="S46" t="s">
         <v>300</v>
@@ -41792,7 +41792,7 @@
         <v>38</v>
       </c>
       <c r="R47">
-        <v>0.30259999999999998</v>
+        <v>0.30260000000000004</v>
       </c>
       <c r="S47" t="s">
         <v>300</v>
@@ -41834,7 +41834,7 @@
         <v>46</v>
       </c>
       <c r="R50">
-        <v>0.24779999999999999</v>
+        <v>0.24780000000000002</v>
       </c>
       <c r="S50" t="s">
         <v>300</v>
@@ -41890,7 +41890,7 @@
         <v>46</v>
       </c>
       <c r="R54">
-        <v>0.22766666666666668</v>
+        <v>0.22766666666666666</v>
       </c>
       <c r="S54" t="s">
         <v>300</v>
@@ -41960,7 +41960,7 @@
         <v>38</v>
       </c>
       <c r="R59">
-        <v>0.29860000000000003</v>
+        <v>0.29859999999999998</v>
       </c>
       <c r="S59" t="s">
         <v>300</v>
@@ -42058,7 +42058,7 @@
         <v>46</v>
       </c>
       <c r="R66">
-        <v>0.19193333333333332</v>
+        <v>0.19193333333333337</v>
       </c>
       <c r="S66" t="s">
         <v>300</v>
@@ -42072,7 +42072,7 @@
         <v>38</v>
       </c>
       <c r="R67">
-        <v>0.37280000000000002</v>
+        <v>0.37279999999999996</v>
       </c>
       <c r="S67" t="s">
         <v>300</v>
@@ -42114,7 +42114,7 @@
         <v>46</v>
       </c>
       <c r="R70">
-        <v>0.27233333333333337</v>
+        <v>0.27233333333333332</v>
       </c>
       <c r="S70" t="s">
         <v>300</v>
@@ -42240,7 +42240,7 @@
         <v>38</v>
       </c>
       <c r="R79">
-        <v>0.3242666666666667</v>
+        <v>0.32426666666666665</v>
       </c>
       <c r="S79" t="s">
         <v>300</v>
@@ -42296,7 +42296,7 @@
         <v>38</v>
       </c>
       <c r="R83">
-        <v>0.30743333333333334</v>
+        <v>0.30743333333333328</v>
       </c>
       <c r="S83" t="s">
         <v>300</v>
@@ -42408,7 +42408,7 @@
         <v>38</v>
       </c>
       <c r="R91">
-        <v>0.3143333333333333</v>
+        <v>0.31433333333333335</v>
       </c>
       <c r="S91" t="s">
         <v>300</v>
@@ -42450,7 +42450,7 @@
         <v>46</v>
       </c>
       <c r="R94">
-        <v>0.21929999999999997</v>
+        <v>0.21930000000000002</v>
       </c>
       <c r="S94" t="s">
         <v>300</v>
@@ -42618,7 +42618,7 @@
         <v>46</v>
       </c>
       <c r="R106">
-        <v>0.17756666666666665</v>
+        <v>0.17756666666666668</v>
       </c>
       <c r="S106" t="s">
         <v>300</v>
@@ -42688,7 +42688,7 @@
         <v>38</v>
       </c>
       <c r="R111">
-        <v>0.31429999999999997</v>
+        <v>0.31430000000000002</v>
       </c>
       <c r="S111" t="s">
         <v>300</v>
@@ -42800,7 +42800,7 @@
         <v>38</v>
       </c>
       <c r="R119">
-        <v>0.31936666666666663</v>
+        <v>0.31936666666666669</v>
       </c>
       <c r="S119" t="s">
         <v>300</v>
@@ -42898,7 +42898,7 @@
         <v>46</v>
       </c>
       <c r="R126">
-        <v>0.21530000000000002</v>
+        <v>0.21529999999999996</v>
       </c>
       <c r="S126" t="s">
         <v>300</v>
